--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -19697,16 +19697,48 @@
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="51">
-      <c r="A27" s="96" t="n"/>
-      <c r="B27" s="96" t="n"/>
-      <c r="C27" s="96" t="n"/>
-      <c r="D27" s="96" t="n"/>
-      <c r="E27" s="96" t="n"/>
-      <c r="F27" s="93" t="n"/>
-      <c r="G27" s="98" t="n"/>
-      <c r="H27" s="98" t="n"/>
-      <c r="I27" s="96" t="n"/>
-      <c r="J27" s="96" t="n"/>
+      <c r="A27" s="96" t="inlineStr">
+        <is>
+          <t>OPP-023</t>
+        </is>
+      </c>
+      <c r="B27" s="96" t="inlineStr">
+        <is>
+          <t>IHS WebEHRS 2027-2032 (SS75H70126R00050) — RFI Response</t>
+        </is>
+      </c>
+      <c r="C27" s="96" t="inlineStr">
+        <is>
+          <t>Indian Health Service (IHS) / HHS</t>
+        </is>
+      </c>
+      <c r="D27" s="96" t="inlineStr">
+        <is>
+          <t>541511</t>
+        </is>
+      </c>
+      <c r="E27" s="96" t="inlineStr">
+        <is>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="F27" s="97" t="n"/>
+      <c r="G27" s="98" t="n">
+        <v>46210</v>
+      </c>
+      <c r="H27" s="98" t="n">
+        <v>46210</v>
+      </c>
+      <c r="I27" s="96" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="J27" s="96" t="inlineStr">
+        <is>
+          <t>Sources Sought / RFI SS75H70126R00050 — IHS Web-based Environmental Health Reporting System (WebEHRS) 2027-2032. VBX responds as subcontractor / integration teammate (not a COTS product vendor). Intent to prime = No; intent to sub = Yes. Socio-econ: Minority-Owned SB, TAA + Section 889 compliant; not an IEE — J02 Buy Indian rep form N/A. Services scope: custom RRM engine + historical reporting, IHS Standard Code Book integration, FDA 2022 Food Code Annex 7 Form 3a e-inspection forms (web+offline), legacy migration + UAT, ATO/FedRAMP/SSO/MFA/PIV/RBAC/audit, standards-based APIs/exports, help-desk/O&amp;M. No solution ROM (services-only ROM on request once platform baseline/teaming defined). CO POC: Daniel Cotto, IHS (daniel.cotto@ihs.gov). Response transmitted before deadline.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="51">
       <c r="A28" s="96" t="n"/>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -18629,7 +18629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="50" min="1" max="1"/>
@@ -18757,37 +18757,35 @@
     <row r="6" ht="15" customHeight="1" s="51">
       <c r="A6" s="96" t="inlineStr">
         <is>
-          <t>OPP-002</t>
+          <t>OPP-019</t>
         </is>
       </c>
       <c r="B6" s="96" t="inlineStr">
         <is>
-          <t>Maryland Statewide Network Services (BPM054667) FA4</t>
+          <t>USDA Community Connect</t>
         </is>
       </c>
       <c r="C6" s="96" t="inlineStr">
         <is>
-          <t>Maryland DoIT</t>
+          <t>USDA Rural Utilities Service</t>
         </is>
       </c>
       <c r="D6" s="96" t="inlineStr">
         <is>
-          <t>541519</t>
+          <t>517311</t>
         </is>
       </c>
       <c r="E6" s="96" t="inlineStr">
         <is>
-          <t>Capture</t>
-        </is>
-      </c>
-      <c r="F6" s="93" t="n">
-        <v>5000000</v>
-      </c>
+          <t>No-Bid</t>
+        </is>
+      </c>
+      <c r="F6" s="93" t="n"/>
       <c r="G6" s="98" t="n">
-        <v>46122</v>
+        <v>46181</v>
       </c>
       <c r="H6" s="98" t="n">
-        <v>46137</v>
+        <v>46181</v>
       </c>
       <c r="I6" s="96" t="inlineStr">
         <is>
@@ -18796,24 +18794,24 @@
       </c>
       <c r="J6" s="96" t="inlineStr">
         <is>
-          <t>BLOCKED: eMMA registration required. Teaming with AG Grace.</t>
+          <t>NO-BID. Capability mismatch — broadband infrastructure, not healthcare IT. Formal DOCX pending.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="51">
       <c r="A7" s="96" t="inlineStr">
         <is>
-          <t>OPP-003</t>
+          <t>OPP-020</t>
         </is>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
-          <t>WA DOH Statewide Rural Health Program (RFP 26-005C)</t>
+          <t>HRSA Rural Residency Planning &amp; Development</t>
         </is>
       </c>
       <c r="C7" s="96" t="inlineStr">
         <is>
-          <t>Washington State DOH</t>
+          <t>HRSA</t>
         </is>
       </c>
       <c r="D7" s="96" t="inlineStr">
@@ -18823,17 +18821,15 @@
       </c>
       <c r="E7" s="96" t="inlineStr">
         <is>
-          <t>Qualified</t>
-        </is>
-      </c>
-      <c r="F7" s="93" t="n">
-        <v>1500000</v>
-      </c>
+          <t>No-Bid</t>
+        </is>
+      </c>
+      <c r="F7" s="93" t="n"/>
       <c r="G7" s="98" t="n">
-        <v>46132</v>
+        <v>46181</v>
       </c>
       <c r="H7" s="98" t="n">
-        <v>46147</v>
+        <v>46181</v>
       </c>
       <c r="I7" s="96" t="inlineStr">
         <is>
@@ -18842,24 +18838,24 @@
       </c>
       <c r="J7" s="96" t="inlineStr">
         <is>
-          <t>BLOCKED: SOC 2 Type II + WA foreign entity registration.</t>
+          <t>NO-BID. Mission mismatch — funds residency programs, not IT vendors. Formal DOCX pending. Track FY26 awardees for downstream EHR/telehealth sub plays.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="51">
       <c r="A8" s="96" t="inlineStr">
         <is>
-          <t>OPP-004</t>
+          <t>OPP-021</t>
         </is>
       </c>
       <c r="B8" s="96" t="inlineStr">
         <is>
-          <t>Rural Health Transformation Program (RHTP) — Maryland state lane</t>
+          <t>VA NEDIIS (36C10B26Q0078)</t>
         </is>
       </c>
       <c r="C8" s="96" t="inlineStr">
         <is>
-          <t>Maryland Dept of Health / CMS</t>
+          <t>VA OIT</t>
         </is>
       </c>
       <c r="D8" s="96" t="inlineStr">
@@ -18869,17 +18865,15 @@
       </c>
       <c r="E8" s="96" t="inlineStr">
         <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="F8" s="93" t="n">
-        <v>3000000</v>
-      </c>
+          <t>No-Bid</t>
+        </is>
+      </c>
+      <c r="F8" s="93" t="n"/>
       <c r="G8" s="98" t="n">
-        <v>46162</v>
+        <v>46175</v>
       </c>
       <c r="H8" s="98" t="n">
-        <v>46162</v>
+        <v>46175</v>
       </c>
       <c r="I8" s="96" t="inlineStr">
         <is>
@@ -18888,24 +18882,24 @@
       </c>
       <c r="J8" s="96" t="inlineStr">
         <is>
-          <t>$50B CMS initiative. GRHD framework alignment. Subcontract path TBD.</t>
+          <t>NO-BID filed 6/2. Window closed + T4NG vehicle closed + 150-FTE PP floor. Watch GSA Alliant 3 SDVOSB pool finalization.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="51">
       <c r="A9" s="96" t="inlineStr">
         <is>
-          <t>OPP-005</t>
+          <t>OPP-022</t>
         </is>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
-          <t>Rural Health Transformation Program (RHTP) — Texas state lane</t>
+          <t>SENTRY (CB26-RFQ0012) — CBO IT Support BPA, SMA 2 Cloud Service Support (J4 + J5)</t>
         </is>
       </c>
       <c r="C9" s="96" t="inlineStr">
         <is>
-          <t>Texas HHS / CMS</t>
+          <t>Congressional Budget Office (CBO)</t>
         </is>
       </c>
       <c r="D9" s="96" t="inlineStr">
@@ -18915,17 +18909,17 @@
       </c>
       <c r="E9" s="96" t="inlineStr">
         <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="F9" s="93" t="n">
-        <v>3000000</v>
+          <t>Capture</t>
+        </is>
+      </c>
+      <c r="F9" s="97" t="n">
+        <v>4000000</v>
       </c>
       <c r="G9" s="98" t="n">
-        <v>46162</v>
+        <v>46200</v>
       </c>
       <c r="H9" s="98" t="n">
-        <v>46162</v>
+        <v>46200</v>
       </c>
       <c r="I9" s="96" t="inlineStr">
         <is>
@@ -18934,42 +18928,42 @@
       </c>
       <c r="J9" s="96" t="inlineStr">
         <is>
-          <t>RHTP Texas. Partner alignment with NCP / BAC for VHA-adjacent.</t>
+          <t>TES x VBX teaming (VBX as sub). VBX quoting SMA 2 LCATs: J4 Microsoft Cloud Engineering SME + J5 Full Stack Developer. 5-yr BPA under GSA IT Schedule SIN 54151S. PoP 8/15/26–8/14/31. Questions due 6/18/26; quote due 7/7/26 5pm ET via OAM@cbo.gov. Public Trust Tier 2 (Capitol Police). Remote w/ on-site option at FHOB DC. VBX share est. = 2 FTE × 5yr.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="51">
       <c r="A10" s="96" t="inlineStr">
         <is>
-          <t>OPP-006</t>
+          <t>OPP-023</t>
         </is>
       </c>
       <c r="B10" s="96" t="inlineStr">
         <is>
-          <t>HRSA Technical Assistance — National Backbone for System Integration</t>
+          <t>IHS WebEHRS 2027-2032 (SS75H70126R00050) — RFI Response</t>
         </is>
       </c>
       <c r="C10" s="96" t="inlineStr">
         <is>
-          <t>HRSA</t>
+          <t>Indian Health Service (IHS) / HHS</t>
         </is>
       </c>
       <c r="D10" s="96" t="inlineStr">
         <is>
-          <t>541512</t>
+          <t>541511</t>
         </is>
       </c>
       <c r="E10" s="96" t="inlineStr">
         <is>
-          <t>Qualified</t>
-        </is>
-      </c>
-      <c r="F10" s="93" t="n"/>
+          <t>Submitted</t>
+        </is>
+      </c>
+      <c r="F10" s="97" t="n"/>
       <c r="G10" s="98" t="n">
-        <v>46181</v>
+        <v>46210</v>
       </c>
       <c r="H10" s="98" t="n">
-        <v>46181</v>
+        <v>46210</v>
       </c>
       <c r="I10" s="96" t="inlineStr">
         <is>
@@ -18978,767 +18972,213 @@
       </c>
       <c r="J10" s="96" t="inlineStr">
         <is>
-          <t>Closes 6/24. L1+L2 fit. Route via Theta HHS SWIFT or GSA MAS direct. Kaiser+DHCS PP map directly. PURSUE.</t>
+          <t>Sources Sought / RFI SS75H70126R00050 — IHS Web-based Environmental Health Reporting System (WebEHRS) 2027-2032. VBX responds as subcontractor / integration teammate (not a COTS product vendor). Intent to prime = No; intent to sub = Yes. Socio-econ: Minority-Owned SB, TAA + Section 889 compliant; not an IEE — J02 Buy Indian rep form N/A. Services scope: custom RRM engine + historical reporting, IHS Standard Code Book integration, FDA 2022 Food Code Annex 7 Form 3a e-inspection forms (web+offline), legacy migration + UAT, ATO/FedRAMP/SSO/MFA/PIV/RBAC/audit, standards-based APIs/exports, help-desk/O&amp;M. No solution ROM (services-only ROM on request once platform baseline/teaming defined). CO POC: Daniel Cotto, IHS (daniel.cotto@ihs.gov). Response transmitted before deadline.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="51">
-      <c r="A11" s="96" t="inlineStr">
-        <is>
-          <t>OPP-007</t>
-        </is>
-      </c>
-      <c r="B11" s="96" t="inlineStr">
-        <is>
-          <t>TN Behavioral Telehealth (Perinatal &amp; Pediatric)</t>
-        </is>
-      </c>
-      <c r="C11" s="96" t="inlineStr">
-        <is>
-          <t>TN Dept of Health</t>
-        </is>
-      </c>
-      <c r="D11" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E11" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
+      <c r="A11" s="96" t="n"/>
+      <c r="B11" s="96" t="n"/>
+      <c r="C11" s="96" t="n"/>
+      <c r="D11" s="96" t="n"/>
+      <c r="E11" s="96" t="n"/>
       <c r="F11" s="93" t="n"/>
-      <c r="G11" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H11" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I11" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J11" s="96" t="inlineStr">
-        <is>
-          <t>Closes 6/15. Kaiser VCare federal analog. Gate 1 + Pwin score due 6/10.</t>
-        </is>
-      </c>
+      <c r="G11" s="98" t="n"/>
+      <c r="H11" s="98" t="n"/>
+      <c r="I11" s="96" t="n"/>
+      <c r="J11" s="96" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="51">
-      <c r="A12" s="96" t="inlineStr">
-        <is>
-          <t>OPP-008</t>
-        </is>
-      </c>
-      <c r="B12" s="96" t="inlineStr">
-        <is>
-          <t>TN Service Line &amp; Co-Location (Specialty Integration)</t>
-        </is>
-      </c>
-      <c r="C12" s="96" t="inlineStr">
-        <is>
-          <t>TN Dept of Health</t>
-        </is>
-      </c>
-      <c r="D12" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E12" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
+      <c r="A12" s="96" t="n"/>
+      <c r="B12" s="96" t="n"/>
+      <c r="C12" s="96" t="n"/>
+      <c r="D12" s="96" t="n"/>
+      <c r="E12" s="96" t="n"/>
       <c r="F12" s="93" t="n"/>
-      <c r="G12" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H12" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I12" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J12" s="96" t="inlineStr">
-        <is>
-          <t>Opens 6/12. Stage Gate 1 for release day. Rolling TN procurement cycle.</t>
-        </is>
-      </c>
+      <c r="G12" s="98" t="n"/>
+      <c r="H12" s="98" t="n"/>
+      <c r="I12" s="96" t="n"/>
+      <c r="J12" s="96" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="51">
-      <c r="A13" s="96" t="inlineStr">
-        <is>
-          <t>OPP-009</t>
-        </is>
-      </c>
-      <c r="B13" s="96" t="inlineStr">
-        <is>
-          <t>OPM OIG BRIDGE BPA RFQ1809527 — FEHBP Claims DW w/ Gen-AI</t>
-        </is>
-      </c>
-      <c r="C13" s="96" t="inlineStr">
-        <is>
-          <t>OPM OIG</t>
-        </is>
-      </c>
-      <c r="D13" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E13" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="F13" s="93" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="G13" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H13" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I13" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J13" s="96" t="inlineStr">
-        <is>
-          <t>$15M ceiling point. 8(a) Pool Competitive. Sub via TES MAS 54151S. Incumbent: Unissant.</t>
-        </is>
-      </c>
+      <c r="A13" s="96" t="n"/>
+      <c r="B13" s="96" t="n"/>
+      <c r="C13" s="96" t="n"/>
+      <c r="D13" s="96" t="n"/>
+      <c r="E13" s="96" t="n"/>
+      <c r="F13" s="93" t="n"/>
+      <c r="G13" s="98" t="n"/>
+      <c r="H13" s="98" t="n"/>
+      <c r="I13" s="96" t="n"/>
+      <c r="J13" s="96" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="51">
-      <c r="A14" s="96" t="inlineStr">
-        <is>
-          <t>OPP-010</t>
-        </is>
-      </c>
-      <c r="B14" s="96" t="inlineStr">
-        <is>
-          <t>VA VIPPS RFQ1809729 (Phase II)</t>
-        </is>
-      </c>
-      <c r="C14" s="96" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="D14" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E14" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="F14" s="93" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="G14" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H14" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I14" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J14" s="96" t="inlineStr">
-        <is>
-          <t>Phase II only through 7/1. VistA/iFAMS integration + AI/ML + FedRAMP Mod. Sub via TES MAS.</t>
-        </is>
-      </c>
+      <c r="A14" s="96" t="n"/>
+      <c r="B14" s="96" t="n"/>
+      <c r="C14" s="96" t="n"/>
+      <c r="D14" s="96" t="n"/>
+      <c r="E14" s="96" t="n"/>
+      <c r="F14" s="93" t="n"/>
+      <c r="G14" s="98" t="n"/>
+      <c r="H14" s="98" t="n"/>
+      <c r="I14" s="96" t="n"/>
+      <c r="J14" s="96" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="51">
-      <c r="A15" s="96" t="inlineStr">
-        <is>
-          <t>OPP-011</t>
-        </is>
-      </c>
-      <c r="B15" s="96" t="inlineStr">
-        <is>
-          <t>NIH Data Access &amp; Linkage BPA</t>
-        </is>
-      </c>
-      <c r="C15" s="96" t="inlineStr">
-        <is>
-          <t>NIH</t>
-        </is>
-      </c>
-      <c r="D15" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E15" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
+      <c r="A15" s="96" t="n"/>
+      <c r="B15" s="96" t="n"/>
+      <c r="C15" s="96" t="n"/>
+      <c r="D15" s="96" t="n"/>
+      <c r="E15" s="96" t="n"/>
       <c r="F15" s="93" t="n"/>
-      <c r="G15" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H15" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I15" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J15" s="96" t="inlineStr">
-        <is>
-          <t>Surfaced via TES eBuy queue (MAS SIN 54151S, updated 6/3 by Alan Sosa). Sub via TES.</t>
-        </is>
-      </c>
+      <c r="G15" s="98" t="n"/>
+      <c r="H15" s="98" t="n"/>
+      <c r="I15" s="96" t="n"/>
+      <c r="J15" s="96" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="51">
-      <c r="A16" s="96" t="inlineStr">
-        <is>
-          <t>OPP-012</t>
-        </is>
-      </c>
-      <c r="B16" s="96" t="inlineStr">
-        <is>
-          <t>VHA Integrated Healthcare Transformation (IHT) 2.0</t>
-        </is>
-      </c>
-      <c r="C16" s="96" t="inlineStr">
-        <is>
-          <t>VA Strategic Acquisition Center</t>
-        </is>
-      </c>
-      <c r="D16" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E16" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
+      <c r="A16" s="96" t="n"/>
+      <c r="B16" s="96" t="n"/>
+      <c r="C16" s="96" t="n"/>
+      <c r="D16" s="96" t="n"/>
+      <c r="E16" s="96" t="n"/>
       <c r="F16" s="93" t="n"/>
-      <c r="G16" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H16" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I16" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J16" s="96" t="inlineStr">
-        <is>
-          <t>$14B 10-yr SDVOSB IDIQ. Presolic. Notice IDs: 36C10X24R0026 / 36C10X23R0032. Non-similarly-situated sub path via BAC (PFS) or OMNI.</t>
-        </is>
-      </c>
+      <c r="G16" s="98" t="n"/>
+      <c r="H16" s="98" t="n"/>
+      <c r="I16" s="96" t="n"/>
+      <c r="J16" s="96" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="51">
-      <c r="A17" s="96" t="inlineStr">
-        <is>
-          <t>OPP-013</t>
-        </is>
-      </c>
-      <c r="B17" s="96" t="inlineStr">
-        <is>
-          <t>VA.gov Replacement Model (DA01)</t>
-        </is>
-      </c>
-      <c r="C17" s="96" t="inlineStr">
-        <is>
-          <t>VA Technology Acquisition Center</t>
-        </is>
-      </c>
-      <c r="D17" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E17" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
+      <c r="A17" s="96" t="n"/>
+      <c r="B17" s="96" t="n"/>
+      <c r="C17" s="96" t="n"/>
+      <c r="D17" s="96" t="n"/>
+      <c r="E17" s="96" t="n"/>
       <c r="F17" s="93" t="n"/>
-      <c r="G17" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H17" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I17" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J17" s="96" t="inlineStr">
-        <is>
-          <t>Notice 36C10B26Q0131. RFI Loopback 5/5. Anticipated solic Q1 FY27. Kaiser VCare = direct analog.</t>
-        </is>
-      </c>
+      <c r="G17" s="98" t="n"/>
+      <c r="H17" s="98" t="n"/>
+      <c r="I17" s="96" t="n"/>
+      <c r="J17" s="96" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="51">
-      <c r="A18" s="96" t="inlineStr">
-        <is>
-          <t>OPP-014</t>
-        </is>
-      </c>
-      <c r="B18" s="96" t="inlineStr">
-        <is>
-          <t>FL &amp; VT RHTP — Remote Patient Monitoring</t>
-        </is>
-      </c>
-      <c r="C18" s="96" t="inlineStr">
-        <is>
-          <t>FL AHCA / VT AHS</t>
-        </is>
-      </c>
-      <c r="D18" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E18" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
+      <c r="A18" s="96" t="n"/>
+      <c r="B18" s="96" t="n"/>
+      <c r="C18" s="96" t="n"/>
+      <c r="D18" s="96" t="n"/>
+      <c r="E18" s="96" t="n"/>
       <c r="F18" s="93" t="n"/>
-      <c r="G18" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H18" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I18" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J18" s="96" t="inlineStr">
-        <is>
-          <t>WATCH. Closes 6/10. State reg gap (FL/VT not on registered-states list) + COTS vendor-type risk. Sub-only or NO-BID.</t>
-        </is>
-      </c>
+      <c r="G18" s="98" t="n"/>
+      <c r="H18" s="98" t="n"/>
+      <c r="I18" s="96" t="n"/>
+      <c r="J18" s="96" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="51">
-      <c r="A19" s="96" t="inlineStr">
-        <is>
-          <t>OPP-015</t>
-        </is>
-      </c>
-      <c r="B19" s="96" t="inlineStr">
-        <is>
-          <t>AR THRIVE — Continuous Patient Monitoring</t>
-        </is>
-      </c>
-      <c r="C19" s="96" t="inlineStr">
-        <is>
-          <t>AR Dept of Human Services</t>
-        </is>
-      </c>
-      <c r="D19" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E19" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="F19" s="93" t="n">
-        <v>18000000</v>
-      </c>
-      <c r="G19" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H19" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I19" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J19" s="96" t="inlineStr">
-        <is>
-          <t>WATCH. Closes 6/12. AR not on registered states; $18M above sweet spot. Sub if integrator scope carved out.</t>
-        </is>
-      </c>
+      <c r="A19" s="96" t="n"/>
+      <c r="B19" s="96" t="n"/>
+      <c r="C19" s="96" t="n"/>
+      <c r="D19" s="96" t="n"/>
+      <c r="E19" s="96" t="n"/>
+      <c r="F19" s="93" t="n"/>
+      <c r="G19" s="98" t="n"/>
+      <c r="H19" s="98" t="n"/>
+      <c r="I19" s="96" t="n"/>
+      <c r="J19" s="96" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="51">
-      <c r="A20" s="96" t="inlineStr">
-        <is>
-          <t>OPP-016</t>
-        </is>
-      </c>
-      <c r="B20" s="96" t="inlineStr">
-        <is>
-          <t>MD Workforce Data Clearinghouse</t>
-        </is>
-      </c>
-      <c r="C20" s="96" t="inlineStr">
-        <is>
-          <t>Maryland State</t>
-        </is>
-      </c>
-      <c r="D20" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E20" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
+      <c r="A20" s="96" t="n"/>
+      <c r="B20" s="96" t="n"/>
+      <c r="C20" s="96" t="n"/>
+      <c r="D20" s="96" t="n"/>
+      <c r="E20" s="96" t="n"/>
       <c r="F20" s="93" t="n"/>
-      <c r="G20" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H20" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I20" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J20" s="96" t="inlineStr">
-        <is>
-          <t>WATCH. May/Jun release. AG Grace MBE/SDVOSB prime; VBX integration sub. Aligned to $163M+ MD RHTP first-budget pillar.</t>
-        </is>
-      </c>
+      <c r="G20" s="98" t="n"/>
+      <c r="H20" s="98" t="n"/>
+      <c r="I20" s="96" t="n"/>
+      <c r="J20" s="96" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="51">
-      <c r="A21" s="96" t="inlineStr">
-        <is>
-          <t>OPP-017</t>
-        </is>
-      </c>
-      <c r="B21" s="96" t="inlineStr">
-        <is>
-          <t>MT RHTP CoE Implementation Vendor (post-NOIA)</t>
-        </is>
-      </c>
-      <c r="C21" s="96" t="inlineStr">
-        <is>
-          <t>Montana DOA</t>
-        </is>
-      </c>
-      <c r="D21" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E21" s="96" t="inlineStr">
-        <is>
-          <t>Identified</t>
-        </is>
-      </c>
-      <c r="F21" s="93" t="n">
-        <v>105500000</v>
-      </c>
-      <c r="G21" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H21" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I21" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J21" s="96" t="inlineStr">
-        <is>
-          <t>WATCH. $105.5M pending NOIA (~30 days). Sub-positioning on awardee immediately. Track Montana DOA NOIA archive.</t>
-        </is>
-      </c>
+      <c r="A21" s="96" t="n"/>
+      <c r="B21" s="96" t="n"/>
+      <c r="C21" s="96" t="n"/>
+      <c r="D21" s="96" t="n"/>
+      <c r="E21" s="96" t="n"/>
+      <c r="F21" s="93" t="n"/>
+      <c r="G21" s="98" t="n"/>
+      <c r="H21" s="98" t="n"/>
+      <c r="I21" s="96" t="n"/>
+      <c r="J21" s="96" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="51">
-      <c r="A22" s="96" t="inlineStr">
-        <is>
-          <t>OPP-018</t>
-        </is>
-      </c>
-      <c r="B22" s="96" t="inlineStr">
-        <is>
-          <t>USAC Enterprise Cybersecurity &amp; Monitoring (IT-26-073)</t>
-        </is>
-      </c>
-      <c r="C22" s="96" t="inlineStr">
-        <is>
-          <t>USAC</t>
-        </is>
-      </c>
-      <c r="D22" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E22" s="96" t="inlineStr">
-        <is>
-          <t>Qualified</t>
-        </is>
-      </c>
+      <c r="A22" s="96" t="n"/>
+      <c r="B22" s="96" t="n"/>
+      <c r="C22" s="96" t="n"/>
+      <c r="D22" s="96" t="n"/>
+      <c r="E22" s="96" t="n"/>
       <c r="F22" s="93" t="n"/>
-      <c r="G22" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H22" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I22" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J22" s="96" t="inlineStr">
-        <is>
-          <t>Closes 6/10 11AM ET. Bilateral outreach sent 6/8 to AG Grace, TES, West Point, ISG. USAC = private NFP, no FAR set-asides.</t>
-        </is>
-      </c>
+      <c r="G22" s="98" t="n"/>
+      <c r="H22" s="98" t="n"/>
+      <c r="I22" s="96" t="n"/>
+      <c r="J22" s="96" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="51">
-      <c r="A23" s="96" t="inlineStr">
-        <is>
-          <t>OPP-019</t>
-        </is>
-      </c>
-      <c r="B23" s="96" t="inlineStr">
-        <is>
-          <t>USDA Community Connect</t>
-        </is>
-      </c>
-      <c r="C23" s="96" t="inlineStr">
-        <is>
-          <t>USDA Rural Utilities Service</t>
-        </is>
-      </c>
-      <c r="D23" s="96" t="inlineStr">
-        <is>
-          <t>517311</t>
-        </is>
-      </c>
-      <c r="E23" s="96" t="inlineStr">
-        <is>
-          <t>No-Bid</t>
-        </is>
-      </c>
+      <c r="A23" s="96" t="n"/>
+      <c r="B23" s="96" t="n"/>
+      <c r="C23" s="96" t="n"/>
+      <c r="D23" s="96" t="n"/>
+      <c r="E23" s="96" t="n"/>
       <c r="F23" s="93" t="n"/>
-      <c r="G23" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H23" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I23" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J23" s="96" t="inlineStr">
-        <is>
-          <t>NO-BID. Capability mismatch — broadband infrastructure, not healthcare IT. Formal DOCX pending.</t>
-        </is>
-      </c>
+      <c r="G23" s="98" t="n"/>
+      <c r="H23" s="98" t="n"/>
+      <c r="I23" s="96" t="n"/>
+      <c r="J23" s="96" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="51">
-      <c r="A24" s="96" t="inlineStr">
-        <is>
-          <t>OPP-020</t>
-        </is>
-      </c>
-      <c r="B24" s="96" t="inlineStr">
-        <is>
-          <t>HRSA Rural Residency Planning &amp; Development</t>
-        </is>
-      </c>
-      <c r="C24" s="96" t="inlineStr">
-        <is>
-          <t>HRSA</t>
-        </is>
-      </c>
-      <c r="D24" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E24" s="96" t="inlineStr">
-        <is>
-          <t>No-Bid</t>
-        </is>
-      </c>
+      <c r="A24" s="96" t="n"/>
+      <c r="B24" s="96" t="n"/>
+      <c r="C24" s="96" t="n"/>
+      <c r="D24" s="96" t="n"/>
+      <c r="E24" s="96" t="n"/>
       <c r="F24" s="93" t="n"/>
-      <c r="G24" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="H24" s="98" t="n">
-        <v>46181</v>
-      </c>
-      <c r="I24" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J24" s="96" t="inlineStr">
-        <is>
-          <t>NO-BID. Mission mismatch — funds residency programs, not IT vendors. Formal DOCX pending. Track FY26 awardees for downstream EHR/telehealth sub plays.</t>
-        </is>
-      </c>
+      <c r="G24" s="98" t="n"/>
+      <c r="H24" s="98" t="n"/>
+      <c r="I24" s="96" t="n"/>
+      <c r="J24" s="96" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="51">
-      <c r="A25" s="96" t="inlineStr">
-        <is>
-          <t>OPP-021</t>
-        </is>
-      </c>
-      <c r="B25" s="96" t="inlineStr">
-        <is>
-          <t>VA NEDIIS (36C10B26Q0078)</t>
-        </is>
-      </c>
-      <c r="C25" s="96" t="inlineStr">
-        <is>
-          <t>VA OIT</t>
-        </is>
-      </c>
-      <c r="D25" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E25" s="96" t="inlineStr">
-        <is>
-          <t>No-Bid</t>
-        </is>
-      </c>
+      <c r="A25" s="96" t="n"/>
+      <c r="B25" s="96" t="n"/>
+      <c r="C25" s="96" t="n"/>
+      <c r="D25" s="96" t="n"/>
+      <c r="E25" s="96" t="n"/>
       <c r="F25" s="93" t="n"/>
-      <c r="G25" s="98" t="n">
-        <v>46175</v>
-      </c>
-      <c r="H25" s="98" t="n">
-        <v>46175</v>
-      </c>
-      <c r="I25" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J25" s="96" t="inlineStr">
-        <is>
-          <t>NO-BID filed 6/2. Window closed + T4NG vehicle closed + 150-FTE PP floor. Watch GSA Alliant 3 SDVOSB pool finalization.</t>
-        </is>
-      </c>
+      <c r="G25" s="98" t="n"/>
+      <c r="H25" s="98" t="n"/>
+      <c r="I25" s="96" t="n"/>
+      <c r="J25" s="96" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="51">
-      <c r="A26" s="96" t="inlineStr">
-        <is>
-          <t>OPP-022</t>
-        </is>
-      </c>
-      <c r="B26" s="96" t="inlineStr">
-        <is>
-          <t>SENTRY (CB26-RFQ0012) — CBO IT Support BPA, SMA 2 Cloud Service Support (J4 + J5)</t>
-        </is>
-      </c>
-      <c r="C26" s="96" t="inlineStr">
-        <is>
-          <t>Congressional Budget Office (CBO)</t>
-        </is>
-      </c>
-      <c r="D26" s="96" t="inlineStr">
-        <is>
-          <t>541512</t>
-        </is>
-      </c>
-      <c r="E26" s="96" t="inlineStr">
-        <is>
-          <t>Capture</t>
-        </is>
-      </c>
-      <c r="F26" s="97" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="G26" s="98" t="n">
-        <v>46200</v>
-      </c>
-      <c r="H26" s="98" t="n">
-        <v>46200</v>
-      </c>
-      <c r="I26" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J26" s="96" t="inlineStr">
-        <is>
-          <t>TES x VBX teaming (VBX as sub). VBX quoting SMA 2 LCATs: J4 Microsoft Cloud Engineering SME + J5 Full Stack Developer. 5-yr BPA under GSA IT Schedule SIN 54151S. PoP 8/15/26–8/14/31. Questions due 6/18/26; quote due 7/7/26 5pm ET via OAM@cbo.gov. Public Trust Tier 2 (Capitol Police). Remote w/ on-site option at FHOB DC. VBX share est. = 2 FTE × 5yr.</t>
-        </is>
-      </c>
+      <c r="A26" s="96" t="n"/>
+      <c r="B26" s="96" t="n"/>
+      <c r="C26" s="96" t="n"/>
+      <c r="D26" s="96" t="n"/>
+      <c r="E26" s="96" t="n"/>
+      <c r="F26" s="93" t="n"/>
+      <c r="G26" s="98" t="n"/>
+      <c r="H26" s="98" t="n"/>
+      <c r="I26" s="96" t="n"/>
+      <c r="J26" s="96" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="51">
-      <c r="A27" s="96" t="inlineStr">
-        <is>
-          <t>OPP-023</t>
-        </is>
-      </c>
-      <c r="B27" s="96" t="inlineStr">
-        <is>
-          <t>IHS WebEHRS 2027-2032 (SS75H70126R00050) — RFI Response</t>
-        </is>
-      </c>
-      <c r="C27" s="96" t="inlineStr">
-        <is>
-          <t>Indian Health Service (IHS) / HHS</t>
-        </is>
-      </c>
-      <c r="D27" s="96" t="inlineStr">
-        <is>
-          <t>541511</t>
-        </is>
-      </c>
-      <c r="E27" s="96" t="inlineStr">
-        <is>
-          <t>Submitted</t>
-        </is>
-      </c>
-      <c r="F27" s="97" t="n"/>
-      <c r="G27" s="98" t="n">
-        <v>46210</v>
-      </c>
-      <c r="H27" s="98" t="n">
-        <v>46210</v>
-      </c>
-      <c r="I27" s="96" t="inlineStr">
-        <is>
-          <t>Khaalis Wooden</t>
-        </is>
-      </c>
-      <c r="J27" s="96" t="inlineStr">
-        <is>
-          <t>Sources Sought / RFI SS75H70126R00050 — IHS Web-based Environmental Health Reporting System (WebEHRS) 2027-2032. VBX responds as subcontractor / integration teammate (not a COTS product vendor). Intent to prime = No; intent to sub = Yes. Socio-econ: Minority-Owned SB, TAA + Section 889 compliant; not an IEE — J02 Buy Indian rep form N/A. Services scope: custom RRM engine + historical reporting, IHS Standard Code Book integration, FDA 2022 Food Code Annex 7 Form 3a e-inspection forms (web+offline), legacy migration + UAT, ATO/FedRAMP/SSO/MFA/PIV/RBAC/audit, standards-based APIs/exports, help-desk/O&amp;M. No solution ROM (services-only ROM on request once platform baseline/teaming defined). CO POC: Daniel Cotto, IHS (daniel.cotto@ihs.gov). Response transmitted before deadline.</t>
-        </is>
-      </c>
+      <c r="A27" s="96" t="n"/>
+      <c r="B27" s="96" t="n"/>
+      <c r="C27" s="96" t="n"/>
+      <c r="D27" s="96" t="n"/>
+      <c r="E27" s="96" t="n"/>
+      <c r="F27" s="93" t="n"/>
+      <c r="G27" s="98" t="n"/>
+      <c r="H27" s="98" t="n"/>
+      <c r="I27" s="96" t="n"/>
+      <c r="J27" s="96" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="51">
       <c r="A28" s="96" t="n"/>
@@ -20400,210 +19840,23 @@
       <c r="I82" s="96" t="n"/>
       <c r="J82" s="96" t="n"/>
     </row>
-    <row r="83" ht="15" customHeight="1" s="51">
-      <c r="A83" s="96" t="n"/>
-      <c r="B83" s="96" t="n"/>
-      <c r="C83" s="96" t="n"/>
-      <c r="D83" s="96" t="n"/>
-      <c r="E83" s="96" t="n"/>
-      <c r="F83" s="93" t="n"/>
-      <c r="G83" s="98" t="n"/>
-      <c r="H83" s="98" t="n"/>
-      <c r="I83" s="96" t="n"/>
-      <c r="J83" s="96" t="n"/>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="51">
-      <c r="A84" s="96" t="n"/>
-      <c r="B84" s="96" t="n"/>
-      <c r="C84" s="96" t="n"/>
-      <c r="D84" s="96" t="n"/>
-      <c r="E84" s="96" t="n"/>
-      <c r="F84" s="93" t="n"/>
-      <c r="G84" s="98" t="n"/>
-      <c r="H84" s="98" t="n"/>
-      <c r="I84" s="96" t="n"/>
-      <c r="J84" s="96" t="n"/>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="51">
-      <c r="A85" s="96" t="n"/>
-      <c r="B85" s="96" t="n"/>
-      <c r="C85" s="96" t="n"/>
-      <c r="D85" s="96" t="n"/>
-      <c r="E85" s="96" t="n"/>
-      <c r="F85" s="93" t="n"/>
-      <c r="G85" s="98" t="n"/>
-      <c r="H85" s="98" t="n"/>
-      <c r="I85" s="96" t="n"/>
-      <c r="J85" s="96" t="n"/>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="51">
-      <c r="A86" s="96" t="n"/>
-      <c r="B86" s="96" t="n"/>
-      <c r="C86" s="96" t="n"/>
-      <c r="D86" s="96" t="n"/>
-      <c r="E86" s="96" t="n"/>
-      <c r="F86" s="93" t="n"/>
-      <c r="G86" s="98" t="n"/>
-      <c r="H86" s="98" t="n"/>
-      <c r="I86" s="96" t="n"/>
-      <c r="J86" s="96" t="n"/>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="51">
-      <c r="A87" s="96" t="n"/>
-      <c r="B87" s="96" t="n"/>
-      <c r="C87" s="96" t="n"/>
-      <c r="D87" s="96" t="n"/>
-      <c r="E87" s="96" t="n"/>
-      <c r="F87" s="93" t="n"/>
-      <c r="G87" s="98" t="n"/>
-      <c r="H87" s="98" t="n"/>
-      <c r="I87" s="96" t="n"/>
-      <c r="J87" s="96" t="n"/>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="51">
-      <c r="A88" s="96" t="n"/>
-      <c r="B88" s="96" t="n"/>
-      <c r="C88" s="96" t="n"/>
-      <c r="D88" s="96" t="n"/>
-      <c r="E88" s="96" t="n"/>
-      <c r="F88" s="93" t="n"/>
-      <c r="G88" s="98" t="n"/>
-      <c r="H88" s="98" t="n"/>
-      <c r="I88" s="96" t="n"/>
-      <c r="J88" s="96" t="n"/>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="51">
-      <c r="A89" s="96" t="n"/>
-      <c r="B89" s="96" t="n"/>
-      <c r="C89" s="96" t="n"/>
-      <c r="D89" s="96" t="n"/>
-      <c r="E89" s="96" t="n"/>
-      <c r="F89" s="93" t="n"/>
-      <c r="G89" s="98" t="n"/>
-      <c r="H89" s="98" t="n"/>
-      <c r="I89" s="96" t="n"/>
-      <c r="J89" s="96" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1" s="51">
-      <c r="A90" s="96" t="n"/>
-      <c r="B90" s="96" t="n"/>
-      <c r="C90" s="96" t="n"/>
-      <c r="D90" s="96" t="n"/>
-      <c r="E90" s="96" t="n"/>
-      <c r="F90" s="93" t="n"/>
-      <c r="G90" s="98" t="n"/>
-      <c r="H90" s="98" t="n"/>
-      <c r="I90" s="96" t="n"/>
-      <c r="J90" s="96" t="n"/>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="51">
-      <c r="A91" s="96" t="n"/>
-      <c r="B91" s="96" t="n"/>
-      <c r="C91" s="96" t="n"/>
-      <c r="D91" s="96" t="n"/>
-      <c r="E91" s="96" t="n"/>
-      <c r="F91" s="93" t="n"/>
-      <c r="G91" s="98" t="n"/>
-      <c r="H91" s="98" t="n"/>
-      <c r="I91" s="96" t="n"/>
-      <c r="J91" s="96" t="n"/>
-    </row>
-    <row r="92" ht="15" customHeight="1" s="51">
-      <c r="A92" s="96" t="n"/>
-      <c r="B92" s="96" t="n"/>
-      <c r="C92" s="96" t="n"/>
-      <c r="D92" s="96" t="n"/>
-      <c r="E92" s="96" t="n"/>
-      <c r="F92" s="93" t="n"/>
-      <c r="G92" s="98" t="n"/>
-      <c r="H92" s="98" t="n"/>
-      <c r="I92" s="96" t="n"/>
-      <c r="J92" s="96" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1" s="51">
-      <c r="A93" s="96" t="n"/>
-      <c r="B93" s="96" t="n"/>
-      <c r="C93" s="96" t="n"/>
-      <c r="D93" s="96" t="n"/>
-      <c r="E93" s="96" t="n"/>
-      <c r="F93" s="93" t="n"/>
-      <c r="G93" s="98" t="n"/>
-      <c r="H93" s="98" t="n"/>
-      <c r="I93" s="96" t="n"/>
-      <c r="J93" s="96" t="n"/>
-    </row>
-    <row r="94" ht="15" customHeight="1" s="51">
-      <c r="A94" s="96" t="n"/>
-      <c r="B94" s="96" t="n"/>
-      <c r="C94" s="96" t="n"/>
-      <c r="D94" s="96" t="n"/>
-      <c r="E94" s="96" t="n"/>
-      <c r="F94" s="93" t="n"/>
-      <c r="G94" s="98" t="n"/>
-      <c r="H94" s="98" t="n"/>
-      <c r="I94" s="96" t="n"/>
-      <c r="J94" s="96" t="n"/>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="51">
-      <c r="A95" s="96" t="n"/>
-      <c r="B95" s="96" t="n"/>
-      <c r="C95" s="96" t="n"/>
-      <c r="D95" s="96" t="n"/>
-      <c r="E95" s="96" t="n"/>
-      <c r="F95" s="93" t="n"/>
-      <c r="G95" s="98" t="n"/>
-      <c r="H95" s="98" t="n"/>
-      <c r="I95" s="96" t="n"/>
-      <c r="J95" s="96" t="n"/>
-    </row>
-    <row r="96" ht="15" customHeight="1" s="51">
-      <c r="A96" s="96" t="n"/>
-      <c r="B96" s="96" t="n"/>
-      <c r="C96" s="96" t="n"/>
-      <c r="D96" s="96" t="n"/>
-      <c r="E96" s="96" t="n"/>
-      <c r="F96" s="93" t="n"/>
-      <c r="G96" s="98" t="n"/>
-      <c r="H96" s="98" t="n"/>
-      <c r="I96" s="96" t="n"/>
-      <c r="J96" s="96" t="n"/>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="51">
-      <c r="A97" s="96" t="n"/>
-      <c r="B97" s="96" t="n"/>
-      <c r="C97" s="96" t="n"/>
-      <c r="D97" s="96" t="n"/>
-      <c r="E97" s="96" t="n"/>
-      <c r="F97" s="93" t="n"/>
-      <c r="G97" s="98" t="n"/>
-      <c r="H97" s="98" t="n"/>
-      <c r="I97" s="96" t="n"/>
-      <c r="J97" s="96" t="n"/>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="51">
-      <c r="A98" s="96" t="n"/>
-      <c r="B98" s="96" t="n"/>
-      <c r="C98" s="96" t="n"/>
-      <c r="D98" s="96" t="n"/>
-      <c r="E98" s="96" t="n"/>
-      <c r="F98" s="93" t="n"/>
-      <c r="G98" s="98" t="n"/>
-      <c r="H98" s="98" t="n"/>
-      <c r="I98" s="96" t="n"/>
-      <c r="J98" s="96" t="n"/>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="51">
-      <c r="A99" s="96" t="n"/>
-      <c r="B99" s="96" t="n"/>
-      <c r="C99" s="96" t="n"/>
-      <c r="D99" s="96" t="n"/>
-      <c r="E99" s="96" t="n"/>
-      <c r="F99" s="93" t="n"/>
-      <c r="G99" s="98" t="n"/>
-      <c r="H99" s="98" t="n"/>
-      <c r="I99" s="96" t="n"/>
-      <c r="J99" s="96" t="n"/>
-    </row>
+    <row r="83" ht="15" customHeight="1" s="51"/>
+    <row r="84" ht="15" customHeight="1" s="51"/>
+    <row r="85" ht="15" customHeight="1" s="51"/>
+    <row r="86" ht="15" customHeight="1" s="51"/>
+    <row r="87" ht="15" customHeight="1" s="51"/>
+    <row r="88" ht="15" customHeight="1" s="51"/>
+    <row r="89" ht="15" customHeight="1" s="51"/>
+    <row r="90" ht="15" customHeight="1" s="51"/>
+    <row r="91" ht="15" customHeight="1" s="51"/>
+    <row r="92" ht="15" customHeight="1" s="51"/>
+    <row r="93" ht="15" customHeight="1" s="51"/>
+    <row r="94" ht="15" customHeight="1" s="51"/>
+    <row r="95" ht="15" customHeight="1" s="51"/>
+    <row r="96" ht="15" customHeight="1" s="51"/>
+    <row r="97" ht="15" customHeight="1" s="51"/>
+    <row r="98" ht="15" customHeight="1" s="51"/>
+    <row r="99" ht="15" customHeight="1" s="51"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -978,6 +978,16 @@
           <t>NDAs Executed YTD</t>
         </is>
       </c>
+      <c r="G11" s="58" t="inlineStr">
+        <is>
+          <t>Awards Won (#)</t>
+        </is>
+      </c>
+      <c r="H11" s="58" t="inlineStr">
+        <is>
+          <t>Awarded TCV ($)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="36" customHeight="1" s="51">
       <c r="C12" s="62">
@@ -994,6 +1004,14 @@
       </c>
       <c r="F12" s="62">
         <f>COUNTIFS(NDAs!D:D,"&gt;="&amp;DATE(YEAR(As_Of_Date),1,1),NDAs!D:D,"&lt;="&amp;As_Of_Date)</f>
+        <v/>
+      </c>
+      <c r="G12" s="62">
+        <f>COUNTIF(Pipeline!E5:E1000,"Awarded")</f>
+        <v/>
+      </c>
+      <c r="H12" s="59">
+        <f>SUMIF(Pipeline!E5:E1000,"Awarded",Pipeline!F5:F1000)</f>
         <v/>
       </c>
     </row>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -29,12 +29,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -253,7 +254,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -557,6 +558,9 @@
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -6716,11 +6720,15 @@
       <c r="E13" s="93" t="n">
         <v>11200</v>
       </c>
-      <c r="F13" s="96" t="n"/>
-      <c r="G13" s="96" t="n"/>
+      <c r="F13" s="96" t="n">
+        <v>11200</v>
+      </c>
+      <c r="G13" s="102" t="n">
+        <v>46202</v>
+      </c>
       <c r="H13" s="96" t="inlineStr">
         <is>
-          <t>Monthly retainer — May 2026 (payment pending)</t>
+          <t>Monthly retainer — May 2026</t>
         </is>
       </c>
     </row>
@@ -6746,33 +6754,85 @@
       <c r="E14" s="93" t="n">
         <v>2500</v>
       </c>
-      <c r="F14" s="96" t="n"/>
-      <c r="G14" s="96" t="n"/>
+      <c r="F14" s="96" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G14" s="102" t="n">
+        <v>46202</v>
+      </c>
       <c r="H14" s="96" t="inlineStr">
         <is>
-          <t>Monthly retainer — May 2026 (payment pending)</t>
+          <t>Monthly retainer — May 2026</t>
         </is>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="51">
-      <c r="A15" s="98" t="n"/>
-      <c r="B15" s="96" t="n"/>
-      <c r="C15" s="96" t="n"/>
-      <c r="D15" s="96" t="n"/>
-      <c r="E15" s="93" t="n"/>
-      <c r="F15" s="93" t="n"/>
-      <c r="G15" s="98" t="n"/>
-      <c r="H15" s="96" t="n"/>
+      <c r="A15" s="98" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B15" s="96" t="inlineStr">
+        <is>
+          <t>HCPSS</t>
+        </is>
+      </c>
+      <c r="C15" s="96" t="inlineStr">
+        <is>
+          <t>HCPSS-2026-CY</t>
+        </is>
+      </c>
+      <c r="D15" s="96" t="inlineStr">
+        <is>
+          <t>INV-2026-011</t>
+        </is>
+      </c>
+      <c r="E15" s="93" t="n">
+        <v>11200</v>
+      </c>
+      <c r="F15" s="93" t="n">
+        <v>11200</v>
+      </c>
+      <c r="G15" s="98" t="n">
+        <v>46232</v>
+      </c>
+      <c r="H15" s="96" t="inlineStr">
+        <is>
+          <t>Monthly retainer — Jun 2026</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="51">
-      <c r="A16" s="98" t="n"/>
-      <c r="B16" s="96" t="n"/>
-      <c r="C16" s="96" t="n"/>
-      <c r="D16" s="96" t="n"/>
-      <c r="E16" s="93" t="n"/>
-      <c r="F16" s="93" t="n"/>
-      <c r="G16" s="98" t="n"/>
-      <c r="H16" s="96" t="n"/>
+      <c r="A16" s="98" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B16" s="96" t="inlineStr">
+        <is>
+          <t>First Brands Group</t>
+        </is>
+      </c>
+      <c r="C16" s="96" t="inlineStr">
+        <is>
+          <t>FBG-2026-CY</t>
+        </is>
+      </c>
+      <c r="D16" s="96" t="inlineStr">
+        <is>
+          <t>INV-2026-012</t>
+        </is>
+      </c>
+      <c r="E16" s="93" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F16" s="93" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G16" s="98" t="n">
+        <v>46232</v>
+      </c>
+      <c r="H16" s="96" t="inlineStr">
+        <is>
+          <t>Monthly retainer — Jun 2026</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="51">
       <c r="A17" s="98" t="n"/>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C14" s="100" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Thomas Radcliffe</t>
         </is>
       </c>
       <c r="D14" s="100" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="C49" s="100" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="D49" s="100" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C50" s="100" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Frank Culmone</t>
         </is>
       </c>
       <c r="D50" s="100" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C52" s="100" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Reginald Phillippes</t>
         </is>
       </c>
       <c r="D52" s="100" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="C7" s="100" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Frank Culmone</t>
         </is>
       </c>
       <c r="D7" s="101" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C10" s="100" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Reginald Phillippes</t>
         </is>
       </c>
       <c r="D10" s="101" t="n">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="C13" s="100" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Alice</t>
         </is>
       </c>
       <c r="D13" s="101" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="C20" s="100" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>Thomas Radcliffe</t>
         </is>
       </c>
       <c r="D20" s="101" t="n">

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -3434,7 +3434,7 @@
       </c>
       <c r="C49" s="100" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Alice Parenti</t>
         </is>
       </c>
       <c r="D49" s="100" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="C13" s="100" t="inlineStr">
         <is>
-          <t>Alice</t>
+          <t>Alice Parenti</t>
         </is>
       </c>
       <c r="D13" s="101" t="n">

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Targets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Metrics_Period" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Revenue_Ledger" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Expense_Ledger" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Meetings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Active_Projects" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Feedback" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Screenings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="NDAs" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Agreements" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics_Period" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue_Ledger" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expense_Ledger" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meetings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active_Projects" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feedback" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screenings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDAs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreements" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="As_Of_Date" hidden="0" function="0" vbProcedure="0">Dashboard!$C$4</definedName>
@@ -4118,7 +4118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -4804,6 +4804,93 @@
       <c r="G23" s="100" t="inlineStr">
         <is>
           <t>BENCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="87" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="100" t="inlineStr">
+        <is>
+          <t>Saarthee LLC</t>
+        </is>
+      </c>
+      <c r="C24" s="100" t="n"/>
+      <c r="D24" s="101" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E24" s="100" t="inlineStr">
+        <is>
+          <t>Visionblox_NDA_Saarthee_20260706.pdf</t>
+        </is>
+      </c>
+      <c r="F24" s="100" t="inlineStr">
+        <is>
+          <t>Executed</t>
+        </is>
+      </c>
+      <c r="G24" s="100" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="87" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="100" t="inlineStr">
+        <is>
+          <t>Zachary Piper Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="C25" s="100" t="inlineStr">
+        <is>
+          <t>Dave Ambrose</t>
+        </is>
+      </c>
+      <c r="D25" s="101" t="n">
+        <v>46208</v>
+      </c>
+      <c r="E25" s="100" t="inlineStr">
+        <is>
+          <t>Visionblox_NDA_ZacharyPiperSolutions_20260705.pdf</t>
+        </is>
+      </c>
+      <c r="F25" s="100" t="inlineStr">
+        <is>
+          <t>Executed</t>
+        </is>
+      </c>
+      <c r="G25" s="100" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="87" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="100" t="inlineStr">
+        <is>
+          <t>Proksi Systems (Penn Testing BPA)</t>
+        </is>
+      </c>
+      <c r="C26" s="100" t="inlineStr">
+        <is>
+          <t>Riddhi Choksi</t>
+        </is>
+      </c>
+      <c r="D26" s="101" t="n">
+        <v>46163</v>
+      </c>
+      <c r="E26" s="100" t="inlineStr">
+        <is>
+          <t>Proksi_VisionBlox_NDA_PennTesting.docx</t>
+        </is>
+      </c>
+      <c r="F26" s="100" t="inlineStr">
+        <is>
+          <t>Executed</t>
+        </is>
+      </c>
+      <c r="G26" s="100" t="inlineStr">
+        <is>
+          <t>PRIORITY</t>
         </is>
       </c>
     </row>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics_Period" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue_Ledger" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expense_Ledger" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meetings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active_Projects" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feedback" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screenings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDAs" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreements" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Targets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics_Period" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Revenue_Ledger" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Expense_Ledger" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Meetings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Active_Projects" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Feedback" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Screenings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="NDAs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Agreements" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="As_Of_Date" hidden="0" function="0" vbProcedure="0">Dashboard!$C$4</definedName>
@@ -29,13 +29,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -1614,7 +1615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="50" min="1" max="1"/>
@@ -4083,6 +4084,86 @@
       <c r="I65" s="100" t="inlineStr">
         <is>
           <t>6/5/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="87" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="100" t="inlineStr">
+        <is>
+          <t>NDS Ventures, LLC dba Artemis HCM</t>
+        </is>
+      </c>
+      <c r="C66" s="100" t="inlineStr">
+        <is>
+          <t>Nick (Nicholas D.) Schutt — CEO</t>
+        </is>
+      </c>
+      <c r="D66" s="100" t="inlineStr">
+        <is>
+          <t>– (VA LLC; staffing vendor)</t>
+        </is>
+      </c>
+      <c r="E66" s="101" t="n">
+        <v>46210</v>
+      </c>
+      <c r="F66" s="101" t="n"/>
+      <c r="G66" s="100" t="inlineStr">
+        <is>
+          <t>GovCon Staffing / Recruiting (J4 LCAT sourcing)</t>
+        </is>
+      </c>
+      <c r="H66" s="100" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="I66" s="100" t="inlineStr">
+        <is>
+          <t>7/7/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="87" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="100" t="inlineStr">
+        <is>
+          <t>Zachary Piper Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="C67" s="100" t="inlineStr">
+        <is>
+          <t>Dave Ambrose — Sales Director</t>
+        </is>
+      </c>
+      <c r="D67" s="100" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E67" s="101" t="n">
+        <v>46210</v>
+      </c>
+      <c r="F67" s="101" t="n">
+        <v>46208</v>
+      </c>
+      <c r="G67" s="100" t="inlineStr">
+        <is>
+          <t>Cleared Staffing / GovCon Labor (J4 LCAT)</t>
+        </is>
+      </c>
+      <c r="H67" s="100" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="I67" s="100" t="inlineStr">
+        <is>
+          <t>7/7/2026</t>
         </is>
       </c>
     </row>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -29,14 +29,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="170" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -6526,7 +6525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H199"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="50" min="1" max="1"/>
@@ -6600,24 +6599,24 @@
       </c>
       <c r="B5" s="96" t="inlineStr">
         <is>
-          <t>HCPSS</t>
+          <t>First Brands Group</t>
         </is>
       </c>
       <c r="C5" s="96" t="inlineStr">
         <is>
-          <t>HCPSS-2026-CY</t>
+          <t>FBG-2026-CY</t>
         </is>
       </c>
       <c r="D5" s="96" t="inlineStr">
         <is>
-          <t>INV-2026-001</t>
+          <t>INV-2026-002</t>
         </is>
       </c>
       <c r="E5" s="93" t="n">
-        <v>11200</v>
+        <v>2500</v>
       </c>
       <c r="F5" s="93" t="n">
-        <v>11200</v>
+        <v>2500</v>
       </c>
       <c r="G5" s="98" t="n">
         <v>46083</v>
@@ -6630,7 +6629,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" s="51">
       <c r="A6" s="98" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B6" s="96" t="inlineStr">
         <is>
@@ -6644,7 +6643,7 @@
       </c>
       <c r="D6" s="96" t="inlineStr">
         <is>
-          <t>INV-2026-002</t>
+          <t>INV-2026-004</t>
         </is>
       </c>
       <c r="E6" s="93" t="n">
@@ -6654,51 +6653,51 @@
         <v>2500</v>
       </c>
       <c r="G6" s="98" t="n">
-        <v>46083</v>
+        <v>46111</v>
       </c>
       <c r="H6" s="96" t="inlineStr">
         <is>
-          <t>Monthly retainer — Jan 2026</t>
+          <t>Monthly retainer — Feb 2026</t>
         </is>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="51">
       <c r="A7" s="98" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B7" s="96" t="inlineStr">
         <is>
-          <t>HCPSS</t>
+          <t>First Brands Group</t>
         </is>
       </c>
       <c r="C7" s="96" t="inlineStr">
         <is>
-          <t>HCPSS-2026-CY</t>
+          <t>FBG-2026-CY</t>
         </is>
       </c>
       <c r="D7" s="96" t="inlineStr">
         <is>
-          <t>INV-2026-003</t>
+          <t>INV-2026-006</t>
         </is>
       </c>
       <c r="E7" s="93" t="n">
-        <v>11200</v>
+        <v>2500</v>
       </c>
       <c r="F7" s="93" t="n">
-        <v>11200</v>
+        <v>2500</v>
       </c>
       <c r="G7" s="98" t="n">
-        <v>46111</v>
+        <v>46142</v>
       </c>
       <c r="H7" s="96" t="inlineStr">
         <is>
-          <t>Monthly retainer — Feb 2026</t>
+          <t>Monthly retainer — Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="51">
       <c r="A8" s="98" t="n">
-        <v>46081</v>
+        <v>46142</v>
       </c>
       <c r="B8" s="96" t="inlineStr">
         <is>
@@ -6712,7 +6711,7 @@
       </c>
       <c r="D8" s="96" t="inlineStr">
         <is>
-          <t>INV-2026-004</t>
+          <t>INV-2026-008</t>
         </is>
       </c>
       <c r="E8" s="93" t="n">
@@ -6722,17 +6721,17 @@
         <v>2500</v>
       </c>
       <c r="G8" s="98" t="n">
-        <v>46111</v>
+        <v>46171</v>
       </c>
       <c r="H8" s="96" t="inlineStr">
         <is>
-          <t>Monthly retainer — Feb 2026</t>
+          <t>Monthly retainer — Apr 2026</t>
         </is>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="51">
       <c r="A9" s="98" t="n">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="B9" s="96" t="inlineStr">
         <is>
@@ -6746,27 +6745,27 @@
       </c>
       <c r="D9" s="96" t="inlineStr">
         <is>
-          <t>INV-2026-005</t>
+          <t>INV-2026-009</t>
         </is>
       </c>
       <c r="E9" s="93" t="n">
         <v>11200</v>
       </c>
-      <c r="F9" s="93" t="n">
+      <c r="F9" s="96" t="n">
         <v>11200</v>
       </c>
       <c r="G9" s="98" t="n">
-        <v>46142</v>
+        <v>46202</v>
       </c>
       <c r="H9" s="96" t="inlineStr">
         <is>
-          <t>Monthly retainer — Mar 2026</t>
+          <t>Monthly retainer — May 2026</t>
         </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="51">
       <c r="A10" s="98" t="n">
-        <v>46112</v>
+        <v>46173</v>
       </c>
       <c r="B10" s="96" t="inlineStr">
         <is>
@@ -6780,27 +6779,27 @@
       </c>
       <c r="D10" s="96" t="inlineStr">
         <is>
-          <t>INV-2026-006</t>
+          <t>INV-2026-010</t>
         </is>
       </c>
       <c r="E10" s="93" t="n">
         <v>2500</v>
       </c>
-      <c r="F10" s="93" t="n">
+      <c r="F10" s="96" t="n">
         <v>2500</v>
       </c>
       <c r="G10" s="98" t="n">
-        <v>46142</v>
+        <v>46202</v>
       </c>
       <c r="H10" s="96" t="inlineStr">
         <is>
-          <t>Monthly retainer — Mar 2026</t>
+          <t>Monthly retainer — May 2026</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="51">
       <c r="A11" s="98" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="B11" s="96" t="inlineStr">
         <is>
@@ -6814,7 +6813,7 @@
       </c>
       <c r="D11" s="96" t="inlineStr">
         <is>
-          <t>INV-2026-007</t>
+          <t>INV-2026-011</t>
         </is>
       </c>
       <c r="E11" s="93" t="n">
@@ -6824,17 +6823,17 @@
         <v>11200</v>
       </c>
       <c r="G11" s="98" t="n">
-        <v>46171</v>
+        <v>46232</v>
       </c>
       <c r="H11" s="96" t="inlineStr">
         <is>
-          <t>Monthly retainer — Apr 2026</t>
+          <t>Monthly retainer — Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="51">
       <c r="A12" s="98" t="n">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="B12" s="96" t="inlineStr">
         <is>
@@ -6848,7 +6847,7 @@
       </c>
       <c r="D12" s="96" t="inlineStr">
         <is>
-          <t>INV-2026-008</t>
+          <t>INV-2026-012</t>
         </is>
       </c>
       <c r="E12" s="93" t="n">
@@ -6858,149 +6857,53 @@
         <v>2500</v>
       </c>
       <c r="G12" s="98" t="n">
-        <v>46171</v>
+        <v>46232</v>
       </c>
       <c r="H12" s="96" t="inlineStr">
         <is>
-          <t>Monthly retainer — Apr 2026</t>
+          <t>Monthly retainer — Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="51">
-      <c r="A13" s="98" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B13" s="96" t="inlineStr">
-        <is>
-          <t>HCPSS</t>
-        </is>
-      </c>
-      <c r="C13" s="96" t="inlineStr">
-        <is>
-          <t>HCPSS-2026-CY</t>
-        </is>
-      </c>
-      <c r="D13" s="96" t="inlineStr">
-        <is>
-          <t>INV-2026-009</t>
-        </is>
-      </c>
-      <c r="E13" s="93" t="n">
-        <v>11200</v>
-      </c>
-      <c r="F13" s="96" t="n">
-        <v>11200</v>
-      </c>
-      <c r="G13" s="102" t="n">
-        <v>46202</v>
-      </c>
-      <c r="H13" s="96" t="inlineStr">
-        <is>
-          <t>Monthly retainer — May 2026</t>
-        </is>
-      </c>
+      <c r="A13" s="98" t="n"/>
+      <c r="B13" s="96" t="n"/>
+      <c r="C13" s="96" t="n"/>
+      <c r="D13" s="96" t="n"/>
+      <c r="E13" s="93" t="n"/>
+      <c r="F13" s="93" t="n"/>
+      <c r="G13" s="98" t="n"/>
+      <c r="H13" s="96" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="51">
-      <c r="A14" s="98" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B14" s="96" t="inlineStr">
-        <is>
-          <t>First Brands Group</t>
-        </is>
-      </c>
-      <c r="C14" s="96" t="inlineStr">
-        <is>
-          <t>FBG-2026-CY</t>
-        </is>
-      </c>
-      <c r="D14" s="96" t="inlineStr">
-        <is>
-          <t>INV-2026-010</t>
-        </is>
-      </c>
-      <c r="E14" s="93" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F14" s="96" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G14" s="102" t="n">
-        <v>46202</v>
-      </c>
-      <c r="H14" s="96" t="inlineStr">
-        <is>
-          <t>Monthly retainer — May 2026</t>
-        </is>
-      </c>
+      <c r="A14" s="98" t="n"/>
+      <c r="B14" s="96" t="n"/>
+      <c r="C14" s="96" t="n"/>
+      <c r="D14" s="96" t="n"/>
+      <c r="E14" s="93" t="n"/>
+      <c r="F14" s="93" t="n"/>
+      <c r="G14" s="98" t="n"/>
+      <c r="H14" s="96" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="51">
-      <c r="A15" s="98" t="n">
-        <v>46203</v>
-      </c>
-      <c r="B15" s="96" t="inlineStr">
-        <is>
-          <t>HCPSS</t>
-        </is>
-      </c>
-      <c r="C15" s="96" t="inlineStr">
-        <is>
-          <t>HCPSS-2026-CY</t>
-        </is>
-      </c>
-      <c r="D15" s="96" t="inlineStr">
-        <is>
-          <t>INV-2026-011</t>
-        </is>
-      </c>
-      <c r="E15" s="93" t="n">
-        <v>11200</v>
-      </c>
-      <c r="F15" s="93" t="n">
-        <v>11200</v>
-      </c>
-      <c r="G15" s="98" t="n">
-        <v>46232</v>
-      </c>
-      <c r="H15" s="96" t="inlineStr">
-        <is>
-          <t>Monthly retainer — Jun 2026</t>
-        </is>
-      </c>
+      <c r="A15" s="98" t="n"/>
+      <c r="B15" s="96" t="n"/>
+      <c r="C15" s="96" t="n"/>
+      <c r="D15" s="96" t="n"/>
+      <c r="E15" s="93" t="n"/>
+      <c r="F15" s="93" t="n"/>
+      <c r="G15" s="98" t="n"/>
+      <c r="H15" s="96" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="51">
-      <c r="A16" s="98" t="n">
-        <v>46203</v>
-      </c>
-      <c r="B16" s="96" t="inlineStr">
-        <is>
-          <t>First Brands Group</t>
-        </is>
-      </c>
-      <c r="C16" s="96" t="inlineStr">
-        <is>
-          <t>FBG-2026-CY</t>
-        </is>
-      </c>
-      <c r="D16" s="96" t="inlineStr">
-        <is>
-          <t>INV-2026-012</t>
-        </is>
-      </c>
-      <c r="E16" s="93" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F16" s="93" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G16" s="98" t="n">
-        <v>46232</v>
-      </c>
-      <c r="H16" s="96" t="inlineStr">
-        <is>
-          <t>Monthly retainer — Jun 2026</t>
-        </is>
-      </c>
+      <c r="A16" s="98" t="n"/>
+      <c r="B16" s="96" t="n"/>
+      <c r="C16" s="96" t="n"/>
+      <c r="D16" s="96" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="F16" s="93" t="n"/>
+      <c r="G16" s="98" t="n"/>
+      <c r="H16" s="96" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="51">
       <c r="A17" s="98" t="n"/>
@@ -8792,46 +8695,10 @@
       <c r="G195" s="98" t="n"/>
       <c r="H195" s="96" t="n"/>
     </row>
-    <row r="196" ht="15" customHeight="1" s="51">
-      <c r="A196" s="98" t="n"/>
-      <c r="B196" s="96" t="n"/>
-      <c r="C196" s="96" t="n"/>
-      <c r="D196" s="96" t="n"/>
-      <c r="E196" s="93" t="n"/>
-      <c r="F196" s="93" t="n"/>
-      <c r="G196" s="98" t="n"/>
-      <c r="H196" s="96" t="n"/>
-    </row>
-    <row r="197" ht="15" customHeight="1" s="51">
-      <c r="A197" s="98" t="n"/>
-      <c r="B197" s="96" t="n"/>
-      <c r="C197" s="96" t="n"/>
-      <c r="D197" s="96" t="n"/>
-      <c r="E197" s="93" t="n"/>
-      <c r="F197" s="93" t="n"/>
-      <c r="G197" s="98" t="n"/>
-      <c r="H197" s="96" t="n"/>
-    </row>
-    <row r="198" ht="15" customHeight="1" s="51">
-      <c r="A198" s="98" t="n"/>
-      <c r="B198" s="96" t="n"/>
-      <c r="C198" s="96" t="n"/>
-      <c r="D198" s="96" t="n"/>
-      <c r="E198" s="93" t="n"/>
-      <c r="F198" s="93" t="n"/>
-      <c r="G198" s="98" t="n"/>
-      <c r="H198" s="96" t="n"/>
-    </row>
-    <row r="199" ht="15" customHeight="1" s="51">
-      <c r="A199" s="98" t="n"/>
-      <c r="B199" s="96" t="n"/>
-      <c r="C199" s="96" t="n"/>
-      <c r="D199" s="96" t="n"/>
-      <c r="E199" s="93" t="n"/>
-      <c r="F199" s="93" t="n"/>
-      <c r="G199" s="98" t="n"/>
-      <c r="H199" s="96" t="n"/>
-    </row>
+    <row r="196" ht="15" customHeight="1" s="51"/>
+    <row r="197" ht="15" customHeight="1" s="51"/>
+    <row r="198" ht="15" customHeight="1" s="51"/>
+    <row r="199" ht="15" customHeight="1" s="51"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="C6" s="76" t="n">
-        <v>212270</v>
+        <v>224631</v>
       </c>
       <c r="D6" s="75" t="inlineStr">
         <is>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="583">
   <si>
     <t xml:space="preserve">  VISIONBLOX COMMAND CENTER  |  CAGE 9Z4X2  |  UEI H4X2Z7R9E3E3</t>
   </si>
@@ -1042,6 +1042,42 @@
   </si>
   <si>
     <t xml:space="preserve">NO-BID as prime — Gate 1 fail (7/7/26). RFI due 7/22/26, 10-page cap. Domain mismatch: geospatial/GIS depth, boundary-domain past performance, and IC-grade hosting not held; NAICS 541360 outside VBX profile; no federal prime past performance. Conditional narrow-sub lane (portal O&amp;M / OCR-ETL / secure hosting) required a geospatial prime identified by ~7/15 — window passed with none surfaced; collapses to straight no-bid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPP-028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARFORRES AI Manpower &amp; Readiness (M6786126IMKMAI) — Sources Sought Response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USMC Forces Reserve (MFR G-1 / MCIRSA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources Sought M6786126IMKMAI — AI-enabled manpower modeling, readiness analytics, personnel allocation (IRR/SMCR). CUI notice; NAICS not stated on notice. Response + cover letter FINALIZED via vbx-solicitation-response gates; send scheduled by 7/29 (due 7/30 12:00pm CDT). Gated on Akil metric/cert checklist. POCs: Jordyn Edwards (jordyn.edwards@usmc.mil, 504-697-8355) + Parren Tatum (parren.tatum.civ@usmc.mil, 504-697-8308). Set-aside blank — SB shaping questions embedded in transmittal. Flip Stage→Submitted + StageDate on transmittal confirmation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPP-029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHA ARMOR — Integrated Workforce &amp; Readiness Platform (ARMOR001) — RFI Response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defense Health Agency (DHMS-CD, Rosslyn VA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFI ARMOR001 — Tier 1 fit (healthcare IT, MHS GENESIS/EHR integration, explainable AI). All FIVE use cases addressed (all-or-nothing per §3.1); 10pp cap; §3.5 OCI access GRANTED (BCG/Andrew Morgan/Monterey). Response + cover letter + cover page FINALIZED; send target 7/22 12:00pm EDT (hard wall 5:00pm EDT/EST discrepancy worst-cased). POCs: Louise Lewis CO (louise.b.lewis.civ@health.mil) + Rachael Bealer CS (rachael.n.bealer.civ@health.mil). OPEN: GSA SIN line ruling BEFORE send — reconciled state per CC Blockers panel: SIN 54151HEAL HELD but under Refresh 31 remediation (7 deficiencies open). Cover currently says 'None currently held' (conservative, OPP-024-style withholding); alternative = cite 54151HEAL since contract is held and §3.2.2 asks. Khaalis to rule. Anticipated RFP = pipeline priority; run scoring engine. Flip Stage→Submitted on confirmation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPP-030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS NEIC AI/ML &amp; Data Streaming Development (140G0226Q0049) — Sources Sought Response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS / DOI (OAG-Denver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources Sought 140G0226Q0049 — NEIC real-time seismic streaming + detection; five SW dev task areas addressed. Tier 2/adjacent fit; candor positioning (transferable production AI/data engineering; NO seismology claims). Response + cover letter FINALIZED; send target 7/23 EOD (due 7/24 2:30pm EDT header vs MST body — worst-cased EDT). POC: Yvette Sornberger (yvette_sornberger@ios.doi.gov, 303-236-9332). OPEN: verify SAM Attachments/Links tab for response instructions before send. Score via capture engine before RFP-stage spend. Flip Stage→Submitted on confirmation.</t>
   </si>
   <si>
     <t xml:space="preserve">  ACTIVE PROJECTS  —  Post-award execution tracking</t>
@@ -2614,7 +2650,7 @@
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="12" t="n">
         <f aca="false">SUMPRODUCT((Pipeline!E5:E1000&lt;&gt;"")*(Pipeline!E5:E1000&lt;&gt;"Awarded")*(Pipeline!E5:E1000&lt;&gt;"Lost")*(Pipeline!E5:E1000&lt;&gt;"No-Bid"))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D12" s="9" t="n">
         <f aca="false">SUMIFS(Pipeline!F5:F1000,Pipeline!E5:E1000,"&lt;&gt;Awarded",Pipeline!E5:E1000,"&lt;&gt;Lost",Pipeline!E5:E1000,"&lt;&gt;No-Bid",Pipeline!E5:E1000,"&lt;&gt;")</f>
@@ -3211,7 +3247,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3224,7 +3260,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3240,28 +3276,28 @@
         <v>102</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3272,10 +3308,10 @@
         <v>157</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E5" s="50" t="n">
         <v>46112</v>
@@ -3284,13 +3320,13 @@
         <v>46038</v>
       </c>
       <c r="G5" s="49" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I5" s="49" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3298,26 +3334,26 @@
         <v>2</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="E6" s="50" t="n">
         <v>46112</v>
       </c>
       <c r="F6" s="50"/>
       <c r="G6" s="49" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="H6" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I6" s="49" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3325,26 +3361,26 @@
         <v>3</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E7" s="50" t="n">
         <v>46112</v>
       </c>
       <c r="F7" s="50"/>
       <c r="G7" s="49" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I7" s="49" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3355,23 +3391,23 @@
         <v>168</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="E8" s="50" t="n">
         <v>46131</v>
       </c>
       <c r="F8" s="50"/>
       <c r="G8" s="49" t="s">
+        <v>391</v>
+      </c>
+      <c r="H8" s="49" t="s">
         <v>379</v>
       </c>
-      <c r="H8" s="49" t="s">
-        <v>367</v>
-      </c>
       <c r="I8" s="49" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3382,23 +3418,23 @@
         <v>173</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="E9" s="50" t="n">
         <v>46131</v>
       </c>
       <c r="F9" s="50"/>
       <c r="G9" s="49" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="H9" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I9" s="49" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3409,10 +3445,10 @@
         <v>183</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E10" s="50" t="n">
         <v>46135</v>
@@ -3421,13 +3457,13 @@
         <v>46148</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I10" s="49" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3438,10 +3474,10 @@
         <v>194</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="E11" s="50" t="n">
         <v>46139</v>
@@ -3450,13 +3486,13 @@
         <v>46148</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H11" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I11" s="49" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3467,10 +3503,10 @@
         <v>201</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="E12" s="50" t="n">
         <v>46140</v>
@@ -3479,13 +3515,13 @@
         <v>46141</v>
       </c>
       <c r="G12" s="49" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="H12" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I12" s="49" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3496,10 +3532,10 @@
         <v>207</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="E13" s="50" t="n">
         <v>46142</v>
@@ -3508,13 +3544,13 @@
         <v>46142</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="H13" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I13" s="49" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3522,26 +3558,26 @@
         <v>10</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E14" s="50"/>
       <c r="F14" s="50" t="n">
         <v>46148</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="H14" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I14" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3549,24 +3585,24 @@
         <v>11</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E15" s="50"/>
       <c r="F15" s="50"/>
       <c r="G15" s="49" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="H15" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3577,23 +3613,23 @@
         <v>232</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="E16" s="50" t="n">
         <v>46154</v>
       </c>
       <c r="F16" s="50"/>
       <c r="G16" s="49" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="H16" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I16" s="49" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3604,23 +3640,23 @@
         <v>236</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="E17" s="50" t="n">
         <v>46154</v>
       </c>
       <c r="F17" s="50"/>
       <c r="G17" s="49" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="H17" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I17" s="49" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3628,13 +3664,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E18" s="50" t="n">
         <v>46127</v>
@@ -3643,13 +3679,13 @@
         <v>46127</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I18" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3657,26 +3693,26 @@
         <v>15</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="E19" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F19" s="50"/>
       <c r="G19" s="49" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="H19" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3687,10 +3723,10 @@
         <v>196</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="E20" s="50" t="n">
         <v>46139</v>
@@ -3699,13 +3735,13 @@
         <v>46141</v>
       </c>
       <c r="G20" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H20" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I20" s="49" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3716,10 +3752,10 @@
         <v>186</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E21" s="50" t="n">
         <v>46135</v>
@@ -3728,13 +3764,13 @@
         <v>46139</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H21" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I21" s="49" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3745,23 +3781,23 @@
         <v>198</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="D22" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E22" s="50" t="n">
         <v>46139</v>
       </c>
       <c r="F22" s="50"/>
       <c r="G22" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H22" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I22" s="49" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3772,23 +3808,23 @@
         <v>204</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E23" s="50" t="n">
         <v>46140</v>
       </c>
       <c r="F23" s="50"/>
       <c r="G23" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H23" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I23" s="49" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3799,10 +3835,10 @@
         <v>176</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="E24" s="50" t="n">
         <v>46132</v>
@@ -3811,13 +3847,13 @@
         <v>46142</v>
       </c>
       <c r="G24" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H24" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I24" s="49" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3828,23 +3864,23 @@
         <v>215</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E25" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="F25" s="50"/>
       <c r="G25" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H25" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I25" s="49" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3855,23 +3891,23 @@
         <v>212</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E26" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="F26" s="50"/>
       <c r="G26" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H26" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I26" s="49" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3879,26 +3915,26 @@
         <v>23</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="E27" s="50" t="n">
         <v>46112</v>
       </c>
       <c r="F27" s="50"/>
       <c r="G27" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H27" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I27" s="49" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3906,26 +3942,26 @@
         <v>24</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E28" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F28" s="50"/>
       <c r="G28" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H28" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I28" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3933,26 +3969,26 @@
         <v>25</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E29" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F29" s="50"/>
       <c r="G29" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H29" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I29" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3960,26 +3996,26 @@
         <v>26</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E30" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F30" s="50"/>
       <c r="G30" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H30" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I30" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3990,10 +4026,10 @@
         <v>210</v>
       </c>
       <c r="C31" s="49" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E31" s="50" t="n">
         <v>46134</v>
@@ -4002,13 +4038,13 @@
         <v>46146</v>
       </c>
       <c r="G31" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H31" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I31" s="49" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4019,10 +4055,10 @@
         <v>188</v>
       </c>
       <c r="C32" s="49" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E32" s="50" t="n">
         <v>46135</v>
@@ -4031,13 +4067,13 @@
         <v>46159</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H32" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I32" s="49" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4048,23 +4084,23 @@
         <v>191</v>
       </c>
       <c r="C33" s="49" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E33" s="50" t="n">
         <v>46138</v>
       </c>
       <c r="F33" s="50"/>
       <c r="G33" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H33" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I33" s="49" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4075,23 +4111,23 @@
         <v>218</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E34" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="F34" s="50"/>
       <c r="G34" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H34" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I34" s="49" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4102,23 +4138,23 @@
         <v>221</v>
       </c>
       <c r="C35" s="49" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E35" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="F35" s="50"/>
       <c r="G35" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H35" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I35" s="49" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4126,26 +4162,26 @@
         <v>32</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="C36" s="49" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E36" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F36" s="50"/>
       <c r="G36" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I36" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4153,26 +4189,26 @@
         <v>33</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C37" s="49" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E37" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F37" s="50"/>
       <c r="G37" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I37" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4180,26 +4216,26 @@
         <v>34</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C38" s="49" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D38" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E38" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F38" s="50"/>
       <c r="G38" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H38" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I38" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4210,23 +4246,23 @@
         <v>163</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E39" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F39" s="50"/>
       <c r="G39" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H39" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I39" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4234,26 +4270,26 @@
         <v>36</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E40" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F40" s="50"/>
       <c r="G40" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H40" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I40" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4261,26 +4297,26 @@
         <v>37</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E41" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F41" s="50"/>
       <c r="G41" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H41" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I41" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4288,26 +4324,26 @@
         <v>38</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E42" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F42" s="50"/>
       <c r="G42" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H42" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I42" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4315,26 +4351,26 @@
         <v>39</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E43" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F43" s="50"/>
       <c r="G43" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H43" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I43" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4342,26 +4378,26 @@
         <v>40</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="D44" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E44" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F44" s="50"/>
       <c r="G44" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H44" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I44" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4369,26 +4405,26 @@
         <v>41</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E45" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F45" s="50"/>
       <c r="G45" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H45" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I45" s="49" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4399,23 +4435,23 @@
         <v>179</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E46" s="50" t="n">
         <v>46132</v>
       </c>
       <c r="F46" s="50"/>
       <c r="G46" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H46" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I46" s="49" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4423,26 +4459,26 @@
         <v>43</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="C47" s="49" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E47" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F47" s="50"/>
       <c r="G47" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H47" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I47" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4450,26 +4486,26 @@
         <v>44</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="C48" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E48" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F48" s="50"/>
       <c r="G48" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H48" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I48" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4477,26 +4513,26 @@
         <v>45</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C49" s="49" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E49" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F49" s="50"/>
       <c r="G49" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H49" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I49" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4504,26 +4540,26 @@
         <v>46</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E50" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F50" s="50"/>
       <c r="G50" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H50" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I50" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4531,26 +4567,26 @@
         <v>47</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C51" s="49" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E51" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F51" s="50"/>
       <c r="G51" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H51" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I51" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4558,26 +4594,26 @@
         <v>48</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E52" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F52" s="50"/>
       <c r="G52" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H52" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I52" s="49" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4585,26 +4621,26 @@
         <v>49</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E53" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F53" s="50"/>
       <c r="G53" s="49" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="H53" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I53" s="49" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4615,23 +4651,23 @@
         <v>266</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E54" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F54" s="50"/>
       <c r="G54" s="49" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="H54" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I54" s="49" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4639,26 +4675,26 @@
         <v>51</v>
       </c>
       <c r="B55" s="49" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="D55" s="49" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="E55" s="50" t="n">
         <v>46168</v>
       </c>
       <c r="F55" s="50"/>
       <c r="G55" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H55" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I55" s="49" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4666,26 +4702,26 @@
         <v>52</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="E56" s="50" t="n">
         <v>46168</v>
       </c>
       <c r="F56" s="50"/>
       <c r="G56" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H56" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="I56" s="49" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4693,26 +4729,26 @@
         <v>53</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E57" s="50" t="n">
         <v>46160</v>
       </c>
       <c r="F57" s="50"/>
       <c r="G57" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H57" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I57" s="49" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4723,23 +4759,23 @@
         <v>259</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E58" s="50" t="n">
         <v>46171</v>
       </c>
       <c r="F58" s="50"/>
       <c r="G58" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H58" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I58" s="49" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4750,23 +4786,23 @@
         <v>261</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E59" s="50" t="n">
         <v>46171</v>
       </c>
       <c r="F59" s="50"/>
       <c r="G59" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H59" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I59" s="49" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4774,26 +4810,26 @@
         <v>56</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="D60" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E60" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F60" s="50"/>
       <c r="G60" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="H60" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I60" s="49" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4804,23 +4840,23 @@
         <v>266</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E61" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F61" s="50"/>
       <c r="G61" s="49" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="H61" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I61" s="49" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4831,23 +4867,23 @@
         <v>263</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="E62" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F62" s="50"/>
       <c r="G62" s="49" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="H62" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="I62" s="49" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4855,26 +4891,26 @@
         <v>59</v>
       </c>
       <c r="B63" s="49" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="E63" s="50" t="n">
         <v>46176</v>
       </c>
       <c r="F63" s="50"/>
       <c r="G63" s="49" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="H63" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I63" s="49" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4882,26 +4918,26 @@
         <v>60</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="E64" s="50" t="n">
         <v>46176</v>
       </c>
       <c r="F64" s="50"/>
       <c r="G64" s="49" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="H64" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I64" s="49" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4912,64 +4948,64 @@
         <v>271</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="E65" s="50" t="n">
         <v>46178</v>
       </c>
       <c r="F65" s="50"/>
       <c r="G65" s="49" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="H65" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="I65" s="49" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="38" t="n">
         <v>62</v>
       </c>
       <c r="B66" s="49" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="C66" s="49" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="E66" s="50" t="n">
         <v>46210</v>
       </c>
       <c r="F66" s="50"/>
       <c r="G66" s="49" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="H66" s="49" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="I66" s="49" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="38" t="n">
         <v>63</v>
       </c>
       <c r="B67" s="49" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="E67" s="50" t="n">
         <v>46210</v>
@@ -4978,13 +5014,13 @@
         <v>46208</v>
       </c>
       <c r="G67" s="49" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="H67" s="49" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="I67" s="49" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -5035,7 +5071,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5046,7 +5082,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5060,22 +5096,22 @@
         <v>102</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5086,19 +5122,19 @@
         <v>163</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="D5" s="50" t="n">
         <v>46129</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G5" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5106,22 +5142,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="D6" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="F6" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G6" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5129,22 +5165,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="D7" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5152,22 +5188,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="D8" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G8" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5175,22 +5211,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="D9" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E9" s="49" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5198,22 +5234,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="D10" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E10" s="49" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="F10" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5221,22 +5257,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="D11" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="F11" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5247,16 +5283,16 @@
         <v>186</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="D12" s="50" t="n">
         <v>46139</v>
       </c>
       <c r="E12" s="49" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="F12" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G12" s="49" t="s">
         <v>217</v>
@@ -5267,22 +5303,22 @@
         <v>9</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D13" s="50" t="n">
         <v>46140</v>
       </c>
       <c r="E13" s="49" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5290,22 +5326,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="D14" s="50" t="n">
         <v>46141</v>
       </c>
       <c r="E14" s="49" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="F14" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5316,16 +5352,16 @@
         <v>196</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="D15" s="50" t="n">
         <v>46141</v>
       </c>
       <c r="E15" s="49" t="s">
+        <v>553</v>
+      </c>
+      <c r="F15" s="49" t="s">
         <v>541</v>
-      </c>
-      <c r="F15" s="49" t="s">
-        <v>529</v>
       </c>
       <c r="G15" s="49" t="s">
         <v>217</v>
@@ -5336,22 +5372,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="D16" s="50" t="n">
         <v>46142</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5362,16 +5398,16 @@
         <v>176</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="D17" s="50" t="n">
         <v>46142</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>217</v>
@@ -5385,19 +5421,19 @@
         <v>210</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="D18" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="F18" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5408,19 +5444,19 @@
         <v>183</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D19" s="50" t="n">
         <v>46148</v>
       </c>
       <c r="E19" s="49" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="F19" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G19" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5428,22 +5464,22 @@
         <v>16</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="D20" s="50" t="n">
         <v>46148</v>
       </c>
       <c r="E20" s="49" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="F20" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G20" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5454,19 +5490,19 @@
         <v>194</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="D21" s="50" t="n">
         <v>46148</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="F21" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5477,19 +5513,19 @@
         <v>188</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="D22" s="50" t="n">
         <v>46159</v>
       </c>
       <c r="E22" s="49" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="F22" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G22" s="49" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5500,82 +5536,82 @@
         <v>245</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="D23" s="50" t="n">
         <v>46162</v>
       </c>
       <c r="E23" s="49" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="F23" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G23" s="49" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="38" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="C24" s="49"/>
       <c r="D24" s="50" t="n">
         <v>46209</v>
       </c>
       <c r="E24" s="49" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F24" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G24" s="49"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="D25" s="50" t="n">
         <v>46208</v>
       </c>
       <c r="E25" s="49" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="F25" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G25" s="49"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="38" t="n">
         <v>22</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="D26" s="50" t="n">
         <v>46163</v>
       </c>
       <c r="E26" s="49" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="F26" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="G26" s="49" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -5614,7 +5650,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5626,7 +5662,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5641,22 +5677,22 @@
         <v>102</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>144</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>89</v>
@@ -5670,22 +5706,22 @@
         <v>163</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="D5" s="50" t="n">
         <v>46159</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="G5" s="49" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5693,23 +5729,23 @@
         <v>2</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="49" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="F6" s="49" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="G6" s="49" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="H6" s="49" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -18867,40 +18903,92 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="43"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
+      <c r="A15" s="43" t="s">
+        <v>336</v>
+      </c>
+      <c r="B15" s="43" t="s">
+        <v>337</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>338</v>
+      </c>
       <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
+      <c r="E15" s="43" t="s">
+        <v>309</v>
+      </c>
       <c r="F15" s="44"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
+      <c r="G15" s="42" t="n">
+        <v>46224</v>
+      </c>
+      <c r="H15" s="42" t="n">
+        <v>46224</v>
+      </c>
+      <c r="I15" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
+      <c r="A16" s="43" t="s">
+        <v>340</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>341</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>342</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>300</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>309</v>
+      </c>
       <c r="F16" s="44"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
+      <c r="G16" s="42" t="n">
+        <v>46224</v>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>46224</v>
+      </c>
+      <c r="I16" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="J16" s="43" t="s">
+        <v>343</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
+      <c r="A17" s="43" t="s">
+        <v>344</v>
+      </c>
+      <c r="B17" s="43" t="s">
+        <v>345</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>288</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>309</v>
+      </c>
       <c r="F17" s="44"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
+      <c r="G17" s="42" t="n">
+        <v>46224</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>46224</v>
+      </c>
+      <c r="I17" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="J17" s="43" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="43"/>
@@ -19734,7 +19822,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19748,7 +19836,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -19762,34 +19850,34 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>118</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20967,7 +21055,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -20979,7 +21067,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -20994,22 +21082,22 @@
         <v>144</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>153</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>156</v>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -1065,7 +1065,7 @@
     <t xml:space="preserve">Defense Health Agency (DHMS-CD, Rosslyn VA)</t>
   </si>
   <si>
-    <t xml:space="preserve">RFI ARMOR001 — Tier 1 fit (healthcare IT, MHS GENESIS/EHR integration, explainable AI). All FIVE use cases addressed (all-or-nothing per §3.1); 10pp cap; §3.5 OCI access GRANTED (BCG/Andrew Morgan/Monterey). Response + cover letter + cover page FINALIZED; send target 7/22 12:00pm EDT (hard wall 5:00pm EDT/EST discrepancy worst-cased). POCs: Louise Lewis CO (louise.b.lewis.civ@health.mil) + Rachael Bealer CS (rachael.n.bealer.civ@health.mil). OPEN: GSA SIN line ruling BEFORE send — reconciled state per CC Blockers panel: SIN 54151HEAL HELD but under Refresh 31 remediation (7 deficiencies open). Cover currently says 'None currently held' (conservative, OPP-024-style withholding); alternative = cite 54151HEAL since contract is held and §3.2.2 asks. Khaalis to rule. Anticipated RFP = pipeline priority; run scoring engine. Flip Stage→Submitted on confirmation.</t>
+    <t xml:space="preserve">RFI ARMOR001 — Tier 1 fit (healthcare IT, MHS GENESIS/EHR integration, explainable AI). All FIVE use cases addressed (all-or-nothing per §3.1); 10pp cap; §3.5 OCI access GRANTED (BCG/Andrew Morgan/Monterey). Response + cover letter + cover page FINALIZED; send target 7/22 12:00pm EDT (hard wall 5:00pm EDT/EST discrepancy worst-cased). POCs: Louise Lewis CO (louise.b.lewis.civ@health.mil) + Rachael Bealer CS (rachael.n.bealer.civ@health.mil). RESOLVED 7/21 (Khaalis ruling): GSA SIN line stays 'None currently held' — conservative wording stands (54151HEAL held but under Refresh 31 remediation, 7 deficiencies open; cite-SIN alternative declined). Anticipated RFP = pipeline priority; run scoring engine. Flip Stage→Submitted on confirmation.</t>
   </si>
   <si>
     <t xml:space="preserve">OPP-030</t>
@@ -2572,7 +2572,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>46222</v>
+        <v>46224</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>3</v>
@@ -2754,11 +2754,11 @@
       </c>
       <c r="D17" s="15" t="n">
         <f aca="false">Metrics_Period!D6</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">Metrics_Period!E6</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15" t="n">
         <f aca="false">Metrics_Period!F6</f>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">Metrics_Period!G6</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" s="16" t="n">
         <f aca="false">Metrics_Period!H6</f>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">Metrics_Period!G8</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H19" s="16" t="n">
         <f aca="false">Metrics_Period!H8</f>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C20" s="15" t="n">
         <f aca="false">Metrics_Period!C9</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="15" t="n">
         <f aca="false">Metrics_Period!D9</f>
@@ -2869,11 +2869,11 @@
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">Metrics_Period!E9</f>
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15" t="n">
         <f aca="false">Metrics_Period!F9</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G20" s="15" t="n">
         <f aca="false">Metrics_Period!G9</f>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="H20" s="16" t="n">
         <f aca="false">Metrics_Period!H9</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="15" t="n">
         <f aca="false">Metrics_Period!I9</f>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="J20" s="16" t="n">
         <f aca="false">Metrics_Period!J9</f>
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="J27" s="17" t="n">
         <f aca="false">Targets!C6/365*(As_Of_Date-DATE(YEAR(As_Of_Date),1,1)+1)</f>
-        <v>123085.479452055</v>
+        <v>124316.334246575</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="J28" s="19" t="n">
         <f aca="false">J24-J27</f>
-        <v>-85685.4794520548</v>
+        <v>-86916.3342465754</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6556,15 +6556,15 @@
       </c>
       <c r="K5" s="39" t="n">
         <f aca="false">COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-91,Screenings!E:E,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L5" s="39" t="n">
         <f aca="false">COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-182,Screenings!E:E,"&lt;"&amp;As_Of_Date-91)</f>
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M5" s="40" t="n">
         <f aca="false">IFERROR((K5-L5)/L5,0)</f>
-        <v>0.44</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="N5" s="40" t="n">
         <f aca="false">IFERROR((COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-365,Screenings!E:E,"&lt;="&amp;As_Of_Date-0)-COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-730,Screenings!E:E,"&lt;"&amp;As_Of_Date-365))/COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-730,Screenings!E:E,"&lt;"&amp;As_Of_Date-365),0)</f>
@@ -6584,11 +6584,11 @@
       </c>
       <c r="D6" s="39" t="n">
         <f aca="false">COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-14,NDAs!D:D,"&lt;"&amp;As_Of_Date-7)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="40" t="n">
         <f aca="false">IFERROR((C6-D6)/D6,0)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="39" t="n">
         <f aca="false">COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-30,NDAs!D:D,"&lt;="&amp;As_Of_Date-0)</f>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="G6" s="39" t="n">
         <f aca="false">COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-60,NDAs!D:D,"&lt;"&amp;As_Of_Date-30)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="40" t="n">
         <f aca="false">IFERROR((F6-G6)/G6,0)</f>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="G8" s="39" t="n">
         <f aca="false">COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-60,Meetings!A:A,"&lt;"&amp;As_Of_Date-30)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H8" s="40" t="n">
         <f aca="false">IFERROR((F8-G8)/G8,0)</f>
@@ -6724,15 +6724,15 @@
       </c>
       <c r="K8" s="39" t="n">
         <f aca="false">COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-91,Meetings!A:A,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L8" s="39" t="n">
         <f aca="false">COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-182,Meetings!A:A,"&lt;"&amp;As_Of_Date-91)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M8" s="40" t="n">
         <f aca="false">IFERROR((K8-L8)/L8,0)</f>
-        <v>2</v>
+        <v>1.11111111111111</v>
       </c>
       <c r="N8" s="40" t="n">
         <f aca="false">IFERROR((COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-365,Meetings!A:A,"&lt;="&amp;As_Of_Date-0)-COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-730,Meetings!A:A,"&lt;"&amp;As_Of_Date-365))/COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-730,Meetings!A:A,"&lt;"&amp;As_Of_Date-365),0)</f>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-7,Pipeline!G:G,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-14,Pipeline!G:G,"&lt;"&amp;As_Of_Date-7)</f>
@@ -6756,11 +6756,11 @@
       </c>
       <c r="E9" s="40" t="n">
         <f aca="false">IFERROR((C9-D9)/D9,0)</f>
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="F9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-30,Pipeline!G:G,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-60,Pipeline!G:G,"&lt;"&amp;As_Of_Date-30)</f>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="H9" s="40" t="n">
         <f aca="false">IFERROR((F9-G9)/G9,0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="39" t="n">
         <f aca="false">Targets!D38</f>
@@ -6776,11 +6776,11 @@
       </c>
       <c r="J9" s="40" t="n">
         <f aca="false">IFERROR((F9-I9)/I9,0)</f>
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="K9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-91,Pipeline!G:G,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-182,Pipeline!G:G,"&lt;"&amp;As_Of_Date-91)</f>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -1053,7 +1053,7 @@
     <t xml:space="preserve">USMC Forces Reserve (MFR G-1 / MCIRSA)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sources Sought M6786126IMKMAI — AI-enabled manpower modeling, readiness analytics, personnel allocation (IRR/SMCR). CUI notice; NAICS not stated on notice. Response + cover letter FINALIZED via vbx-solicitation-response gates; send scheduled by 7/29 (due 7/30 12:00pm CDT). Gated on Akil metric/cert checklist. POCs: Jordyn Edwards (jordyn.edwards@usmc.mil, 504-697-8355) + Parren Tatum (parren.tatum.civ@usmc.mil, 504-697-8308). Set-aside blank — SB shaping questions embedded in transmittal. Flip Stage→Submitted + StageDate on transmittal confirmation.</t>
+    <t xml:space="preserve">Sources Sought M6786126IMKMAI — AI-enabled manpower modeling, readiness analytics, personnel allocation (IRR/SMCR). CUI notice; NAICS not stated on notice. Response + cover letter FINALIZED via vbx-solicitation-response gates; TRANSMITTED 7/21/2026 7:00am CT (due 7/30 12:00pm CDT). POCs: Jordyn Edwards (jordyn.edwards@usmc.mil, 504-697-8355) + Parren Tatum (parren.tatum.civ@usmc.mil, 504-697-8308). Set-aside blank — SB shaping questions embedded in transmittal. Stage→Submitted 7/21/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">OPP-029</t>
@@ -1065,7 +1065,7 @@
     <t xml:space="preserve">Defense Health Agency (DHMS-CD, Rosslyn VA)</t>
   </si>
   <si>
-    <t xml:space="preserve">RFI ARMOR001 — Tier 1 fit (healthcare IT, MHS GENESIS/EHR integration, explainable AI). All FIVE use cases addressed (all-or-nothing per §3.1); 10pp cap; §3.5 OCI access GRANTED (BCG/Andrew Morgan/Monterey). Response + cover letter + cover page FINALIZED; send target 7/22 12:00pm EDT (hard wall 5:00pm EDT/EST discrepancy worst-cased). POCs: Louise Lewis CO (louise.b.lewis.civ@health.mil) + Rachael Bealer CS (rachael.n.bealer.civ@health.mil). RESOLVED 7/21 (Khaalis ruling): GSA SIN line stays 'None currently held' — conservative wording stands (54151HEAL held but under Refresh 31 remediation, 7 deficiencies open; cite-SIN alternative declined). Anticipated RFP = pipeline priority; run scoring engine. Flip Stage→Submitted on confirmation.</t>
+    <t xml:space="preserve">RFI ARMOR001 — Tier 1 fit (healthcare IT, MHS GENESIS/EHR integration, explainable AI). All FIVE use cases addressed (all-or-nothing per §3.1); 10pp cap; §3.5 OCI access GRANTED (BCG/Andrew Morgan/Monterey). Response + cover letter + cover page FINALIZED; TRANSMITTED 7/21/2026 7:00am CT (ahead of 7/22 12:00pm EDT target; 5:00pm hard wall). POCs: Louise Lewis CO (louise.b.lewis.civ@health.mil) + Rachael Bealer CS (rachael.n.bealer.civ@health.mil). RESOLVED 7/21 (Khaalis ruling): GSA SIN line stays 'None currently held' — conservative wording stands (54151HEAL held but under Refresh 31 remediation, 7 deficiencies open; cite-SIN alternative declined). Anticipated RFP = pipeline priority; run scoring engine. Stage→Submitted 7/21/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">OPP-030</t>
@@ -1077,7 +1077,7 @@
     <t xml:space="preserve">USGS / DOI (OAG-Denver)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sources Sought 140G0226Q0049 — NEIC real-time seismic streaming + detection; five SW dev task areas addressed. Tier 2/adjacent fit; candor positioning (transferable production AI/data engineering; NO seismology claims). Response + cover letter FINALIZED; send target 7/23 EOD (due 7/24 2:30pm EDT header vs MST body — worst-cased EDT). POC: Yvette Sornberger (yvette_sornberger@ios.doi.gov, 303-236-9332). OPEN: verify SAM Attachments/Links tab for response instructions before send. Score via capture engine before RFP-stage spend. Flip Stage→Submitted on confirmation.</t>
+    <t xml:space="preserve">Sources Sought 140G0226Q0049 — NEIC real-time seismic streaming + detection; five SW dev task areas addressed. Tier 2/adjacent fit; candor positioning (transferable production AI/data engineering; NO seismology claims). Response + cover letter FINALIZED; TRANSMITTED 7/21/2026 7:00am CT (due 7/24 2:30pm EDT worst-cased). POC: Yvette Sornberger (yvette_sornberger@ios.doi.gov, 303-236-9332). Pre-send SAM Attachments/Links check superseded by 7/21 transmittal. Score via capture engine before RFP-stage spend. Stage→Submitted 7/21/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">  ACTIVE PROJECTS  —  Post-award execution tracking</t>
@@ -18914,7 +18914,7 @@
       </c>
       <c r="D15" s="43"/>
       <c r="E15" s="43" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F15" s="44"/>
       <c r="G15" s="42" t="n">
@@ -18944,7 +18944,7 @@
         <v>300</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F16" s="44"/>
       <c r="G16" s="42" t="n">
@@ -18974,7 +18974,7 @@
         <v>288</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F17" s="44"/>
       <c r="G17" s="42" t="n">

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="601">
   <si>
     <t xml:space="preserve">  VISIONBLOX COMMAND CENTER  |  CAGE 9Z4X2  |  UEI H4X2Z7R9E3E3</t>
   </si>
@@ -858,6 +858,15 @@
     <t xml:space="preserve">FILED — quarterly re-screen on healthcare federal pivot</t>
   </si>
   <si>
+    <t xml:space="preserve">Khaalis Wooden, Alan Sosa (TES)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly TES × VBX sync — joint NO-BID on CBO SENTRY BPA (CB26-RFQ0012): Model C 5.35/10, net EV ~$3.3K/yr; required gap closures not secured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redirect TES to set-aside-accessible RFQs; ≥2 qualified pursuits scored by 8/31</t>
+  </si>
+  <si>
     <t xml:space="preserve">  PIPELINE  —  Active Opportunities</t>
   </si>
   <si>
@@ -963,10 +972,7 @@
     <t xml:space="preserve">Congressional Budget Office (CBO)</t>
   </si>
   <si>
-    <t xml:space="preserve">Capture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TES x VBX teaming (VBX as sub). VBX quoting SMA 2 LCATs: J4 Microsoft Cloud Engineering SME + J5 Full Stack Developer. 5-yr BPA under GSA IT Schedule SIN 54151S. PoP 8/15/26–8/14/31. Questions due 6/18/26; quote due 7/7/26 5pm ET via OAM@cbo.gov. Public Trust Tier 2 (Capitol Police). Remote w/ on-site option at FHOB DC. VBX share est. = 2 FTE × 5yr.</t>
+    <t xml:space="preserve">NO-BID 8/5/26 — joint TES × VBX decision at monthly sync, 5 days before the 8/10 1300 ET deadline; TES will not prime, VBX will not sub. Gate 1 passed; fails Gate 2 on economics: Model C score 5.35/10 (Moderate, 25% Pwin), inside the 5.0–5.5 window that permits a bid only with named gap closures secured — none were (officer-signed TA w/ workshare floor + SMA 2 exclusivity; a PP reference slot; VBX named in Factor 3). Structural finding: ceiling &gt;$1M–&lt;$10M across 6 SMAs, 1–3 awards; VBX addressable slice ≈ $458K/5yr → net EV ~$16.4K/5yr (~$3.3K/yr) vs $5M ARR target. All four scoring gaps (F4/F5/F6/F7) structural — no partner closes them. Work product retained: SMA 2 Vol I v2.0 (29pp, requirement traceability), Vol II v2.0 (11pp, federal-analog PP framing), Amendment 0004 / 995-item Q&amp;A analysis. Lessons → Gate 1: add vehicle-economics screen (ceiling ÷ lots ÷ awards ÷ PoP ≥ $500K/yr) + subcontractor citability test; execute teaming instrument BEFORE transmitting volumes. TES relationship intact — redirect to smaller set-aside RFQs/RFPs by 8/31.</t>
   </si>
   <si>
     <t xml:space="preserve">OPP-023</t>
@@ -1636,6 +1642,54 @@
   </si>
   <si>
     <t xml:space="preserve">Cleared Staffing / GovCon Labor (J4 LCAT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Technology Solutions (TTS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hesh Ansari, Ph.D., PMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8(a) / SDVOSB / VA SwaM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal IT / Health IT / VA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8/5/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sampson, Jefferson &amp; Associates (SJA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiffanye Paige</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8(a) / WOSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Healthcare QA / Mgmt Consulting — HHS/CMS corridor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triton Light Medical (TLM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kennon Artis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VA Medical Products / Distribution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BuenaVista Information Systems (BVIS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adrian J. Lorduy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDVOSB / VOSB — SAM expired 1/6/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial MSP / Cyber (SC)</t>
   </si>
   <si>
     <t xml:space="preserve">  NDAs  —  Executed NDA Register</t>
@@ -2572,7 +2626,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>46224</v>
+        <v>46239</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>3</v>
@@ -2650,11 +2704,11 @@
     <row r="12" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="12" t="n">
         <f aca="false">SUMPRODUCT((Pipeline!E5:E1000&lt;&gt;"")*(Pipeline!E5:E1000&lt;&gt;"Awarded")*(Pipeline!E5:E1000&lt;&gt;"Lost")*(Pipeline!E5:E1000&lt;&gt;"No-Bid"))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="9" t="n">
         <f aca="false">SUMIFS(Pipeline!F5:F1000,Pipeline!E5:E1000,"&lt;&gt;Awarded",Pipeline!E5:E1000,"&lt;&gt;Lost",Pipeline!E5:E1000,"&lt;&gt;No-Bid",Pipeline!E5:E1000,"&lt;&gt;")</f>
-        <v>4000000</v>
+        <v>0</v>
       </c>
       <c r="E12" s="12" t="n">
         <f aca="false">COUNTIFS(Active_Projects!H:H,"Active")</f>
@@ -2713,27 +2767,27 @@
       </c>
       <c r="C16" s="15" t="n">
         <f aca="false">Metrics_Period!C5</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D16" s="15" t="n">
         <f aca="false">Metrics_Period!D5</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="16" t="n">
         <f aca="false">Metrics_Period!E5</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15" t="n">
         <f aca="false">Metrics_Period!F5</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15" t="n">
         <f aca="false">Metrics_Period!G5</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H16" s="16" t="n">
         <f aca="false">Metrics_Period!H5</f>
-        <v>-0.833333333333333</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15" t="n">
         <f aca="false">Metrics_Period!I5</f>
@@ -2741,7 +2795,7 @@
       </c>
       <c r="J16" s="16" t="n">
         <f aca="false">Metrics_Period!J5</f>
-        <v>-0.923076923076923</v>
+        <v>-0.769230769230769</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2762,11 +2816,11 @@
       </c>
       <c r="F17" s="15" t="n">
         <f aca="false">Metrics_Period!F6</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">Metrics_Period!G6</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="16" t="n">
         <f aca="false">Metrics_Period!H6</f>
@@ -2778,7 +2832,7 @@
       </c>
       <c r="J17" s="16" t="n">
         <f aca="false">Metrics_Period!J6</f>
-        <v>-0.777777777777778</v>
+        <v>-0.888888888888889</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2824,7 +2878,7 @@
       </c>
       <c r="C19" s="15" t="n">
         <f aca="false">Metrics_Period!C8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="15" t="n">
         <f aca="false">Metrics_Period!D8</f>
@@ -2836,15 +2890,15 @@
       </c>
       <c r="F19" s="15" t="n">
         <f aca="false">Metrics_Period!F8</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">Metrics_Period!G8</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H19" s="16" t="n">
         <f aca="false">Metrics_Period!H8</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15" t="n">
         <f aca="false">Metrics_Period!I8</f>
@@ -2852,7 +2906,7 @@
       </c>
       <c r="J19" s="16" t="n">
         <f aca="false">Metrics_Period!J8</f>
-        <v>-1</v>
+        <v>-0.888888888888889</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2861,11 +2915,11 @@
       </c>
       <c r="C20" s="15" t="n">
         <f aca="false">Metrics_Period!C9</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D20" s="15" t="n">
         <f aca="false">Metrics_Period!D9</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
         <f aca="false">Metrics_Period!E9</f>
@@ -2873,7 +2927,7 @@
       </c>
       <c r="F20" s="15" t="n">
         <f aca="false">Metrics_Period!F9</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="15" t="n">
         <f aca="false">Metrics_Period!G9</f>
@@ -2881,7 +2935,7 @@
       </c>
       <c r="H20" s="16" t="n">
         <f aca="false">Metrics_Period!H9</f>
-        <v>2</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="I20" s="15" t="n">
         <f aca="false">Metrics_Period!I9</f>
@@ -2889,7 +2943,7 @@
       </c>
       <c r="J20" s="16" t="n">
         <f aca="false">Metrics_Period!J9</f>
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2944,7 +2998,7 @@
       </c>
       <c r="F24" s="17" t="n">
         <f aca="false">Metrics_Period!F13</f>
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="G24" s="17" t="n">
         <f aca="false">Metrics_Period!G13</f>
@@ -2952,11 +3006,11 @@
       </c>
       <c r="H24" s="16" t="n">
         <f aca="false">Metrics_Period!H13</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I24" s="17" t="n">
         <f aca="false">Metrics_Period!K13</f>
-        <v>29900</v>
+        <v>27400</v>
       </c>
       <c r="J24" s="17" t="n">
         <f aca="false">Metrics_Period!L13</f>
@@ -3018,7 +3072,7 @@
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">Metrics_Period!F15</f>
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="G26" s="17" t="n">
         <f aca="false">Metrics_Period!G15</f>
@@ -3026,11 +3080,11 @@
       </c>
       <c r="H26" s="16" t="n">
         <f aca="false">Metrics_Period!H15</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I26" s="17" t="n">
         <f aca="false">Metrics_Period!K15</f>
-        <v>29900</v>
+        <v>27400</v>
       </c>
       <c r="J26" s="17" t="n">
         <f aca="false">Metrics_Period!L15</f>
@@ -3071,7 +3125,7 @@
       </c>
       <c r="J27" s="17" t="n">
         <f aca="false">Targets!C6/365*(As_Of_Date-DATE(YEAR(As_Of_Date),1,1)+1)</f>
-        <v>124316.334246575</v>
+        <v>133547.745205479</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3092,7 +3146,7 @@
       </c>
       <c r="F28" s="19" t="n">
         <f aca="false">F24-F27</f>
-        <v>-4762.82191780822</v>
+        <v>-18462.8219178082</v>
       </c>
       <c r="G28" s="19" t="n">
         <f aca="false">G24-G27</f>
@@ -3100,15 +3154,15 @@
       </c>
       <c r="H28" s="20" t="n">
         <f aca="false">IFERROR((F28-G28)/IF(G28=0,1,ABS(G28)),0)</f>
-        <v>0</v>
+        <v>-2.87644598862192</v>
       </c>
       <c r="I28" s="19" t="n">
         <f aca="false">I24-I27</f>
-        <v>-26103.8931506849</v>
+        <v>-28603.8931506849</v>
       </c>
       <c r="J28" s="19" t="n">
         <f aca="false">J24-J27</f>
-        <v>-86916.3342465754</v>
+        <v>-96147.7452054795</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3233,7 +3287,7 @@
     <tabColor rgb="FF90A4AE"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -3247,7 +3301,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3260,7 +3314,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3276,28 +3330,28 @@
         <v>102</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3308,10 +3362,10 @@
         <v>157</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E5" s="50" t="n">
         <v>46112</v>
@@ -3320,13 +3374,13 @@
         <v>46038</v>
       </c>
       <c r="G5" s="49" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I5" s="49" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3334,26 +3388,26 @@
         <v>2</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D6" s="49" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E6" s="50" t="n">
         <v>46112</v>
       </c>
       <c r="F6" s="50"/>
       <c r="G6" s="49" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H6" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I6" s="49" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3361,26 +3415,26 @@
         <v>3</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E7" s="50" t="n">
         <v>46112</v>
       </c>
       <c r="F7" s="50"/>
       <c r="G7" s="49" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I7" s="49" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3391,23 +3445,23 @@
         <v>168</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D8" s="49" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E8" s="50" t="n">
         <v>46131</v>
       </c>
       <c r="F8" s="50"/>
       <c r="G8" s="49" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H8" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I8" s="49" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3418,23 +3472,23 @@
         <v>173</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E9" s="50" t="n">
         <v>46131</v>
       </c>
       <c r="F9" s="50"/>
       <c r="G9" s="49" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H9" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I9" s="49" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3445,10 +3499,10 @@
         <v>183</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D10" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E10" s="50" t="n">
         <v>46135</v>
@@ -3457,13 +3511,13 @@
         <v>46148</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="H10" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I10" s="49" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3474,10 +3528,10 @@
         <v>194</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E11" s="50" t="n">
         <v>46139</v>
@@ -3486,13 +3540,13 @@
         <v>46148</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H11" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I11" s="49" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3503,10 +3557,10 @@
         <v>201</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D12" s="49" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E12" s="50" t="n">
         <v>46140</v>
@@ -3515,13 +3569,13 @@
         <v>46141</v>
       </c>
       <c r="G12" s="49" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H12" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I12" s="49" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3532,10 +3586,10 @@
         <v>207</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E13" s="50" t="n">
         <v>46142</v>
@@ -3544,13 +3598,13 @@
         <v>46142</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H13" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I13" s="49" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3558,26 +3612,26 @@
         <v>10</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D14" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E14" s="50"/>
       <c r="F14" s="50" t="n">
         <v>46148</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H14" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I14" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3585,24 +3639,24 @@
         <v>11</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E15" s="50"/>
       <c r="F15" s="50"/>
       <c r="G15" s="49" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H15" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I15" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3613,23 +3667,23 @@
         <v>232</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D16" s="49" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E16" s="50" t="n">
         <v>46154</v>
       </c>
       <c r="F16" s="50"/>
       <c r="G16" s="49" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H16" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I16" s="49" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3640,23 +3694,23 @@
         <v>236</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E17" s="50" t="n">
         <v>46154</v>
       </c>
       <c r="F17" s="50"/>
       <c r="G17" s="49" t="s">
+        <v>423</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="I17" s="49" t="s">
         <v>421</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>379</v>
-      </c>
-      <c r="I17" s="49" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3664,13 +3718,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D18" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E18" s="50" t="n">
         <v>46127</v>
@@ -3679,13 +3733,13 @@
         <v>46127</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H18" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I18" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3693,26 +3747,26 @@
         <v>15</v>
       </c>
       <c r="B19" s="49" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D19" s="49" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E19" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F19" s="50"/>
       <c r="G19" s="49" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="H19" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I19" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3723,10 +3777,10 @@
         <v>196</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D20" s="49" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E20" s="50" t="n">
         <v>46139</v>
@@ -3735,13 +3789,13 @@
         <v>46141</v>
       </c>
       <c r="G20" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H20" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I20" s="49" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3752,10 +3806,10 @@
         <v>186</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D21" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E21" s="50" t="n">
         <v>46135</v>
@@ -3764,13 +3818,13 @@
         <v>46139</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H21" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I21" s="49" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3781,23 +3835,23 @@
         <v>198</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D22" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E22" s="50" t="n">
         <v>46139</v>
       </c>
       <c r="F22" s="50"/>
       <c r="G22" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H22" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I22" s="49" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3808,23 +3862,23 @@
         <v>204</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D23" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E23" s="50" t="n">
         <v>46140</v>
       </c>
       <c r="F23" s="50"/>
       <c r="G23" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H23" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I23" s="49" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3835,10 +3889,10 @@
         <v>176</v>
       </c>
       <c r="C24" s="49" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D24" s="49" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E24" s="50" t="n">
         <v>46132</v>
@@ -3847,13 +3901,13 @@
         <v>46142</v>
       </c>
       <c r="G24" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H24" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I24" s="49" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3864,23 +3918,23 @@
         <v>215</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D25" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E25" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="F25" s="50"/>
       <c r="G25" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H25" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I25" s="49" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3891,23 +3945,23 @@
         <v>212</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D26" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E26" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="F26" s="50"/>
       <c r="G26" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H26" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I26" s="49" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3915,26 +3969,26 @@
         <v>23</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E27" s="50" t="n">
         <v>46112</v>
       </c>
       <c r="F27" s="50"/>
       <c r="G27" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H27" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I27" s="49" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3942,26 +3996,26 @@
         <v>24</v>
       </c>
       <c r="B28" s="49" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D28" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E28" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F28" s="50"/>
       <c r="G28" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H28" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I28" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3969,26 +4023,26 @@
         <v>25</v>
       </c>
       <c r="B29" s="49" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C29" s="49" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D29" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E29" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F29" s="50"/>
       <c r="G29" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H29" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I29" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3996,26 +4050,26 @@
         <v>26</v>
       </c>
       <c r="B30" s="49" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C30" s="49" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D30" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E30" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F30" s="50"/>
       <c r="G30" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H30" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I30" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4026,10 +4080,10 @@
         <v>210</v>
       </c>
       <c r="C31" s="49" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D31" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E31" s="50" t="n">
         <v>46134</v>
@@ -4038,13 +4092,13 @@
         <v>46146</v>
       </c>
       <c r="G31" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H31" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I31" s="49" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4055,10 +4109,10 @@
         <v>188</v>
       </c>
       <c r="C32" s="49" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D32" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E32" s="50" t="n">
         <v>46135</v>
@@ -4067,13 +4121,13 @@
         <v>46159</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H32" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I32" s="49" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4084,23 +4138,23 @@
         <v>191</v>
       </c>
       <c r="C33" s="49" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D33" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E33" s="50" t="n">
         <v>46138</v>
       </c>
       <c r="F33" s="50"/>
       <c r="G33" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H33" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I33" s="49" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4111,23 +4165,23 @@
         <v>218</v>
       </c>
       <c r="C34" s="49" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D34" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E34" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="F34" s="50"/>
       <c r="G34" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H34" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I34" s="49" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4138,23 +4192,23 @@
         <v>221</v>
       </c>
       <c r="C35" s="49" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D35" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E35" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="F35" s="50"/>
       <c r="G35" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H35" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I35" s="49" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4162,26 +4216,26 @@
         <v>32</v>
       </c>
       <c r="B36" s="49" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C36" s="49" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D36" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E36" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F36" s="50"/>
       <c r="G36" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H36" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I36" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4189,26 +4243,26 @@
         <v>33</v>
       </c>
       <c r="B37" s="49" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C37" s="49" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D37" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E37" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F37" s="50"/>
       <c r="G37" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H37" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I37" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4216,26 +4270,26 @@
         <v>34</v>
       </c>
       <c r="B38" s="49" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C38" s="49" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D38" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E38" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F38" s="50"/>
       <c r="G38" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H38" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I38" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4246,23 +4300,23 @@
         <v>163</v>
       </c>
       <c r="C39" s="49" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D39" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E39" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F39" s="50"/>
       <c r="G39" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H39" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I39" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4270,26 +4324,26 @@
         <v>36</v>
       </c>
       <c r="B40" s="49" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C40" s="49" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D40" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E40" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F40" s="50"/>
       <c r="G40" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H40" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I40" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4297,26 +4351,26 @@
         <v>37</v>
       </c>
       <c r="B41" s="49" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C41" s="49" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D41" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E41" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F41" s="50"/>
       <c r="G41" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H41" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I41" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4324,26 +4378,26 @@
         <v>38</v>
       </c>
       <c r="B42" s="49" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C42" s="49" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D42" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E42" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F42" s="50"/>
       <c r="G42" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H42" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I42" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4351,26 +4405,26 @@
         <v>39</v>
       </c>
       <c r="B43" s="49" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C43" s="49" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D43" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E43" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F43" s="50"/>
       <c r="G43" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H43" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I43" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4378,26 +4432,26 @@
         <v>40</v>
       </c>
       <c r="B44" s="49" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C44" s="49" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D44" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E44" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F44" s="50"/>
       <c r="G44" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H44" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I44" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4405,26 +4459,26 @@
         <v>41</v>
       </c>
       <c r="B45" s="49" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C45" s="49" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D45" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E45" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F45" s="50"/>
       <c r="G45" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H45" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I45" s="49" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4435,23 +4489,23 @@
         <v>179</v>
       </c>
       <c r="C46" s="49" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D46" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E46" s="50" t="n">
         <v>46132</v>
       </c>
       <c r="F46" s="50"/>
       <c r="G46" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H46" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I46" s="49" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4459,26 +4513,26 @@
         <v>43</v>
       </c>
       <c r="B47" s="49" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C47" s="49" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D47" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E47" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F47" s="50"/>
       <c r="G47" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H47" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I47" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4486,26 +4540,26 @@
         <v>44</v>
       </c>
       <c r="B48" s="49" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C48" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D48" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E48" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F48" s="50"/>
       <c r="G48" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H48" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I48" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4513,26 +4567,26 @@
         <v>45</v>
       </c>
       <c r="B49" s="49" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C49" s="49" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D49" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E49" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F49" s="50"/>
       <c r="G49" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H49" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I49" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4540,26 +4594,26 @@
         <v>46</v>
       </c>
       <c r="B50" s="49" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C50" s="49" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E50" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F50" s="50"/>
       <c r="G50" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H50" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I50" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4567,26 +4621,26 @@
         <v>47</v>
       </c>
       <c r="B51" s="49" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C51" s="49" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E51" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F51" s="50"/>
       <c r="G51" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H51" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I51" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4594,26 +4648,26 @@
         <v>48</v>
       </c>
       <c r="B52" s="49" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C52" s="49" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E52" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="F52" s="50"/>
       <c r="G52" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H52" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I52" s="49" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4621,26 +4675,26 @@
         <v>49</v>
       </c>
       <c r="B53" s="49" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C53" s="49" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E53" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F53" s="50"/>
       <c r="G53" s="49" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="H53" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I53" s="49" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4651,23 +4705,23 @@
         <v>266</v>
       </c>
       <c r="C54" s="49" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E54" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F54" s="50"/>
       <c r="G54" s="49" t="s">
+        <v>495</v>
+      </c>
+      <c r="H54" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="I54" s="49" t="s">
         <v>493</v>
-      </c>
-      <c r="H54" s="49" t="s">
-        <v>379</v>
-      </c>
-      <c r="I54" s="49" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4675,26 +4729,26 @@
         <v>51</v>
       </c>
       <c r="B55" s="49" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C55" s="49" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D55" s="49" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E55" s="50" t="n">
         <v>46168</v>
       </c>
       <c r="F55" s="50"/>
       <c r="G55" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H55" s="49" t="s">
         <v>217</v>
       </c>
       <c r="I55" s="49" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4702,26 +4756,26 @@
         <v>52</v>
       </c>
       <c r="B56" s="49" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C56" s="49" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D56" s="49" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E56" s="50" t="n">
         <v>46168</v>
       </c>
       <c r="F56" s="50"/>
       <c r="G56" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H56" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="I56" s="49" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4729,26 +4783,26 @@
         <v>53</v>
       </c>
       <c r="B57" s="49" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C57" s="49" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D57" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E57" s="50" t="n">
         <v>46160</v>
       </c>
       <c r="F57" s="50"/>
       <c r="G57" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H57" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I57" s="49" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4759,23 +4813,23 @@
         <v>259</v>
       </c>
       <c r="C58" s="49" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D58" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E58" s="50" t="n">
         <v>46171</v>
       </c>
       <c r="F58" s="50"/>
       <c r="G58" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H58" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I58" s="49" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4786,23 +4840,23 @@
         <v>261</v>
       </c>
       <c r="C59" s="49" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D59" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E59" s="50" t="n">
         <v>46171</v>
       </c>
       <c r="F59" s="50"/>
       <c r="G59" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H59" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I59" s="49" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4810,26 +4864,26 @@
         <v>56</v>
       </c>
       <c r="B60" s="49" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C60" s="49" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D60" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E60" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F60" s="50"/>
       <c r="G60" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H60" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I60" s="49" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4840,23 +4894,23 @@
         <v>266</v>
       </c>
       <c r="C61" s="49" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D61" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E61" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F61" s="50"/>
       <c r="G61" s="49" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="H61" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I61" s="49" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4867,23 +4921,23 @@
         <v>263</v>
       </c>
       <c r="C62" s="49" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D62" s="49" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E62" s="50" t="n">
         <v>46174</v>
       </c>
       <c r="F62" s="50"/>
       <c r="G62" s="49" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H62" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="I62" s="49" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4891,26 +4945,26 @@
         <v>59</v>
       </c>
       <c r="B63" s="49" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C63" s="49" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D63" s="49" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E63" s="50" t="n">
         <v>46176</v>
       </c>
       <c r="F63" s="50"/>
       <c r="G63" s="49" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H63" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I63" s="49" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4918,26 +4972,26 @@
         <v>60</v>
       </c>
       <c r="B64" s="49" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C64" s="49" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D64" s="49" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E64" s="50" t="n">
         <v>46176</v>
       </c>
       <c r="F64" s="50"/>
       <c r="G64" s="49" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H64" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I64" s="49" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4948,23 +5002,23 @@
         <v>271</v>
       </c>
       <c r="C65" s="49" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D65" s="49" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E65" s="50" t="n">
         <v>46178</v>
       </c>
       <c r="F65" s="50"/>
       <c r="G65" s="49" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H65" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="I65" s="49" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4972,26 +5026,26 @@
         <v>62</v>
       </c>
       <c r="B66" s="49" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C66" s="49" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D66" s="49" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E66" s="50" t="n">
         <v>46210</v>
       </c>
       <c r="F66" s="50"/>
       <c r="G66" s="49" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H66" s="49" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I66" s="49" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4999,13 +5053,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C67" s="49" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D67" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E67" s="50" t="n">
         <v>46210</v>
@@ -5014,13 +5068,121 @@
         <v>46208</v>
       </c>
       <c r="G67" s="49" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="H67" s="49" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I67" s="49" t="s">
-        <v>530</v>
+        <v>532</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="38" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="49" t="s">
+        <v>536</v>
+      </c>
+      <c r="C68" s="49" t="s">
+        <v>537</v>
+      </c>
+      <c r="D68" s="49" t="s">
+        <v>538</v>
+      </c>
+      <c r="E68" s="50" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F68" s="50"/>
+      <c r="G68" s="49" t="s">
+        <v>539</v>
+      </c>
+      <c r="H68" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="I68" s="49" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="38" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="49" t="s">
+        <v>541</v>
+      </c>
+      <c r="C69" s="49" t="s">
+        <v>542</v>
+      </c>
+      <c r="D69" s="49" t="s">
+        <v>543</v>
+      </c>
+      <c r="E69" s="50" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F69" s="50"/>
+      <c r="G69" s="49" t="s">
+        <v>544</v>
+      </c>
+      <c r="H69" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="I69" s="49" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="38" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="49" t="s">
+        <v>545</v>
+      </c>
+      <c r="C70" s="49" t="s">
+        <v>546</v>
+      </c>
+      <c r="D70" s="49" t="s">
+        <v>389</v>
+      </c>
+      <c r="E70" s="50" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F70" s="50"/>
+      <c r="G70" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="H70" s="49" t="s">
+        <v>447</v>
+      </c>
+      <c r="I70" s="49" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="38" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="C71" s="49" t="s">
+        <v>549</v>
+      </c>
+      <c r="D71" s="49" t="s">
+        <v>550</v>
+      </c>
+      <c r="E71" s="50" t="n">
+        <v>46239</v>
+      </c>
+      <c r="F71" s="50"/>
+      <c r="G71" s="49" t="s">
+        <v>551</v>
+      </c>
+      <c r="H71" s="49" t="s">
+        <v>447</v>
+      </c>
+      <c r="I71" s="49" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -5071,7 +5233,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5082,7 +5244,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5096,22 +5258,22 @@
         <v>102</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5122,19 +5284,19 @@
         <v>163</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D5" s="50" t="n">
         <v>46129</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G5" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5142,22 +5304,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D6" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="F6" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G6" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5165,22 +5327,22 @@
         <v>3</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D7" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5188,22 +5350,22 @@
         <v>4</v>
       </c>
       <c r="B8" s="49" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D8" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E8" s="49" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="F8" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G8" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5211,22 +5373,22 @@
         <v>5</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D9" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E9" s="49" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5234,22 +5396,22 @@
         <v>6</v>
       </c>
       <c r="B10" s="49" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D10" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E10" s="49" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="F10" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5257,22 +5419,22 @@
         <v>7</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D11" s="50" t="n">
         <v>46127</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="F11" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5283,16 +5445,16 @@
         <v>186</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D12" s="50" t="n">
         <v>46139</v>
       </c>
       <c r="E12" s="49" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="F12" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G12" s="49" t="s">
         <v>217</v>
@@ -5303,22 +5465,22 @@
         <v>9</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D13" s="50" t="n">
         <v>46140</v>
       </c>
       <c r="E13" s="49" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G13" s="49" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5326,22 +5488,22 @@
         <v>10</v>
       </c>
       <c r="B14" s="49" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D14" s="50" t="n">
         <v>46141</v>
       </c>
       <c r="E14" s="49" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="F14" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G14" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5352,16 +5514,16 @@
         <v>196</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D15" s="50" t="n">
         <v>46141</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G15" s="49" t="s">
         <v>217</v>
@@ -5372,22 +5534,22 @@
         <v>12</v>
       </c>
       <c r="B16" s="49" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D16" s="50" t="n">
         <v>46142</v>
       </c>
       <c r="E16" s="49" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G16" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5398,16 +5560,16 @@
         <v>176</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D17" s="50" t="n">
         <v>46142</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>217</v>
@@ -5421,19 +5583,19 @@
         <v>210</v>
       </c>
       <c r="C18" s="49" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D18" s="50" t="n">
         <v>46146</v>
       </c>
       <c r="E18" s="49" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="F18" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G18" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5444,19 +5606,19 @@
         <v>183</v>
       </c>
       <c r="C19" s="49" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D19" s="50" t="n">
         <v>46148</v>
       </c>
       <c r="E19" s="49" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="F19" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G19" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5464,22 +5626,22 @@
         <v>16</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>559</v>
+        <v>577</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D20" s="50" t="n">
         <v>46148</v>
       </c>
       <c r="E20" s="49" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="F20" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G20" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5490,19 +5652,19 @@
         <v>194</v>
       </c>
       <c r="C21" s="49" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D21" s="50" t="n">
         <v>46148</v>
       </c>
       <c r="E21" s="49" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="F21" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G21" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5513,19 +5675,19 @@
         <v>188</v>
       </c>
       <c r="C22" s="49" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D22" s="50" t="n">
         <v>46159</v>
       </c>
       <c r="E22" s="49" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="F22" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G22" s="49" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5536,16 +5698,16 @@
         <v>245</v>
       </c>
       <c r="C23" s="49" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="D23" s="50" t="n">
         <v>46162</v>
       </c>
       <c r="E23" s="49" t="s">
-        <v>564</v>
+        <v>582</v>
       </c>
       <c r="F23" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G23" s="49" t="s">
         <v>217</v>
@@ -5556,17 +5718,17 @@
         <v>20</v>
       </c>
       <c r="B24" s="49" t="s">
-        <v>565</v>
+        <v>583</v>
       </c>
       <c r="C24" s="49"/>
       <c r="D24" s="50" t="n">
         <v>46209</v>
       </c>
       <c r="E24" s="49" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="F24" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G24" s="49"/>
     </row>
@@ -5575,19 +5737,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="49" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="D25" s="50" t="n">
         <v>46208</v>
       </c>
       <c r="E25" s="49" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="F25" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G25" s="49"/>
     </row>
@@ -5596,22 +5758,22 @@
         <v>22</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="C26" s="49" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D26" s="50" t="n">
         <v>46163</v>
       </c>
       <c r="E26" s="49" t="s">
-        <v>570</v>
+        <v>588</v>
       </c>
       <c r="F26" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="G26" s="49" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -5650,7 +5812,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5662,7 +5824,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5677,22 +5839,22 @@
         <v>102</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>144</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>89</v>
@@ -5706,22 +5868,22 @@
         <v>163</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D5" s="50" t="n">
         <v>46159</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="G5" s="49" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5729,23 +5891,23 @@
         <v>2</v>
       </c>
       <c r="B6" s="49" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D6" s="50"/>
       <c r="E6" s="49" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="F6" s="49" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
       <c r="G6" s="49" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="H6" s="49" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -6524,27 +6686,27 @@
       </c>
       <c r="C5" s="39" t="n">
         <f aca="false">COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-7,Screenings!E:E,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="39" t="n">
         <f aca="false">COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-14,Screenings!E:E,"&lt;"&amp;As_Of_Date-7)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5" s="40" t="n">
         <f aca="false">IFERROR((C5-D5)/D5,0)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="39" t="n">
         <f aca="false">COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-30,Screenings!E:E,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G5" s="39" t="n">
         <f aca="false">COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-60,Screenings!E:E,"&lt;"&amp;As_Of_Date-30)</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H5" s="40" t="n">
         <f aca="false">IFERROR((F5-G5)/G5,0)</f>
-        <v>-0.833333333333333</v>
+        <v>0</v>
       </c>
       <c r="I5" s="39" t="n">
         <f aca="false">Targets!D34</f>
@@ -6552,19 +6714,19 @@
       </c>
       <c r="J5" s="40" t="n">
         <f aca="false">IFERROR((F5-I5)/I5,0)</f>
-        <v>-0.923076923076923</v>
+        <v>-0.769230769230769</v>
       </c>
       <c r="K5" s="39" t="n">
         <f aca="false">COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-91,Screenings!E:E,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L5" s="39" t="n">
         <f aca="false">COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-182,Screenings!E:E,"&lt;"&amp;As_Of_Date-91)</f>
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M5" s="40" t="n">
         <f aca="false">IFERROR((K5-L5)/L5,0)</f>
-        <v>0.103448275862069</v>
+        <v>-0.522727272727273</v>
       </c>
       <c r="N5" s="40" t="n">
         <f aca="false">IFERROR((COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-365,Screenings!E:E,"&lt;="&amp;As_Of_Date-0)-COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-730,Screenings!E:E,"&lt;"&amp;As_Of_Date-365))/COUNTIFS(Screenings!E:E,"&gt;="&amp;As_Of_Date-730,Screenings!E:E,"&lt;"&amp;As_Of_Date-365),0)</f>
@@ -6592,11 +6754,11 @@
       </c>
       <c r="F6" s="39" t="n">
         <f aca="false">COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-30,NDAs!D:D,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="39" t="n">
         <f aca="false">COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-60,NDAs!D:D,"&lt;"&amp;As_Of_Date-30)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="40" t="n">
         <f aca="false">IFERROR((F6-G6)/G6,0)</f>
@@ -6608,19 +6770,19 @@
       </c>
       <c r="J6" s="40" t="n">
         <f aca="false">IFERROR((F6-I6)/I6,0)</f>
-        <v>-0.777777777777778</v>
+        <v>-0.888888888888889</v>
       </c>
       <c r="K6" s="39" t="n">
         <f aca="false">COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-91,NDAs!D:D,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L6" s="39" t="n">
         <f aca="false">COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-182,NDAs!D:D,"&lt;"&amp;As_Of_Date-91)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M6" s="40" t="n">
         <f aca="false">IFERROR((K6-L6)/L6,0)</f>
-        <v>1.14285714285714</v>
+        <v>-0.428571428571429</v>
       </c>
       <c r="N6" s="40" t="n">
         <f aca="false">IFERROR((COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-365,NDAs!D:D,"&lt;="&amp;As_Of_Date-0)-COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-730,NDAs!D:D,"&lt;"&amp;As_Of_Date-365))/COUNTIFS(NDAs!D:D,"&gt;="&amp;As_Of_Date-730,NDAs!D:D,"&lt;"&amp;As_Of_Date-365),0)</f>
@@ -6692,7 +6854,7 @@
       </c>
       <c r="C8" s="39" t="n">
         <f aca="false">COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-7,Meetings!A:A,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="39" t="n">
         <f aca="false">COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-14,Meetings!A:A,"&lt;"&amp;As_Of_Date-7)</f>
@@ -6704,15 +6866,15 @@
       </c>
       <c r="F8" s="39" t="n">
         <f aca="false">COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-30,Meetings!A:A,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="39" t="n">
         <f aca="false">COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-60,Meetings!A:A,"&lt;"&amp;As_Of_Date-30)</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H8" s="40" t="n">
         <f aca="false">IFERROR((F8-G8)/G8,0)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="39" t="n">
         <f aca="false">Targets!D37</f>
@@ -6720,19 +6882,19 @@
       </c>
       <c r="J8" s="40" t="n">
         <f aca="false">IFERROR((F8-I8)/I8,0)</f>
-        <v>-1</v>
+        <v>-0.888888888888889</v>
       </c>
       <c r="K8" s="39" t="n">
         <f aca="false">COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-91,Meetings!A:A,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="L8" s="39" t="n">
         <f aca="false">COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-182,Meetings!A:A,"&lt;"&amp;As_Of_Date-91)</f>
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="M8" s="40" t="n">
         <f aca="false">IFERROR((K8-L8)/L8,0)</f>
-        <v>1.11111111111111</v>
+        <v>-0.333333333333333</v>
       </c>
       <c r="N8" s="40" t="n">
         <f aca="false">IFERROR((COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-365,Meetings!A:A,"&lt;="&amp;As_Of_Date-0)-COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-730,Meetings!A:A,"&lt;"&amp;As_Of_Date-365))/COUNTIFS(Meetings!A:A,"&gt;="&amp;As_Of_Date-730,Meetings!A:A,"&lt;"&amp;As_Of_Date-365),0)</f>
@@ -6748,11 +6910,11 @@
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-7,Pipeline!G:G,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-14,Pipeline!G:G,"&lt;"&amp;As_Of_Date-7)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="40" t="n">
         <f aca="false">IFERROR((C9-D9)/D9,0)</f>
@@ -6760,7 +6922,7 @@
       </c>
       <c r="F9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-30,Pipeline!G:G,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-60,Pipeline!G:G,"&lt;"&amp;As_Of_Date-30)</f>
@@ -6768,7 +6930,7 @@
       </c>
       <c r="H9" s="40" t="n">
         <f aca="false">IFERROR((F9-G9)/G9,0)</f>
-        <v>2</v>
+        <v>1.66666666666667</v>
       </c>
       <c r="I9" s="39" t="n">
         <f aca="false">Targets!D38</f>
@@ -6776,7 +6938,7 @@
       </c>
       <c r="J9" s="40" t="n">
         <f aca="false">IFERROR((F9-I9)/I9,0)</f>
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="K9" s="39" t="n">
         <f aca="false">COUNTIFS(Pipeline!G:G,"&gt;="&amp;As_Of_Date-91,Pipeline!G:G,"&lt;="&amp;As_Of_Date-0)</f>
@@ -6821,7 +6983,7 @@
       </c>
       <c r="F13" s="41" t="n">
         <f aca="false">SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-30,Revenue_Ledger!A:A,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="G13" s="41" t="n">
         <f aca="false">SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-60,Revenue_Ledger!A:A,"&lt;"&amp;As_Of_Date-30)</f>
@@ -6829,7 +6991,7 @@
       </c>
       <c r="H13" s="40" t="n">
         <f aca="false">IFERROR((F13-G13)/G13,0)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I13" s="41" t="n">
         <f aca="false">Targets!C5/12</f>
@@ -6837,11 +6999,11 @@
       </c>
       <c r="J13" s="40" t="n">
         <f aca="false">IFERROR((F13-I13)/I13,0)</f>
-        <v>-0.6712</v>
+        <v>-1</v>
       </c>
       <c r="K13" s="41" t="n">
         <f aca="false">SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-91,Revenue_Ledger!A:A,"&lt;="&amp;As_Of_Date-0)</f>
-        <v>29900</v>
+        <v>27400</v>
       </c>
       <c r="L13" s="41" t="n">
         <f aca="false">SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;DATE(YEAR(As_Of_Date),1,1),Revenue_Ledger!A:A,"&lt;="&amp;As_Of_Date)</f>
@@ -6849,7 +7011,7 @@
       </c>
       <c r="M13" s="40" t="n">
         <f aca="false">IFERROR((K13-SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-182,Revenue_Ledger!A:A,"&lt;"&amp;As_Of_Date-91))/SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-182,Revenue_Ledger!A:A,"&lt;"&amp;As_Of_Date-91),0)</f>
-        <v>2.98666666666667</v>
+        <v>2.65333333333333</v>
       </c>
       <c r="N13" s="40" t="n">
         <f aca="false">IFERROR((SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-365,Revenue_Ledger!A:A,"&lt;="&amp;As_Of_Date-0)-SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-730,Revenue_Ledger!A:A,"&lt;"&amp;As_Of_Date-365))/SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-730,Revenue_Ledger!A:A,"&lt;"&amp;As_Of_Date-365),0)</f>
@@ -6933,7 +7095,7 @@
       </c>
       <c r="F15" s="41" t="n">
         <f aca="false">F13-F14</f>
-        <v>13700</v>
+        <v>0</v>
       </c>
       <c r="G15" s="41" t="n">
         <f aca="false">G13-G14</f>
@@ -6941,7 +7103,7 @@
       </c>
       <c r="H15" s="40" t="n">
         <f aca="false">IFERROR((F15-G15)/G15,0)</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I15" s="41" t="n">
         <f aca="false">I13-I14</f>
@@ -6949,11 +7111,11 @@
       </c>
       <c r="J15" s="40" t="n">
         <f aca="false">IFERROR((F15-I15)/IF(I15=0,1,ABS(I15)),0)</f>
-        <v>-0.402982906572635</v>
+        <v>-1</v>
       </c>
       <c r="K15" s="41" t="n">
         <f aca="false">K13-K14</f>
-        <v>29900</v>
+        <v>27400</v>
       </c>
       <c r="L15" s="41" t="n">
         <f aca="false">L13-L14</f>
@@ -6961,7 +7123,7 @@
       </c>
       <c r="M15" s="40" t="n">
         <f aca="false">IFERROR((K15-((SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-182,Revenue_Ledger!A:A,"&lt;"&amp;As_Of_Date-91))-(SUMIFS(Expense_Ledger!D:D,Expense_Ledger!A:A,"&gt;="&amp;As_Of_Date-182,Expense_Ledger!A:A,"&lt;"&amp;As_Of_Date-91))))/IF(((SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-182,Revenue_Ledger!A:A,"&lt;"&amp;As_Of_Date-91))-(SUMIFS(Expense_Ledger!D:D,Expense_Ledger!A:A,"&gt;="&amp;As_Of_Date-182,Expense_Ledger!A:A,"&lt;"&amp;As_Of_Date-91)))=0,1,ABS((SUMIFS(Revenue_Ledger!E:E,Revenue_Ledger!A:A,"&gt;="&amp;As_Of_Date-182,Revenue_Ledger!A:A,"&lt;"&amp;As_Of_Date-91))-(SUMIFS(Expense_Ledger!D:D,Expense_Ledger!A:A,"&gt;="&amp;As_Of_Date-182,Expense_Ledger!A:A,"&lt;"&amp;As_Of_Date-91)))),0)</f>
-        <v>2.98666666666667</v>
+        <v>2.65333333333333</v>
       </c>
       <c r="N15" s="40" t="n">
         <v>0</v>
@@ -14554,13 +14716,27 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="42"/>
-      <c r="B61" s="43"/>
-      <c r="C61" s="43"/>
-      <c r="D61" s="43"/>
-      <c r="E61" s="43"/>
-      <c r="F61" s="43"/>
-      <c r="G61" s="43"/>
+      <c r="A61" s="45" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B61" s="46" t="s">
+        <v>201</v>
+      </c>
+      <c r="C61" s="46" t="s">
+        <v>274</v>
+      </c>
+      <c r="D61" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="E61" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="F61" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="G61" s="46" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="42"/>
@@ -18540,7 +18716,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18554,7 +18730,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -18568,31 +18744,31 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J4" s="13" t="s">
         <v>89</v>
@@ -18600,19 +18776,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="43" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B5" s="43" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C5" s="43" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E5" s="43" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F5" s="44" t="n">
         <v>2000000</v>
@@ -18627,24 +18803,24 @@
         <v>164</v>
       </c>
       <c r="J5" s="43" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="43" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="42" t="n">
@@ -18657,24 +18833,24 @@
         <v>164</v>
       </c>
       <c r="J6" s="43" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="43" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B7" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="43" t="s">
         <v>298</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>299</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>300</v>
-      </c>
-      <c r="E7" s="43" t="s">
-        <v>295</v>
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="42" t="n">
@@ -18687,24 +18863,24 @@
         <v>164</v>
       </c>
       <c r="J7" s="43" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="43" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B8" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="D8" s="43" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="43" t="s">
-        <v>304</v>
-      </c>
-      <c r="D8" s="43" t="s">
-        <v>300</v>
-      </c>
       <c r="E8" s="43" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F8" s="44"/>
       <c r="G8" s="42" t="n">
@@ -18717,24 +18893,24 @@
         <v>164</v>
       </c>
       <c r="J8" s="43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B9" s="43" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C9" s="43" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D9" s="43" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="F9" s="47" t="n">
         <v>4000000</v>
@@ -18743,30 +18919,30 @@
         <v>46200</v>
       </c>
       <c r="H9" s="42" t="n">
-        <v>46200</v>
+        <v>46239</v>
       </c>
       <c r="I9" s="43" t="s">
         <v>164</v>
       </c>
       <c r="J9" s="43" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B10" s="43" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C10" s="43" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D10" s="43" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F10" s="47"/>
       <c r="G10" s="42" t="n">
@@ -18779,24 +18955,24 @@
         <v>164</v>
       </c>
       <c r="J10" s="43" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="43" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B11" s="43" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C11" s="43" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D11" s="43" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F11" s="47"/>
       <c r="G11" s="42" t="n">
@@ -18809,24 +18985,24 @@
         <v>164</v>
       </c>
       <c r="J11" s="43" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="43" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B12" s="43" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C12" s="43" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D12" s="43" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F12" s="47"/>
       <c r="G12" s="42" t="n">
@@ -18839,24 +19015,24 @@
         <v>164</v>
       </c>
       <c r="J12" s="43" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="43" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B13" s="43" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C13" s="43" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D13" s="43" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F13" s="47"/>
       <c r="G13" s="42" t="n">
@@ -18869,24 +19045,24 @@
         <v>164</v>
       </c>
       <c r="J13" s="43" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="43" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C14" s="43" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D14" s="43" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F14" s="47"/>
       <c r="G14" s="42" t="n">
@@ -18899,22 +19075,22 @@
         <v>164</v>
       </c>
       <c r="J14" s="43" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="43" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B15" s="43" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C15" s="43" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D15" s="43"/>
       <c r="E15" s="43" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F15" s="44"/>
       <c r="G15" s="42" t="n">
@@ -18927,24 +19103,24 @@
         <v>164</v>
       </c>
       <c r="J15" s="43" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="43" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D16" s="43" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E16" s="43" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F16" s="44"/>
       <c r="G16" s="42" t="n">
@@ -18957,24 +19133,24 @@
         <v>164</v>
       </c>
       <c r="J16" s="43" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="43" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B17" s="43" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D17" s="43" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E17" s="43" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F17" s="44"/>
       <c r="G17" s="42" t="n">
@@ -18987,7 +19163,7 @@
         <v>164</v>
       </c>
       <c r="J17" s="43" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19822,7 +19998,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19836,7 +20012,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -19850,34 +20026,34 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>118</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21055,7 +21231,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -21067,7 +21243,7 @@
     </row>
     <row r="2" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -21082,22 +21258,22 @@
         <v>144</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>153</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H4" s="13" t="s">
         <v>156</v>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics_Period" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue_Ledger" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expense_Ledger" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meetings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active_Projects" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feedback" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screenings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NDAs" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreements" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Targets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics_Period" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Revenue_Ledger" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Expense_Ledger" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Meetings" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Active_Projects" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Feedback" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Screenings" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="NDAs" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Agreements" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Actions" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="As_Of_Date" hidden="0" function="0" vbProcedure="0">Dashboard!$C$4</definedName>
@@ -954,6 +954,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="52">
       <c r="B4" s="55" t="inlineStr">
         <is>
@@ -969,6 +970,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="52">
       <c r="B6" s="58" t="inlineStr">
         <is>
@@ -1025,6 +1027,7 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="52">
       <c r="B10" s="58" t="inlineStr">
         <is>
@@ -1090,6 +1093,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="52">
       <c r="B14" s="58" t="inlineStr">
         <is>
@@ -1339,6 +1343,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="52">
       <c r="B22" s="58" t="inlineStr">
         <is>
@@ -1588,6 +1593,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="36" customHeight="1" s="52">
       <c r="B30" s="72" t="inlineStr">
         <is>
@@ -1595,6 +1601,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="52">
       <c r="B32" s="58" t="inlineStr">
         <is>
@@ -1711,6 +1718,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -4678,6 +4686,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -5549,6 +5558,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -5720,6 +5730,7 @@
       <c r="F2" s="112" t="n"/>
       <c r="G2" s="112" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="113" t="inlineStr">
         <is>
@@ -5924,6 +5935,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="52">
       <c r="B4" s="58" t="inlineStr">
         <is>
@@ -6076,6 +6088,8 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="52">
       <c r="B17" s="58" t="inlineStr">
         <is>
@@ -6386,6 +6400,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="52">
       <c r="B32" s="58" t="inlineStr">
         <is>
@@ -6560,6 +6575,8 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41" ht="15" customHeight="1" s="52">
       <c r="B41" s="58" t="inlineStr">
         <is>
@@ -6638,6 +6655,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -7000,6 +7018,8 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="52">
       <c r="B12" s="58" t="inlineStr">
         <is>
@@ -7180,6 +7200,8 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="52">
       <c r="B18" s="74" t="inlineStr">
         <is>
@@ -7299,6 +7321,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -9489,6 +9512,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -13524,6 +13548,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -19595,6 +19620,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -20227,7 +20253,7 @@
       </c>
       <c r="B18" s="100" t="inlineStr">
         <is>
-          <t>CMS ICAT RFI (270196) — HHS-RADV Independent Coding Audit Tool</t>
+          <t>CMS ICAT RFI (270196) — HHS-RADV Intelligent Coding Assistance Tool</t>
         </is>
       </c>
       <c r="C18" s="100" t="inlineStr">
@@ -20242,7 +20268,7 @@
       </c>
       <c r="E18" s="100" t="inlineStr">
         <is>
-          <t>Capture</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="F18" s="101" t="n"/>
@@ -20250,7 +20276,7 @@
         <v>46245</v>
       </c>
       <c r="H18" s="102" t="n">
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="I18" s="100" t="inlineStr">
         <is>
@@ -20259,7 +20285,7 @@
       </c>
       <c r="J18" s="100" t="inlineStr">
         <is>
-          <t>Teamed RFI response with CAGAIL LLC (PRIORITY, opportunity-scoped; NDA-before-substance). Scores: solo 5.60 / teamed 6.38; Pwin 45–50%. KPMG = structurally conflicted incumbent. Bandwidth collision with FSIPAP managed — drafting strictly confined to Mon 8/17. CAGAIL NDA drafted 8/12; execution + opportunity scope memo due 8/14; draft exchange 8/17. RISK: unidentified 'Shan' (only identifier jasminejew4@yahoo.com) proposed as prime on an unsupported veteran-preference premise — Gate 0 + COI blocked pending identity; resolve whether Shan = Cadence Procurement (FILED) before any VBX association; if so joint track dies on standing disposition. KW decisions due 8/14 EOD: (a) solo go/no-go (engine recommends GO — preserves VBX attribution in CCIIO market-research file, ~$2.5K B&amp;P, Monday drafting only); (b) joint-track continuation, conditional on NDA execution + Shan identity/COI + DSBS WOSB/EDWOSB pull + team COI confirmations. RFI due 8/20/26 10:00 ET.</t>
+          <t>SUBMITTED 8/19/26 — TEAMED track, one day ahead of the 8/20 10:00 ET deadline. Structure: Aurelus Solutions (prime; CAGE 18WY1, UEI MEA6HMN29JB1; POC Chyanne T. Thomas) / CAGAIL LLC (sub, PRIORITY) / Visionblox (sub). Health GREEN. HARD GATE CLOSED: the 3 COI attestations (Aurelus, CAGAIL, VBX) executed; Q13 team-wide COI assertion backed by evidence; solo 5.60 fallback not needed. Pre-submission clearances all held: prime identified &amp; cleared by KW 8/15 (the 8/13 'Shan' placeholder resolved to Aurelus — NOT Cadence / Shaneiqua Johnson; FILED contingency closed); NDA executed 8/16; response redlined 8/17 (6 tracked VBX edits); VBX rep cleared 8/18 with zero residual false VBX claims (GSA MAS/SIN 54151HEAL struck, 'HITRUST-audited' → 'assessor-on-staff', CMS/FEMA mis-attribution fixed). Teamed score 6.38, Pwin 45–50%; KPMG = structurally conflicted incumbent. Per-question limit 3,000 chars; FSIPAP 8/19 → ICAT 8/20 sequential. NEXT: (1) archive submission receipt/confirmation [Khaalis Wooden, 8/20, portal receipt or acknowledgment filed]; (2) monitor CMS for ICAT RFI disposition / follow-on RFP or market-research outcome [Khaalis Wooden, re-check 9/19, disposition logged or next milestone dated]. Branded pursuit status record ICAT_Pursuit_Status_270196_20260819.docx (+ .pdf) — Capture &amp; Compliance work product, delivered to owner out-of-repo (partner/NDA detail; not committed per Hard Rule #1).</t>
         </is>
       </c>
     </row>
@@ -21446,6 +21472,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -22682,6 +22709,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -954,7 +954,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="52">
       <c r="B4" s="55" t="inlineStr">
         <is>
@@ -970,7 +969,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="52">
       <c r="B6" s="58" t="inlineStr">
         <is>
@@ -1027,7 +1025,6 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="52">
       <c r="B10" s="58" t="inlineStr">
         <is>
@@ -1093,7 +1090,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="52">
       <c r="B14" s="58" t="inlineStr">
         <is>
@@ -1343,7 +1339,6 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="52">
       <c r="B22" s="58" t="inlineStr">
         <is>
@@ -1593,7 +1588,6 @@
         <v/>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="36" customHeight="1" s="52">
       <c r="B30" s="72" t="inlineStr">
         <is>
@@ -1601,7 +1595,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="52">
       <c r="B32" s="58" t="inlineStr">
         <is>
@@ -1718,7 +1711,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -4686,7 +4678,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -5558,7 +5549,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -5730,7 +5720,6 @@
       <c r="F2" s="112" t="n"/>
       <c r="G2" s="112" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="113" t="inlineStr">
         <is>
@@ -5935,7 +5924,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="52">
       <c r="B4" s="58" t="inlineStr">
         <is>
@@ -6088,8 +6076,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="52">
       <c r="B17" s="58" t="inlineStr">
         <is>
@@ -6400,7 +6386,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="52">
       <c r="B32" s="58" t="inlineStr">
         <is>
@@ -6575,8 +6560,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41" ht="15" customHeight="1" s="52">
       <c r="B41" s="58" t="inlineStr">
         <is>
@@ -6655,7 +6638,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="36" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -7018,8 +7000,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="52">
       <c r="B12" s="58" t="inlineStr">
         <is>
@@ -7200,8 +7180,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="52">
       <c r="B18" s="74" t="inlineStr">
         <is>
@@ -7321,7 +7299,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -9512,7 +9489,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -13548,7 +13524,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -19620,7 +19595,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -20576,7 +20550,7 @@
       </c>
       <c r="E25" s="100" t="inlineStr">
         <is>
-          <t>Identified</t>
+          <t>Submitted</t>
         </is>
       </c>
       <c r="F25" s="101" t="n"/>
@@ -20593,7 +20567,7 @@
       </c>
       <c r="J25" s="100" t="inlineStr">
         <is>
-          <t>SHAPING / WATCH — market-research RFI, NO AWARD; not a valued pursuit. Est. Value intentionally blank (No award — RFI); excluded from forecast / weighted-pipeline / revenue roll-up. Notice ID fa0630b52e8643468f1c7d0cba7ba961; Sol 28321326RI0000041; Type RFI (market research only); Sector Federal; Issuing office SSA Office of the CIO (NOT Office of Acquisition &amp; Grants); PSC DF01; Set-aside None (full &amp; open); Vehicle none required; Contract type N/A. Released 08/14/2026; Response due 09/28/2026 17:00 ET; Archives 10/13/2026; Incumbent N/A. Pre-RFP shaping: No — this response IS the first contact. Submission: email, 6-page max, PDF/Word/text. Source: https://sam.gov/opp/fa0630b52e8643468f1c7d0cba7ba961/view. GATE 1: PASS (no kill triggers; non-informative for a no-award RFI). SCORE 4.20/10 (downstream hypothetical award, Federal rubric) | BAND Moderate | Pwin 25%. Factors: F1 0.50 | F2 0.30 | F3 1.00 | F4 0.50 | F5 0.10 | F6 0.10 | F7 0.60 | F8 0.40. B&amp;P actual ~8 hrs (capped). RECOMMENDATION: Respond — limited scope; no capture plan; no B&amp;P beyond cap. CONTACTS: Marissa Piegols (POC, submissions + inquiries) Marissa.Piegols@ssa.gov; William Guo (submissions + inquiries) William.Guo@ssa.gov; Brian Peltier (SSA Chief AI Officer / Deputy CIO for Strategy; owns enterprise architecture + innovation; SUBMISSIONS ONLY, not on inquiry line) brian.peltier@ssa.gov [durable federal AI contact, independent of this pursuit]. MILESTONES (owner Khaalis unless noted): 09/08/2026 send pre-submission inquiry re attribution + page cap -&gt; email sent to Piegols + Guo; 09/18/2026 verify '12 of 68 dual-track' vs public MT NOIA -&gt; figure confirmed or corrected in doc; 09/22/2026 vendor-neutrality review of Area 3 (owner Akil) -&gt; zero named products/platforms/models; 09/25/2026 transmit response + PDF to all three addressees -&gt; sent-mail confirmation; 09/29/2026 file response as reusable agency-AI-RFI template -&gt; template file exists in library. ARTIFACTS: RFI_Response_SSA_EnterpriseAI_Visionblox_v1_0_2026-09.pdf (submission); RFI_Response_SSA_EnterpriseAI_Visionblox_v1_0_2026-09.docx (source). DISCLOSURE: SSA may publish responses -&gt; treat as public. EXCLUDE absolutely: CAHSP / GRHD; Kaiser (no disclosure permission); GSA MAS / SIN 54151HEAL (suppressed pending Refresh 31, wrong SIN anyway); VBX Montana evaluation scores / cost score / pricing. Named client in doc: Montana ONLY (public procurement record). CA DHCS and the commercial claims client appear unnamed, metrics preserved.</t>
+          <t>SUBMITTED 08/19/2026 — response transmitted by EMAIL to SSA ahead of the 09/28 due date; sent-mail confirmation (Outlook print-to-PDF, 'RFI Response - SSA AI Strategy', 08/19/2026) on file. Still a no-award market-research RFI (SHAPING / WATCH origin): Est. Value intentionally blank (No award — RFI); EXCLUDED from forecast / weighted-pipeline / revenue roll-up. Notice ID fa0630b52e8643468f1c7d0cba7ba961; Sol 28321326RI0000041; Type RFI (market research only); Sector Federal; Issuing office SSA Office of the CIO (NOT Office of Acquisition &amp; Grants); PSC DF01; Set-aside None (full &amp; open); Vehicle none required; Contract type N/A. Released 08/14/2026; Response due 09/28/2026 17:00 ET; Archives 10/13/2026; Incumbent N/A. Pre-RFP shaping: No — this response was the first contact. Submission: email, 6-page max, PDF/Word/text. Source: https://sam.gov/opp/fa0630b52e8643468f1c7d0cba7ba961/view. GATE 1: PASS (no kill triggers; non-informative for a no-award RFI). SCORE 4.20/10 (downstream hypothetical award, Federal rubric) | BAND Moderate | Pwin 25%. Factors: F1 0.50 | F2 0.30 | F3 1.00 | F4 0.50 | F5 0.10 | F6 0.10 | F7 0.60 | F8 0.40. B&amp;P actual ~8 hrs (capped). RECOMMENDATION was: Respond — limited scope; no capture plan; no B&amp;P beyond cap. CONTACTS: Marissa Piegols (POC, submissions + inquiries) Marissa.Piegols@ssa.gov; William Guo (submissions + inquiries) William.Guo@ssa.gov; Brian Peltier (SSA Chief AI Officer / Deputy CIO for Strategy; owns enterprise architecture + innovation; SUBMISSIONS ONLY, not on inquiry line) brian.peltier@ssa.gov [durable federal AI contact, independent of this pursuit]. MILESTONES: TRANSMIT response + PDF to addressees — DONE 08/19/2026 (early; sent-mail confirmation captured). Pre-submission steps (09/08 attribution/page-cap inquiry; 09/18 verify '12 of 68 dual-track' vs public MT NOIA; 09/22 Area-3 vendor-neutrality review, owner Akil) overtaken by the early 08/19 submission. REMAINING: file response as reusable agency-AI-RFI template (target 09/29, owner Khaalis) -&gt; template file in library. ARTIFACTS: submission sent by email 08/19/2026; sent-mail confirmation PDF (Outlook print-to-PDF) on file; response docs RFI_Response_SSA_EnterpriseAI_Visionblox_v1_0.pdf / .docx (source). DISCLOSURE: SSA may publish responses -&gt; treat as public. EXCLUDED from submission: CAHSP / GRHD (absolute); Kaiser (no disclosure permission); GSA MAS / SIN 54151HEAL (suppressed pending Refresh 31, wrong SIN anyway); VBX Montana evaluation scores / cost score / pricing. Named client in doc: Montana ONLY (public procurement record). CA DHCS and the commercial claims client appear unnamed, metrics preserved.</t>
         </is>
       </c>
     </row>
@@ -21472,7 +21446,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -22709,7 +22682,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -5682,7 +5682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="52" min="1" max="1"/>
@@ -5886,6 +5886,204 @@
       <c r="G8" s="114" t="inlineStr">
         <is>
           <t>OPP-041 / LADBS AIP-PPC No-Bid 8/19/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="114" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="115" t="inlineStr">
+        <is>
+          <t>Validate §5.7 ROM against VBX cost model</t>
+        </is>
+      </c>
+      <c r="C9" s="114" t="inlineStr">
+        <is>
+          <t>Akil Chellam / Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D9" s="116" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E9" s="115" t="inlineStr">
+        <is>
+          <t>ROM confirmed or revised</t>
+        </is>
+      </c>
+      <c r="F9" s="114" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G9" s="114" t="inlineStr">
+        <is>
+          <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="114" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="115" t="inlineStr">
+        <is>
+          <t>Confirm §5.4 SOC 2 / attestation language</t>
+        </is>
+      </c>
+      <c r="C10" s="114" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden / Tony Paul</t>
+        </is>
+      </c>
+      <c r="D10" s="116" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E10" s="115" t="inlineStr">
+        <is>
+          <t>Language approved</t>
+        </is>
+      </c>
+      <c r="F10" s="114" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G10" s="114" t="inlineStr">
+        <is>
+          <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="114" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="115" t="inlineStr">
+        <is>
+          <t>Cyber-insurance tier check ($10M vs $6M held) with Grace Waring</t>
+        </is>
+      </c>
+      <c r="C11" s="114" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D11" s="116" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E11" s="115" t="inlineStr">
+        <is>
+          <t>Tier confirmed</t>
+        </is>
+      </c>
+      <c r="F11" s="114" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G11" s="114" t="inlineStr">
+        <is>
+          <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="114" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="115" t="inlineStr">
+        <is>
+          <t>Apply §4.7 per-page Confidential marks on §5.3 pages</t>
+        </is>
+      </c>
+      <c r="C12" s="114" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D12" s="116" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E12" s="115" t="inlineStr">
+        <is>
+          <t>Marks applied</t>
+        </is>
+      </c>
+      <c r="F12" s="114" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G12" s="114" t="inlineStr">
+        <is>
+          <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 17</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="114" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="115" t="inlineStr">
+        <is>
+          <t>Pink/red review + guardrail sweep</t>
+        </is>
+      </c>
+      <c r="C13" s="114" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D13" s="116" t="n">
+        <v>46259</v>
+      </c>
+      <c r="E13" s="115" t="inlineStr">
+        <is>
+          <t>Sweep complete</t>
+        </is>
+      </c>
+      <c r="F13" s="114" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G13" s="114" t="inlineStr">
+        <is>
+          <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="114" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="115" t="inlineStr">
+        <is>
+          <t>Submit RFI response (email, ≤20pp, subject "RFI 2026HCA13_Visionblox LLC" + Attachment A, no zip)</t>
+        </is>
+      </c>
+      <c r="C14" s="114" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D14" s="116" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E14" s="115" t="inlineStr">
+        <is>
+          <t>Response submitted</t>
+        </is>
+      </c>
+      <c r="F14" s="114" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G14" s="114" t="inlineStr">
+        <is>
+          <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 19</t>
         </is>
       </c>
     </row>
@@ -19923,7 +20121,7 @@
       </c>
       <c r="B11" s="100" t="inlineStr">
         <is>
-          <t>WA HCA FSIPAP (RFI 2026HCA13) — Policy Transformation Lane</t>
+          <t>WA HCA FSIPAP (RFI 2026HCA13) — Federal &amp; State Interoperability and Prior Authorization Project</t>
         </is>
       </c>
       <c r="C11" s="100" t="inlineStr">
@@ -19933,7 +20131,7 @@
       </c>
       <c r="D11" s="100" t="inlineStr">
         <is>
-          <t>541511</t>
+          <t>541511 / 541512</t>
         </is>
       </c>
       <c r="E11" s="100" t="inlineStr">
@@ -19955,7 +20153,7 @@
       </c>
       <c r="J11" s="100" t="inlineStr">
         <is>
-          <t>WA HCA FSIPAP RFI 2026HCA13 — policy/program transformation lane (Posture B: PA-workflow-complete — CRD + DTR-approach + PAS + policy transformation). Score ~5.38/10 (Moderate+); ~25% Pwin on downstream RFP. Da Vinci CRD/PAS past-performance verified; DTR is the shallowest remaining gap (AJ owns Da Vinci PP verification). Governing deadline 8/19/26 17:00 PT; 10-page cap; B&amp;P ~$6K. Contact: Jack Kent. Do NOT cite GSA SIN 54151HEAL (suppressed, Refresh 31); descriptive capability language only (RFI Sec. 4.6 IP-assignment breadth). Pre-submission blockers: SOC 2 Type II; WA SoS registration. Incumbent risk: Acentra (ProviderOne + FHIR). Account-map intel appended from WA DES 13225 purchaser data (HCA confirmed top-3 WA language-access buyer). No published ceiling — RFI intelligence play, excluded from win-rate scenario math.</t>
+          <t>WA HCA FSIPAP RFI 2026HCA13 — Federal &amp; State Interoperability and Prior Authorization Project. Updated 2026-08-19 (Rev.6). CUSTOMER: WA Health Care Authority (HCA) · SLED (State) · Medicaid/CHIP FFS · driver CMS-0057-F. DISPOSITION: Active — RESPOND (bid). POSTURE B — PA-workflow-complete (CRD + DTR-approach + PAS + policy transformation; LEAD with policy transformation). SCORE 5.83/10 CREDIBLE (Gate 1 PASS; solo); Pwin 38%. Score movement: 4.6 baseline → 5.26 (Am.1) → 5.38 (capability) → 5.83 (Am.3). Next re-score trigger: RFP release. B&amp;P $12K–$15K. VEHICLE: none required to prime (Am.3 #45); NASPO Cloud Solutions DES #05116 available if teaming; multi-tier subs allowed w/ HCA approval (#77). KEY FACTS: program FUNDED (state funds + CMS APD/FFP); Acentra integration at no cost (#44); Acentra builds FHIR adjudication endpoints (#59A); FHIR-native, no X12 278 (#22); policy volume ~760, largest guide 338pp/153 PA policies (#40); vendor-hosted cloud-native expected (#20/#58); competitive RFP intended (#37); SOC 2 not hard-mandated (#42) but cyber may reach $10M for high-risk data vs $6M held (#76); possible minimum-revenue rule (#73). DATES: RFI response due 2026-08-26 17:00 PT; full compliance 01/01/2028; vendor onboard ~Q1 2027; RFP expected Q4 2026 / Q1 2027. TEAM: Akil Chellam (Principal Architect), Saravanan Swaminathan (Sr Solution Architect / policy transformation), Antony Jayaraj (Data Eng), Tony Paul (CISO), Khaalis Wooden (capture). GUARDRAILS: do NOT cite GSA MAS SIN (suppressed pending Refresh 31) — descriptive capability language only (RFI Sec. 4.6 IP-assignment breadth); internal framework names not referenced externally. No published ceiling — RFI intelligence play, excluded from win-rate scenario math. Incumbent risk: Acentra (ProviderOne + FHIR). Contact: Jack Kent. ACTIVITY LOG: 2026-08-01 Registration confirmed — VBX on RFI distribution list; 2026-08-03 Round 2 questions submitted, receipt confirmed; 2026-08-11 Da Vinci PP verified (CRD+PAS, no DTR), scope set Posture B; 2026-08-11 Amendment 2 — schedule +1 week (answers 08/19; due 08/26); 2026-08-19 Amendment 3 (Q&amp;A Round 2) — all 10 VBX questions answered, re-score to 5.83 CREDIBLE; 2026-08-19 Full §4.4 response draft delivered; 2026-08-19 Attachment A architecture/data-flow diagrams delivered. OPEN NEXT STEPS 14–19 tracked on the Actions tab (items #5–10). ARTIFACTS: WinProb_2026HCA13_SOLO_20260819_r6.docx (win-prob analysis — source of truth); RFI 2026HCA13_Visionblox LLC_FULL-DRAFT_20260819.docx (response draft); Attachment_A_RFI2026HCA13_Visionblox_Architecture.pdf (architecture diagrams).</t>
         </is>
       </c>
     </row>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -14,12 +14,13 @@
     <sheet name="Expense_Ledger" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Meetings" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Pipeline" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Active_Projects" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Feedback" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Screenings" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="NDAs" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Agreements" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Actions" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Opportunity_Detail" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Active_Projects" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Feedback" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Screenings" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="NDAs" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Agreements" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Actions" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="As_Of_Date" hidden="0" function="0" vbProcedure="0">Dashboard!$C$4</definedName>
@@ -37,7 +38,7 @@
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -186,6 +187,12 @@
       <color rgb="FF0000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF232D5A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -253,7 +260,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -276,6 +283,11 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FFC8CDD7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -287,7 +299,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -633,6 +645,18 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -954,6 +978,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="52">
       <c r="B4" s="55" t="inlineStr">
         <is>
@@ -969,6 +994,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="52">
       <c r="B6" s="58" t="inlineStr">
         <is>
@@ -1025,6 +1051,7 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="52">
       <c r="B10" s="58" t="inlineStr">
         <is>
@@ -1090,6 +1117,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="15" customHeight="1" s="52">
       <c r="B14" s="58" t="inlineStr">
         <is>
@@ -1339,6 +1367,7 @@
         <v/>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="52">
       <c r="B22" s="58" t="inlineStr">
         <is>
@@ -1588,6 +1617,7 @@
         <v/>
       </c>
     </row>
+    <row r="29"/>
     <row r="30" ht="36" customHeight="1" s="52">
       <c r="B30" s="72" t="inlineStr">
         <is>
@@ -1595,6 +1625,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="52">
       <c r="B32" s="58" t="inlineStr">
         <is>
@@ -1681,6 +1712,2043 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
+    <tabColor rgb="FFB0BEC5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:H199"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="14" customWidth="1" style="51" min="1" max="2"/>
+    <col width="22" customWidth="1" style="51" min="3" max="3"/>
+    <col width="16" customWidth="1" style="51" min="4" max="4"/>
+    <col width="14" customWidth="1" style="51" min="5" max="5"/>
+    <col width="34" customWidth="1" style="51" min="6" max="6"/>
+    <col width="28" customWidth="1" style="51" min="7" max="7"/>
+    <col width="14" customWidth="1" style="51" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.75" customHeight="1" s="52">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FEEDBACK LOG  —  Internal &amp; External</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21.75" customHeight="1" s="52">
+      <c r="A2" s="54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Source: Internal | External.  Type: CPARS | Survey | Email | Verbal | Slack.  Sentiment: + | 0 | −</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1" s="52">
+      <c r="A4" s="64" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="64" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C4" s="64" t="inlineStr">
+        <is>
+          <t>Party</t>
+        </is>
+      </c>
+      <c r="D4" s="64" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E4" s="64" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="F4" s="64" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="G4" s="64" t="inlineStr">
+        <is>
+          <t>Action Required</t>
+        </is>
+      </c>
+      <c r="H4" s="64" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="52">
+      <c r="A5" s="102" t="n"/>
+      <c r="B5" s="100" t="n"/>
+      <c r="C5" s="100" t="n"/>
+      <c r="D5" s="100" t="n"/>
+      <c r="E5" s="100" t="n"/>
+      <c r="F5" s="100" t="n"/>
+      <c r="G5" s="100" t="n"/>
+      <c r="H5" s="100" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="52">
+      <c r="A6" s="102" t="n"/>
+      <c r="B6" s="100" t="n"/>
+      <c r="C6" s="100" t="n"/>
+      <c r="D6" s="100" t="n"/>
+      <c r="E6" s="100" t="n"/>
+      <c r="F6" s="100" t="n"/>
+      <c r="G6" s="100" t="n"/>
+      <c r="H6" s="100" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="52">
+      <c r="A7" s="102" t="n"/>
+      <c r="B7" s="100" t="n"/>
+      <c r="C7" s="100" t="n"/>
+      <c r="D7" s="100" t="n"/>
+      <c r="E7" s="100" t="n"/>
+      <c r="F7" s="100" t="n"/>
+      <c r="G7" s="100" t="n"/>
+      <c r="H7" s="100" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="52">
+      <c r="A8" s="102" t="n"/>
+      <c r="B8" s="100" t="n"/>
+      <c r="C8" s="100" t="n"/>
+      <c r="D8" s="100" t="n"/>
+      <c r="E8" s="100" t="n"/>
+      <c r="F8" s="100" t="n"/>
+      <c r="G8" s="100" t="n"/>
+      <c r="H8" s="100" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="52">
+      <c r="A9" s="102" t="n"/>
+      <c r="B9" s="100" t="n"/>
+      <c r="C9" s="100" t="n"/>
+      <c r="D9" s="100" t="n"/>
+      <c r="E9" s="100" t="n"/>
+      <c r="F9" s="100" t="n"/>
+      <c r="G9" s="100" t="n"/>
+      <c r="H9" s="100" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="52">
+      <c r="A10" s="102" t="n"/>
+      <c r="B10" s="100" t="n"/>
+      <c r="C10" s="100" t="n"/>
+      <c r="D10" s="100" t="n"/>
+      <c r="E10" s="100" t="n"/>
+      <c r="F10" s="100" t="n"/>
+      <c r="G10" s="100" t="n"/>
+      <c r="H10" s="100" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="52">
+      <c r="A11" s="102" t="n"/>
+      <c r="B11" s="100" t="n"/>
+      <c r="C11" s="100" t="n"/>
+      <c r="D11" s="100" t="n"/>
+      <c r="E11" s="100" t="n"/>
+      <c r="F11" s="100" t="n"/>
+      <c r="G11" s="100" t="n"/>
+      <c r="H11" s="100" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="52">
+      <c r="A12" s="102" t="n"/>
+      <c r="B12" s="100" t="n"/>
+      <c r="C12" s="100" t="n"/>
+      <c r="D12" s="100" t="n"/>
+      <c r="E12" s="100" t="n"/>
+      <c r="F12" s="100" t="n"/>
+      <c r="G12" s="100" t="n"/>
+      <c r="H12" s="100" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="52">
+      <c r="A13" s="102" t="n"/>
+      <c r="B13" s="100" t="n"/>
+      <c r="C13" s="100" t="n"/>
+      <c r="D13" s="100" t="n"/>
+      <c r="E13" s="100" t="n"/>
+      <c r="F13" s="100" t="n"/>
+      <c r="G13" s="100" t="n"/>
+      <c r="H13" s="100" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="52">
+      <c r="A14" s="102" t="n"/>
+      <c r="B14" s="100" t="n"/>
+      <c r="C14" s="100" t="n"/>
+      <c r="D14" s="100" t="n"/>
+      <c r="E14" s="100" t="n"/>
+      <c r="F14" s="100" t="n"/>
+      <c r="G14" s="100" t="n"/>
+      <c r="H14" s="100" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="52">
+      <c r="A15" s="102" t="n"/>
+      <c r="B15" s="100" t="n"/>
+      <c r="C15" s="100" t="n"/>
+      <c r="D15" s="100" t="n"/>
+      <c r="E15" s="100" t="n"/>
+      <c r="F15" s="100" t="n"/>
+      <c r="G15" s="100" t="n"/>
+      <c r="H15" s="100" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="52">
+      <c r="A16" s="102" t="n"/>
+      <c r="B16" s="100" t="n"/>
+      <c r="C16" s="100" t="n"/>
+      <c r="D16" s="100" t="n"/>
+      <c r="E16" s="100" t="n"/>
+      <c r="F16" s="100" t="n"/>
+      <c r="G16" s="100" t="n"/>
+      <c r="H16" s="100" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="52">
+      <c r="A17" s="102" t="n"/>
+      <c r="B17" s="100" t="n"/>
+      <c r="C17" s="100" t="n"/>
+      <c r="D17" s="100" t="n"/>
+      <c r="E17" s="100" t="n"/>
+      <c r="F17" s="100" t="n"/>
+      <c r="G17" s="100" t="n"/>
+      <c r="H17" s="100" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="52">
+      <c r="A18" s="102" t="n"/>
+      <c r="B18" s="100" t="n"/>
+      <c r="C18" s="100" t="n"/>
+      <c r="D18" s="100" t="n"/>
+      <c r="E18" s="100" t="n"/>
+      <c r="F18" s="100" t="n"/>
+      <c r="G18" s="100" t="n"/>
+      <c r="H18" s="100" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="52">
+      <c r="A19" s="102" t="n"/>
+      <c r="B19" s="100" t="n"/>
+      <c r="C19" s="100" t="n"/>
+      <c r="D19" s="100" t="n"/>
+      <c r="E19" s="100" t="n"/>
+      <c r="F19" s="100" t="n"/>
+      <c r="G19" s="100" t="n"/>
+      <c r="H19" s="100" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="52">
+      <c r="A20" s="102" t="n"/>
+      <c r="B20" s="100" t="n"/>
+      <c r="C20" s="100" t="n"/>
+      <c r="D20" s="100" t="n"/>
+      <c r="E20" s="100" t="n"/>
+      <c r="F20" s="100" t="n"/>
+      <c r="G20" s="100" t="n"/>
+      <c r="H20" s="100" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="52">
+      <c r="A21" s="102" t="n"/>
+      <c r="B21" s="100" t="n"/>
+      <c r="C21" s="100" t="n"/>
+      <c r="D21" s="100" t="n"/>
+      <c r="E21" s="100" t="n"/>
+      <c r="F21" s="100" t="n"/>
+      <c r="G21" s="100" t="n"/>
+      <c r="H21" s="100" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="52">
+      <c r="A22" s="102" t="n"/>
+      <c r="B22" s="100" t="n"/>
+      <c r="C22" s="100" t="n"/>
+      <c r="D22" s="100" t="n"/>
+      <c r="E22" s="100" t="n"/>
+      <c r="F22" s="100" t="n"/>
+      <c r="G22" s="100" t="n"/>
+      <c r="H22" s="100" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="52">
+      <c r="A23" s="102" t="n"/>
+      <c r="B23" s="100" t="n"/>
+      <c r="C23" s="100" t="n"/>
+      <c r="D23" s="100" t="n"/>
+      <c r="E23" s="100" t="n"/>
+      <c r="F23" s="100" t="n"/>
+      <c r="G23" s="100" t="n"/>
+      <c r="H23" s="100" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="52">
+      <c r="A24" s="102" t="n"/>
+      <c r="B24" s="100" t="n"/>
+      <c r="C24" s="100" t="n"/>
+      <c r="D24" s="100" t="n"/>
+      <c r="E24" s="100" t="n"/>
+      <c r="F24" s="100" t="n"/>
+      <c r="G24" s="100" t="n"/>
+      <c r="H24" s="100" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="52">
+      <c r="A25" s="102" t="n"/>
+      <c r="B25" s="100" t="n"/>
+      <c r="C25" s="100" t="n"/>
+      <c r="D25" s="100" t="n"/>
+      <c r="E25" s="100" t="n"/>
+      <c r="F25" s="100" t="n"/>
+      <c r="G25" s="100" t="n"/>
+      <c r="H25" s="100" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="52">
+      <c r="A26" s="102" t="n"/>
+      <c r="B26" s="100" t="n"/>
+      <c r="C26" s="100" t="n"/>
+      <c r="D26" s="100" t="n"/>
+      <c r="E26" s="100" t="n"/>
+      <c r="F26" s="100" t="n"/>
+      <c r="G26" s="100" t="n"/>
+      <c r="H26" s="100" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="52">
+      <c r="A27" s="102" t="n"/>
+      <c r="B27" s="100" t="n"/>
+      <c r="C27" s="100" t="n"/>
+      <c r="D27" s="100" t="n"/>
+      <c r="E27" s="100" t="n"/>
+      <c r="F27" s="100" t="n"/>
+      <c r="G27" s="100" t="n"/>
+      <c r="H27" s="100" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="52">
+      <c r="A28" s="102" t="n"/>
+      <c r="B28" s="100" t="n"/>
+      <c r="C28" s="100" t="n"/>
+      <c r="D28" s="100" t="n"/>
+      <c r="E28" s="100" t="n"/>
+      <c r="F28" s="100" t="n"/>
+      <c r="G28" s="100" t="n"/>
+      <c r="H28" s="100" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="52">
+      <c r="A29" s="102" t="n"/>
+      <c r="B29" s="100" t="n"/>
+      <c r="C29" s="100" t="n"/>
+      <c r="D29" s="100" t="n"/>
+      <c r="E29" s="100" t="n"/>
+      <c r="F29" s="100" t="n"/>
+      <c r="G29" s="100" t="n"/>
+      <c r="H29" s="100" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="52">
+      <c r="A30" s="102" t="n"/>
+      <c r="B30" s="100" t="n"/>
+      <c r="C30" s="100" t="n"/>
+      <c r="D30" s="100" t="n"/>
+      <c r="E30" s="100" t="n"/>
+      <c r="F30" s="100" t="n"/>
+      <c r="G30" s="100" t="n"/>
+      <c r="H30" s="100" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="52">
+      <c r="A31" s="102" t="n"/>
+      <c r="B31" s="100" t="n"/>
+      <c r="C31" s="100" t="n"/>
+      <c r="D31" s="100" t="n"/>
+      <c r="E31" s="100" t="n"/>
+      <c r="F31" s="100" t="n"/>
+      <c r="G31" s="100" t="n"/>
+      <c r="H31" s="100" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="52">
+      <c r="A32" s="102" t="n"/>
+      <c r="B32" s="100" t="n"/>
+      <c r="C32" s="100" t="n"/>
+      <c r="D32" s="100" t="n"/>
+      <c r="E32" s="100" t="n"/>
+      <c r="F32" s="100" t="n"/>
+      <c r="G32" s="100" t="n"/>
+      <c r="H32" s="100" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="52">
+      <c r="A33" s="102" t="n"/>
+      <c r="B33" s="100" t="n"/>
+      <c r="C33" s="100" t="n"/>
+      <c r="D33" s="100" t="n"/>
+      <c r="E33" s="100" t="n"/>
+      <c r="F33" s="100" t="n"/>
+      <c r="G33" s="100" t="n"/>
+      <c r="H33" s="100" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="52">
+      <c r="A34" s="102" t="n"/>
+      <c r="B34" s="100" t="n"/>
+      <c r="C34" s="100" t="n"/>
+      <c r="D34" s="100" t="n"/>
+      <c r="E34" s="100" t="n"/>
+      <c r="F34" s="100" t="n"/>
+      <c r="G34" s="100" t="n"/>
+      <c r="H34" s="100" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="52">
+      <c r="A35" s="102" t="n"/>
+      <c r="B35" s="100" t="n"/>
+      <c r="C35" s="100" t="n"/>
+      <c r="D35" s="100" t="n"/>
+      <c r="E35" s="100" t="n"/>
+      <c r="F35" s="100" t="n"/>
+      <c r="G35" s="100" t="n"/>
+      <c r="H35" s="100" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="52">
+      <c r="A36" s="102" t="n"/>
+      <c r="B36" s="100" t="n"/>
+      <c r="C36" s="100" t="n"/>
+      <c r="D36" s="100" t="n"/>
+      <c r="E36" s="100" t="n"/>
+      <c r="F36" s="100" t="n"/>
+      <c r="G36" s="100" t="n"/>
+      <c r="H36" s="100" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="52">
+      <c r="A37" s="102" t="n"/>
+      <c r="B37" s="100" t="n"/>
+      <c r="C37" s="100" t="n"/>
+      <c r="D37" s="100" t="n"/>
+      <c r="E37" s="100" t="n"/>
+      <c r="F37" s="100" t="n"/>
+      <c r="G37" s="100" t="n"/>
+      <c r="H37" s="100" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="52">
+      <c r="A38" s="102" t="n"/>
+      <c r="B38" s="100" t="n"/>
+      <c r="C38" s="100" t="n"/>
+      <c r="D38" s="100" t="n"/>
+      <c r="E38" s="100" t="n"/>
+      <c r="F38" s="100" t="n"/>
+      <c r="G38" s="100" t="n"/>
+      <c r="H38" s="100" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="52">
+      <c r="A39" s="102" t="n"/>
+      <c r="B39" s="100" t="n"/>
+      <c r="C39" s="100" t="n"/>
+      <c r="D39" s="100" t="n"/>
+      <c r="E39" s="100" t="n"/>
+      <c r="F39" s="100" t="n"/>
+      <c r="G39" s="100" t="n"/>
+      <c r="H39" s="100" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="52">
+      <c r="A40" s="102" t="n"/>
+      <c r="B40" s="100" t="n"/>
+      <c r="C40" s="100" t="n"/>
+      <c r="D40" s="100" t="n"/>
+      <c r="E40" s="100" t="n"/>
+      <c r="F40" s="100" t="n"/>
+      <c r="G40" s="100" t="n"/>
+      <c r="H40" s="100" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="52">
+      <c r="A41" s="102" t="n"/>
+      <c r="B41" s="100" t="n"/>
+      <c r="C41" s="100" t="n"/>
+      <c r="D41" s="100" t="n"/>
+      <c r="E41" s="100" t="n"/>
+      <c r="F41" s="100" t="n"/>
+      <c r="G41" s="100" t="n"/>
+      <c r="H41" s="100" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="52">
+      <c r="A42" s="102" t="n"/>
+      <c r="B42" s="100" t="n"/>
+      <c r="C42" s="100" t="n"/>
+      <c r="D42" s="100" t="n"/>
+      <c r="E42" s="100" t="n"/>
+      <c r="F42" s="100" t="n"/>
+      <c r="G42" s="100" t="n"/>
+      <c r="H42" s="100" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="52">
+      <c r="A43" s="102" t="n"/>
+      <c r="B43" s="100" t="n"/>
+      <c r="C43" s="100" t="n"/>
+      <c r="D43" s="100" t="n"/>
+      <c r="E43" s="100" t="n"/>
+      <c r="F43" s="100" t="n"/>
+      <c r="G43" s="100" t="n"/>
+      <c r="H43" s="100" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="52">
+      <c r="A44" s="102" t="n"/>
+      <c r="B44" s="100" t="n"/>
+      <c r="C44" s="100" t="n"/>
+      <c r="D44" s="100" t="n"/>
+      <c r="E44" s="100" t="n"/>
+      <c r="F44" s="100" t="n"/>
+      <c r="G44" s="100" t="n"/>
+      <c r="H44" s="100" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="52">
+      <c r="A45" s="102" t="n"/>
+      <c r="B45" s="100" t="n"/>
+      <c r="C45" s="100" t="n"/>
+      <c r="D45" s="100" t="n"/>
+      <c r="E45" s="100" t="n"/>
+      <c r="F45" s="100" t="n"/>
+      <c r="G45" s="100" t="n"/>
+      <c r="H45" s="100" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="52">
+      <c r="A46" s="102" t="n"/>
+      <c r="B46" s="100" t="n"/>
+      <c r="C46" s="100" t="n"/>
+      <c r="D46" s="100" t="n"/>
+      <c r="E46" s="100" t="n"/>
+      <c r="F46" s="100" t="n"/>
+      <c r="G46" s="100" t="n"/>
+      <c r="H46" s="100" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="52">
+      <c r="A47" s="102" t="n"/>
+      <c r="B47" s="100" t="n"/>
+      <c r="C47" s="100" t="n"/>
+      <c r="D47" s="100" t="n"/>
+      <c r="E47" s="100" t="n"/>
+      <c r="F47" s="100" t="n"/>
+      <c r="G47" s="100" t="n"/>
+      <c r="H47" s="100" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="52">
+      <c r="A48" s="102" t="n"/>
+      <c r="B48" s="100" t="n"/>
+      <c r="C48" s="100" t="n"/>
+      <c r="D48" s="100" t="n"/>
+      <c r="E48" s="100" t="n"/>
+      <c r="F48" s="100" t="n"/>
+      <c r="G48" s="100" t="n"/>
+      <c r="H48" s="100" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="52">
+      <c r="A49" s="102" t="n"/>
+      <c r="B49" s="100" t="n"/>
+      <c r="C49" s="100" t="n"/>
+      <c r="D49" s="100" t="n"/>
+      <c r="E49" s="100" t="n"/>
+      <c r="F49" s="100" t="n"/>
+      <c r="G49" s="100" t="n"/>
+      <c r="H49" s="100" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="52">
+      <c r="A50" s="102" t="n"/>
+      <c r="B50" s="100" t="n"/>
+      <c r="C50" s="100" t="n"/>
+      <c r="D50" s="100" t="n"/>
+      <c r="E50" s="100" t="n"/>
+      <c r="F50" s="100" t="n"/>
+      <c r="G50" s="100" t="n"/>
+      <c r="H50" s="100" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="52">
+      <c r="A51" s="102" t="n"/>
+      <c r="B51" s="100" t="n"/>
+      <c r="C51" s="100" t="n"/>
+      <c r="D51" s="100" t="n"/>
+      <c r="E51" s="100" t="n"/>
+      <c r="F51" s="100" t="n"/>
+      <c r="G51" s="100" t="n"/>
+      <c r="H51" s="100" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="52">
+      <c r="A52" s="102" t="n"/>
+      <c r="B52" s="100" t="n"/>
+      <c r="C52" s="100" t="n"/>
+      <c r="D52" s="100" t="n"/>
+      <c r="E52" s="100" t="n"/>
+      <c r="F52" s="100" t="n"/>
+      <c r="G52" s="100" t="n"/>
+      <c r="H52" s="100" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="52">
+      <c r="A53" s="102" t="n"/>
+      <c r="B53" s="100" t="n"/>
+      <c r="C53" s="100" t="n"/>
+      <c r="D53" s="100" t="n"/>
+      <c r="E53" s="100" t="n"/>
+      <c r="F53" s="100" t="n"/>
+      <c r="G53" s="100" t="n"/>
+      <c r="H53" s="100" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="52">
+      <c r="A54" s="102" t="n"/>
+      <c r="B54" s="100" t="n"/>
+      <c r="C54" s="100" t="n"/>
+      <c r="D54" s="100" t="n"/>
+      <c r="E54" s="100" t="n"/>
+      <c r="F54" s="100" t="n"/>
+      <c r="G54" s="100" t="n"/>
+      <c r="H54" s="100" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="52">
+      <c r="A55" s="102" t="n"/>
+      <c r="B55" s="100" t="n"/>
+      <c r="C55" s="100" t="n"/>
+      <c r="D55" s="100" t="n"/>
+      <c r="E55" s="100" t="n"/>
+      <c r="F55" s="100" t="n"/>
+      <c r="G55" s="100" t="n"/>
+      <c r="H55" s="100" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="52">
+      <c r="A56" s="102" t="n"/>
+      <c r="B56" s="100" t="n"/>
+      <c r="C56" s="100" t="n"/>
+      <c r="D56" s="100" t="n"/>
+      <c r="E56" s="100" t="n"/>
+      <c r="F56" s="100" t="n"/>
+      <c r="G56" s="100" t="n"/>
+      <c r="H56" s="100" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="52">
+      <c r="A57" s="102" t="n"/>
+      <c r="B57" s="100" t="n"/>
+      <c r="C57" s="100" t="n"/>
+      <c r="D57" s="100" t="n"/>
+      <c r="E57" s="100" t="n"/>
+      <c r="F57" s="100" t="n"/>
+      <c r="G57" s="100" t="n"/>
+      <c r="H57" s="100" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="52">
+      <c r="A58" s="102" t="n"/>
+      <c r="B58" s="100" t="n"/>
+      <c r="C58" s="100" t="n"/>
+      <c r="D58" s="100" t="n"/>
+      <c r="E58" s="100" t="n"/>
+      <c r="F58" s="100" t="n"/>
+      <c r="G58" s="100" t="n"/>
+      <c r="H58" s="100" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="52">
+      <c r="A59" s="102" t="n"/>
+      <c r="B59" s="100" t="n"/>
+      <c r="C59" s="100" t="n"/>
+      <c r="D59" s="100" t="n"/>
+      <c r="E59" s="100" t="n"/>
+      <c r="F59" s="100" t="n"/>
+      <c r="G59" s="100" t="n"/>
+      <c r="H59" s="100" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="52">
+      <c r="A60" s="102" t="n"/>
+      <c r="B60" s="100" t="n"/>
+      <c r="C60" s="100" t="n"/>
+      <c r="D60" s="100" t="n"/>
+      <c r="E60" s="100" t="n"/>
+      <c r="F60" s="100" t="n"/>
+      <c r="G60" s="100" t="n"/>
+      <c r="H60" s="100" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="52">
+      <c r="A61" s="102" t="n"/>
+      <c r="B61" s="100" t="n"/>
+      <c r="C61" s="100" t="n"/>
+      <c r="D61" s="100" t="n"/>
+      <c r="E61" s="100" t="n"/>
+      <c r="F61" s="100" t="n"/>
+      <c r="G61" s="100" t="n"/>
+      <c r="H61" s="100" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="52">
+      <c r="A62" s="102" t="n"/>
+      <c r="B62" s="100" t="n"/>
+      <c r="C62" s="100" t="n"/>
+      <c r="D62" s="100" t="n"/>
+      <c r="E62" s="100" t="n"/>
+      <c r="F62" s="100" t="n"/>
+      <c r="G62" s="100" t="n"/>
+      <c r="H62" s="100" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="52">
+      <c r="A63" s="102" t="n"/>
+      <c r="B63" s="100" t="n"/>
+      <c r="C63" s="100" t="n"/>
+      <c r="D63" s="100" t="n"/>
+      <c r="E63" s="100" t="n"/>
+      <c r="F63" s="100" t="n"/>
+      <c r="G63" s="100" t="n"/>
+      <c r="H63" s="100" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="52">
+      <c r="A64" s="102" t="n"/>
+      <c r="B64" s="100" t="n"/>
+      <c r="C64" s="100" t="n"/>
+      <c r="D64" s="100" t="n"/>
+      <c r="E64" s="100" t="n"/>
+      <c r="F64" s="100" t="n"/>
+      <c r="G64" s="100" t="n"/>
+      <c r="H64" s="100" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="52">
+      <c r="A65" s="102" t="n"/>
+      <c r="B65" s="100" t="n"/>
+      <c r="C65" s="100" t="n"/>
+      <c r="D65" s="100" t="n"/>
+      <c r="E65" s="100" t="n"/>
+      <c r="F65" s="100" t="n"/>
+      <c r="G65" s="100" t="n"/>
+      <c r="H65" s="100" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="52">
+      <c r="A66" s="102" t="n"/>
+      <c r="B66" s="100" t="n"/>
+      <c r="C66" s="100" t="n"/>
+      <c r="D66" s="100" t="n"/>
+      <c r="E66" s="100" t="n"/>
+      <c r="F66" s="100" t="n"/>
+      <c r="G66" s="100" t="n"/>
+      <c r="H66" s="100" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="52">
+      <c r="A67" s="102" t="n"/>
+      <c r="B67" s="100" t="n"/>
+      <c r="C67" s="100" t="n"/>
+      <c r="D67" s="100" t="n"/>
+      <c r="E67" s="100" t="n"/>
+      <c r="F67" s="100" t="n"/>
+      <c r="G67" s="100" t="n"/>
+      <c r="H67" s="100" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="52">
+      <c r="A68" s="102" t="n"/>
+      <c r="B68" s="100" t="n"/>
+      <c r="C68" s="100" t="n"/>
+      <c r="D68" s="100" t="n"/>
+      <c r="E68" s="100" t="n"/>
+      <c r="F68" s="100" t="n"/>
+      <c r="G68" s="100" t="n"/>
+      <c r="H68" s="100" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="52">
+      <c r="A69" s="102" t="n"/>
+      <c r="B69" s="100" t="n"/>
+      <c r="C69" s="100" t="n"/>
+      <c r="D69" s="100" t="n"/>
+      <c r="E69" s="100" t="n"/>
+      <c r="F69" s="100" t="n"/>
+      <c r="G69" s="100" t="n"/>
+      <c r="H69" s="100" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="52">
+      <c r="A70" s="102" t="n"/>
+      <c r="B70" s="100" t="n"/>
+      <c r="C70" s="100" t="n"/>
+      <c r="D70" s="100" t="n"/>
+      <c r="E70" s="100" t="n"/>
+      <c r="F70" s="100" t="n"/>
+      <c r="G70" s="100" t="n"/>
+      <c r="H70" s="100" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="52">
+      <c r="A71" s="102" t="n"/>
+      <c r="B71" s="100" t="n"/>
+      <c r="C71" s="100" t="n"/>
+      <c r="D71" s="100" t="n"/>
+      <c r="E71" s="100" t="n"/>
+      <c r="F71" s="100" t="n"/>
+      <c r="G71" s="100" t="n"/>
+      <c r="H71" s="100" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="52">
+      <c r="A72" s="102" t="n"/>
+      <c r="B72" s="100" t="n"/>
+      <c r="C72" s="100" t="n"/>
+      <c r="D72" s="100" t="n"/>
+      <c r="E72" s="100" t="n"/>
+      <c r="F72" s="100" t="n"/>
+      <c r="G72" s="100" t="n"/>
+      <c r="H72" s="100" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="52">
+      <c r="A73" s="102" t="n"/>
+      <c r="B73" s="100" t="n"/>
+      <c r="C73" s="100" t="n"/>
+      <c r="D73" s="100" t="n"/>
+      <c r="E73" s="100" t="n"/>
+      <c r="F73" s="100" t="n"/>
+      <c r="G73" s="100" t="n"/>
+      <c r="H73" s="100" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="52">
+      <c r="A74" s="102" t="n"/>
+      <c r="B74" s="100" t="n"/>
+      <c r="C74" s="100" t="n"/>
+      <c r="D74" s="100" t="n"/>
+      <c r="E74" s="100" t="n"/>
+      <c r="F74" s="100" t="n"/>
+      <c r="G74" s="100" t="n"/>
+      <c r="H74" s="100" t="n"/>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="52">
+      <c r="A75" s="102" t="n"/>
+      <c r="B75" s="100" t="n"/>
+      <c r="C75" s="100" t="n"/>
+      <c r="D75" s="100" t="n"/>
+      <c r="E75" s="100" t="n"/>
+      <c r="F75" s="100" t="n"/>
+      <c r="G75" s="100" t="n"/>
+      <c r="H75" s="100" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="52">
+      <c r="A76" s="102" t="n"/>
+      <c r="B76" s="100" t="n"/>
+      <c r="C76" s="100" t="n"/>
+      <c r="D76" s="100" t="n"/>
+      <c r="E76" s="100" t="n"/>
+      <c r="F76" s="100" t="n"/>
+      <c r="G76" s="100" t="n"/>
+      <c r="H76" s="100" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="52">
+      <c r="A77" s="102" t="n"/>
+      <c r="B77" s="100" t="n"/>
+      <c r="C77" s="100" t="n"/>
+      <c r="D77" s="100" t="n"/>
+      <c r="E77" s="100" t="n"/>
+      <c r="F77" s="100" t="n"/>
+      <c r="G77" s="100" t="n"/>
+      <c r="H77" s="100" t="n"/>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="52">
+      <c r="A78" s="102" t="n"/>
+      <c r="B78" s="100" t="n"/>
+      <c r="C78" s="100" t="n"/>
+      <c r="D78" s="100" t="n"/>
+      <c r="E78" s="100" t="n"/>
+      <c r="F78" s="100" t="n"/>
+      <c r="G78" s="100" t="n"/>
+      <c r="H78" s="100" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="52">
+      <c r="A79" s="102" t="n"/>
+      <c r="B79" s="100" t="n"/>
+      <c r="C79" s="100" t="n"/>
+      <c r="D79" s="100" t="n"/>
+      <c r="E79" s="100" t="n"/>
+      <c r="F79" s="100" t="n"/>
+      <c r="G79" s="100" t="n"/>
+      <c r="H79" s="100" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="52">
+      <c r="A80" s="102" t="n"/>
+      <c r="B80" s="100" t="n"/>
+      <c r="C80" s="100" t="n"/>
+      <c r="D80" s="100" t="n"/>
+      <c r="E80" s="100" t="n"/>
+      <c r="F80" s="100" t="n"/>
+      <c r="G80" s="100" t="n"/>
+      <c r="H80" s="100" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="52">
+      <c r="A81" s="102" t="n"/>
+      <c r="B81" s="100" t="n"/>
+      <c r="C81" s="100" t="n"/>
+      <c r="D81" s="100" t="n"/>
+      <c r="E81" s="100" t="n"/>
+      <c r="F81" s="100" t="n"/>
+      <c r="G81" s="100" t="n"/>
+      <c r="H81" s="100" t="n"/>
+    </row>
+    <row r="82" ht="15" customHeight="1" s="52">
+      <c r="A82" s="102" t="n"/>
+      <c r="B82" s="100" t="n"/>
+      <c r="C82" s="100" t="n"/>
+      <c r="D82" s="100" t="n"/>
+      <c r="E82" s="100" t="n"/>
+      <c r="F82" s="100" t="n"/>
+      <c r="G82" s="100" t="n"/>
+      <c r="H82" s="100" t="n"/>
+    </row>
+    <row r="83" ht="15" customHeight="1" s="52">
+      <c r="A83" s="102" t="n"/>
+      <c r="B83" s="100" t="n"/>
+      <c r="C83" s="100" t="n"/>
+      <c r="D83" s="100" t="n"/>
+      <c r="E83" s="100" t="n"/>
+      <c r="F83" s="100" t="n"/>
+      <c r="G83" s="100" t="n"/>
+      <c r="H83" s="100" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="52">
+      <c r="A84" s="102" t="n"/>
+      <c r="B84" s="100" t="n"/>
+      <c r="C84" s="100" t="n"/>
+      <c r="D84" s="100" t="n"/>
+      <c r="E84" s="100" t="n"/>
+      <c r="F84" s="100" t="n"/>
+      <c r="G84" s="100" t="n"/>
+      <c r="H84" s="100" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="52">
+      <c r="A85" s="102" t="n"/>
+      <c r="B85" s="100" t="n"/>
+      <c r="C85" s="100" t="n"/>
+      <c r="D85" s="100" t="n"/>
+      <c r="E85" s="100" t="n"/>
+      <c r="F85" s="100" t="n"/>
+      <c r="G85" s="100" t="n"/>
+      <c r="H85" s="100" t="n"/>
+    </row>
+    <row r="86" ht="15" customHeight="1" s="52">
+      <c r="A86" s="102" t="n"/>
+      <c r="B86" s="100" t="n"/>
+      <c r="C86" s="100" t="n"/>
+      <c r="D86" s="100" t="n"/>
+      <c r="E86" s="100" t="n"/>
+      <c r="F86" s="100" t="n"/>
+      <c r="G86" s="100" t="n"/>
+      <c r="H86" s="100" t="n"/>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="52">
+      <c r="A87" s="102" t="n"/>
+      <c r="B87" s="100" t="n"/>
+      <c r="C87" s="100" t="n"/>
+      <c r="D87" s="100" t="n"/>
+      <c r="E87" s="100" t="n"/>
+      <c r="F87" s="100" t="n"/>
+      <c r="G87" s="100" t="n"/>
+      <c r="H87" s="100" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="52">
+      <c r="A88" s="102" t="n"/>
+      <c r="B88" s="100" t="n"/>
+      <c r="C88" s="100" t="n"/>
+      <c r="D88" s="100" t="n"/>
+      <c r="E88" s="100" t="n"/>
+      <c r="F88" s="100" t="n"/>
+      <c r="G88" s="100" t="n"/>
+      <c r="H88" s="100" t="n"/>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="52">
+      <c r="A89" s="102" t="n"/>
+      <c r="B89" s="100" t="n"/>
+      <c r="C89" s="100" t="n"/>
+      <c r="D89" s="100" t="n"/>
+      <c r="E89" s="100" t="n"/>
+      <c r="F89" s="100" t="n"/>
+      <c r="G89" s="100" t="n"/>
+      <c r="H89" s="100" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="52">
+      <c r="A90" s="102" t="n"/>
+      <c r="B90" s="100" t="n"/>
+      <c r="C90" s="100" t="n"/>
+      <c r="D90" s="100" t="n"/>
+      <c r="E90" s="100" t="n"/>
+      <c r="F90" s="100" t="n"/>
+      <c r="G90" s="100" t="n"/>
+      <c r="H90" s="100" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="52">
+      <c r="A91" s="102" t="n"/>
+      <c r="B91" s="100" t="n"/>
+      <c r="C91" s="100" t="n"/>
+      <c r="D91" s="100" t="n"/>
+      <c r="E91" s="100" t="n"/>
+      <c r="F91" s="100" t="n"/>
+      <c r="G91" s="100" t="n"/>
+      <c r="H91" s="100" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1" s="52">
+      <c r="A92" s="102" t="n"/>
+      <c r="B92" s="100" t="n"/>
+      <c r="C92" s="100" t="n"/>
+      <c r="D92" s="100" t="n"/>
+      <c r="E92" s="100" t="n"/>
+      <c r="F92" s="100" t="n"/>
+      <c r="G92" s="100" t="n"/>
+      <c r="H92" s="100" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="52">
+      <c r="A93" s="102" t="n"/>
+      <c r="B93" s="100" t="n"/>
+      <c r="C93" s="100" t="n"/>
+      <c r="D93" s="100" t="n"/>
+      <c r="E93" s="100" t="n"/>
+      <c r="F93" s="100" t="n"/>
+      <c r="G93" s="100" t="n"/>
+      <c r="H93" s="100" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="52">
+      <c r="A94" s="102" t="n"/>
+      <c r="B94" s="100" t="n"/>
+      <c r="C94" s="100" t="n"/>
+      <c r="D94" s="100" t="n"/>
+      <c r="E94" s="100" t="n"/>
+      <c r="F94" s="100" t="n"/>
+      <c r="G94" s="100" t="n"/>
+      <c r="H94" s="100" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="52">
+      <c r="A95" s="102" t="n"/>
+      <c r="B95" s="100" t="n"/>
+      <c r="C95" s="100" t="n"/>
+      <c r="D95" s="100" t="n"/>
+      <c r="E95" s="100" t="n"/>
+      <c r="F95" s="100" t="n"/>
+      <c r="G95" s="100" t="n"/>
+      <c r="H95" s="100" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="52">
+      <c r="A96" s="102" t="n"/>
+      <c r="B96" s="100" t="n"/>
+      <c r="C96" s="100" t="n"/>
+      <c r="D96" s="100" t="n"/>
+      <c r="E96" s="100" t="n"/>
+      <c r="F96" s="100" t="n"/>
+      <c r="G96" s="100" t="n"/>
+      <c r="H96" s="100" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="52">
+      <c r="A97" s="102" t="n"/>
+      <c r="B97" s="100" t="n"/>
+      <c r="C97" s="100" t="n"/>
+      <c r="D97" s="100" t="n"/>
+      <c r="E97" s="100" t="n"/>
+      <c r="F97" s="100" t="n"/>
+      <c r="G97" s="100" t="n"/>
+      <c r="H97" s="100" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1" s="52">
+      <c r="A98" s="102" t="n"/>
+      <c r="B98" s="100" t="n"/>
+      <c r="C98" s="100" t="n"/>
+      <c r="D98" s="100" t="n"/>
+      <c r="E98" s="100" t="n"/>
+      <c r="F98" s="100" t="n"/>
+      <c r="G98" s="100" t="n"/>
+      <c r="H98" s="100" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="52">
+      <c r="A99" s="102" t="n"/>
+      <c r="B99" s="100" t="n"/>
+      <c r="C99" s="100" t="n"/>
+      <c r="D99" s="100" t="n"/>
+      <c r="E99" s="100" t="n"/>
+      <c r="F99" s="100" t="n"/>
+      <c r="G99" s="100" t="n"/>
+      <c r="H99" s="100" t="n"/>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="52">
+      <c r="A100" s="102" t="n"/>
+      <c r="B100" s="100" t="n"/>
+      <c r="C100" s="100" t="n"/>
+      <c r="D100" s="100" t="n"/>
+      <c r="E100" s="100" t="n"/>
+      <c r="F100" s="100" t="n"/>
+      <c r="G100" s="100" t="n"/>
+      <c r="H100" s="100" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="52">
+      <c r="A101" s="102" t="n"/>
+      <c r="B101" s="100" t="n"/>
+      <c r="C101" s="100" t="n"/>
+      <c r="D101" s="100" t="n"/>
+      <c r="E101" s="100" t="n"/>
+      <c r="F101" s="100" t="n"/>
+      <c r="G101" s="100" t="n"/>
+      <c r="H101" s="100" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="52">
+      <c r="A102" s="102" t="n"/>
+      <c r="B102" s="100" t="n"/>
+      <c r="C102" s="100" t="n"/>
+      <c r="D102" s="100" t="n"/>
+      <c r="E102" s="100" t="n"/>
+      <c r="F102" s="100" t="n"/>
+      <c r="G102" s="100" t="n"/>
+      <c r="H102" s="100" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1" s="52">
+      <c r="A103" s="102" t="n"/>
+      <c r="B103" s="100" t="n"/>
+      <c r="C103" s="100" t="n"/>
+      <c r="D103" s="100" t="n"/>
+      <c r="E103" s="100" t="n"/>
+      <c r="F103" s="100" t="n"/>
+      <c r="G103" s="100" t="n"/>
+      <c r="H103" s="100" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="52">
+      <c r="A104" s="102" t="n"/>
+      <c r="B104" s="100" t="n"/>
+      <c r="C104" s="100" t="n"/>
+      <c r="D104" s="100" t="n"/>
+      <c r="E104" s="100" t="n"/>
+      <c r="F104" s="100" t="n"/>
+      <c r="G104" s="100" t="n"/>
+      <c r="H104" s="100" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1" s="52">
+      <c r="A105" s="102" t="n"/>
+      <c r="B105" s="100" t="n"/>
+      <c r="C105" s="100" t="n"/>
+      <c r="D105" s="100" t="n"/>
+      <c r="E105" s="100" t="n"/>
+      <c r="F105" s="100" t="n"/>
+      <c r="G105" s="100" t="n"/>
+      <c r="H105" s="100" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1" s="52">
+      <c r="A106" s="102" t="n"/>
+      <c r="B106" s="100" t="n"/>
+      <c r="C106" s="100" t="n"/>
+      <c r="D106" s="100" t="n"/>
+      <c r="E106" s="100" t="n"/>
+      <c r="F106" s="100" t="n"/>
+      <c r="G106" s="100" t="n"/>
+      <c r="H106" s="100" t="n"/>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="52">
+      <c r="A107" s="102" t="n"/>
+      <c r="B107" s="100" t="n"/>
+      <c r="C107" s="100" t="n"/>
+      <c r="D107" s="100" t="n"/>
+      <c r="E107" s="100" t="n"/>
+      <c r="F107" s="100" t="n"/>
+      <c r="G107" s="100" t="n"/>
+      <c r="H107" s="100" t="n"/>
+    </row>
+    <row r="108" ht="15" customHeight="1" s="52">
+      <c r="A108" s="102" t="n"/>
+      <c r="B108" s="100" t="n"/>
+      <c r="C108" s="100" t="n"/>
+      <c r="D108" s="100" t="n"/>
+      <c r="E108" s="100" t="n"/>
+      <c r="F108" s="100" t="n"/>
+      <c r="G108" s="100" t="n"/>
+      <c r="H108" s="100" t="n"/>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="52">
+      <c r="A109" s="102" t="n"/>
+      <c r="B109" s="100" t="n"/>
+      <c r="C109" s="100" t="n"/>
+      <c r="D109" s="100" t="n"/>
+      <c r="E109" s="100" t="n"/>
+      <c r="F109" s="100" t="n"/>
+      <c r="G109" s="100" t="n"/>
+      <c r="H109" s="100" t="n"/>
+    </row>
+    <row r="110" ht="15" customHeight="1" s="52">
+      <c r="A110" s="102" t="n"/>
+      <c r="B110" s="100" t="n"/>
+      <c r="C110" s="100" t="n"/>
+      <c r="D110" s="100" t="n"/>
+      <c r="E110" s="100" t="n"/>
+      <c r="F110" s="100" t="n"/>
+      <c r="G110" s="100" t="n"/>
+      <c r="H110" s="100" t="n"/>
+    </row>
+    <row r="111" ht="15" customHeight="1" s="52">
+      <c r="A111" s="102" t="n"/>
+      <c r="B111" s="100" t="n"/>
+      <c r="C111" s="100" t="n"/>
+      <c r="D111" s="100" t="n"/>
+      <c r="E111" s="100" t="n"/>
+      <c r="F111" s="100" t="n"/>
+      <c r="G111" s="100" t="n"/>
+      <c r="H111" s="100" t="n"/>
+    </row>
+    <row r="112" ht="15" customHeight="1" s="52">
+      <c r="A112" s="102" t="n"/>
+      <c r="B112" s="100" t="n"/>
+      <c r="C112" s="100" t="n"/>
+      <c r="D112" s="100" t="n"/>
+      <c r="E112" s="100" t="n"/>
+      <c r="F112" s="100" t="n"/>
+      <c r="G112" s="100" t="n"/>
+      <c r="H112" s="100" t="n"/>
+    </row>
+    <row r="113" ht="15" customHeight="1" s="52">
+      <c r="A113" s="102" t="n"/>
+      <c r="B113" s="100" t="n"/>
+      <c r="C113" s="100" t="n"/>
+      <c r="D113" s="100" t="n"/>
+      <c r="E113" s="100" t="n"/>
+      <c r="F113" s="100" t="n"/>
+      <c r="G113" s="100" t="n"/>
+      <c r="H113" s="100" t="n"/>
+    </row>
+    <row r="114" ht="15" customHeight="1" s="52">
+      <c r="A114" s="102" t="n"/>
+      <c r="B114" s="100" t="n"/>
+      <c r="C114" s="100" t="n"/>
+      <c r="D114" s="100" t="n"/>
+      <c r="E114" s="100" t="n"/>
+      <c r="F114" s="100" t="n"/>
+      <c r="G114" s="100" t="n"/>
+      <c r="H114" s="100" t="n"/>
+    </row>
+    <row r="115" ht="15" customHeight="1" s="52">
+      <c r="A115" s="102" t="n"/>
+      <c r="B115" s="100" t="n"/>
+      <c r="C115" s="100" t="n"/>
+      <c r="D115" s="100" t="n"/>
+      <c r="E115" s="100" t="n"/>
+      <c r="F115" s="100" t="n"/>
+      <c r="G115" s="100" t="n"/>
+      <c r="H115" s="100" t="n"/>
+    </row>
+    <row r="116" ht="15" customHeight="1" s="52">
+      <c r="A116" s="102" t="n"/>
+      <c r="B116" s="100" t="n"/>
+      <c r="C116" s="100" t="n"/>
+      <c r="D116" s="100" t="n"/>
+      <c r="E116" s="100" t="n"/>
+      <c r="F116" s="100" t="n"/>
+      <c r="G116" s="100" t="n"/>
+      <c r="H116" s="100" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1" s="52">
+      <c r="A117" s="102" t="n"/>
+      <c r="B117" s="100" t="n"/>
+      <c r="C117" s="100" t="n"/>
+      <c r="D117" s="100" t="n"/>
+      <c r="E117" s="100" t="n"/>
+      <c r="F117" s="100" t="n"/>
+      <c r="G117" s="100" t="n"/>
+      <c r="H117" s="100" t="n"/>
+    </row>
+    <row r="118" ht="15" customHeight="1" s="52">
+      <c r="A118" s="102" t="n"/>
+      <c r="B118" s="100" t="n"/>
+      <c r="C118" s="100" t="n"/>
+      <c r="D118" s="100" t="n"/>
+      <c r="E118" s="100" t="n"/>
+      <c r="F118" s="100" t="n"/>
+      <c r="G118" s="100" t="n"/>
+      <c r="H118" s="100" t="n"/>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="52">
+      <c r="A119" s="102" t="n"/>
+      <c r="B119" s="100" t="n"/>
+      <c r="C119" s="100" t="n"/>
+      <c r="D119" s="100" t="n"/>
+      <c r="E119" s="100" t="n"/>
+      <c r="F119" s="100" t="n"/>
+      <c r="G119" s="100" t="n"/>
+      <c r="H119" s="100" t="n"/>
+    </row>
+    <row r="120" ht="15" customHeight="1" s="52">
+      <c r="A120" s="102" t="n"/>
+      <c r="B120" s="100" t="n"/>
+      <c r="C120" s="100" t="n"/>
+      <c r="D120" s="100" t="n"/>
+      <c r="E120" s="100" t="n"/>
+      <c r="F120" s="100" t="n"/>
+      <c r="G120" s="100" t="n"/>
+      <c r="H120" s="100" t="n"/>
+    </row>
+    <row r="121" ht="15" customHeight="1" s="52">
+      <c r="A121" s="102" t="n"/>
+      <c r="B121" s="100" t="n"/>
+      <c r="C121" s="100" t="n"/>
+      <c r="D121" s="100" t="n"/>
+      <c r="E121" s="100" t="n"/>
+      <c r="F121" s="100" t="n"/>
+      <c r="G121" s="100" t="n"/>
+      <c r="H121" s="100" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="52">
+      <c r="A122" s="102" t="n"/>
+      <c r="B122" s="100" t="n"/>
+      <c r="C122" s="100" t="n"/>
+      <c r="D122" s="100" t="n"/>
+      <c r="E122" s="100" t="n"/>
+      <c r="F122" s="100" t="n"/>
+      <c r="G122" s="100" t="n"/>
+      <c r="H122" s="100" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="52">
+      <c r="A123" s="102" t="n"/>
+      <c r="B123" s="100" t="n"/>
+      <c r="C123" s="100" t="n"/>
+      <c r="D123" s="100" t="n"/>
+      <c r="E123" s="100" t="n"/>
+      <c r="F123" s="100" t="n"/>
+      <c r="G123" s="100" t="n"/>
+      <c r="H123" s="100" t="n"/>
+    </row>
+    <row r="124" ht="15" customHeight="1" s="52">
+      <c r="A124" s="102" t="n"/>
+      <c r="B124" s="100" t="n"/>
+      <c r="C124" s="100" t="n"/>
+      <c r="D124" s="100" t="n"/>
+      <c r="E124" s="100" t="n"/>
+      <c r="F124" s="100" t="n"/>
+      <c r="G124" s="100" t="n"/>
+      <c r="H124" s="100" t="n"/>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="52">
+      <c r="A125" s="102" t="n"/>
+      <c r="B125" s="100" t="n"/>
+      <c r="C125" s="100" t="n"/>
+      <c r="D125" s="100" t="n"/>
+      <c r="E125" s="100" t="n"/>
+      <c r="F125" s="100" t="n"/>
+      <c r="G125" s="100" t="n"/>
+      <c r="H125" s="100" t="n"/>
+    </row>
+    <row r="126" ht="15" customHeight="1" s="52">
+      <c r="A126" s="102" t="n"/>
+      <c r="B126" s="100" t="n"/>
+      <c r="C126" s="100" t="n"/>
+      <c r="D126" s="100" t="n"/>
+      <c r="E126" s="100" t="n"/>
+      <c r="F126" s="100" t="n"/>
+      <c r="G126" s="100" t="n"/>
+      <c r="H126" s="100" t="n"/>
+    </row>
+    <row r="127" ht="15" customHeight="1" s="52">
+      <c r="A127" s="102" t="n"/>
+      <c r="B127" s="100" t="n"/>
+      <c r="C127" s="100" t="n"/>
+      <c r="D127" s="100" t="n"/>
+      <c r="E127" s="100" t="n"/>
+      <c r="F127" s="100" t="n"/>
+      <c r="G127" s="100" t="n"/>
+      <c r="H127" s="100" t="n"/>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="52">
+      <c r="A128" s="102" t="n"/>
+      <c r="B128" s="100" t="n"/>
+      <c r="C128" s="100" t="n"/>
+      <c r="D128" s="100" t="n"/>
+      <c r="E128" s="100" t="n"/>
+      <c r="F128" s="100" t="n"/>
+      <c r="G128" s="100" t="n"/>
+      <c r="H128" s="100" t="n"/>
+    </row>
+    <row r="129" ht="15" customHeight="1" s="52">
+      <c r="A129" s="102" t="n"/>
+      <c r="B129" s="100" t="n"/>
+      <c r="C129" s="100" t="n"/>
+      <c r="D129" s="100" t="n"/>
+      <c r="E129" s="100" t="n"/>
+      <c r="F129" s="100" t="n"/>
+      <c r="G129" s="100" t="n"/>
+      <c r="H129" s="100" t="n"/>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="52">
+      <c r="A130" s="102" t="n"/>
+      <c r="B130" s="100" t="n"/>
+      <c r="C130" s="100" t="n"/>
+      <c r="D130" s="100" t="n"/>
+      <c r="E130" s="100" t="n"/>
+      <c r="F130" s="100" t="n"/>
+      <c r="G130" s="100" t="n"/>
+      <c r="H130" s="100" t="n"/>
+    </row>
+    <row r="131" ht="15" customHeight="1" s="52">
+      <c r="A131" s="102" t="n"/>
+      <c r="B131" s="100" t="n"/>
+      <c r="C131" s="100" t="n"/>
+      <c r="D131" s="100" t="n"/>
+      <c r="E131" s="100" t="n"/>
+      <c r="F131" s="100" t="n"/>
+      <c r="G131" s="100" t="n"/>
+      <c r="H131" s="100" t="n"/>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="52">
+      <c r="A132" s="102" t="n"/>
+      <c r="B132" s="100" t="n"/>
+      <c r="C132" s="100" t="n"/>
+      <c r="D132" s="100" t="n"/>
+      <c r="E132" s="100" t="n"/>
+      <c r="F132" s="100" t="n"/>
+      <c r="G132" s="100" t="n"/>
+      <c r="H132" s="100" t="n"/>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="52">
+      <c r="A133" s="102" t="n"/>
+      <c r="B133" s="100" t="n"/>
+      <c r="C133" s="100" t="n"/>
+      <c r="D133" s="100" t="n"/>
+      <c r="E133" s="100" t="n"/>
+      <c r="F133" s="100" t="n"/>
+      <c r="G133" s="100" t="n"/>
+      <c r="H133" s="100" t="n"/>
+    </row>
+    <row r="134" ht="15" customHeight="1" s="52">
+      <c r="A134" s="102" t="n"/>
+      <c r="B134" s="100" t="n"/>
+      <c r="C134" s="100" t="n"/>
+      <c r="D134" s="100" t="n"/>
+      <c r="E134" s="100" t="n"/>
+      <c r="F134" s="100" t="n"/>
+      <c r="G134" s="100" t="n"/>
+      <c r="H134" s="100" t="n"/>
+    </row>
+    <row r="135" ht="15" customHeight="1" s="52">
+      <c r="A135" s="102" t="n"/>
+      <c r="B135" s="100" t="n"/>
+      <c r="C135" s="100" t="n"/>
+      <c r="D135" s="100" t="n"/>
+      <c r="E135" s="100" t="n"/>
+      <c r="F135" s="100" t="n"/>
+      <c r="G135" s="100" t="n"/>
+      <c r="H135" s="100" t="n"/>
+    </row>
+    <row r="136" ht="15" customHeight="1" s="52">
+      <c r="A136" s="102" t="n"/>
+      <c r="B136" s="100" t="n"/>
+      <c r="C136" s="100" t="n"/>
+      <c r="D136" s="100" t="n"/>
+      <c r="E136" s="100" t="n"/>
+      <c r="F136" s="100" t="n"/>
+      <c r="G136" s="100" t="n"/>
+      <c r="H136" s="100" t="n"/>
+    </row>
+    <row r="137" ht="15" customHeight="1" s="52">
+      <c r="A137" s="102" t="n"/>
+      <c r="B137" s="100" t="n"/>
+      <c r="C137" s="100" t="n"/>
+      <c r="D137" s="100" t="n"/>
+      <c r="E137" s="100" t="n"/>
+      <c r="F137" s="100" t="n"/>
+      <c r="G137" s="100" t="n"/>
+      <c r="H137" s="100" t="n"/>
+    </row>
+    <row r="138" ht="15" customHeight="1" s="52">
+      <c r="A138" s="102" t="n"/>
+      <c r="B138" s="100" t="n"/>
+      <c r="C138" s="100" t="n"/>
+      <c r="D138" s="100" t="n"/>
+      <c r="E138" s="100" t="n"/>
+      <c r="F138" s="100" t="n"/>
+      <c r="G138" s="100" t="n"/>
+      <c r="H138" s="100" t="n"/>
+    </row>
+    <row r="139" ht="15" customHeight="1" s="52">
+      <c r="A139" s="102" t="n"/>
+      <c r="B139" s="100" t="n"/>
+      <c r="C139" s="100" t="n"/>
+      <c r="D139" s="100" t="n"/>
+      <c r="E139" s="100" t="n"/>
+      <c r="F139" s="100" t="n"/>
+      <c r="G139" s="100" t="n"/>
+      <c r="H139" s="100" t="n"/>
+    </row>
+    <row r="140" ht="15" customHeight="1" s="52">
+      <c r="A140" s="102" t="n"/>
+      <c r="B140" s="100" t="n"/>
+      <c r="C140" s="100" t="n"/>
+      <c r="D140" s="100" t="n"/>
+      <c r="E140" s="100" t="n"/>
+      <c r="F140" s="100" t="n"/>
+      <c r="G140" s="100" t="n"/>
+      <c r="H140" s="100" t="n"/>
+    </row>
+    <row r="141" ht="15" customHeight="1" s="52">
+      <c r="A141" s="102" t="n"/>
+      <c r="B141" s="100" t="n"/>
+      <c r="C141" s="100" t="n"/>
+      <c r="D141" s="100" t="n"/>
+      <c r="E141" s="100" t="n"/>
+      <c r="F141" s="100" t="n"/>
+      <c r="G141" s="100" t="n"/>
+      <c r="H141" s="100" t="n"/>
+    </row>
+    <row r="142" ht="15" customHeight="1" s="52">
+      <c r="A142" s="102" t="n"/>
+      <c r="B142" s="100" t="n"/>
+      <c r="C142" s="100" t="n"/>
+      <c r="D142" s="100" t="n"/>
+      <c r="E142" s="100" t="n"/>
+      <c r="F142" s="100" t="n"/>
+      <c r="G142" s="100" t="n"/>
+      <c r="H142" s="100" t="n"/>
+    </row>
+    <row r="143" ht="15" customHeight="1" s="52">
+      <c r="A143" s="102" t="n"/>
+      <c r="B143" s="100" t="n"/>
+      <c r="C143" s="100" t="n"/>
+      <c r="D143" s="100" t="n"/>
+      <c r="E143" s="100" t="n"/>
+      <c r="F143" s="100" t="n"/>
+      <c r="G143" s="100" t="n"/>
+      <c r="H143" s="100" t="n"/>
+    </row>
+    <row r="144" ht="15" customHeight="1" s="52">
+      <c r="A144" s="102" t="n"/>
+      <c r="B144" s="100" t="n"/>
+      <c r="C144" s="100" t="n"/>
+      <c r="D144" s="100" t="n"/>
+      <c r="E144" s="100" t="n"/>
+      <c r="F144" s="100" t="n"/>
+      <c r="G144" s="100" t="n"/>
+      <c r="H144" s="100" t="n"/>
+    </row>
+    <row r="145" ht="15" customHeight="1" s="52">
+      <c r="A145" s="102" t="n"/>
+      <c r="B145" s="100" t="n"/>
+      <c r="C145" s="100" t="n"/>
+      <c r="D145" s="100" t="n"/>
+      <c r="E145" s="100" t="n"/>
+      <c r="F145" s="100" t="n"/>
+      <c r="G145" s="100" t="n"/>
+      <c r="H145" s="100" t="n"/>
+    </row>
+    <row r="146" ht="15" customHeight="1" s="52">
+      <c r="A146" s="102" t="n"/>
+      <c r="B146" s="100" t="n"/>
+      <c r="C146" s="100" t="n"/>
+      <c r="D146" s="100" t="n"/>
+      <c r="E146" s="100" t="n"/>
+      <c r="F146" s="100" t="n"/>
+      <c r="G146" s="100" t="n"/>
+      <c r="H146" s="100" t="n"/>
+    </row>
+    <row r="147" ht="15" customHeight="1" s="52">
+      <c r="A147" s="102" t="n"/>
+      <c r="B147" s="100" t="n"/>
+      <c r="C147" s="100" t="n"/>
+      <c r="D147" s="100" t="n"/>
+      <c r="E147" s="100" t="n"/>
+      <c r="F147" s="100" t="n"/>
+      <c r="G147" s="100" t="n"/>
+      <c r="H147" s="100" t="n"/>
+    </row>
+    <row r="148" ht="15" customHeight="1" s="52">
+      <c r="A148" s="102" t="n"/>
+      <c r="B148" s="100" t="n"/>
+      <c r="C148" s="100" t="n"/>
+      <c r="D148" s="100" t="n"/>
+      <c r="E148" s="100" t="n"/>
+      <c r="F148" s="100" t="n"/>
+      <c r="G148" s="100" t="n"/>
+      <c r="H148" s="100" t="n"/>
+    </row>
+    <row r="149" ht="15" customHeight="1" s="52">
+      <c r="A149" s="102" t="n"/>
+      <c r="B149" s="100" t="n"/>
+      <c r="C149" s="100" t="n"/>
+      <c r="D149" s="100" t="n"/>
+      <c r="E149" s="100" t="n"/>
+      <c r="F149" s="100" t="n"/>
+      <c r="G149" s="100" t="n"/>
+      <c r="H149" s="100" t="n"/>
+    </row>
+    <row r="150" ht="15" customHeight="1" s="52">
+      <c r="A150" s="102" t="n"/>
+      <c r="B150" s="100" t="n"/>
+      <c r="C150" s="100" t="n"/>
+      <c r="D150" s="100" t="n"/>
+      <c r="E150" s="100" t="n"/>
+      <c r="F150" s="100" t="n"/>
+      <c r="G150" s="100" t="n"/>
+      <c r="H150" s="100" t="n"/>
+    </row>
+    <row r="151" ht="15" customHeight="1" s="52">
+      <c r="A151" s="102" t="n"/>
+      <c r="B151" s="100" t="n"/>
+      <c r="C151" s="100" t="n"/>
+      <c r="D151" s="100" t="n"/>
+      <c r="E151" s="100" t="n"/>
+      <c r="F151" s="100" t="n"/>
+      <c r="G151" s="100" t="n"/>
+      <c r="H151" s="100" t="n"/>
+    </row>
+    <row r="152" ht="15" customHeight="1" s="52">
+      <c r="A152" s="102" t="n"/>
+      <c r="B152" s="100" t="n"/>
+      <c r="C152" s="100" t="n"/>
+      <c r="D152" s="100" t="n"/>
+      <c r="E152" s="100" t="n"/>
+      <c r="F152" s="100" t="n"/>
+      <c r="G152" s="100" t="n"/>
+      <c r="H152" s="100" t="n"/>
+    </row>
+    <row r="153" ht="15" customHeight="1" s="52">
+      <c r="A153" s="102" t="n"/>
+      <c r="B153" s="100" t="n"/>
+      <c r="C153" s="100" t="n"/>
+      <c r="D153" s="100" t="n"/>
+      <c r="E153" s="100" t="n"/>
+      <c r="F153" s="100" t="n"/>
+      <c r="G153" s="100" t="n"/>
+      <c r="H153" s="100" t="n"/>
+    </row>
+    <row r="154" ht="15" customHeight="1" s="52">
+      <c r="A154" s="102" t="n"/>
+      <c r="B154" s="100" t="n"/>
+      <c r="C154" s="100" t="n"/>
+      <c r="D154" s="100" t="n"/>
+      <c r="E154" s="100" t="n"/>
+      <c r="F154" s="100" t="n"/>
+      <c r="G154" s="100" t="n"/>
+      <c r="H154" s="100" t="n"/>
+    </row>
+    <row r="155" ht="15" customHeight="1" s="52">
+      <c r="A155" s="102" t="n"/>
+      <c r="B155" s="100" t="n"/>
+      <c r="C155" s="100" t="n"/>
+      <c r="D155" s="100" t="n"/>
+      <c r="E155" s="100" t="n"/>
+      <c r="F155" s="100" t="n"/>
+      <c r="G155" s="100" t="n"/>
+      <c r="H155" s="100" t="n"/>
+    </row>
+    <row r="156" ht="15" customHeight="1" s="52">
+      <c r="A156" s="102" t="n"/>
+      <c r="B156" s="100" t="n"/>
+      <c r="C156" s="100" t="n"/>
+      <c r="D156" s="100" t="n"/>
+      <c r="E156" s="100" t="n"/>
+      <c r="F156" s="100" t="n"/>
+      <c r="G156" s="100" t="n"/>
+      <c r="H156" s="100" t="n"/>
+    </row>
+    <row r="157" ht="15" customHeight="1" s="52">
+      <c r="A157" s="102" t="n"/>
+      <c r="B157" s="100" t="n"/>
+      <c r="C157" s="100" t="n"/>
+      <c r="D157" s="100" t="n"/>
+      <c r="E157" s="100" t="n"/>
+      <c r="F157" s="100" t="n"/>
+      <c r="G157" s="100" t="n"/>
+      <c r="H157" s="100" t="n"/>
+    </row>
+    <row r="158" ht="15" customHeight="1" s="52">
+      <c r="A158" s="102" t="n"/>
+      <c r="B158" s="100" t="n"/>
+      <c r="C158" s="100" t="n"/>
+      <c r="D158" s="100" t="n"/>
+      <c r="E158" s="100" t="n"/>
+      <c r="F158" s="100" t="n"/>
+      <c r="G158" s="100" t="n"/>
+      <c r="H158" s="100" t="n"/>
+    </row>
+    <row r="159" ht="15" customHeight="1" s="52">
+      <c r="A159" s="102" t="n"/>
+      <c r="B159" s="100" t="n"/>
+      <c r="C159" s="100" t="n"/>
+      <c r="D159" s="100" t="n"/>
+      <c r="E159" s="100" t="n"/>
+      <c r="F159" s="100" t="n"/>
+      <c r="G159" s="100" t="n"/>
+      <c r="H159" s="100" t="n"/>
+    </row>
+    <row r="160" ht="15" customHeight="1" s="52">
+      <c r="A160" s="102" t="n"/>
+      <c r="B160" s="100" t="n"/>
+      <c r="C160" s="100" t="n"/>
+      <c r="D160" s="100" t="n"/>
+      <c r="E160" s="100" t="n"/>
+      <c r="F160" s="100" t="n"/>
+      <c r="G160" s="100" t="n"/>
+      <c r="H160" s="100" t="n"/>
+    </row>
+    <row r="161" ht="15" customHeight="1" s="52">
+      <c r="A161" s="102" t="n"/>
+      <c r="B161" s="100" t="n"/>
+      <c r="C161" s="100" t="n"/>
+      <c r="D161" s="100" t="n"/>
+      <c r="E161" s="100" t="n"/>
+      <c r="F161" s="100" t="n"/>
+      <c r="G161" s="100" t="n"/>
+      <c r="H161" s="100" t="n"/>
+    </row>
+    <row r="162" ht="15" customHeight="1" s="52">
+      <c r="A162" s="102" t="n"/>
+      <c r="B162" s="100" t="n"/>
+      <c r="C162" s="100" t="n"/>
+      <c r="D162" s="100" t="n"/>
+      <c r="E162" s="100" t="n"/>
+      <c r="F162" s="100" t="n"/>
+      <c r="G162" s="100" t="n"/>
+      <c r="H162" s="100" t="n"/>
+    </row>
+    <row r="163" ht="15" customHeight="1" s="52">
+      <c r="A163" s="102" t="n"/>
+      <c r="B163" s="100" t="n"/>
+      <c r="C163" s="100" t="n"/>
+      <c r="D163" s="100" t="n"/>
+      <c r="E163" s="100" t="n"/>
+      <c r="F163" s="100" t="n"/>
+      <c r="G163" s="100" t="n"/>
+      <c r="H163" s="100" t="n"/>
+    </row>
+    <row r="164" ht="15" customHeight="1" s="52">
+      <c r="A164" s="102" t="n"/>
+      <c r="B164" s="100" t="n"/>
+      <c r="C164" s="100" t="n"/>
+      <c r="D164" s="100" t="n"/>
+      <c r="E164" s="100" t="n"/>
+      <c r="F164" s="100" t="n"/>
+      <c r="G164" s="100" t="n"/>
+      <c r="H164" s="100" t="n"/>
+    </row>
+    <row r="165" ht="15" customHeight="1" s="52">
+      <c r="A165" s="102" t="n"/>
+      <c r="B165" s="100" t="n"/>
+      <c r="C165" s="100" t="n"/>
+      <c r="D165" s="100" t="n"/>
+      <c r="E165" s="100" t="n"/>
+      <c r="F165" s="100" t="n"/>
+      <c r="G165" s="100" t="n"/>
+      <c r="H165" s="100" t="n"/>
+    </row>
+    <row r="166" ht="15" customHeight="1" s="52">
+      <c r="A166" s="102" t="n"/>
+      <c r="B166" s="100" t="n"/>
+      <c r="C166" s="100" t="n"/>
+      <c r="D166" s="100" t="n"/>
+      <c r="E166" s="100" t="n"/>
+      <c r="F166" s="100" t="n"/>
+      <c r="G166" s="100" t="n"/>
+      <c r="H166" s="100" t="n"/>
+    </row>
+    <row r="167" ht="15" customHeight="1" s="52">
+      <c r="A167" s="102" t="n"/>
+      <c r="B167" s="100" t="n"/>
+      <c r="C167" s="100" t="n"/>
+      <c r="D167" s="100" t="n"/>
+      <c r="E167" s="100" t="n"/>
+      <c r="F167" s="100" t="n"/>
+      <c r="G167" s="100" t="n"/>
+      <c r="H167" s="100" t="n"/>
+    </row>
+    <row r="168" ht="15" customHeight="1" s="52">
+      <c r="A168" s="102" t="n"/>
+      <c r="B168" s="100" t="n"/>
+      <c r="C168" s="100" t="n"/>
+      <c r="D168" s="100" t="n"/>
+      <c r="E168" s="100" t="n"/>
+      <c r="F168" s="100" t="n"/>
+      <c r="G168" s="100" t="n"/>
+      <c r="H168" s="100" t="n"/>
+    </row>
+    <row r="169" ht="15" customHeight="1" s="52">
+      <c r="A169" s="102" t="n"/>
+      <c r="B169" s="100" t="n"/>
+      <c r="C169" s="100" t="n"/>
+      <c r="D169" s="100" t="n"/>
+      <c r="E169" s="100" t="n"/>
+      <c r="F169" s="100" t="n"/>
+      <c r="G169" s="100" t="n"/>
+      <c r="H169" s="100" t="n"/>
+    </row>
+    <row r="170" ht="15" customHeight="1" s="52">
+      <c r="A170" s="102" t="n"/>
+      <c r="B170" s="100" t="n"/>
+      <c r="C170" s="100" t="n"/>
+      <c r="D170" s="100" t="n"/>
+      <c r="E170" s="100" t="n"/>
+      <c r="F170" s="100" t="n"/>
+      <c r="G170" s="100" t="n"/>
+      <c r="H170" s="100" t="n"/>
+    </row>
+    <row r="171" ht="15" customHeight="1" s="52">
+      <c r="A171" s="102" t="n"/>
+      <c r="B171" s="100" t="n"/>
+      <c r="C171" s="100" t="n"/>
+      <c r="D171" s="100" t="n"/>
+      <c r="E171" s="100" t="n"/>
+      <c r="F171" s="100" t="n"/>
+      <c r="G171" s="100" t="n"/>
+      <c r="H171" s="100" t="n"/>
+    </row>
+    <row r="172" ht="15" customHeight="1" s="52">
+      <c r="A172" s="102" t="n"/>
+      <c r="B172" s="100" t="n"/>
+      <c r="C172" s="100" t="n"/>
+      <c r="D172" s="100" t="n"/>
+      <c r="E172" s="100" t="n"/>
+      <c r="F172" s="100" t="n"/>
+      <c r="G172" s="100" t="n"/>
+      <c r="H172" s="100" t="n"/>
+    </row>
+    <row r="173" ht="15" customHeight="1" s="52">
+      <c r="A173" s="102" t="n"/>
+      <c r="B173" s="100" t="n"/>
+      <c r="C173" s="100" t="n"/>
+      <c r="D173" s="100" t="n"/>
+      <c r="E173" s="100" t="n"/>
+      <c r="F173" s="100" t="n"/>
+      <c r="G173" s="100" t="n"/>
+      <c r="H173" s="100" t="n"/>
+    </row>
+    <row r="174" ht="15" customHeight="1" s="52">
+      <c r="A174" s="102" t="n"/>
+      <c r="B174" s="100" t="n"/>
+      <c r="C174" s="100" t="n"/>
+      <c r="D174" s="100" t="n"/>
+      <c r="E174" s="100" t="n"/>
+      <c r="F174" s="100" t="n"/>
+      <c r="G174" s="100" t="n"/>
+      <c r="H174" s="100" t="n"/>
+    </row>
+    <row r="175" ht="15" customHeight="1" s="52">
+      <c r="A175" s="102" t="n"/>
+      <c r="B175" s="100" t="n"/>
+      <c r="C175" s="100" t="n"/>
+      <c r="D175" s="100" t="n"/>
+      <c r="E175" s="100" t="n"/>
+      <c r="F175" s="100" t="n"/>
+      <c r="G175" s="100" t="n"/>
+      <c r="H175" s="100" t="n"/>
+    </row>
+    <row r="176" ht="15" customHeight="1" s="52">
+      <c r="A176" s="102" t="n"/>
+      <c r="B176" s="100" t="n"/>
+      <c r="C176" s="100" t="n"/>
+      <c r="D176" s="100" t="n"/>
+      <c r="E176" s="100" t="n"/>
+      <c r="F176" s="100" t="n"/>
+      <c r="G176" s="100" t="n"/>
+      <c r="H176" s="100" t="n"/>
+    </row>
+    <row r="177" ht="15" customHeight="1" s="52">
+      <c r="A177" s="102" t="n"/>
+      <c r="B177" s="100" t="n"/>
+      <c r="C177" s="100" t="n"/>
+      <c r="D177" s="100" t="n"/>
+      <c r="E177" s="100" t="n"/>
+      <c r="F177" s="100" t="n"/>
+      <c r="G177" s="100" t="n"/>
+      <c r="H177" s="100" t="n"/>
+    </row>
+    <row r="178" ht="15" customHeight="1" s="52">
+      <c r="A178" s="102" t="n"/>
+      <c r="B178" s="100" t="n"/>
+      <c r="C178" s="100" t="n"/>
+      <c r="D178" s="100" t="n"/>
+      <c r="E178" s="100" t="n"/>
+      <c r="F178" s="100" t="n"/>
+      <c r="G178" s="100" t="n"/>
+      <c r="H178" s="100" t="n"/>
+    </row>
+    <row r="179" ht="15" customHeight="1" s="52">
+      <c r="A179" s="102" t="n"/>
+      <c r="B179" s="100" t="n"/>
+      <c r="C179" s="100" t="n"/>
+      <c r="D179" s="100" t="n"/>
+      <c r="E179" s="100" t="n"/>
+      <c r="F179" s="100" t="n"/>
+      <c r="G179" s="100" t="n"/>
+      <c r="H179" s="100" t="n"/>
+    </row>
+    <row r="180" ht="15" customHeight="1" s="52">
+      <c r="A180" s="102" t="n"/>
+      <c r="B180" s="100" t="n"/>
+      <c r="C180" s="100" t="n"/>
+      <c r="D180" s="100" t="n"/>
+      <c r="E180" s="100" t="n"/>
+      <c r="F180" s="100" t="n"/>
+      <c r="G180" s="100" t="n"/>
+      <c r="H180" s="100" t="n"/>
+    </row>
+    <row r="181" ht="15" customHeight="1" s="52">
+      <c r="A181" s="102" t="n"/>
+      <c r="B181" s="100" t="n"/>
+      <c r="C181" s="100" t="n"/>
+      <c r="D181" s="100" t="n"/>
+      <c r="E181" s="100" t="n"/>
+      <c r="F181" s="100" t="n"/>
+      <c r="G181" s="100" t="n"/>
+      <c r="H181" s="100" t="n"/>
+    </row>
+    <row r="182" ht="15" customHeight="1" s="52">
+      <c r="A182" s="102" t="n"/>
+      <c r="B182" s="100" t="n"/>
+      <c r="C182" s="100" t="n"/>
+      <c r="D182" s="100" t="n"/>
+      <c r="E182" s="100" t="n"/>
+      <c r="F182" s="100" t="n"/>
+      <c r="G182" s="100" t="n"/>
+      <c r="H182" s="100" t="n"/>
+    </row>
+    <row r="183" ht="15" customHeight="1" s="52">
+      <c r="A183" s="102" t="n"/>
+      <c r="B183" s="100" t="n"/>
+      <c r="C183" s="100" t="n"/>
+      <c r="D183" s="100" t="n"/>
+      <c r="E183" s="100" t="n"/>
+      <c r="F183" s="100" t="n"/>
+      <c r="G183" s="100" t="n"/>
+      <c r="H183" s="100" t="n"/>
+    </row>
+    <row r="184" ht="15" customHeight="1" s="52">
+      <c r="A184" s="102" t="n"/>
+      <c r="B184" s="100" t="n"/>
+      <c r="C184" s="100" t="n"/>
+      <c r="D184" s="100" t="n"/>
+      <c r="E184" s="100" t="n"/>
+      <c r="F184" s="100" t="n"/>
+      <c r="G184" s="100" t="n"/>
+      <c r="H184" s="100" t="n"/>
+    </row>
+    <row r="185" ht="15" customHeight="1" s="52">
+      <c r="A185" s="102" t="n"/>
+      <c r="B185" s="100" t="n"/>
+      <c r="C185" s="100" t="n"/>
+      <c r="D185" s="100" t="n"/>
+      <c r="E185" s="100" t="n"/>
+      <c r="F185" s="100" t="n"/>
+      <c r="G185" s="100" t="n"/>
+      <c r="H185" s="100" t="n"/>
+    </row>
+    <row r="186" ht="15" customHeight="1" s="52">
+      <c r="A186" s="102" t="n"/>
+      <c r="B186" s="100" t="n"/>
+      <c r="C186" s="100" t="n"/>
+      <c r="D186" s="100" t="n"/>
+      <c r="E186" s="100" t="n"/>
+      <c r="F186" s="100" t="n"/>
+      <c r="G186" s="100" t="n"/>
+      <c r="H186" s="100" t="n"/>
+    </row>
+    <row r="187" ht="15" customHeight="1" s="52">
+      <c r="A187" s="102" t="n"/>
+      <c r="B187" s="100" t="n"/>
+      <c r="C187" s="100" t="n"/>
+      <c r="D187" s="100" t="n"/>
+      <c r="E187" s="100" t="n"/>
+      <c r="F187" s="100" t="n"/>
+      <c r="G187" s="100" t="n"/>
+      <c r="H187" s="100" t="n"/>
+    </row>
+    <row r="188" ht="15" customHeight="1" s="52">
+      <c r="A188" s="102" t="n"/>
+      <c r="B188" s="100" t="n"/>
+      <c r="C188" s="100" t="n"/>
+      <c r="D188" s="100" t="n"/>
+      <c r="E188" s="100" t="n"/>
+      <c r="F188" s="100" t="n"/>
+      <c r="G188" s="100" t="n"/>
+      <c r="H188" s="100" t="n"/>
+    </row>
+    <row r="189" ht="15" customHeight="1" s="52">
+      <c r="A189" s="102" t="n"/>
+      <c r="B189" s="100" t="n"/>
+      <c r="C189" s="100" t="n"/>
+      <c r="D189" s="100" t="n"/>
+      <c r="E189" s="100" t="n"/>
+      <c r="F189" s="100" t="n"/>
+      <c r="G189" s="100" t="n"/>
+      <c r="H189" s="100" t="n"/>
+    </row>
+    <row r="190" ht="15" customHeight="1" s="52">
+      <c r="A190" s="102" t="n"/>
+      <c r="B190" s="100" t="n"/>
+      <c r="C190" s="100" t="n"/>
+      <c r="D190" s="100" t="n"/>
+      <c r="E190" s="100" t="n"/>
+      <c r="F190" s="100" t="n"/>
+      <c r="G190" s="100" t="n"/>
+      <c r="H190" s="100" t="n"/>
+    </row>
+    <row r="191" ht="15" customHeight="1" s="52">
+      <c r="A191" s="102" t="n"/>
+      <c r="B191" s="100" t="n"/>
+      <c r="C191" s="100" t="n"/>
+      <c r="D191" s="100" t="n"/>
+      <c r="E191" s="100" t="n"/>
+      <c r="F191" s="100" t="n"/>
+      <c r="G191" s="100" t="n"/>
+      <c r="H191" s="100" t="n"/>
+    </row>
+    <row r="192" ht="15" customHeight="1" s="52">
+      <c r="A192" s="102" t="n"/>
+      <c r="B192" s="100" t="n"/>
+      <c r="C192" s="100" t="n"/>
+      <c r="D192" s="100" t="n"/>
+      <c r="E192" s="100" t="n"/>
+      <c r="F192" s="100" t="n"/>
+      <c r="G192" s="100" t="n"/>
+      <c r="H192" s="100" t="n"/>
+    </row>
+    <row r="193" ht="15" customHeight="1" s="52">
+      <c r="A193" s="102" t="n"/>
+      <c r="B193" s="100" t="n"/>
+      <c r="C193" s="100" t="n"/>
+      <c r="D193" s="100" t="n"/>
+      <c r="E193" s="100" t="n"/>
+      <c r="F193" s="100" t="n"/>
+      <c r="G193" s="100" t="n"/>
+      <c r="H193" s="100" t="n"/>
+    </row>
+    <row r="194" ht="15" customHeight="1" s="52">
+      <c r="A194" s="102" t="n"/>
+      <c r="B194" s="100" t="n"/>
+      <c r="C194" s="100" t="n"/>
+      <c r="D194" s="100" t="n"/>
+      <c r="E194" s="100" t="n"/>
+      <c r="F194" s="100" t="n"/>
+      <c r="G194" s="100" t="n"/>
+      <c r="H194" s="100" t="n"/>
+    </row>
+    <row r="195" ht="15" customHeight="1" s="52">
+      <c r="A195" s="102" t="n"/>
+      <c r="B195" s="100" t="n"/>
+      <c r="C195" s="100" t="n"/>
+      <c r="D195" s="100" t="n"/>
+      <c r="E195" s="100" t="n"/>
+      <c r="F195" s="100" t="n"/>
+      <c r="G195" s="100" t="n"/>
+      <c r="H195" s="100" t="n"/>
+    </row>
+    <row r="196" ht="15" customHeight="1" s="52">
+      <c r="A196" s="102" t="n"/>
+      <c r="B196" s="100" t="n"/>
+      <c r="C196" s="100" t="n"/>
+      <c r="D196" s="100" t="n"/>
+      <c r="E196" s="100" t="n"/>
+      <c r="F196" s="100" t="n"/>
+      <c r="G196" s="100" t="n"/>
+      <c r="H196" s="100" t="n"/>
+    </row>
+    <row r="197" ht="15" customHeight="1" s="52">
+      <c r="A197" s="102" t="n"/>
+      <c r="B197" s="100" t="n"/>
+      <c r="C197" s="100" t="n"/>
+      <c r="D197" s="100" t="n"/>
+      <c r="E197" s="100" t="n"/>
+      <c r="F197" s="100" t="n"/>
+      <c r="G197" s="100" t="n"/>
+      <c r="H197" s="100" t="n"/>
+    </row>
+    <row r="198" ht="15" customHeight="1" s="52">
+      <c r="A198" s="102" t="n"/>
+      <c r="B198" s="100" t="n"/>
+      <c r="C198" s="100" t="n"/>
+      <c r="D198" s="100" t="n"/>
+      <c r="E198" s="100" t="n"/>
+      <c r="F198" s="100" t="n"/>
+      <c r="G198" s="100" t="n"/>
+      <c r="H198" s="100" t="n"/>
+    </row>
+    <row r="199" ht="15" customHeight="1" s="52">
+      <c r="A199" s="102" t="n"/>
+      <c r="B199" s="100" t="n"/>
+      <c r="C199" s="100" t="n"/>
+      <c r="D199" s="100" t="n"/>
+      <c r="E199" s="100" t="n"/>
+      <c r="F199" s="100" t="n"/>
+      <c r="G199" s="100" t="n"/>
+      <c r="H199" s="100" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
     <tabColor rgb="FF90A4AE"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
@@ -1711,6 +3779,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -4646,7 +6715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF90A4AE"/>
@@ -4678,6 +6747,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -5515,7 +7585,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FF90A4AE"/>
@@ -5549,6 +7619,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -5676,7 +7747,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5720,6 +7791,7 @@
       <c r="F2" s="112" t="n"/>
       <c r="G2" s="112" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="113" t="inlineStr">
         <is>
@@ -6122,6 +8194,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="52">
       <c r="B4" s="58" t="inlineStr">
         <is>
@@ -6274,6 +8347,8 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17" ht="15" customHeight="1" s="52">
       <c r="B17" s="58" t="inlineStr">
         <is>
@@ -6584,6 +8659,7 @@
         <v/>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="15" customHeight="1" s="52">
       <c r="B32" s="58" t="inlineStr">
         <is>
@@ -6758,6 +8834,8 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41" ht="15" customHeight="1" s="52">
       <c r="B41" s="58" t="inlineStr">
         <is>
@@ -6836,6 +8914,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="36" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -7198,6 +9277,8 @@
         <v/>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="52">
       <c r="B12" s="58" t="inlineStr">
         <is>
@@ -7378,6 +9459,8 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18" ht="15" customHeight="1" s="52">
       <c r="B18" s="74" t="inlineStr">
         <is>
@@ -7497,6 +9580,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -9687,6 +11771,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -13722,6 +15807,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -19793,6 +21879,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -21613,6 +23700,1465 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFB0BEC5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="52" min="1" max="1"/>
+    <col width="36" customWidth="1" style="52" min="2" max="2"/>
+    <col width="14" customWidth="1" style="52" min="3" max="3"/>
+    <col width="22" customWidth="1" style="52" min="4" max="4"/>
+    <col width="14" customWidth="1" style="52" min="5" max="5"/>
+    <col width="34" customWidth="1" style="52" min="6" max="6"/>
+    <col width="18" customWidth="1" style="52" min="7" max="7"/>
+    <col width="34" customWidth="1" style="52" min="8" max="8"/>
+    <col width="46" customWidth="1" style="52" min="9" max="9"/>
+    <col width="34" customWidth="1" style="52" min="10" max="10"/>
+    <col width="30" customWidth="1" style="52" min="11" max="11"/>
+    <col width="26" customWidth="1" style="52" min="12" max="12"/>
+    <col width="26" customWidth="1" style="52" min="13" max="13"/>
+    <col width="22" customWidth="1" style="52" min="14" max="14"/>
+    <col width="30" customWidth="1" style="52" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.75" customHeight="1" s="52">
+      <c r="A1" s="117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OPPORTUNITY DETAIL  —  BD Posture &amp; Technical Scope  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="21.75" customHeight="1" s="52">
+      <c r="A2" s="118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  One row per Pipeline opportunity, same order. BD posture + technical scope so operations and delivery can plan support. INTERNAL — not published to the leadership site.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1" s="52">
+      <c r="A4" s="119" t="inlineStr">
+        <is>
+          <t>Opp ID</t>
+        </is>
+      </c>
+      <c r="B4" s="119" t="inlineStr">
+        <is>
+          <t>Opportunity Name</t>
+        </is>
+      </c>
+      <c r="C4" s="119" t="inlineStr">
+        <is>
+          <t>BD Posture</t>
+        </is>
+      </c>
+      <c r="D4" s="119" t="inlineStr">
+        <is>
+          <t>Teaming Status</t>
+        </is>
+      </c>
+      <c r="E4" s="119" t="inlineStr">
+        <is>
+          <t>Response Due</t>
+        </is>
+      </c>
+      <c r="F4" s="119" t="inlineStr">
+        <is>
+          <t>Next Milestone</t>
+        </is>
+      </c>
+      <c r="G4" s="119" t="inlineStr">
+        <is>
+          <t>Milestone Owner</t>
+        </is>
+      </c>
+      <c r="H4" s="119" t="inlineStr">
+        <is>
+          <t>Win Theme</t>
+        </is>
+      </c>
+      <c r="I4" s="119" t="inlineStr">
+        <is>
+          <t>Scope Summary</t>
+        </is>
+      </c>
+      <c r="J4" s="119" t="inlineStr">
+        <is>
+          <t>Capabilities Required</t>
+        </is>
+      </c>
+      <c r="K4" s="119" t="inlineStr">
+        <is>
+          <t>Labor Categories</t>
+        </is>
+      </c>
+      <c r="L4" s="119" t="inlineStr">
+        <is>
+          <t>Compliance Gates</t>
+        </is>
+      </c>
+      <c r="M4" s="119" t="inlineStr">
+        <is>
+          <t>Place of Performance</t>
+        </is>
+      </c>
+      <c r="N4" s="119" t="inlineStr">
+        <is>
+          <t>Period of Performance</t>
+        </is>
+      </c>
+      <c r="O4" s="119" t="inlineStr">
+        <is>
+          <t>Staffing Gap</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="115" t="inlineStr">
+        <is>
+          <t>OPP-001</t>
+        </is>
+      </c>
+      <c r="B5" s="115" t="inlineStr">
+        <is>
+          <t>Montana AI Products &amp; Services (SPB-RFP-2026-0608GW) — Tracks 1 &amp; 2</t>
+        </is>
+      </c>
+      <c r="C5" s="115" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+      <c r="D5" s="115" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
+      </c>
+      <c r="E5" s="120" t="n"/>
+      <c r="F5" s="115" t="inlineStr">
+        <is>
+          <t>Execute the DocuSign contract; complete eMACS awarded-vendor registration + insurance filing (10 business days from NOIA)</t>
+        </is>
+      </c>
+      <c r="G5" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H5" s="115" t="n"/>
+      <c r="I5" s="115" t="inlineStr">
+        <is>
+          <t>Statewide AI products and services on Tracks 1 and 2 of the Montana cooperative vehicle. Vehicle executed 8/14/26 (SPB26-0608GW-VSNBLX) and is nationwide-accessible.</t>
+        </is>
+      </c>
+      <c r="J5" s="115" t="inlineStr">
+        <is>
+          <t>AI/ML solution delivery</t>
+        </is>
+      </c>
+      <c r="K5" s="115" t="n"/>
+      <c r="L5" s="115" t="inlineStr">
+        <is>
+          <t>WC + GL insurance ($2M/$2M) — secured; Cyber/Info Security insurance ($6M) — secured; eMACS awarded-vendor registration; SOC 2 Type 2 — decision open, gates Tier Two &gt; $100K</t>
+        </is>
+      </c>
+      <c r="M5" s="115" t="n"/>
+      <c r="N5" s="115" t="n"/>
+      <c r="O5" s="115" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="115" t="inlineStr">
+        <is>
+          <t>OPP-019</t>
+        </is>
+      </c>
+      <c r="B6" s="115" t="inlineStr">
+        <is>
+          <t>USDA Community Connect</t>
+        </is>
+      </c>
+      <c r="C6" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D6" s="115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" s="120" t="n"/>
+      <c r="F6" s="115" t="inlineStr">
+        <is>
+          <t>File the formal no-bid record (DOCX pending)</t>
+        </is>
+      </c>
+      <c r="G6" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H6" s="115" t="n"/>
+      <c r="I6" s="115" t="inlineStr">
+        <is>
+          <t>Broadband infrastructure buildout — outside the VBX healthcare IT lane.</t>
+        </is>
+      </c>
+      <c r="J6" s="115" t="n"/>
+      <c r="K6" s="115" t="n"/>
+      <c r="L6" s="115" t="n"/>
+      <c r="M6" s="115" t="n"/>
+      <c r="N6" s="115" t="n"/>
+      <c r="O6" s="115" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="115" t="inlineStr">
+        <is>
+          <t>OPP-020</t>
+        </is>
+      </c>
+      <c r="B7" s="115" t="inlineStr">
+        <is>
+          <t>HRSA Rural Residency Planning &amp; Development</t>
+        </is>
+      </c>
+      <c r="C7" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D7" s="115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="120" t="n"/>
+      <c r="F7" s="115" t="inlineStr">
+        <is>
+          <t>File the formal no-bid DOCX; track FY26 awardees for downstream EHR/telehealth sub plays</t>
+        </is>
+      </c>
+      <c r="G7" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H7" s="115" t="n"/>
+      <c r="I7" s="115" t="inlineStr">
+        <is>
+          <t>Funds residency programs, not IT vendors — no delivery scope for VBX.</t>
+        </is>
+      </c>
+      <c r="J7" s="115" t="n"/>
+      <c r="K7" s="115" t="n"/>
+      <c r="L7" s="115" t="n"/>
+      <c r="M7" s="115" t="n"/>
+      <c r="N7" s="115" t="n"/>
+      <c r="O7" s="115" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="115" t="inlineStr">
+        <is>
+          <t>OPP-021</t>
+        </is>
+      </c>
+      <c r="B8" s="115" t="inlineStr">
+        <is>
+          <t>VA NEDIIS (36C10B26Q0078)</t>
+        </is>
+      </c>
+      <c r="C8" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D8" s="115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="120" t="n"/>
+      <c r="F8" s="115" t="inlineStr">
+        <is>
+          <t>Watch GSA Alliant 3 SDVOSB pool finalization</t>
+        </is>
+      </c>
+      <c r="G8" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H8" s="115" t="n"/>
+      <c r="I8" s="115" t="inlineStr">
+        <is>
+          <t>VA OIT support services; access gated by the T4NG vehicle, which is closed.</t>
+        </is>
+      </c>
+      <c r="J8" s="115" t="n"/>
+      <c r="K8" s="115" t="n"/>
+      <c r="L8" s="115" t="inlineStr">
+        <is>
+          <t>150-FTE past-performance floor</t>
+        </is>
+      </c>
+      <c r="M8" s="115" t="n"/>
+      <c r="N8" s="115" t="n"/>
+      <c r="O8" s="115" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="115" t="inlineStr">
+        <is>
+          <t>OPP-022</t>
+        </is>
+      </c>
+      <c r="B9" s="115" t="inlineStr">
+        <is>
+          <t>SENTRY (CB26-RFQ0012) — CBO IT Support BPA, SMA 2 Cloud Service Support (J4 + J5)</t>
+        </is>
+      </c>
+      <c r="C9" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D9" s="115" t="inlineStr">
+        <is>
+          <t>Teaming declined</t>
+        </is>
+      </c>
+      <c r="E9" s="120" t="n">
+        <v>46244</v>
+      </c>
+      <c r="F9" s="115" t="inlineStr">
+        <is>
+          <t>Redirect the prime relationship to smaller set-aside RFQs/RFPs by 8/31</t>
+        </is>
+      </c>
+      <c r="G9" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H9" s="115" t="n"/>
+      <c r="I9" s="115" t="inlineStr">
+        <is>
+          <t>Cloud service support (J4 + J5) under Service Management Area 2 of the CBO IT Support BPA.</t>
+        </is>
+      </c>
+      <c r="J9" s="115" t="inlineStr">
+        <is>
+          <t>Cloud service support</t>
+        </is>
+      </c>
+      <c r="K9" s="115" t="n"/>
+      <c r="L9" s="115" t="n"/>
+      <c r="M9" s="115" t="n"/>
+      <c r="N9" s="115" t="inlineStr">
+        <is>
+          <t>5-year BPA</t>
+        </is>
+      </c>
+      <c r="O9" s="115" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="115" t="inlineStr">
+        <is>
+          <t>OPP-023</t>
+        </is>
+      </c>
+      <c r="B10" s="115" t="inlineStr">
+        <is>
+          <t>IHS WebEHRS 2027-2032 (SS75H70126R00050) — RFI Response</t>
+        </is>
+      </c>
+      <c r="C10" s="115" t="inlineStr">
+        <is>
+          <t>Sub</t>
+        </is>
+      </c>
+      <c r="D10" s="115" t="inlineStr">
+        <is>
+          <t>Partner needed</t>
+        </is>
+      </c>
+      <c r="E10" s="120" t="n"/>
+      <c r="F10" s="115" t="inlineStr">
+        <is>
+          <t>Provide a services-only ROM once the platform baseline and teaming are defined</t>
+        </is>
+      </c>
+      <c r="G10" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H10" s="115" t="inlineStr">
+        <is>
+          <t>Integration and custom-build teammate to a platform vendor — services depth with no COTS product conflict.</t>
+        </is>
+      </c>
+      <c r="I10" s="115" t="inlineStr">
+        <is>
+          <t>Custom RRM engine and historical reporting for the IHS Web-based Environmental Health Reporting System, with IHS Standard Code Book integration, FDA 2022 Food Code Annex 7 Form 3a e-inspection forms (web + offline), legacy migration and UAT, and help-desk/O&amp;M. Services-only — VBX is the integration teammate, not the platform vendor.</t>
+        </is>
+      </c>
+      <c r="J10" s="115" t="inlineStr">
+        <is>
+          <t>Custom RRM engine + historical reporting; IHS Standard Code Book integration; Offline-capable web inspection forms; Legacy data migration + UAT; Standards-based APIs / data export; Help desk + O&amp;M</t>
+        </is>
+      </c>
+      <c r="K10" s="115" t="n"/>
+      <c r="L10" s="115" t="inlineStr">
+        <is>
+          <t>ATO; FedRAMP; SSO / MFA / PIV; RBAC + audit logging; TAA; Section 889</t>
+        </is>
+      </c>
+      <c r="M10" s="115" t="n"/>
+      <c r="N10" s="115" t="inlineStr">
+        <is>
+          <t>2027–2032</t>
+        </is>
+      </c>
+      <c r="O10" s="115" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="115" t="inlineStr">
+        <is>
+          <t>OPP-024</t>
+        </is>
+      </c>
+      <c r="B11" s="115" t="inlineStr">
+        <is>
+          <t>WA HCA FSIPAP (RFI 2026HCA13) — Federal &amp; State Interoperability and Prior Authorization Project</t>
+        </is>
+      </c>
+      <c r="C11" s="115" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+      <c r="D11" s="115" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
+      </c>
+      <c r="E11" s="120" t="n">
+        <v>46260</v>
+      </c>
+      <c r="F11" s="115" t="inlineStr">
+        <is>
+          <t>Work open next steps #14–19 on the Actions tab; re-score at RFP release (expected Q4 2026 / Q1 2027)</t>
+        </is>
+      </c>
+      <c r="G11" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H11" s="115" t="inlineStr">
+        <is>
+          <t>Posture B, PA-workflow-complete (CRD + DTR approach + PAS) leading with policy transformation as the discriminator.</t>
+        </is>
+      </c>
+      <c r="I11" s="115" t="inlineStr">
+        <is>
+          <t>FHIR-native prior-authorization interoperability for Medicaid/CHIP fee-for-service under CMS-0057-F: CRD, a DTR approach, and PAS workflow, plus transformation of roughly 760 prior-authorization policies (largest guide 338pp / 153 PA policies) into executable rules. Vendor-hosted cloud-native; the incumbent integrator builds the FHIR adjudication endpoints at no cost. FHIR-native throughout — no X12 278.</t>
+        </is>
+      </c>
+      <c r="J11" s="115" t="inlineStr">
+        <is>
+          <t>FHIR — Da Vinci CRD + PAS; DTR approach; Prior-authorization policy transformation; Cloud-native vendor-hosted delivery; Data engineering</t>
+        </is>
+      </c>
+      <c r="K11" s="115" t="inlineStr">
+        <is>
+          <t>Principal Architect; Sr. Solution Architect — policy transformation; Data Engineer; CISO</t>
+        </is>
+      </c>
+      <c r="L11" s="115" t="inlineStr">
+        <is>
+          <t>SOC 2 — not hard-mandated (Q&amp;A #42); Cyber liability — up to $10M may be required for high-risk data vs $6M held; Possible minimum-revenue rule (Q&amp;A #73) — unresolved</t>
+        </is>
+      </c>
+      <c r="M11" s="115" t="inlineStr">
+        <is>
+          <t>Washington State (SLED); vendor-hosted cloud</t>
+        </is>
+      </c>
+      <c r="N11" s="115" t="inlineStr">
+        <is>
+          <t>Vendor onboard ~Q1 2027; full compliance 01/01/2028</t>
+        </is>
+      </c>
+      <c r="O11" s="115" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="115" t="inlineStr">
+        <is>
+          <t>OPP-025</t>
+        </is>
+      </c>
+      <c r="B12" s="115" t="inlineStr">
+        <is>
+          <t>WA DRS E-File Tax Reporting (RFP 26-03)</t>
+        </is>
+      </c>
+      <c r="C12" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D12" s="115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="120" t="n"/>
+      <c r="F12" s="115" t="inlineStr">
+        <is>
+          <t>None — Gate 1 fail recorded 7/10/26</t>
+        </is>
+      </c>
+      <c r="G12" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H12" s="115" t="n"/>
+      <c r="I12" s="115" t="inlineStr">
+        <is>
+          <t>Read-only e-file transmission of tax reporting data — no meaningful build or ETL scope, LPTA in substance.</t>
+        </is>
+      </c>
+      <c r="J12" s="115" t="n"/>
+      <c r="K12" s="115" t="n"/>
+      <c r="L12" s="115" t="inlineStr">
+        <is>
+          <t>IRS-authorized e-file transmission provider with a 5-year production track record; IRS Pub 1075 FTI regime; SOC 2; Heavy insurance minimums</t>
+        </is>
+      </c>
+      <c r="M12" s="115" t="n"/>
+      <c r="N12" s="115" t="n"/>
+      <c r="O12" s="115" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="115" t="inlineStr">
+        <is>
+          <t>OPP-026</t>
+        </is>
+      </c>
+      <c r="B13" s="115" t="inlineStr">
+        <is>
+          <t>Army Enterprise IT Support — OTSG/MEDCOM (W9124J-27-R-ENTR)</t>
+        </is>
+      </c>
+      <c r="C13" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D13" s="115" t="inlineStr">
+        <is>
+          <t>Teaming declined</t>
+        </is>
+      </c>
+      <c r="E13" s="120" t="n"/>
+      <c r="F13" s="115" t="inlineStr">
+        <is>
+          <t>Redirect to fit-lane federal health IT (VA OIT, HHS, CMS)</t>
+        </is>
+      </c>
+      <c r="G13" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H13" s="115" t="n"/>
+      <c r="I13" s="115" t="inlineStr">
+        <is>
+          <t>Pure O&amp;M help-desk support under NAICS 541513 with contractor AI explicitly excluded (Q&amp;A #62). The OTSG/MEDCOM label carries no health-IT delivery scope.</t>
+        </is>
+      </c>
+      <c r="J13" s="115" t="n"/>
+      <c r="K13" s="115" t="n"/>
+      <c r="L13" s="115" t="inlineStr">
+        <is>
+          <t>Secret facility clearance + cleared bench at submission, subs included; CMMI-SVC Level 3</t>
+        </is>
+      </c>
+      <c r="M13" s="115" t="n"/>
+      <c r="N13" s="115" t="inlineStr">
+        <is>
+          <t>~5 years (~$9M est.)</t>
+        </is>
+      </c>
+      <c r="O13" s="115" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="115" t="inlineStr">
+        <is>
+          <t>OPP-027</t>
+        </is>
+      </c>
+      <c r="B14" s="115" t="inlineStr">
+        <is>
+          <t>DoS BASE — Boundaries &amp; Sovereignty Encyclopedia (19AQMM26N0296)</t>
+        </is>
+      </c>
+      <c r="C14" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D14" s="115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" s="120" t="n">
+        <v>46225</v>
+      </c>
+      <c r="F14" s="115" t="inlineStr">
+        <is>
+          <t>None — collapsed to a straight no-bid</t>
+        </is>
+      </c>
+      <c r="G14" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H14" s="115" t="n"/>
+      <c r="I14" s="115" t="inlineStr">
+        <is>
+          <t>Boundaries and sovereignty encyclopedia — a geospatial content system. The conditional narrow-sub lane would have been portal O&amp;M, OCR-ETL, and secure hosting under a geospatial prime.</t>
+        </is>
+      </c>
+      <c r="J14" s="115" t="inlineStr">
+        <is>
+          <t>Geospatial / GIS; OCR-ETL; Portal O&amp;M; Secure hosting</t>
+        </is>
+      </c>
+      <c r="K14" s="115" t="n"/>
+      <c r="L14" s="115" t="n"/>
+      <c r="M14" s="115" t="n"/>
+      <c r="N14" s="115" t="n"/>
+      <c r="O14" s="115" t="inlineStr">
+        <is>
+          <t>Geospatial/GIS depth, boundary-domain past performance, and IC-grade hosting are not held; no geospatial prime surfaced before the ~7/15 window closed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="115" t="inlineStr">
+        <is>
+          <t>OPP-028</t>
+        </is>
+      </c>
+      <c r="B15" s="115" t="inlineStr">
+        <is>
+          <t>MARFORRES AI Manpower &amp; Readiness (M6786126IMKMAI) — Sources Sought Response</t>
+        </is>
+      </c>
+      <c r="C15" s="115" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+      <c r="D15" s="115" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
+      </c>
+      <c r="E15" s="120" t="n">
+        <v>46233</v>
+      </c>
+      <c r="F15" s="115" t="inlineStr">
+        <is>
+          <t>Monitor for the follow-on RFP</t>
+        </is>
+      </c>
+      <c r="G15" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H15" s="115" t="n"/>
+      <c r="I15" s="115" t="inlineStr">
+        <is>
+          <t>AI-enabled manpower modeling, readiness analytics, and personnel allocation across the Individual Ready Reserve and Selected Marine Corps Reserve.</t>
+        </is>
+      </c>
+      <c r="J15" s="115" t="inlineStr">
+        <is>
+          <t>AI/ML modeling; Readiness analytics; Personnel data integration</t>
+        </is>
+      </c>
+      <c r="K15" s="115" t="n"/>
+      <c r="L15" s="115" t="inlineStr">
+        <is>
+          <t>CUI handling — CUI notice on the solicitation</t>
+        </is>
+      </c>
+      <c r="M15" s="115" t="n"/>
+      <c r="N15" s="115" t="n"/>
+      <c r="O15" s="115" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="115" t="inlineStr">
+        <is>
+          <t>OPP-029</t>
+        </is>
+      </c>
+      <c r="B16" s="115" t="inlineStr">
+        <is>
+          <t>DHA ARMOR — Integrated Workforce &amp; Readiness Platform (ARMOR001) — RFI Response</t>
+        </is>
+      </c>
+      <c r="C16" s="115" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+      <c r="D16" s="115" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
+      </c>
+      <c r="E16" s="120" t="n">
+        <v>46225</v>
+      </c>
+      <c r="F16" s="115" t="inlineStr">
+        <is>
+          <t>Run the scoring engine on the anticipated RFP — pipeline priority</t>
+        </is>
+      </c>
+      <c r="G16" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H16" s="115" t="inlineStr">
+        <is>
+          <t>Tier 1 fit — healthcare IT with EHR-integration and explainable-AI depth.</t>
+        </is>
+      </c>
+      <c r="I16" s="115" t="inlineStr">
+        <is>
+          <t>Integrated workforce and readiness platform for DHA. All five RFI use cases addressed (all-or-nothing per §3.1), centred on MHS GENESIS / EHR integration and explainable AI.</t>
+        </is>
+      </c>
+      <c r="J16" s="115" t="inlineStr">
+        <is>
+          <t>MHS GENESIS / EHR integration; Explainable AI; Workforce + readiness analytics</t>
+        </is>
+      </c>
+      <c r="K16" s="115" t="n"/>
+      <c r="L16" s="115" t="inlineStr">
+        <is>
+          <t>§3.5 OCI access — granted</t>
+        </is>
+      </c>
+      <c r="M16" s="115" t="n"/>
+      <c r="N16" s="115" t="n"/>
+      <c r="O16" s="115" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="115" t="inlineStr">
+        <is>
+          <t>OPP-030</t>
+        </is>
+      </c>
+      <c r="B17" s="115" t="inlineStr">
+        <is>
+          <t>USGS NEIC AI/ML &amp; Data Streaming Development (140G0226Q0049) — Sources Sought Response</t>
+        </is>
+      </c>
+      <c r="C17" s="115" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+      <c r="D17" s="115" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
+      </c>
+      <c r="E17" s="120" t="n">
+        <v>46227</v>
+      </c>
+      <c r="F17" s="115" t="inlineStr">
+        <is>
+          <t>Score via the capture engine before any RFP-stage spend</t>
+        </is>
+      </c>
+      <c r="G17" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H17" s="115" t="inlineStr">
+        <is>
+          <t>Candor positioning — transferable production AI and data engineering, with no seismology claims made.</t>
+        </is>
+      </c>
+      <c r="I17" s="115" t="inlineStr">
+        <is>
+          <t>Real-time seismic data streaming and event detection for the National Earthquake Information Center, across five software-development task areas.</t>
+        </is>
+      </c>
+      <c r="J17" s="115" t="inlineStr">
+        <is>
+          <t>Real-time data streaming; AI/ML detection; Production data engineering; Software development</t>
+        </is>
+      </c>
+      <c r="K17" s="115" t="n"/>
+      <c r="L17" s="115" t="n"/>
+      <c r="M17" s="115" t="n"/>
+      <c r="N17" s="115" t="n"/>
+      <c r="O17" s="115" t="inlineStr">
+        <is>
+          <t>No seismology domain depth on the bench — deliberately not claimed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="115" t="inlineStr">
+        <is>
+          <t>OPP-031</t>
+        </is>
+      </c>
+      <c r="B18" s="115" t="inlineStr">
+        <is>
+          <t>CMS ICAT RFI (270196) — HHS-RADV Intelligent Coding Assistance Tool</t>
+        </is>
+      </c>
+      <c r="C18" s="115" t="inlineStr">
+        <is>
+          <t>Sub</t>
+        </is>
+      </c>
+      <c r="D18" s="115" t="inlineStr">
+        <is>
+          <t>NDA executed</t>
+        </is>
+      </c>
+      <c r="E18" s="120" t="n">
+        <v>46254</v>
+      </c>
+      <c r="F18" s="115" t="inlineStr">
+        <is>
+          <t>Monitor CMS for ICAT disposition or a follow-on RFP (re-check 9/19)</t>
+        </is>
+      </c>
+      <c r="G18" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H18" s="115" t="inlineStr">
+        <is>
+          <t>A conflict-free team against a structurally conflicted incumbent.</t>
+        </is>
+      </c>
+      <c r="I18" s="115" t="inlineStr">
+        <is>
+          <t>Intelligent coding assistance for HHS-RADV risk-adjustment data validation. VBX delivers as a subcontractor on a three-party team; per-question limit 3,000 characters.</t>
+        </is>
+      </c>
+      <c r="J18" s="115" t="inlineStr">
+        <is>
+          <t>Medical coding automation; Risk-adjustment data validation</t>
+        </is>
+      </c>
+      <c r="K18" s="115" t="n"/>
+      <c r="L18" s="115" t="inlineStr">
+        <is>
+          <t>Team-wide COI attestations — all three executed; NDA — executed 8/16</t>
+        </is>
+      </c>
+      <c r="M18" s="115" t="n"/>
+      <c r="N18" s="115" t="n"/>
+      <c r="O18" s="115" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="115" t="inlineStr">
+        <is>
+          <t>OPP-032</t>
+        </is>
+      </c>
+      <c r="B19" s="115" t="inlineStr">
+        <is>
+          <t>NIST QNAP (RFQ1816699 / NB676020-26-01781) — quantum sub posture</t>
+        </is>
+      </c>
+      <c r="C19" s="115" t="inlineStr">
+        <is>
+          <t>Sub</t>
+        </is>
+      </c>
+      <c r="D19" s="115" t="inlineStr">
+        <is>
+          <t>Partner identified</t>
+        </is>
+      </c>
+      <c r="E19" s="120" t="n"/>
+      <c r="F19" s="115" t="inlineStr">
+        <is>
+          <t>Maintain the workshare dialogue; no action until the award notice</t>
+        </is>
+      </c>
+      <c r="G19" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H19" s="115" t="n"/>
+      <c r="I19" s="115" t="inlineStr">
+        <is>
+          <t>Quantum technical support delivered as workshare under a prime's pending award. Solicitation closed 7/1/26 — capture framing is moot; the live conversation is delivery workshare only.</t>
+        </is>
+      </c>
+      <c r="J19" s="115" t="n"/>
+      <c r="K19" s="115" t="inlineStr">
+        <is>
+          <t>Quantum physicist (PhD) — key personnel</t>
+        </is>
+      </c>
+      <c r="L19" s="115" t="n"/>
+      <c r="M19" s="115" t="n"/>
+      <c r="N19" s="115" t="n"/>
+      <c r="O19" s="115" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="115" t="inlineStr">
+        <is>
+          <t>OPP-033</t>
+        </is>
+      </c>
+      <c r="B20" s="115" t="inlineStr">
+        <is>
+          <t>WA DES 13225 — CAT Tool Contracts</t>
+        </is>
+      </c>
+      <c r="C20" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D20" s="115" t="inlineStr">
+        <is>
+          <t>Teaming declined</t>
+        </is>
+      </c>
+      <c r="E20" s="120" t="n"/>
+      <c r="F20" s="115" t="inlineStr">
+        <is>
+          <t>None — WA purchaser intel folded into the FSIPAP account map</t>
+        </is>
+      </c>
+      <c r="G20" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H20" s="115" t="n"/>
+      <c r="I20" s="115" t="inlineStr">
+        <is>
+          <t>Proprietary SaaS computer-assisted-translation product with a mandatory live product demo and ~76% of points on license pricing — a product buy, not integration work.</t>
+        </is>
+      </c>
+      <c r="J20" s="115" t="n"/>
+      <c r="K20" s="115" t="n"/>
+      <c r="L20" s="115" t="inlineStr">
+        <is>
+          <t>WA Small Business / VOSB reserved-lane status — not held</t>
+        </is>
+      </c>
+      <c r="M20" s="115" t="n"/>
+      <c r="N20" s="115" t="n"/>
+      <c r="O20" s="115" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="115" t="inlineStr">
+        <is>
+          <t>OPP-034</t>
+        </is>
+      </c>
+      <c r="B21" s="115" t="inlineStr">
+        <is>
+          <t>VA Digital GI Bill RFI (36C10D26Q0186)</t>
+        </is>
+      </c>
+      <c r="C21" s="115" t="inlineStr">
+        <is>
+          <t>Sub</t>
+        </is>
+      </c>
+      <c r="D21" s="115" t="inlineStr">
+        <is>
+          <t>In discussion</t>
+        </is>
+      </c>
+      <c r="E21" s="120" t="n">
+        <v>46276</v>
+      </c>
+      <c r="F21" s="115" t="inlineStr">
+        <is>
+          <t>Tech input to the prime by 9/4; RFI due 9/11/26 10:00 ET</t>
+        </is>
+      </c>
+      <c r="G21" s="115" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="H21" s="115" t="n"/>
+      <c r="I21" s="115" t="inlineStr">
+        <is>
+          <t>VA benefits-system modernization at RFI stage. VBX sits in a subcontractor lane through a partner channel.</t>
+        </is>
+      </c>
+      <c r="J21" s="115" t="n"/>
+      <c r="K21" s="115" t="n"/>
+      <c r="L21" s="115" t="n"/>
+      <c r="M21" s="115" t="n"/>
+      <c r="N21" s="115" t="n"/>
+      <c r="O21" s="115" t="inlineStr">
+        <is>
+          <t>Citable past performance is $0 until a workshare floor and reference rights are negotiated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="115" t="inlineStr">
+        <is>
+          <t>OPP-035</t>
+        </is>
+      </c>
+      <c r="B22" s="115" t="inlineStr">
+        <is>
+          <t>VA PATS-R (36C10B26Q0662) — Patient Advocate Tracking System-Replacement</t>
+        </is>
+      </c>
+      <c r="C22" s="115" t="inlineStr">
+        <is>
+          <t>Sub</t>
+        </is>
+      </c>
+      <c r="D22" s="115" t="inlineStr">
+        <is>
+          <t>In discussion</t>
+        </is>
+      </c>
+      <c r="E22" s="120" t="n"/>
+      <c r="F22" s="115" t="inlineStr">
+        <is>
+          <t>SAM alert set; re-score at strategy release</t>
+        </is>
+      </c>
+      <c r="G22" s="115" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="H22" s="115" t="n"/>
+      <c r="I22" s="115" t="inlineStr">
+        <is>
+          <t>Replacement of the VA Patient Advocate Tracking System. Same Gate 0 → NDA → teaming pre-conditions as the Digital GI Bill row.</t>
+        </is>
+      </c>
+      <c r="J22" s="115" t="n"/>
+      <c r="K22" s="115" t="n"/>
+      <c r="L22" s="115" t="n"/>
+      <c r="M22" s="115" t="n"/>
+      <c r="N22" s="115" t="n"/>
+      <c r="O22" s="115" t="inlineStr">
+        <is>
+          <t>Citable past performance is $0 until a workshare floor and reference rights are negotiated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="115" t="inlineStr">
+        <is>
+          <t>OPP-036</t>
+        </is>
+      </c>
+      <c r="B23" s="115" t="inlineStr">
+        <is>
+          <t>CDC KMTSS (SSN26-7571-CDC96901) — Knowledge Mgmt Technical Support Services</t>
+        </is>
+      </c>
+      <c r="C23" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D23" s="115" t="inlineStr">
+        <is>
+          <t>Partner needed</t>
+        </is>
+      </c>
+      <c r="E23" s="120" t="n"/>
+      <c r="F23" s="115" t="inlineStr">
+        <is>
+          <t>Closed unless an ECM anchor is fielded</t>
+        </is>
+      </c>
+      <c r="G23" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H23" s="115" t="n"/>
+      <c r="I23" s="115" t="inlineStr">
+        <is>
+          <t>Knowledge-management technical support. Viable only as a niche sub behind an enterprise content management anchor.</t>
+        </is>
+      </c>
+      <c r="J23" s="115" t="inlineStr">
+        <is>
+          <t>Enterprise content management (ECM); Knowledge management</t>
+        </is>
+      </c>
+      <c r="K23" s="115" t="n"/>
+      <c r="L23" s="115" t="n"/>
+      <c r="M23" s="115" t="n"/>
+      <c r="N23" s="115" t="n"/>
+      <c r="O23" s="115" t="inlineStr">
+        <is>
+          <t>No ECM anchor — the pursuit reopens only if the partner channel fields one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="115" t="inlineStr">
+        <is>
+          <t>OPP-037</t>
+        </is>
+      </c>
+      <c r="B24" s="115" t="inlineStr">
+        <is>
+          <t>VA BioDose 23.x</t>
+        </is>
+      </c>
+      <c r="C24" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D24" s="115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E24" s="120" t="n"/>
+      <c r="F24" s="115" t="inlineStr">
+        <is>
+          <t>None — declined at Gate 1 with a Digital GI Bill redirect</t>
+        </is>
+      </c>
+      <c r="G24" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H24" s="115" t="n"/>
+      <c r="I24" s="115" t="n"/>
+      <c r="J24" s="115" t="n"/>
+      <c r="K24" s="115" t="n"/>
+      <c r="L24" s="115" t="n"/>
+      <c r="M24" s="115" t="n"/>
+      <c r="N24" s="115" t="n"/>
+      <c r="O24" s="115" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="115" t="inlineStr">
+        <is>
+          <t>OPP-038</t>
+        </is>
+      </c>
+      <c r="B25" s="115" t="inlineStr">
+        <is>
+          <t>SSA Enterprise Artificial Intelligence (AI) Strategy (28321326RI0000041) - RFI, market research only</t>
+        </is>
+      </c>
+      <c r="C25" s="115" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+      <c r="D25" s="115" t="inlineStr">
+        <is>
+          <t>Solo</t>
+        </is>
+      </c>
+      <c r="E25" s="120" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F25" s="115" t="inlineStr">
+        <is>
+          <t>File the response as a reusable agency-AI-RFI template (target 9/29)</t>
+        </is>
+      </c>
+      <c r="G25" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H25" s="115" t="n"/>
+      <c r="I25" s="115" t="inlineStr">
+        <is>
+          <t>Enterprise AI strategy market research for the SSA Office of the CIO — a 6-page RFI response on enterprise AI architecture and adoption. Market research only; no award.</t>
+        </is>
+      </c>
+      <c r="J25" s="115" t="n"/>
+      <c r="K25" s="115" t="n"/>
+      <c r="L25" s="115" t="inlineStr">
+        <is>
+          <t>SSA may publish responses — treat the submission as public</t>
+        </is>
+      </c>
+      <c r="M25" s="115" t="n"/>
+      <c r="N25" s="115" t="n"/>
+      <c r="O25" s="115" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="115" t="inlineStr">
+        <is>
+          <t>OPP-039</t>
+        </is>
+      </c>
+      <c r="B26" s="115" t="inlineStr">
+        <is>
+          <t>AI Technologies for Procurement Modernization (CSO General Solicitation)</t>
+        </is>
+      </c>
+      <c r="C26" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D26" s="115" t="inlineStr">
+        <is>
+          <t>Teaming declined</t>
+        </is>
+      </c>
+      <c r="E26" s="120" t="n"/>
+      <c r="F26" s="115" t="inlineStr">
+        <is>
+          <t>Re-check the SAM notice monthly through 9/10/26 for a services-scoped topic call</t>
+        </is>
+      </c>
+      <c r="G26" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H26" s="115" t="n"/>
+      <c r="I26" s="115" t="inlineStr">
+        <is>
+          <t>Commercial-item buy of a production-ready acquisition-technology product for a centralized OCPO tool portfolio — a product purchase, not integration services.</t>
+        </is>
+      </c>
+      <c r="J26" s="115" t="n"/>
+      <c r="K26" s="115" t="n"/>
+      <c r="L26" s="115" t="n"/>
+      <c r="M26" s="115" t="inlineStr">
+        <is>
+          <t>Springfield, VA</t>
+        </is>
+      </c>
+      <c r="N26" s="115" t="n"/>
+      <c r="O26" s="115" t="inlineStr">
+        <is>
+          <t>No federal acquisition-domain past-performance analog and no productized tool to demonstrate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="115" t="inlineStr">
+        <is>
+          <t>OPP-040</t>
+        </is>
+      </c>
+      <c r="B27" s="115" t="inlineStr">
+        <is>
+          <t>DoWEA/DoDEA Data, Analytics &amp; AI Modernization (HE125426RE037)</t>
+        </is>
+      </c>
+      <c r="C27" s="115" t="inlineStr">
+        <is>
+          <t>Undecided</t>
+        </is>
+      </c>
+      <c r="D27" s="115" t="n"/>
+      <c r="E27" s="120" t="n"/>
+      <c r="F27" s="115" t="inlineStr">
+        <is>
+          <t>Re-check 9/15/26 for re-issue; monitor HE125426RE037 and sources-sought DoWEA-PSN-26-002</t>
+        </is>
+      </c>
+      <c r="G27" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H27" s="115" t="n"/>
+      <c r="I27" s="115" t="inlineStr">
+        <is>
+          <t>Single-award FFP IDIQ for data, analytics, and AI modernization. Task Order 1 'Foundational Services' is CUI//SP-SSEL and runs concurrent with award at roughly 396 person-months/year (about 33 FTE).</t>
+        </is>
+      </c>
+      <c r="J27" s="115" t="inlineStr">
+        <is>
+          <t>Data engineering + analytics; AI/ML modernization; Ed-Fi / K-12 data standards; Microsoft Fabric</t>
+        </is>
+      </c>
+      <c r="K27" s="115" t="n"/>
+      <c r="L27" s="115" t="inlineStr">
+        <is>
+          <t>CMMC — DFARS 7021 Level 1 vs PWS 3.8 CUI Level 2 conflict UNRESOLVED; CUI//SP-SSEL handling</t>
+        </is>
+      </c>
+      <c r="M27" s="115" t="n"/>
+      <c r="N27" s="115" t="inlineStr">
+        <is>
+          <t>Base + 4 option years + 6 months</t>
+        </is>
+      </c>
+      <c r="O27" s="115" t="inlineStr">
+        <is>
+          <t>About 33 FTE required against a 3-person bench already committed to Montana; no DoD, K-12, Ed-Fi, or Fabric past performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="115" t="inlineStr">
+        <is>
+          <t>OPP-041</t>
+        </is>
+      </c>
+      <c r="B28" s="115" t="inlineStr">
+        <is>
+          <t>AI-Powered Pre-Plan Check (AIP-PPC) Assistant (RAMP 222114 / RFP 2025AIP007)</t>
+        </is>
+      </c>
+      <c r="C28" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D28" s="115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E28" s="120" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F28" s="115" t="inlineStr">
+        <is>
+          <t>Review 10/15/26 — reopens only if reissued as integration/implementation services</t>
+        </is>
+      </c>
+      <c r="G28" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H28" s="115" t="n"/>
+      <c r="I28" s="115" t="inlineStr">
+        <is>
+          <t>AI-powered pre-plan-check assistant for building-permit plan review — a vendor-hosted product buy with an embedded zero-cost incumbent.</t>
+        </is>
+      </c>
+      <c r="J28" s="115" t="n"/>
+      <c r="K28" s="115" t="n"/>
+      <c r="L28" s="115" t="n"/>
+      <c r="M28" s="115" t="n"/>
+      <c r="N28" s="115" t="n"/>
+      <c r="O28" s="115" t="inlineStr">
+        <is>
+          <t>No plan-review or building-code past performance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="115" t="inlineStr">
+        <is>
+          <t>OPP-042</t>
+        </is>
+      </c>
+      <c r="B29" s="115" t="inlineStr">
+        <is>
+          <t>Region 4 ESC RFP 26-14 — Artificial Intelligence and Total Cloud Solutions</t>
+        </is>
+      </c>
+      <c r="C29" s="115" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="D29" s="115" t="inlineStr">
+        <is>
+          <t>Partner needed</t>
+        </is>
+      </c>
+      <c r="E29" s="120" t="n">
+        <v>46273</v>
+      </c>
+      <c r="F29" s="115" t="inlineStr">
+        <is>
+          <t>Pull the 26-14 award list at board publication (target 12/15/26) and screen awardees for authorized-partner admission</t>
+        </is>
+      </c>
+      <c r="G29" s="115" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="H29" s="115" t="n"/>
+      <c r="I29" s="115" t="inlineStr">
+        <is>
+          <t>Cooperative catalog / price-list vehicle for AI and cloud solutions — a catalog buy requiring manufacturer LOAs and distribution margin. The EV-positive path is authorized-partner admission under an awardee, at zero B&amp;P and no admin-fee exposure.</t>
+        </is>
+      </c>
+      <c r="J29" s="115" t="n"/>
+      <c r="K29" s="115" t="n"/>
+      <c r="L29" s="115" t="inlineStr">
+        <is>
+          <t>SOC 2 Type 2 — absent, not remediable by 9/8/26; FedRAMP / StateRAMP — not held; K-12 student privacy (NY Ed Law 2-d, CA SOPIPA) — posture unestablished</t>
+        </is>
+      </c>
+      <c r="M29" s="115" t="n"/>
+      <c r="N29" s="115" t="inlineStr">
+        <is>
+          <t>3 base + 2 option years</t>
+        </is>
+      </c>
+      <c r="O29" s="115" t="inlineStr">
+        <is>
+          <t>No catalog, manufacturer LOAs, distribution margin, or national sales force.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <tabColor rgb="FFB0BEC5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21644,6 +25190,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="52">
       <c r="A4" s="64" t="inlineStr">
         <is>
@@ -22845,2040 +26392,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <tabColor rgb="FFB0BEC5"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:H199"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="14" customWidth="1" style="51" min="1" max="2"/>
-    <col width="22" customWidth="1" style="51" min="3" max="3"/>
-    <col width="16" customWidth="1" style="51" min="4" max="4"/>
-    <col width="14" customWidth="1" style="51" min="5" max="5"/>
-    <col width="34" customWidth="1" style="51" min="6" max="6"/>
-    <col width="28" customWidth="1" style="51" min="7" max="7"/>
-    <col width="14" customWidth="1" style="51" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="52">
-      <c r="A1" s="53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  FEEDBACK LOG  —  Internal &amp; External</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="21.75" customHeight="1" s="52">
-      <c r="A2" s="54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Source: Internal | External.  Type: CPARS | Survey | Email | Verbal | Slack.  Sentiment: + | 0 | −</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" s="52">
-      <c r="A4" s="64" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B4" s="64" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="C4" s="64" t="inlineStr">
-        <is>
-          <t>Party</t>
-        </is>
-      </c>
-      <c r="D4" s="64" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E4" s="64" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="F4" s="64" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="G4" s="64" t="inlineStr">
-        <is>
-          <t>Action Required</t>
-        </is>
-      </c>
-      <c r="H4" s="64" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="52">
-      <c r="A5" s="102" t="n"/>
-      <c r="B5" s="100" t="n"/>
-      <c r="C5" s="100" t="n"/>
-      <c r="D5" s="100" t="n"/>
-      <c r="E5" s="100" t="n"/>
-      <c r="F5" s="100" t="n"/>
-      <c r="G5" s="100" t="n"/>
-      <c r="H5" s="100" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="52">
-      <c r="A6" s="102" t="n"/>
-      <c r="B6" s="100" t="n"/>
-      <c r="C6" s="100" t="n"/>
-      <c r="D6" s="100" t="n"/>
-      <c r="E6" s="100" t="n"/>
-      <c r="F6" s="100" t="n"/>
-      <c r="G6" s="100" t="n"/>
-      <c r="H6" s="100" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="52">
-      <c r="A7" s="102" t="n"/>
-      <c r="B7" s="100" t="n"/>
-      <c r="C7" s="100" t="n"/>
-      <c r="D7" s="100" t="n"/>
-      <c r="E7" s="100" t="n"/>
-      <c r="F7" s="100" t="n"/>
-      <c r="G7" s="100" t="n"/>
-      <c r="H7" s="100" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="52">
-      <c r="A8" s="102" t="n"/>
-      <c r="B8" s="100" t="n"/>
-      <c r="C8" s="100" t="n"/>
-      <c r="D8" s="100" t="n"/>
-      <c r="E8" s="100" t="n"/>
-      <c r="F8" s="100" t="n"/>
-      <c r="G8" s="100" t="n"/>
-      <c r="H8" s="100" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="52">
-      <c r="A9" s="102" t="n"/>
-      <c r="B9" s="100" t="n"/>
-      <c r="C9" s="100" t="n"/>
-      <c r="D9" s="100" t="n"/>
-      <c r="E9" s="100" t="n"/>
-      <c r="F9" s="100" t="n"/>
-      <c r="G9" s="100" t="n"/>
-      <c r="H9" s="100" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="52">
-      <c r="A10" s="102" t="n"/>
-      <c r="B10" s="100" t="n"/>
-      <c r="C10" s="100" t="n"/>
-      <c r="D10" s="100" t="n"/>
-      <c r="E10" s="100" t="n"/>
-      <c r="F10" s="100" t="n"/>
-      <c r="G10" s="100" t="n"/>
-      <c r="H10" s="100" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="52">
-      <c r="A11" s="102" t="n"/>
-      <c r="B11" s="100" t="n"/>
-      <c r="C11" s="100" t="n"/>
-      <c r="D11" s="100" t="n"/>
-      <c r="E11" s="100" t="n"/>
-      <c r="F11" s="100" t="n"/>
-      <c r="G11" s="100" t="n"/>
-      <c r="H11" s="100" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="52">
-      <c r="A12" s="102" t="n"/>
-      <c r="B12" s="100" t="n"/>
-      <c r="C12" s="100" t="n"/>
-      <c r="D12" s="100" t="n"/>
-      <c r="E12" s="100" t="n"/>
-      <c r="F12" s="100" t="n"/>
-      <c r="G12" s="100" t="n"/>
-      <c r="H12" s="100" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="52">
-      <c r="A13" s="102" t="n"/>
-      <c r="B13" s="100" t="n"/>
-      <c r="C13" s="100" t="n"/>
-      <c r="D13" s="100" t="n"/>
-      <c r="E13" s="100" t="n"/>
-      <c r="F13" s="100" t="n"/>
-      <c r="G13" s="100" t="n"/>
-      <c r="H13" s="100" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="52">
-      <c r="A14" s="102" t="n"/>
-      <c r="B14" s="100" t="n"/>
-      <c r="C14" s="100" t="n"/>
-      <c r="D14" s="100" t="n"/>
-      <c r="E14" s="100" t="n"/>
-      <c r="F14" s="100" t="n"/>
-      <c r="G14" s="100" t="n"/>
-      <c r="H14" s="100" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="52">
-      <c r="A15" s="102" t="n"/>
-      <c r="B15" s="100" t="n"/>
-      <c r="C15" s="100" t="n"/>
-      <c r="D15" s="100" t="n"/>
-      <c r="E15" s="100" t="n"/>
-      <c r="F15" s="100" t="n"/>
-      <c r="G15" s="100" t="n"/>
-      <c r="H15" s="100" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="52">
-      <c r="A16" s="102" t="n"/>
-      <c r="B16" s="100" t="n"/>
-      <c r="C16" s="100" t="n"/>
-      <c r="D16" s="100" t="n"/>
-      <c r="E16" s="100" t="n"/>
-      <c r="F16" s="100" t="n"/>
-      <c r="G16" s="100" t="n"/>
-      <c r="H16" s="100" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="52">
-      <c r="A17" s="102" t="n"/>
-      <c r="B17" s="100" t="n"/>
-      <c r="C17" s="100" t="n"/>
-      <c r="D17" s="100" t="n"/>
-      <c r="E17" s="100" t="n"/>
-      <c r="F17" s="100" t="n"/>
-      <c r="G17" s="100" t="n"/>
-      <c r="H17" s="100" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="52">
-      <c r="A18" s="102" t="n"/>
-      <c r="B18" s="100" t="n"/>
-      <c r="C18" s="100" t="n"/>
-      <c r="D18" s="100" t="n"/>
-      <c r="E18" s="100" t="n"/>
-      <c r="F18" s="100" t="n"/>
-      <c r="G18" s="100" t="n"/>
-      <c r="H18" s="100" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="52">
-      <c r="A19" s="102" t="n"/>
-      <c r="B19" s="100" t="n"/>
-      <c r="C19" s="100" t="n"/>
-      <c r="D19" s="100" t="n"/>
-      <c r="E19" s="100" t="n"/>
-      <c r="F19" s="100" t="n"/>
-      <c r="G19" s="100" t="n"/>
-      <c r="H19" s="100" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="52">
-      <c r="A20" s="102" t="n"/>
-      <c r="B20" s="100" t="n"/>
-      <c r="C20" s="100" t="n"/>
-      <c r="D20" s="100" t="n"/>
-      <c r="E20" s="100" t="n"/>
-      <c r="F20" s="100" t="n"/>
-      <c r="G20" s="100" t="n"/>
-      <c r="H20" s="100" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="52">
-      <c r="A21" s="102" t="n"/>
-      <c r="B21" s="100" t="n"/>
-      <c r="C21" s="100" t="n"/>
-      <c r="D21" s="100" t="n"/>
-      <c r="E21" s="100" t="n"/>
-      <c r="F21" s="100" t="n"/>
-      <c r="G21" s="100" t="n"/>
-      <c r="H21" s="100" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="52">
-      <c r="A22" s="102" t="n"/>
-      <c r="B22" s="100" t="n"/>
-      <c r="C22" s="100" t="n"/>
-      <c r="D22" s="100" t="n"/>
-      <c r="E22" s="100" t="n"/>
-      <c r="F22" s="100" t="n"/>
-      <c r="G22" s="100" t="n"/>
-      <c r="H22" s="100" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="52">
-      <c r="A23" s="102" t="n"/>
-      <c r="B23" s="100" t="n"/>
-      <c r="C23" s="100" t="n"/>
-      <c r="D23" s="100" t="n"/>
-      <c r="E23" s="100" t="n"/>
-      <c r="F23" s="100" t="n"/>
-      <c r="G23" s="100" t="n"/>
-      <c r="H23" s="100" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="52">
-      <c r="A24" s="102" t="n"/>
-      <c r="B24" s="100" t="n"/>
-      <c r="C24" s="100" t="n"/>
-      <c r="D24" s="100" t="n"/>
-      <c r="E24" s="100" t="n"/>
-      <c r="F24" s="100" t="n"/>
-      <c r="G24" s="100" t="n"/>
-      <c r="H24" s="100" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="52">
-      <c r="A25" s="102" t="n"/>
-      <c r="B25" s="100" t="n"/>
-      <c r="C25" s="100" t="n"/>
-      <c r="D25" s="100" t="n"/>
-      <c r="E25" s="100" t="n"/>
-      <c r="F25" s="100" t="n"/>
-      <c r="G25" s="100" t="n"/>
-      <c r="H25" s="100" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="52">
-      <c r="A26" s="102" t="n"/>
-      <c r="B26" s="100" t="n"/>
-      <c r="C26" s="100" t="n"/>
-      <c r="D26" s="100" t="n"/>
-      <c r="E26" s="100" t="n"/>
-      <c r="F26" s="100" t="n"/>
-      <c r="G26" s="100" t="n"/>
-      <c r="H26" s="100" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="52">
-      <c r="A27" s="102" t="n"/>
-      <c r="B27" s="100" t="n"/>
-      <c r="C27" s="100" t="n"/>
-      <c r="D27" s="100" t="n"/>
-      <c r="E27" s="100" t="n"/>
-      <c r="F27" s="100" t="n"/>
-      <c r="G27" s="100" t="n"/>
-      <c r="H27" s="100" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="52">
-      <c r="A28" s="102" t="n"/>
-      <c r="B28" s="100" t="n"/>
-      <c r="C28" s="100" t="n"/>
-      <c r="D28" s="100" t="n"/>
-      <c r="E28" s="100" t="n"/>
-      <c r="F28" s="100" t="n"/>
-      <c r="G28" s="100" t="n"/>
-      <c r="H28" s="100" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="52">
-      <c r="A29" s="102" t="n"/>
-      <c r="B29" s="100" t="n"/>
-      <c r="C29" s="100" t="n"/>
-      <c r="D29" s="100" t="n"/>
-      <c r="E29" s="100" t="n"/>
-      <c r="F29" s="100" t="n"/>
-      <c r="G29" s="100" t="n"/>
-      <c r="H29" s="100" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="52">
-      <c r="A30" s="102" t="n"/>
-      <c r="B30" s="100" t="n"/>
-      <c r="C30" s="100" t="n"/>
-      <c r="D30" s="100" t="n"/>
-      <c r="E30" s="100" t="n"/>
-      <c r="F30" s="100" t="n"/>
-      <c r="G30" s="100" t="n"/>
-      <c r="H30" s="100" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="52">
-      <c r="A31" s="102" t="n"/>
-      <c r="B31" s="100" t="n"/>
-      <c r="C31" s="100" t="n"/>
-      <c r="D31" s="100" t="n"/>
-      <c r="E31" s="100" t="n"/>
-      <c r="F31" s="100" t="n"/>
-      <c r="G31" s="100" t="n"/>
-      <c r="H31" s="100" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="52">
-      <c r="A32" s="102" t="n"/>
-      <c r="B32" s="100" t="n"/>
-      <c r="C32" s="100" t="n"/>
-      <c r="D32" s="100" t="n"/>
-      <c r="E32" s="100" t="n"/>
-      <c r="F32" s="100" t="n"/>
-      <c r="G32" s="100" t="n"/>
-      <c r="H32" s="100" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="52">
-      <c r="A33" s="102" t="n"/>
-      <c r="B33" s="100" t="n"/>
-      <c r="C33" s="100" t="n"/>
-      <c r="D33" s="100" t="n"/>
-      <c r="E33" s="100" t="n"/>
-      <c r="F33" s="100" t="n"/>
-      <c r="G33" s="100" t="n"/>
-      <c r="H33" s="100" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="52">
-      <c r="A34" s="102" t="n"/>
-      <c r="B34" s="100" t="n"/>
-      <c r="C34" s="100" t="n"/>
-      <c r="D34" s="100" t="n"/>
-      <c r="E34" s="100" t="n"/>
-      <c r="F34" s="100" t="n"/>
-      <c r="G34" s="100" t="n"/>
-      <c r="H34" s="100" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="52">
-      <c r="A35" s="102" t="n"/>
-      <c r="B35" s="100" t="n"/>
-      <c r="C35" s="100" t="n"/>
-      <c r="D35" s="100" t="n"/>
-      <c r="E35" s="100" t="n"/>
-      <c r="F35" s="100" t="n"/>
-      <c r="G35" s="100" t="n"/>
-      <c r="H35" s="100" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="52">
-      <c r="A36" s="102" t="n"/>
-      <c r="B36" s="100" t="n"/>
-      <c r="C36" s="100" t="n"/>
-      <c r="D36" s="100" t="n"/>
-      <c r="E36" s="100" t="n"/>
-      <c r="F36" s="100" t="n"/>
-      <c r="G36" s="100" t="n"/>
-      <c r="H36" s="100" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="52">
-      <c r="A37" s="102" t="n"/>
-      <c r="B37" s="100" t="n"/>
-      <c r="C37" s="100" t="n"/>
-      <c r="D37" s="100" t="n"/>
-      <c r="E37" s="100" t="n"/>
-      <c r="F37" s="100" t="n"/>
-      <c r="G37" s="100" t="n"/>
-      <c r="H37" s="100" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="52">
-      <c r="A38" s="102" t="n"/>
-      <c r="B38" s="100" t="n"/>
-      <c r="C38" s="100" t="n"/>
-      <c r="D38" s="100" t="n"/>
-      <c r="E38" s="100" t="n"/>
-      <c r="F38" s="100" t="n"/>
-      <c r="G38" s="100" t="n"/>
-      <c r="H38" s="100" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="52">
-      <c r="A39" s="102" t="n"/>
-      <c r="B39" s="100" t="n"/>
-      <c r="C39" s="100" t="n"/>
-      <c r="D39" s="100" t="n"/>
-      <c r="E39" s="100" t="n"/>
-      <c r="F39" s="100" t="n"/>
-      <c r="G39" s="100" t="n"/>
-      <c r="H39" s="100" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="52">
-      <c r="A40" s="102" t="n"/>
-      <c r="B40" s="100" t="n"/>
-      <c r="C40" s="100" t="n"/>
-      <c r="D40" s="100" t="n"/>
-      <c r="E40" s="100" t="n"/>
-      <c r="F40" s="100" t="n"/>
-      <c r="G40" s="100" t="n"/>
-      <c r="H40" s="100" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="52">
-      <c r="A41" s="102" t="n"/>
-      <c r="B41" s="100" t="n"/>
-      <c r="C41" s="100" t="n"/>
-      <c r="D41" s="100" t="n"/>
-      <c r="E41" s="100" t="n"/>
-      <c r="F41" s="100" t="n"/>
-      <c r="G41" s="100" t="n"/>
-      <c r="H41" s="100" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="52">
-      <c r="A42" s="102" t="n"/>
-      <c r="B42" s="100" t="n"/>
-      <c r="C42" s="100" t="n"/>
-      <c r="D42" s="100" t="n"/>
-      <c r="E42" s="100" t="n"/>
-      <c r="F42" s="100" t="n"/>
-      <c r="G42" s="100" t="n"/>
-      <c r="H42" s="100" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="52">
-      <c r="A43" s="102" t="n"/>
-      <c r="B43" s="100" t="n"/>
-      <c r="C43" s="100" t="n"/>
-      <c r="D43" s="100" t="n"/>
-      <c r="E43" s="100" t="n"/>
-      <c r="F43" s="100" t="n"/>
-      <c r="G43" s="100" t="n"/>
-      <c r="H43" s="100" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="52">
-      <c r="A44" s="102" t="n"/>
-      <c r="B44" s="100" t="n"/>
-      <c r="C44" s="100" t="n"/>
-      <c r="D44" s="100" t="n"/>
-      <c r="E44" s="100" t="n"/>
-      <c r="F44" s="100" t="n"/>
-      <c r="G44" s="100" t="n"/>
-      <c r="H44" s="100" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="52">
-      <c r="A45" s="102" t="n"/>
-      <c r="B45" s="100" t="n"/>
-      <c r="C45" s="100" t="n"/>
-      <c r="D45" s="100" t="n"/>
-      <c r="E45" s="100" t="n"/>
-      <c r="F45" s="100" t="n"/>
-      <c r="G45" s="100" t="n"/>
-      <c r="H45" s="100" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="52">
-      <c r="A46" s="102" t="n"/>
-      <c r="B46" s="100" t="n"/>
-      <c r="C46" s="100" t="n"/>
-      <c r="D46" s="100" t="n"/>
-      <c r="E46" s="100" t="n"/>
-      <c r="F46" s="100" t="n"/>
-      <c r="G46" s="100" t="n"/>
-      <c r="H46" s="100" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="52">
-      <c r="A47" s="102" t="n"/>
-      <c r="B47" s="100" t="n"/>
-      <c r="C47" s="100" t="n"/>
-      <c r="D47" s="100" t="n"/>
-      <c r="E47" s="100" t="n"/>
-      <c r="F47" s="100" t="n"/>
-      <c r="G47" s="100" t="n"/>
-      <c r="H47" s="100" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="52">
-      <c r="A48" s="102" t="n"/>
-      <c r="B48" s="100" t="n"/>
-      <c r="C48" s="100" t="n"/>
-      <c r="D48" s="100" t="n"/>
-      <c r="E48" s="100" t="n"/>
-      <c r="F48" s="100" t="n"/>
-      <c r="G48" s="100" t="n"/>
-      <c r="H48" s="100" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="52">
-      <c r="A49" s="102" t="n"/>
-      <c r="B49" s="100" t="n"/>
-      <c r="C49" s="100" t="n"/>
-      <c r="D49" s="100" t="n"/>
-      <c r="E49" s="100" t="n"/>
-      <c r="F49" s="100" t="n"/>
-      <c r="G49" s="100" t="n"/>
-      <c r="H49" s="100" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="52">
-      <c r="A50" s="102" t="n"/>
-      <c r="B50" s="100" t="n"/>
-      <c r="C50" s="100" t="n"/>
-      <c r="D50" s="100" t="n"/>
-      <c r="E50" s="100" t="n"/>
-      <c r="F50" s="100" t="n"/>
-      <c r="G50" s="100" t="n"/>
-      <c r="H50" s="100" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="52">
-      <c r="A51" s="102" t="n"/>
-      <c r="B51" s="100" t="n"/>
-      <c r="C51" s="100" t="n"/>
-      <c r="D51" s="100" t="n"/>
-      <c r="E51" s="100" t="n"/>
-      <c r="F51" s="100" t="n"/>
-      <c r="G51" s="100" t="n"/>
-      <c r="H51" s="100" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="52">
-      <c r="A52" s="102" t="n"/>
-      <c r="B52" s="100" t="n"/>
-      <c r="C52" s="100" t="n"/>
-      <c r="D52" s="100" t="n"/>
-      <c r="E52" s="100" t="n"/>
-      <c r="F52" s="100" t="n"/>
-      <c r="G52" s="100" t="n"/>
-      <c r="H52" s="100" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="52">
-      <c r="A53" s="102" t="n"/>
-      <c r="B53" s="100" t="n"/>
-      <c r="C53" s="100" t="n"/>
-      <c r="D53" s="100" t="n"/>
-      <c r="E53" s="100" t="n"/>
-      <c r="F53" s="100" t="n"/>
-      <c r="G53" s="100" t="n"/>
-      <c r="H53" s="100" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="52">
-      <c r="A54" s="102" t="n"/>
-      <c r="B54" s="100" t="n"/>
-      <c r="C54" s="100" t="n"/>
-      <c r="D54" s="100" t="n"/>
-      <c r="E54" s="100" t="n"/>
-      <c r="F54" s="100" t="n"/>
-      <c r="G54" s="100" t="n"/>
-      <c r="H54" s="100" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="52">
-      <c r="A55" s="102" t="n"/>
-      <c r="B55" s="100" t="n"/>
-      <c r="C55" s="100" t="n"/>
-      <c r="D55" s="100" t="n"/>
-      <c r="E55" s="100" t="n"/>
-      <c r="F55" s="100" t="n"/>
-      <c r="G55" s="100" t="n"/>
-      <c r="H55" s="100" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="52">
-      <c r="A56" s="102" t="n"/>
-      <c r="B56" s="100" t="n"/>
-      <c r="C56" s="100" t="n"/>
-      <c r="D56" s="100" t="n"/>
-      <c r="E56" s="100" t="n"/>
-      <c r="F56" s="100" t="n"/>
-      <c r="G56" s="100" t="n"/>
-      <c r="H56" s="100" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="52">
-      <c r="A57" s="102" t="n"/>
-      <c r="B57" s="100" t="n"/>
-      <c r="C57" s="100" t="n"/>
-      <c r="D57" s="100" t="n"/>
-      <c r="E57" s="100" t="n"/>
-      <c r="F57" s="100" t="n"/>
-      <c r="G57" s="100" t="n"/>
-      <c r="H57" s="100" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="52">
-      <c r="A58" s="102" t="n"/>
-      <c r="B58" s="100" t="n"/>
-      <c r="C58" s="100" t="n"/>
-      <c r="D58" s="100" t="n"/>
-      <c r="E58" s="100" t="n"/>
-      <c r="F58" s="100" t="n"/>
-      <c r="G58" s="100" t="n"/>
-      <c r="H58" s="100" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="52">
-      <c r="A59" s="102" t="n"/>
-      <c r="B59" s="100" t="n"/>
-      <c r="C59" s="100" t="n"/>
-      <c r="D59" s="100" t="n"/>
-      <c r="E59" s="100" t="n"/>
-      <c r="F59" s="100" t="n"/>
-      <c r="G59" s="100" t="n"/>
-      <c r="H59" s="100" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="52">
-      <c r="A60" s="102" t="n"/>
-      <c r="B60" s="100" t="n"/>
-      <c r="C60" s="100" t="n"/>
-      <c r="D60" s="100" t="n"/>
-      <c r="E60" s="100" t="n"/>
-      <c r="F60" s="100" t="n"/>
-      <c r="G60" s="100" t="n"/>
-      <c r="H60" s="100" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="52">
-      <c r="A61" s="102" t="n"/>
-      <c r="B61" s="100" t="n"/>
-      <c r="C61" s="100" t="n"/>
-      <c r="D61" s="100" t="n"/>
-      <c r="E61" s="100" t="n"/>
-      <c r="F61" s="100" t="n"/>
-      <c r="G61" s="100" t="n"/>
-      <c r="H61" s="100" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="52">
-      <c r="A62" s="102" t="n"/>
-      <c r="B62" s="100" t="n"/>
-      <c r="C62" s="100" t="n"/>
-      <c r="D62" s="100" t="n"/>
-      <c r="E62" s="100" t="n"/>
-      <c r="F62" s="100" t="n"/>
-      <c r="G62" s="100" t="n"/>
-      <c r="H62" s="100" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="52">
-      <c r="A63" s="102" t="n"/>
-      <c r="B63" s="100" t="n"/>
-      <c r="C63" s="100" t="n"/>
-      <c r="D63" s="100" t="n"/>
-      <c r="E63" s="100" t="n"/>
-      <c r="F63" s="100" t="n"/>
-      <c r="G63" s="100" t="n"/>
-      <c r="H63" s="100" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="52">
-      <c r="A64" s="102" t="n"/>
-      <c r="B64" s="100" t="n"/>
-      <c r="C64" s="100" t="n"/>
-      <c r="D64" s="100" t="n"/>
-      <c r="E64" s="100" t="n"/>
-      <c r="F64" s="100" t="n"/>
-      <c r="G64" s="100" t="n"/>
-      <c r="H64" s="100" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="52">
-      <c r="A65" s="102" t="n"/>
-      <c r="B65" s="100" t="n"/>
-      <c r="C65" s="100" t="n"/>
-      <c r="D65" s="100" t="n"/>
-      <c r="E65" s="100" t="n"/>
-      <c r="F65" s="100" t="n"/>
-      <c r="G65" s="100" t="n"/>
-      <c r="H65" s="100" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="52">
-      <c r="A66" s="102" t="n"/>
-      <c r="B66" s="100" t="n"/>
-      <c r="C66" s="100" t="n"/>
-      <c r="D66" s="100" t="n"/>
-      <c r="E66" s="100" t="n"/>
-      <c r="F66" s="100" t="n"/>
-      <c r="G66" s="100" t="n"/>
-      <c r="H66" s="100" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="52">
-      <c r="A67" s="102" t="n"/>
-      <c r="B67" s="100" t="n"/>
-      <c r="C67" s="100" t="n"/>
-      <c r="D67" s="100" t="n"/>
-      <c r="E67" s="100" t="n"/>
-      <c r="F67" s="100" t="n"/>
-      <c r="G67" s="100" t="n"/>
-      <c r="H67" s="100" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="52">
-      <c r="A68" s="102" t="n"/>
-      <c r="B68" s="100" t="n"/>
-      <c r="C68" s="100" t="n"/>
-      <c r="D68" s="100" t="n"/>
-      <c r="E68" s="100" t="n"/>
-      <c r="F68" s="100" t="n"/>
-      <c r="G68" s="100" t="n"/>
-      <c r="H68" s="100" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="52">
-      <c r="A69" s="102" t="n"/>
-      <c r="B69" s="100" t="n"/>
-      <c r="C69" s="100" t="n"/>
-      <c r="D69" s="100" t="n"/>
-      <c r="E69" s="100" t="n"/>
-      <c r="F69" s="100" t="n"/>
-      <c r="G69" s="100" t="n"/>
-      <c r="H69" s="100" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="52">
-      <c r="A70" s="102" t="n"/>
-      <c r="B70" s="100" t="n"/>
-      <c r="C70" s="100" t="n"/>
-      <c r="D70" s="100" t="n"/>
-      <c r="E70" s="100" t="n"/>
-      <c r="F70" s="100" t="n"/>
-      <c r="G70" s="100" t="n"/>
-      <c r="H70" s="100" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="52">
-      <c r="A71" s="102" t="n"/>
-      <c r="B71" s="100" t="n"/>
-      <c r="C71" s="100" t="n"/>
-      <c r="D71" s="100" t="n"/>
-      <c r="E71" s="100" t="n"/>
-      <c r="F71" s="100" t="n"/>
-      <c r="G71" s="100" t="n"/>
-      <c r="H71" s="100" t="n"/>
-    </row>
-    <row r="72" ht="15" customHeight="1" s="52">
-      <c r="A72" s="102" t="n"/>
-      <c r="B72" s="100" t="n"/>
-      <c r="C72" s="100" t="n"/>
-      <c r="D72" s="100" t="n"/>
-      <c r="E72" s="100" t="n"/>
-      <c r="F72" s="100" t="n"/>
-      <c r="G72" s="100" t="n"/>
-      <c r="H72" s="100" t="n"/>
-    </row>
-    <row r="73" ht="15" customHeight="1" s="52">
-      <c r="A73" s="102" t="n"/>
-      <c r="B73" s="100" t="n"/>
-      <c r="C73" s="100" t="n"/>
-      <c r="D73" s="100" t="n"/>
-      <c r="E73" s="100" t="n"/>
-      <c r="F73" s="100" t="n"/>
-      <c r="G73" s="100" t="n"/>
-      <c r="H73" s="100" t="n"/>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="52">
-      <c r="A74" s="102" t="n"/>
-      <c r="B74" s="100" t="n"/>
-      <c r="C74" s="100" t="n"/>
-      <c r="D74" s="100" t="n"/>
-      <c r="E74" s="100" t="n"/>
-      <c r="F74" s="100" t="n"/>
-      <c r="G74" s="100" t="n"/>
-      <c r="H74" s="100" t="n"/>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="52">
-      <c r="A75" s="102" t="n"/>
-      <c r="B75" s="100" t="n"/>
-      <c r="C75" s="100" t="n"/>
-      <c r="D75" s="100" t="n"/>
-      <c r="E75" s="100" t="n"/>
-      <c r="F75" s="100" t="n"/>
-      <c r="G75" s="100" t="n"/>
-      <c r="H75" s="100" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="52">
-      <c r="A76" s="102" t="n"/>
-      <c r="B76" s="100" t="n"/>
-      <c r="C76" s="100" t="n"/>
-      <c r="D76" s="100" t="n"/>
-      <c r="E76" s="100" t="n"/>
-      <c r="F76" s="100" t="n"/>
-      <c r="G76" s="100" t="n"/>
-      <c r="H76" s="100" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="52">
-      <c r="A77" s="102" t="n"/>
-      <c r="B77" s="100" t="n"/>
-      <c r="C77" s="100" t="n"/>
-      <c r="D77" s="100" t="n"/>
-      <c r="E77" s="100" t="n"/>
-      <c r="F77" s="100" t="n"/>
-      <c r="G77" s="100" t="n"/>
-      <c r="H77" s="100" t="n"/>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="52">
-      <c r="A78" s="102" t="n"/>
-      <c r="B78" s="100" t="n"/>
-      <c r="C78" s="100" t="n"/>
-      <c r="D78" s="100" t="n"/>
-      <c r="E78" s="100" t="n"/>
-      <c r="F78" s="100" t="n"/>
-      <c r="G78" s="100" t="n"/>
-      <c r="H78" s="100" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="52">
-      <c r="A79" s="102" t="n"/>
-      <c r="B79" s="100" t="n"/>
-      <c r="C79" s="100" t="n"/>
-      <c r="D79" s="100" t="n"/>
-      <c r="E79" s="100" t="n"/>
-      <c r="F79" s="100" t="n"/>
-      <c r="G79" s="100" t="n"/>
-      <c r="H79" s="100" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="52">
-      <c r="A80" s="102" t="n"/>
-      <c r="B80" s="100" t="n"/>
-      <c r="C80" s="100" t="n"/>
-      <c r="D80" s="100" t="n"/>
-      <c r="E80" s="100" t="n"/>
-      <c r="F80" s="100" t="n"/>
-      <c r="G80" s="100" t="n"/>
-      <c r="H80" s="100" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1" s="52">
-      <c r="A81" s="102" t="n"/>
-      <c r="B81" s="100" t="n"/>
-      <c r="C81" s="100" t="n"/>
-      <c r="D81" s="100" t="n"/>
-      <c r="E81" s="100" t="n"/>
-      <c r="F81" s="100" t="n"/>
-      <c r="G81" s="100" t="n"/>
-      <c r="H81" s="100" t="n"/>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="52">
-      <c r="A82" s="102" t="n"/>
-      <c r="B82" s="100" t="n"/>
-      <c r="C82" s="100" t="n"/>
-      <c r="D82" s="100" t="n"/>
-      <c r="E82" s="100" t="n"/>
-      <c r="F82" s="100" t="n"/>
-      <c r="G82" s="100" t="n"/>
-      <c r="H82" s="100" t="n"/>
-    </row>
-    <row r="83" ht="15" customHeight="1" s="52">
-      <c r="A83" s="102" t="n"/>
-      <c r="B83" s="100" t="n"/>
-      <c r="C83" s="100" t="n"/>
-      <c r="D83" s="100" t="n"/>
-      <c r="E83" s="100" t="n"/>
-      <c r="F83" s="100" t="n"/>
-      <c r="G83" s="100" t="n"/>
-      <c r="H83" s="100" t="n"/>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="52">
-      <c r="A84" s="102" t="n"/>
-      <c r="B84" s="100" t="n"/>
-      <c r="C84" s="100" t="n"/>
-      <c r="D84" s="100" t="n"/>
-      <c r="E84" s="100" t="n"/>
-      <c r="F84" s="100" t="n"/>
-      <c r="G84" s="100" t="n"/>
-      <c r="H84" s="100" t="n"/>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="52">
-      <c r="A85" s="102" t="n"/>
-      <c r="B85" s="100" t="n"/>
-      <c r="C85" s="100" t="n"/>
-      <c r="D85" s="100" t="n"/>
-      <c r="E85" s="100" t="n"/>
-      <c r="F85" s="100" t="n"/>
-      <c r="G85" s="100" t="n"/>
-      <c r="H85" s="100" t="n"/>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="52">
-      <c r="A86" s="102" t="n"/>
-      <c r="B86" s="100" t="n"/>
-      <c r="C86" s="100" t="n"/>
-      <c r="D86" s="100" t="n"/>
-      <c r="E86" s="100" t="n"/>
-      <c r="F86" s="100" t="n"/>
-      <c r="G86" s="100" t="n"/>
-      <c r="H86" s="100" t="n"/>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="52">
-      <c r="A87" s="102" t="n"/>
-      <c r="B87" s="100" t="n"/>
-      <c r="C87" s="100" t="n"/>
-      <c r="D87" s="100" t="n"/>
-      <c r="E87" s="100" t="n"/>
-      <c r="F87" s="100" t="n"/>
-      <c r="G87" s="100" t="n"/>
-      <c r="H87" s="100" t="n"/>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="52">
-      <c r="A88" s="102" t="n"/>
-      <c r="B88" s="100" t="n"/>
-      <c r="C88" s="100" t="n"/>
-      <c r="D88" s="100" t="n"/>
-      <c r="E88" s="100" t="n"/>
-      <c r="F88" s="100" t="n"/>
-      <c r="G88" s="100" t="n"/>
-      <c r="H88" s="100" t="n"/>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="52">
-      <c r="A89" s="102" t="n"/>
-      <c r="B89" s="100" t="n"/>
-      <c r="C89" s="100" t="n"/>
-      <c r="D89" s="100" t="n"/>
-      <c r="E89" s="100" t="n"/>
-      <c r="F89" s="100" t="n"/>
-      <c r="G89" s="100" t="n"/>
-      <c r="H89" s="100" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1" s="52">
-      <c r="A90" s="102" t="n"/>
-      <c r="B90" s="100" t="n"/>
-      <c r="C90" s="100" t="n"/>
-      <c r="D90" s="100" t="n"/>
-      <c r="E90" s="100" t="n"/>
-      <c r="F90" s="100" t="n"/>
-      <c r="G90" s="100" t="n"/>
-      <c r="H90" s="100" t="n"/>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="52">
-      <c r="A91" s="102" t="n"/>
-      <c r="B91" s="100" t="n"/>
-      <c r="C91" s="100" t="n"/>
-      <c r="D91" s="100" t="n"/>
-      <c r="E91" s="100" t="n"/>
-      <c r="F91" s="100" t="n"/>
-      <c r="G91" s="100" t="n"/>
-      <c r="H91" s="100" t="n"/>
-    </row>
-    <row r="92" ht="15" customHeight="1" s="52">
-      <c r="A92" s="102" t="n"/>
-      <c r="B92" s="100" t="n"/>
-      <c r="C92" s="100" t="n"/>
-      <c r="D92" s="100" t="n"/>
-      <c r="E92" s="100" t="n"/>
-      <c r="F92" s="100" t="n"/>
-      <c r="G92" s="100" t="n"/>
-      <c r="H92" s="100" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1" s="52">
-      <c r="A93" s="102" t="n"/>
-      <c r="B93" s="100" t="n"/>
-      <c r="C93" s="100" t="n"/>
-      <c r="D93" s="100" t="n"/>
-      <c r="E93" s="100" t="n"/>
-      <c r="F93" s="100" t="n"/>
-      <c r="G93" s="100" t="n"/>
-      <c r="H93" s="100" t="n"/>
-    </row>
-    <row r="94" ht="15" customHeight="1" s="52">
-      <c r="A94" s="102" t="n"/>
-      <c r="B94" s="100" t="n"/>
-      <c r="C94" s="100" t="n"/>
-      <c r="D94" s="100" t="n"/>
-      <c r="E94" s="100" t="n"/>
-      <c r="F94" s="100" t="n"/>
-      <c r="G94" s="100" t="n"/>
-      <c r="H94" s="100" t="n"/>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="52">
-      <c r="A95" s="102" t="n"/>
-      <c r="B95" s="100" t="n"/>
-      <c r="C95" s="100" t="n"/>
-      <c r="D95" s="100" t="n"/>
-      <c r="E95" s="100" t="n"/>
-      <c r="F95" s="100" t="n"/>
-      <c r="G95" s="100" t="n"/>
-      <c r="H95" s="100" t="n"/>
-    </row>
-    <row r="96" ht="15" customHeight="1" s="52">
-      <c r="A96" s="102" t="n"/>
-      <c r="B96" s="100" t="n"/>
-      <c r="C96" s="100" t="n"/>
-      <c r="D96" s="100" t="n"/>
-      <c r="E96" s="100" t="n"/>
-      <c r="F96" s="100" t="n"/>
-      <c r="G96" s="100" t="n"/>
-      <c r="H96" s="100" t="n"/>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="52">
-      <c r="A97" s="102" t="n"/>
-      <c r="B97" s="100" t="n"/>
-      <c r="C97" s="100" t="n"/>
-      <c r="D97" s="100" t="n"/>
-      <c r="E97" s="100" t="n"/>
-      <c r="F97" s="100" t="n"/>
-      <c r="G97" s="100" t="n"/>
-      <c r="H97" s="100" t="n"/>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="52">
-      <c r="A98" s="102" t="n"/>
-      <c r="B98" s="100" t="n"/>
-      <c r="C98" s="100" t="n"/>
-      <c r="D98" s="100" t="n"/>
-      <c r="E98" s="100" t="n"/>
-      <c r="F98" s="100" t="n"/>
-      <c r="G98" s="100" t="n"/>
-      <c r="H98" s="100" t="n"/>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="52">
-      <c r="A99" s="102" t="n"/>
-      <c r="B99" s="100" t="n"/>
-      <c r="C99" s="100" t="n"/>
-      <c r="D99" s="100" t="n"/>
-      <c r="E99" s="100" t="n"/>
-      <c r="F99" s="100" t="n"/>
-      <c r="G99" s="100" t="n"/>
-      <c r="H99" s="100" t="n"/>
-    </row>
-    <row r="100" ht="15" customHeight="1" s="52">
-      <c r="A100" s="102" t="n"/>
-      <c r="B100" s="100" t="n"/>
-      <c r="C100" s="100" t="n"/>
-      <c r="D100" s="100" t="n"/>
-      <c r="E100" s="100" t="n"/>
-      <c r="F100" s="100" t="n"/>
-      <c r="G100" s="100" t="n"/>
-      <c r="H100" s="100" t="n"/>
-    </row>
-    <row r="101" ht="15" customHeight="1" s="52">
-      <c r="A101" s="102" t="n"/>
-      <c r="B101" s="100" t="n"/>
-      <c r="C101" s="100" t="n"/>
-      <c r="D101" s="100" t="n"/>
-      <c r="E101" s="100" t="n"/>
-      <c r="F101" s="100" t="n"/>
-      <c r="G101" s="100" t="n"/>
-      <c r="H101" s="100" t="n"/>
-    </row>
-    <row r="102" ht="15" customHeight="1" s="52">
-      <c r="A102" s="102" t="n"/>
-      <c r="B102" s="100" t="n"/>
-      <c r="C102" s="100" t="n"/>
-      <c r="D102" s="100" t="n"/>
-      <c r="E102" s="100" t="n"/>
-      <c r="F102" s="100" t="n"/>
-      <c r="G102" s="100" t="n"/>
-      <c r="H102" s="100" t="n"/>
-    </row>
-    <row r="103" ht="15" customHeight="1" s="52">
-      <c r="A103" s="102" t="n"/>
-      <c r="B103" s="100" t="n"/>
-      <c r="C103" s="100" t="n"/>
-      <c r="D103" s="100" t="n"/>
-      <c r="E103" s="100" t="n"/>
-      <c r="F103" s="100" t="n"/>
-      <c r="G103" s="100" t="n"/>
-      <c r="H103" s="100" t="n"/>
-    </row>
-    <row r="104" ht="15" customHeight="1" s="52">
-      <c r="A104" s="102" t="n"/>
-      <c r="B104" s="100" t="n"/>
-      <c r="C104" s="100" t="n"/>
-      <c r="D104" s="100" t="n"/>
-      <c r="E104" s="100" t="n"/>
-      <c r="F104" s="100" t="n"/>
-      <c r="G104" s="100" t="n"/>
-      <c r="H104" s="100" t="n"/>
-    </row>
-    <row r="105" ht="15" customHeight="1" s="52">
-      <c r="A105" s="102" t="n"/>
-      <c r="B105" s="100" t="n"/>
-      <c r="C105" s="100" t="n"/>
-      <c r="D105" s="100" t="n"/>
-      <c r="E105" s="100" t="n"/>
-      <c r="F105" s="100" t="n"/>
-      <c r="G105" s="100" t="n"/>
-      <c r="H105" s="100" t="n"/>
-    </row>
-    <row r="106" ht="15" customHeight="1" s="52">
-      <c r="A106" s="102" t="n"/>
-      <c r="B106" s="100" t="n"/>
-      <c r="C106" s="100" t="n"/>
-      <c r="D106" s="100" t="n"/>
-      <c r="E106" s="100" t="n"/>
-      <c r="F106" s="100" t="n"/>
-      <c r="G106" s="100" t="n"/>
-      <c r="H106" s="100" t="n"/>
-    </row>
-    <row r="107" ht="15" customHeight="1" s="52">
-      <c r="A107" s="102" t="n"/>
-      <c r="B107" s="100" t="n"/>
-      <c r="C107" s="100" t="n"/>
-      <c r="D107" s="100" t="n"/>
-      <c r="E107" s="100" t="n"/>
-      <c r="F107" s="100" t="n"/>
-      <c r="G107" s="100" t="n"/>
-      <c r="H107" s="100" t="n"/>
-    </row>
-    <row r="108" ht="15" customHeight="1" s="52">
-      <c r="A108" s="102" t="n"/>
-      <c r="B108" s="100" t="n"/>
-      <c r="C108" s="100" t="n"/>
-      <c r="D108" s="100" t="n"/>
-      <c r="E108" s="100" t="n"/>
-      <c r="F108" s="100" t="n"/>
-      <c r="G108" s="100" t="n"/>
-      <c r="H108" s="100" t="n"/>
-    </row>
-    <row r="109" ht="15" customHeight="1" s="52">
-      <c r="A109" s="102" t="n"/>
-      <c r="B109" s="100" t="n"/>
-      <c r="C109" s="100" t="n"/>
-      <c r="D109" s="100" t="n"/>
-      <c r="E109" s="100" t="n"/>
-      <c r="F109" s="100" t="n"/>
-      <c r="G109" s="100" t="n"/>
-      <c r="H109" s="100" t="n"/>
-    </row>
-    <row r="110" ht="15" customHeight="1" s="52">
-      <c r="A110" s="102" t="n"/>
-      <c r="B110" s="100" t="n"/>
-      <c r="C110" s="100" t="n"/>
-      <c r="D110" s="100" t="n"/>
-      <c r="E110" s="100" t="n"/>
-      <c r="F110" s="100" t="n"/>
-      <c r="G110" s="100" t="n"/>
-      <c r="H110" s="100" t="n"/>
-    </row>
-    <row r="111" ht="15" customHeight="1" s="52">
-      <c r="A111" s="102" t="n"/>
-      <c r="B111" s="100" t="n"/>
-      <c r="C111" s="100" t="n"/>
-      <c r="D111" s="100" t="n"/>
-      <c r="E111" s="100" t="n"/>
-      <c r="F111" s="100" t="n"/>
-      <c r="G111" s="100" t="n"/>
-      <c r="H111" s="100" t="n"/>
-    </row>
-    <row r="112" ht="15" customHeight="1" s="52">
-      <c r="A112" s="102" t="n"/>
-      <c r="B112" s="100" t="n"/>
-      <c r="C112" s="100" t="n"/>
-      <c r="D112" s="100" t="n"/>
-      <c r="E112" s="100" t="n"/>
-      <c r="F112" s="100" t="n"/>
-      <c r="G112" s="100" t="n"/>
-      <c r="H112" s="100" t="n"/>
-    </row>
-    <row r="113" ht="15" customHeight="1" s="52">
-      <c r="A113" s="102" t="n"/>
-      <c r="B113" s="100" t="n"/>
-      <c r="C113" s="100" t="n"/>
-      <c r="D113" s="100" t="n"/>
-      <c r="E113" s="100" t="n"/>
-      <c r="F113" s="100" t="n"/>
-      <c r="G113" s="100" t="n"/>
-      <c r="H113" s="100" t="n"/>
-    </row>
-    <row r="114" ht="15" customHeight="1" s="52">
-      <c r="A114" s="102" t="n"/>
-      <c r="B114" s="100" t="n"/>
-      <c r="C114" s="100" t="n"/>
-      <c r="D114" s="100" t="n"/>
-      <c r="E114" s="100" t="n"/>
-      <c r="F114" s="100" t="n"/>
-      <c r="G114" s="100" t="n"/>
-      <c r="H114" s="100" t="n"/>
-    </row>
-    <row r="115" ht="15" customHeight="1" s="52">
-      <c r="A115" s="102" t="n"/>
-      <c r="B115" s="100" t="n"/>
-      <c r="C115" s="100" t="n"/>
-      <c r="D115" s="100" t="n"/>
-      <c r="E115" s="100" t="n"/>
-      <c r="F115" s="100" t="n"/>
-      <c r="G115" s="100" t="n"/>
-      <c r="H115" s="100" t="n"/>
-    </row>
-    <row r="116" ht="15" customHeight="1" s="52">
-      <c r="A116" s="102" t="n"/>
-      <c r="B116" s="100" t="n"/>
-      <c r="C116" s="100" t="n"/>
-      <c r="D116" s="100" t="n"/>
-      <c r="E116" s="100" t="n"/>
-      <c r="F116" s="100" t="n"/>
-      <c r="G116" s="100" t="n"/>
-      <c r="H116" s="100" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1" s="52">
-      <c r="A117" s="102" t="n"/>
-      <c r="B117" s="100" t="n"/>
-      <c r="C117" s="100" t="n"/>
-      <c r="D117" s="100" t="n"/>
-      <c r="E117" s="100" t="n"/>
-      <c r="F117" s="100" t="n"/>
-      <c r="G117" s="100" t="n"/>
-      <c r="H117" s="100" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1" s="52">
-      <c r="A118" s="102" t="n"/>
-      <c r="B118" s="100" t="n"/>
-      <c r="C118" s="100" t="n"/>
-      <c r="D118" s="100" t="n"/>
-      <c r="E118" s="100" t="n"/>
-      <c r="F118" s="100" t="n"/>
-      <c r="G118" s="100" t="n"/>
-      <c r="H118" s="100" t="n"/>
-    </row>
-    <row r="119" ht="15" customHeight="1" s="52">
-      <c r="A119" s="102" t="n"/>
-      <c r="B119" s="100" t="n"/>
-      <c r="C119" s="100" t="n"/>
-      <c r="D119" s="100" t="n"/>
-      <c r="E119" s="100" t="n"/>
-      <c r="F119" s="100" t="n"/>
-      <c r="G119" s="100" t="n"/>
-      <c r="H119" s="100" t="n"/>
-    </row>
-    <row r="120" ht="15" customHeight="1" s="52">
-      <c r="A120" s="102" t="n"/>
-      <c r="B120" s="100" t="n"/>
-      <c r="C120" s="100" t="n"/>
-      <c r="D120" s="100" t="n"/>
-      <c r="E120" s="100" t="n"/>
-      <c r="F120" s="100" t="n"/>
-      <c r="G120" s="100" t="n"/>
-      <c r="H120" s="100" t="n"/>
-    </row>
-    <row r="121" ht="15" customHeight="1" s="52">
-      <c r="A121" s="102" t="n"/>
-      <c r="B121" s="100" t="n"/>
-      <c r="C121" s="100" t="n"/>
-      <c r="D121" s="100" t="n"/>
-      <c r="E121" s="100" t="n"/>
-      <c r="F121" s="100" t="n"/>
-      <c r="G121" s="100" t="n"/>
-      <c r="H121" s="100" t="n"/>
-    </row>
-    <row r="122" ht="15" customHeight="1" s="52">
-      <c r="A122" s="102" t="n"/>
-      <c r="B122" s="100" t="n"/>
-      <c r="C122" s="100" t="n"/>
-      <c r="D122" s="100" t="n"/>
-      <c r="E122" s="100" t="n"/>
-      <c r="F122" s="100" t="n"/>
-      <c r="G122" s="100" t="n"/>
-      <c r="H122" s="100" t="n"/>
-    </row>
-    <row r="123" ht="15" customHeight="1" s="52">
-      <c r="A123" s="102" t="n"/>
-      <c r="B123" s="100" t="n"/>
-      <c r="C123" s="100" t="n"/>
-      <c r="D123" s="100" t="n"/>
-      <c r="E123" s="100" t="n"/>
-      <c r="F123" s="100" t="n"/>
-      <c r="G123" s="100" t="n"/>
-      <c r="H123" s="100" t="n"/>
-    </row>
-    <row r="124" ht="15" customHeight="1" s="52">
-      <c r="A124" s="102" t="n"/>
-      <c r="B124" s="100" t="n"/>
-      <c r="C124" s="100" t="n"/>
-      <c r="D124" s="100" t="n"/>
-      <c r="E124" s="100" t="n"/>
-      <c r="F124" s="100" t="n"/>
-      <c r="G124" s="100" t="n"/>
-      <c r="H124" s="100" t="n"/>
-    </row>
-    <row r="125" ht="15" customHeight="1" s="52">
-      <c r="A125" s="102" t="n"/>
-      <c r="B125" s="100" t="n"/>
-      <c r="C125" s="100" t="n"/>
-      <c r="D125" s="100" t="n"/>
-      <c r="E125" s="100" t="n"/>
-      <c r="F125" s="100" t="n"/>
-      <c r="G125" s="100" t="n"/>
-      <c r="H125" s="100" t="n"/>
-    </row>
-    <row r="126" ht="15" customHeight="1" s="52">
-      <c r="A126" s="102" t="n"/>
-      <c r="B126" s="100" t="n"/>
-      <c r="C126" s="100" t="n"/>
-      <c r="D126" s="100" t="n"/>
-      <c r="E126" s="100" t="n"/>
-      <c r="F126" s="100" t="n"/>
-      <c r="G126" s="100" t="n"/>
-      <c r="H126" s="100" t="n"/>
-    </row>
-    <row r="127" ht="15" customHeight="1" s="52">
-      <c r="A127" s="102" t="n"/>
-      <c r="B127" s="100" t="n"/>
-      <c r="C127" s="100" t="n"/>
-      <c r="D127" s="100" t="n"/>
-      <c r="E127" s="100" t="n"/>
-      <c r="F127" s="100" t="n"/>
-      <c r="G127" s="100" t="n"/>
-      <c r="H127" s="100" t="n"/>
-    </row>
-    <row r="128" ht="15" customHeight="1" s="52">
-      <c r="A128" s="102" t="n"/>
-      <c r="B128" s="100" t="n"/>
-      <c r="C128" s="100" t="n"/>
-      <c r="D128" s="100" t="n"/>
-      <c r="E128" s="100" t="n"/>
-      <c r="F128" s="100" t="n"/>
-      <c r="G128" s="100" t="n"/>
-      <c r="H128" s="100" t="n"/>
-    </row>
-    <row r="129" ht="15" customHeight="1" s="52">
-      <c r="A129" s="102" t="n"/>
-      <c r="B129" s="100" t="n"/>
-      <c r="C129" s="100" t="n"/>
-      <c r="D129" s="100" t="n"/>
-      <c r="E129" s="100" t="n"/>
-      <c r="F129" s="100" t="n"/>
-      <c r="G129" s="100" t="n"/>
-      <c r="H129" s="100" t="n"/>
-    </row>
-    <row r="130" ht="15" customHeight="1" s="52">
-      <c r="A130" s="102" t="n"/>
-      <c r="B130" s="100" t="n"/>
-      <c r="C130" s="100" t="n"/>
-      <c r="D130" s="100" t="n"/>
-      <c r="E130" s="100" t="n"/>
-      <c r="F130" s="100" t="n"/>
-      <c r="G130" s="100" t="n"/>
-      <c r="H130" s="100" t="n"/>
-    </row>
-    <row r="131" ht="15" customHeight="1" s="52">
-      <c r="A131" s="102" t="n"/>
-      <c r="B131" s="100" t="n"/>
-      <c r="C131" s="100" t="n"/>
-      <c r="D131" s="100" t="n"/>
-      <c r="E131" s="100" t="n"/>
-      <c r="F131" s="100" t="n"/>
-      <c r="G131" s="100" t="n"/>
-      <c r="H131" s="100" t="n"/>
-    </row>
-    <row r="132" ht="15" customHeight="1" s="52">
-      <c r="A132" s="102" t="n"/>
-      <c r="B132" s="100" t="n"/>
-      <c r="C132" s="100" t="n"/>
-      <c r="D132" s="100" t="n"/>
-      <c r="E132" s="100" t="n"/>
-      <c r="F132" s="100" t="n"/>
-      <c r="G132" s="100" t="n"/>
-      <c r="H132" s="100" t="n"/>
-    </row>
-    <row r="133" ht="15" customHeight="1" s="52">
-      <c r="A133" s="102" t="n"/>
-      <c r="B133" s="100" t="n"/>
-      <c r="C133" s="100" t="n"/>
-      <c r="D133" s="100" t="n"/>
-      <c r="E133" s="100" t="n"/>
-      <c r="F133" s="100" t="n"/>
-      <c r="G133" s="100" t="n"/>
-      <c r="H133" s="100" t="n"/>
-    </row>
-    <row r="134" ht="15" customHeight="1" s="52">
-      <c r="A134" s="102" t="n"/>
-      <c r="B134" s="100" t="n"/>
-      <c r="C134" s="100" t="n"/>
-      <c r="D134" s="100" t="n"/>
-      <c r="E134" s="100" t="n"/>
-      <c r="F134" s="100" t="n"/>
-      <c r="G134" s="100" t="n"/>
-      <c r="H134" s="100" t="n"/>
-    </row>
-    <row r="135" ht="15" customHeight="1" s="52">
-      <c r="A135" s="102" t="n"/>
-      <c r="B135" s="100" t="n"/>
-      <c r="C135" s="100" t="n"/>
-      <c r="D135" s="100" t="n"/>
-      <c r="E135" s="100" t="n"/>
-      <c r="F135" s="100" t="n"/>
-      <c r="G135" s="100" t="n"/>
-      <c r="H135" s="100" t="n"/>
-    </row>
-    <row r="136" ht="15" customHeight="1" s="52">
-      <c r="A136" s="102" t="n"/>
-      <c r="B136" s="100" t="n"/>
-      <c r="C136" s="100" t="n"/>
-      <c r="D136" s="100" t="n"/>
-      <c r="E136" s="100" t="n"/>
-      <c r="F136" s="100" t="n"/>
-      <c r="G136" s="100" t="n"/>
-      <c r="H136" s="100" t="n"/>
-    </row>
-    <row r="137" ht="15" customHeight="1" s="52">
-      <c r="A137" s="102" t="n"/>
-      <c r="B137" s="100" t="n"/>
-      <c r="C137" s="100" t="n"/>
-      <c r="D137" s="100" t="n"/>
-      <c r="E137" s="100" t="n"/>
-      <c r="F137" s="100" t="n"/>
-      <c r="G137" s="100" t="n"/>
-      <c r="H137" s="100" t="n"/>
-    </row>
-    <row r="138" ht="15" customHeight="1" s="52">
-      <c r="A138" s="102" t="n"/>
-      <c r="B138" s="100" t="n"/>
-      <c r="C138" s="100" t="n"/>
-      <c r="D138" s="100" t="n"/>
-      <c r="E138" s="100" t="n"/>
-      <c r="F138" s="100" t="n"/>
-      <c r="G138" s="100" t="n"/>
-      <c r="H138" s="100" t="n"/>
-    </row>
-    <row r="139" ht="15" customHeight="1" s="52">
-      <c r="A139" s="102" t="n"/>
-      <c r="B139" s="100" t="n"/>
-      <c r="C139" s="100" t="n"/>
-      <c r="D139" s="100" t="n"/>
-      <c r="E139" s="100" t="n"/>
-      <c r="F139" s="100" t="n"/>
-      <c r="G139" s="100" t="n"/>
-      <c r="H139" s="100" t="n"/>
-    </row>
-    <row r="140" ht="15" customHeight="1" s="52">
-      <c r="A140" s="102" t="n"/>
-      <c r="B140" s="100" t="n"/>
-      <c r="C140" s="100" t="n"/>
-      <c r="D140" s="100" t="n"/>
-      <c r="E140" s="100" t="n"/>
-      <c r="F140" s="100" t="n"/>
-      <c r="G140" s="100" t="n"/>
-      <c r="H140" s="100" t="n"/>
-    </row>
-    <row r="141" ht="15" customHeight="1" s="52">
-      <c r="A141" s="102" t="n"/>
-      <c r="B141" s="100" t="n"/>
-      <c r="C141" s="100" t="n"/>
-      <c r="D141" s="100" t="n"/>
-      <c r="E141" s="100" t="n"/>
-      <c r="F141" s="100" t="n"/>
-      <c r="G141" s="100" t="n"/>
-      <c r="H141" s="100" t="n"/>
-    </row>
-    <row r="142" ht="15" customHeight="1" s="52">
-      <c r="A142" s="102" t="n"/>
-      <c r="B142" s="100" t="n"/>
-      <c r="C142" s="100" t="n"/>
-      <c r="D142" s="100" t="n"/>
-      <c r="E142" s="100" t="n"/>
-      <c r="F142" s="100" t="n"/>
-      <c r="G142" s="100" t="n"/>
-      <c r="H142" s="100" t="n"/>
-    </row>
-    <row r="143" ht="15" customHeight="1" s="52">
-      <c r="A143" s="102" t="n"/>
-      <c r="B143" s="100" t="n"/>
-      <c r="C143" s="100" t="n"/>
-      <c r="D143" s="100" t="n"/>
-      <c r="E143" s="100" t="n"/>
-      <c r="F143" s="100" t="n"/>
-      <c r="G143" s="100" t="n"/>
-      <c r="H143" s="100" t="n"/>
-    </row>
-    <row r="144" ht="15" customHeight="1" s="52">
-      <c r="A144" s="102" t="n"/>
-      <c r="B144" s="100" t="n"/>
-      <c r="C144" s="100" t="n"/>
-      <c r="D144" s="100" t="n"/>
-      <c r="E144" s="100" t="n"/>
-      <c r="F144" s="100" t="n"/>
-      <c r="G144" s="100" t="n"/>
-      <c r="H144" s="100" t="n"/>
-    </row>
-    <row r="145" ht="15" customHeight="1" s="52">
-      <c r="A145" s="102" t="n"/>
-      <c r="B145" s="100" t="n"/>
-      <c r="C145" s="100" t="n"/>
-      <c r="D145" s="100" t="n"/>
-      <c r="E145" s="100" t="n"/>
-      <c r="F145" s="100" t="n"/>
-      <c r="G145" s="100" t="n"/>
-      <c r="H145" s="100" t="n"/>
-    </row>
-    <row r="146" ht="15" customHeight="1" s="52">
-      <c r="A146" s="102" t="n"/>
-      <c r="B146" s="100" t="n"/>
-      <c r="C146" s="100" t="n"/>
-      <c r="D146" s="100" t="n"/>
-      <c r="E146" s="100" t="n"/>
-      <c r="F146" s="100" t="n"/>
-      <c r="G146" s="100" t="n"/>
-      <c r="H146" s="100" t="n"/>
-    </row>
-    <row r="147" ht="15" customHeight="1" s="52">
-      <c r="A147" s="102" t="n"/>
-      <c r="B147" s="100" t="n"/>
-      <c r="C147" s="100" t="n"/>
-      <c r="D147" s="100" t="n"/>
-      <c r="E147" s="100" t="n"/>
-      <c r="F147" s="100" t="n"/>
-      <c r="G147" s="100" t="n"/>
-      <c r="H147" s="100" t="n"/>
-    </row>
-    <row r="148" ht="15" customHeight="1" s="52">
-      <c r="A148" s="102" t="n"/>
-      <c r="B148" s="100" t="n"/>
-      <c r="C148" s="100" t="n"/>
-      <c r="D148" s="100" t="n"/>
-      <c r="E148" s="100" t="n"/>
-      <c r="F148" s="100" t="n"/>
-      <c r="G148" s="100" t="n"/>
-      <c r="H148" s="100" t="n"/>
-    </row>
-    <row r="149" ht="15" customHeight="1" s="52">
-      <c r="A149" s="102" t="n"/>
-      <c r="B149" s="100" t="n"/>
-      <c r="C149" s="100" t="n"/>
-      <c r="D149" s="100" t="n"/>
-      <c r="E149" s="100" t="n"/>
-      <c r="F149" s="100" t="n"/>
-      <c r="G149" s="100" t="n"/>
-      <c r="H149" s="100" t="n"/>
-    </row>
-    <row r="150" ht="15" customHeight="1" s="52">
-      <c r="A150" s="102" t="n"/>
-      <c r="B150" s="100" t="n"/>
-      <c r="C150" s="100" t="n"/>
-      <c r="D150" s="100" t="n"/>
-      <c r="E150" s="100" t="n"/>
-      <c r="F150" s="100" t="n"/>
-      <c r="G150" s="100" t="n"/>
-      <c r="H150" s="100" t="n"/>
-    </row>
-    <row r="151" ht="15" customHeight="1" s="52">
-      <c r="A151" s="102" t="n"/>
-      <c r="B151" s="100" t="n"/>
-      <c r="C151" s="100" t="n"/>
-      <c r="D151" s="100" t="n"/>
-      <c r="E151" s="100" t="n"/>
-      <c r="F151" s="100" t="n"/>
-      <c r="G151" s="100" t="n"/>
-      <c r="H151" s="100" t="n"/>
-    </row>
-    <row r="152" ht="15" customHeight="1" s="52">
-      <c r="A152" s="102" t="n"/>
-      <c r="B152" s="100" t="n"/>
-      <c r="C152" s="100" t="n"/>
-      <c r="D152" s="100" t="n"/>
-      <c r="E152" s="100" t="n"/>
-      <c r="F152" s="100" t="n"/>
-      <c r="G152" s="100" t="n"/>
-      <c r="H152" s="100" t="n"/>
-    </row>
-    <row r="153" ht="15" customHeight="1" s="52">
-      <c r="A153" s="102" t="n"/>
-      <c r="B153" s="100" t="n"/>
-      <c r="C153" s="100" t="n"/>
-      <c r="D153" s="100" t="n"/>
-      <c r="E153" s="100" t="n"/>
-      <c r="F153" s="100" t="n"/>
-      <c r="G153" s="100" t="n"/>
-      <c r="H153" s="100" t="n"/>
-    </row>
-    <row r="154" ht="15" customHeight="1" s="52">
-      <c r="A154" s="102" t="n"/>
-      <c r="B154" s="100" t="n"/>
-      <c r="C154" s="100" t="n"/>
-      <c r="D154" s="100" t="n"/>
-      <c r="E154" s="100" t="n"/>
-      <c r="F154" s="100" t="n"/>
-      <c r="G154" s="100" t="n"/>
-      <c r="H154" s="100" t="n"/>
-    </row>
-    <row r="155" ht="15" customHeight="1" s="52">
-      <c r="A155" s="102" t="n"/>
-      <c r="B155" s="100" t="n"/>
-      <c r="C155" s="100" t="n"/>
-      <c r="D155" s="100" t="n"/>
-      <c r="E155" s="100" t="n"/>
-      <c r="F155" s="100" t="n"/>
-      <c r="G155" s="100" t="n"/>
-      <c r="H155" s="100" t="n"/>
-    </row>
-    <row r="156" ht="15" customHeight="1" s="52">
-      <c r="A156" s="102" t="n"/>
-      <c r="B156" s="100" t="n"/>
-      <c r="C156" s="100" t="n"/>
-      <c r="D156" s="100" t="n"/>
-      <c r="E156" s="100" t="n"/>
-      <c r="F156" s="100" t="n"/>
-      <c r="G156" s="100" t="n"/>
-      <c r="H156" s="100" t="n"/>
-    </row>
-    <row r="157" ht="15" customHeight="1" s="52">
-      <c r="A157" s="102" t="n"/>
-      <c r="B157" s="100" t="n"/>
-      <c r="C157" s="100" t="n"/>
-      <c r="D157" s="100" t="n"/>
-      <c r="E157" s="100" t="n"/>
-      <c r="F157" s="100" t="n"/>
-      <c r="G157" s="100" t="n"/>
-      <c r="H157" s="100" t="n"/>
-    </row>
-    <row r="158" ht="15" customHeight="1" s="52">
-      <c r="A158" s="102" t="n"/>
-      <c r="B158" s="100" t="n"/>
-      <c r="C158" s="100" t="n"/>
-      <c r="D158" s="100" t="n"/>
-      <c r="E158" s="100" t="n"/>
-      <c r="F158" s="100" t="n"/>
-      <c r="G158" s="100" t="n"/>
-      <c r="H158" s="100" t="n"/>
-    </row>
-    <row r="159" ht="15" customHeight="1" s="52">
-      <c r="A159" s="102" t="n"/>
-      <c r="B159" s="100" t="n"/>
-      <c r="C159" s="100" t="n"/>
-      <c r="D159" s="100" t="n"/>
-      <c r="E159" s="100" t="n"/>
-      <c r="F159" s="100" t="n"/>
-      <c r="G159" s="100" t="n"/>
-      <c r="H159" s="100" t="n"/>
-    </row>
-    <row r="160" ht="15" customHeight="1" s="52">
-      <c r="A160" s="102" t="n"/>
-      <c r="B160" s="100" t="n"/>
-      <c r="C160" s="100" t="n"/>
-      <c r="D160" s="100" t="n"/>
-      <c r="E160" s="100" t="n"/>
-      <c r="F160" s="100" t="n"/>
-      <c r="G160" s="100" t="n"/>
-      <c r="H160" s="100" t="n"/>
-    </row>
-    <row r="161" ht="15" customHeight="1" s="52">
-      <c r="A161" s="102" t="n"/>
-      <c r="B161" s="100" t="n"/>
-      <c r="C161" s="100" t="n"/>
-      <c r="D161" s="100" t="n"/>
-      <c r="E161" s="100" t="n"/>
-      <c r="F161" s="100" t="n"/>
-      <c r="G161" s="100" t="n"/>
-      <c r="H161" s="100" t="n"/>
-    </row>
-    <row r="162" ht="15" customHeight="1" s="52">
-      <c r="A162" s="102" t="n"/>
-      <c r="B162" s="100" t="n"/>
-      <c r="C162" s="100" t="n"/>
-      <c r="D162" s="100" t="n"/>
-      <c r="E162" s="100" t="n"/>
-      <c r="F162" s="100" t="n"/>
-      <c r="G162" s="100" t="n"/>
-      <c r="H162" s="100" t="n"/>
-    </row>
-    <row r="163" ht="15" customHeight="1" s="52">
-      <c r="A163" s="102" t="n"/>
-      <c r="B163" s="100" t="n"/>
-      <c r="C163" s="100" t="n"/>
-      <c r="D163" s="100" t="n"/>
-      <c r="E163" s="100" t="n"/>
-      <c r="F163" s="100" t="n"/>
-      <c r="G163" s="100" t="n"/>
-      <c r="H163" s="100" t="n"/>
-    </row>
-    <row r="164" ht="15" customHeight="1" s="52">
-      <c r="A164" s="102" t="n"/>
-      <c r="B164" s="100" t="n"/>
-      <c r="C164" s="100" t="n"/>
-      <c r="D164" s="100" t="n"/>
-      <c r="E164" s="100" t="n"/>
-      <c r="F164" s="100" t="n"/>
-      <c r="G164" s="100" t="n"/>
-      <c r="H164" s="100" t="n"/>
-    </row>
-    <row r="165" ht="15" customHeight="1" s="52">
-      <c r="A165" s="102" t="n"/>
-      <c r="B165" s="100" t="n"/>
-      <c r="C165" s="100" t="n"/>
-      <c r="D165" s="100" t="n"/>
-      <c r="E165" s="100" t="n"/>
-      <c r="F165" s="100" t="n"/>
-      <c r="G165" s="100" t="n"/>
-      <c r="H165" s="100" t="n"/>
-    </row>
-    <row r="166" ht="15" customHeight="1" s="52">
-      <c r="A166" s="102" t="n"/>
-      <c r="B166" s="100" t="n"/>
-      <c r="C166" s="100" t="n"/>
-      <c r="D166" s="100" t="n"/>
-      <c r="E166" s="100" t="n"/>
-      <c r="F166" s="100" t="n"/>
-      <c r="G166" s="100" t="n"/>
-      <c r="H166" s="100" t="n"/>
-    </row>
-    <row r="167" ht="15" customHeight="1" s="52">
-      <c r="A167" s="102" t="n"/>
-      <c r="B167" s="100" t="n"/>
-      <c r="C167" s="100" t="n"/>
-      <c r="D167" s="100" t="n"/>
-      <c r="E167" s="100" t="n"/>
-      <c r="F167" s="100" t="n"/>
-      <c r="G167" s="100" t="n"/>
-      <c r="H167" s="100" t="n"/>
-    </row>
-    <row r="168" ht="15" customHeight="1" s="52">
-      <c r="A168" s="102" t="n"/>
-      <c r="B168" s="100" t="n"/>
-      <c r="C168" s="100" t="n"/>
-      <c r="D168" s="100" t="n"/>
-      <c r="E168" s="100" t="n"/>
-      <c r="F168" s="100" t="n"/>
-      <c r="G168" s="100" t="n"/>
-      <c r="H168" s="100" t="n"/>
-    </row>
-    <row r="169" ht="15" customHeight="1" s="52">
-      <c r="A169" s="102" t="n"/>
-      <c r="B169" s="100" t="n"/>
-      <c r="C169" s="100" t="n"/>
-      <c r="D169" s="100" t="n"/>
-      <c r="E169" s="100" t="n"/>
-      <c r="F169" s="100" t="n"/>
-      <c r="G169" s="100" t="n"/>
-      <c r="H169" s="100" t="n"/>
-    </row>
-    <row r="170" ht="15" customHeight="1" s="52">
-      <c r="A170" s="102" t="n"/>
-      <c r="B170" s="100" t="n"/>
-      <c r="C170" s="100" t="n"/>
-      <c r="D170" s="100" t="n"/>
-      <c r="E170" s="100" t="n"/>
-      <c r="F170" s="100" t="n"/>
-      <c r="G170" s="100" t="n"/>
-      <c r="H170" s="100" t="n"/>
-    </row>
-    <row r="171" ht="15" customHeight="1" s="52">
-      <c r="A171" s="102" t="n"/>
-      <c r="B171" s="100" t="n"/>
-      <c r="C171" s="100" t="n"/>
-      <c r="D171" s="100" t="n"/>
-      <c r="E171" s="100" t="n"/>
-      <c r="F171" s="100" t="n"/>
-      <c r="G171" s="100" t="n"/>
-      <c r="H171" s="100" t="n"/>
-    </row>
-    <row r="172" ht="15" customHeight="1" s="52">
-      <c r="A172" s="102" t="n"/>
-      <c r="B172" s="100" t="n"/>
-      <c r="C172" s="100" t="n"/>
-      <c r="D172" s="100" t="n"/>
-      <c r="E172" s="100" t="n"/>
-      <c r="F172" s="100" t="n"/>
-      <c r="G172" s="100" t="n"/>
-      <c r="H172" s="100" t="n"/>
-    </row>
-    <row r="173" ht="15" customHeight="1" s="52">
-      <c r="A173" s="102" t="n"/>
-      <c r="B173" s="100" t="n"/>
-      <c r="C173" s="100" t="n"/>
-      <c r="D173" s="100" t="n"/>
-      <c r="E173" s="100" t="n"/>
-      <c r="F173" s="100" t="n"/>
-      <c r="G173" s="100" t="n"/>
-      <c r="H173" s="100" t="n"/>
-    </row>
-    <row r="174" ht="15" customHeight="1" s="52">
-      <c r="A174" s="102" t="n"/>
-      <c r="B174" s="100" t="n"/>
-      <c r="C174" s="100" t="n"/>
-      <c r="D174" s="100" t="n"/>
-      <c r="E174" s="100" t="n"/>
-      <c r="F174" s="100" t="n"/>
-      <c r="G174" s="100" t="n"/>
-      <c r="H174" s="100" t="n"/>
-    </row>
-    <row r="175" ht="15" customHeight="1" s="52">
-      <c r="A175" s="102" t="n"/>
-      <c r="B175" s="100" t="n"/>
-      <c r="C175" s="100" t="n"/>
-      <c r="D175" s="100" t="n"/>
-      <c r="E175" s="100" t="n"/>
-      <c r="F175" s="100" t="n"/>
-      <c r="G175" s="100" t="n"/>
-      <c r="H175" s="100" t="n"/>
-    </row>
-    <row r="176" ht="15" customHeight="1" s="52">
-      <c r="A176" s="102" t="n"/>
-      <c r="B176" s="100" t="n"/>
-      <c r="C176" s="100" t="n"/>
-      <c r="D176" s="100" t="n"/>
-      <c r="E176" s="100" t="n"/>
-      <c r="F176" s="100" t="n"/>
-      <c r="G176" s="100" t="n"/>
-      <c r="H176" s="100" t="n"/>
-    </row>
-    <row r="177" ht="15" customHeight="1" s="52">
-      <c r="A177" s="102" t="n"/>
-      <c r="B177" s="100" t="n"/>
-      <c r="C177" s="100" t="n"/>
-      <c r="D177" s="100" t="n"/>
-      <c r="E177" s="100" t="n"/>
-      <c r="F177" s="100" t="n"/>
-      <c r="G177" s="100" t="n"/>
-      <c r="H177" s="100" t="n"/>
-    </row>
-    <row r="178" ht="15" customHeight="1" s="52">
-      <c r="A178" s="102" t="n"/>
-      <c r="B178" s="100" t="n"/>
-      <c r="C178" s="100" t="n"/>
-      <c r="D178" s="100" t="n"/>
-      <c r="E178" s="100" t="n"/>
-      <c r="F178" s="100" t="n"/>
-      <c r="G178" s="100" t="n"/>
-      <c r="H178" s="100" t="n"/>
-    </row>
-    <row r="179" ht="15" customHeight="1" s="52">
-      <c r="A179" s="102" t="n"/>
-      <c r="B179" s="100" t="n"/>
-      <c r="C179" s="100" t="n"/>
-      <c r="D179" s="100" t="n"/>
-      <c r="E179" s="100" t="n"/>
-      <c r="F179" s="100" t="n"/>
-      <c r="G179" s="100" t="n"/>
-      <c r="H179" s="100" t="n"/>
-    </row>
-    <row r="180" ht="15" customHeight="1" s="52">
-      <c r="A180" s="102" t="n"/>
-      <c r="B180" s="100" t="n"/>
-      <c r="C180" s="100" t="n"/>
-      <c r="D180" s="100" t="n"/>
-      <c r="E180" s="100" t="n"/>
-      <c r="F180" s="100" t="n"/>
-      <c r="G180" s="100" t="n"/>
-      <c r="H180" s="100" t="n"/>
-    </row>
-    <row r="181" ht="15" customHeight="1" s="52">
-      <c r="A181" s="102" t="n"/>
-      <c r="B181" s="100" t="n"/>
-      <c r="C181" s="100" t="n"/>
-      <c r="D181" s="100" t="n"/>
-      <c r="E181" s="100" t="n"/>
-      <c r="F181" s="100" t="n"/>
-      <c r="G181" s="100" t="n"/>
-      <c r="H181" s="100" t="n"/>
-    </row>
-    <row r="182" ht="15" customHeight="1" s="52">
-      <c r="A182" s="102" t="n"/>
-      <c r="B182" s="100" t="n"/>
-      <c r="C182" s="100" t="n"/>
-      <c r="D182" s="100" t="n"/>
-      <c r="E182" s="100" t="n"/>
-      <c r="F182" s="100" t="n"/>
-      <c r="G182" s="100" t="n"/>
-      <c r="H182" s="100" t="n"/>
-    </row>
-    <row r="183" ht="15" customHeight="1" s="52">
-      <c r="A183" s="102" t="n"/>
-      <c r="B183" s="100" t="n"/>
-      <c r="C183" s="100" t="n"/>
-      <c r="D183" s="100" t="n"/>
-      <c r="E183" s="100" t="n"/>
-      <c r="F183" s="100" t="n"/>
-      <c r="G183" s="100" t="n"/>
-      <c r="H183" s="100" t="n"/>
-    </row>
-    <row r="184" ht="15" customHeight="1" s="52">
-      <c r="A184" s="102" t="n"/>
-      <c r="B184" s="100" t="n"/>
-      <c r="C184" s="100" t="n"/>
-      <c r="D184" s="100" t="n"/>
-      <c r="E184" s="100" t="n"/>
-      <c r="F184" s="100" t="n"/>
-      <c r="G184" s="100" t="n"/>
-      <c r="H184" s="100" t="n"/>
-    </row>
-    <row r="185" ht="15" customHeight="1" s="52">
-      <c r="A185" s="102" t="n"/>
-      <c r="B185" s="100" t="n"/>
-      <c r="C185" s="100" t="n"/>
-      <c r="D185" s="100" t="n"/>
-      <c r="E185" s="100" t="n"/>
-      <c r="F185" s="100" t="n"/>
-      <c r="G185" s="100" t="n"/>
-      <c r="H185" s="100" t="n"/>
-    </row>
-    <row r="186" ht="15" customHeight="1" s="52">
-      <c r="A186" s="102" t="n"/>
-      <c r="B186" s="100" t="n"/>
-      <c r="C186" s="100" t="n"/>
-      <c r="D186" s="100" t="n"/>
-      <c r="E186" s="100" t="n"/>
-      <c r="F186" s="100" t="n"/>
-      <c r="G186" s="100" t="n"/>
-      <c r="H186" s="100" t="n"/>
-    </row>
-    <row r="187" ht="15" customHeight="1" s="52">
-      <c r="A187" s="102" t="n"/>
-      <c r="B187" s="100" t="n"/>
-      <c r="C187" s="100" t="n"/>
-      <c r="D187" s="100" t="n"/>
-      <c r="E187" s="100" t="n"/>
-      <c r="F187" s="100" t="n"/>
-      <c r="G187" s="100" t="n"/>
-      <c r="H187" s="100" t="n"/>
-    </row>
-    <row r="188" ht="15" customHeight="1" s="52">
-      <c r="A188" s="102" t="n"/>
-      <c r="B188" s="100" t="n"/>
-      <c r="C188" s="100" t="n"/>
-      <c r="D188" s="100" t="n"/>
-      <c r="E188" s="100" t="n"/>
-      <c r="F188" s="100" t="n"/>
-      <c r="G188" s="100" t="n"/>
-      <c r="H188" s="100" t="n"/>
-    </row>
-    <row r="189" ht="15" customHeight="1" s="52">
-      <c r="A189" s="102" t="n"/>
-      <c r="B189" s="100" t="n"/>
-      <c r="C189" s="100" t="n"/>
-      <c r="D189" s="100" t="n"/>
-      <c r="E189" s="100" t="n"/>
-      <c r="F189" s="100" t="n"/>
-      <c r="G189" s="100" t="n"/>
-      <c r="H189" s="100" t="n"/>
-    </row>
-    <row r="190" ht="15" customHeight="1" s="52">
-      <c r="A190" s="102" t="n"/>
-      <c r="B190" s="100" t="n"/>
-      <c r="C190" s="100" t="n"/>
-      <c r="D190" s="100" t="n"/>
-      <c r="E190" s="100" t="n"/>
-      <c r="F190" s="100" t="n"/>
-      <c r="G190" s="100" t="n"/>
-      <c r="H190" s="100" t="n"/>
-    </row>
-    <row r="191" ht="15" customHeight="1" s="52">
-      <c r="A191" s="102" t="n"/>
-      <c r="B191" s="100" t="n"/>
-      <c r="C191" s="100" t="n"/>
-      <c r="D191" s="100" t="n"/>
-      <c r="E191" s="100" t="n"/>
-      <c r="F191" s="100" t="n"/>
-      <c r="G191" s="100" t="n"/>
-      <c r="H191" s="100" t="n"/>
-    </row>
-    <row r="192" ht="15" customHeight="1" s="52">
-      <c r="A192" s="102" t="n"/>
-      <c r="B192" s="100" t="n"/>
-      <c r="C192" s="100" t="n"/>
-      <c r="D192" s="100" t="n"/>
-      <c r="E192" s="100" t="n"/>
-      <c r="F192" s="100" t="n"/>
-      <c r="G192" s="100" t="n"/>
-      <c r="H192" s="100" t="n"/>
-    </row>
-    <row r="193" ht="15" customHeight="1" s="52">
-      <c r="A193" s="102" t="n"/>
-      <c r="B193" s="100" t="n"/>
-      <c r="C193" s="100" t="n"/>
-      <c r="D193" s="100" t="n"/>
-      <c r="E193" s="100" t="n"/>
-      <c r="F193" s="100" t="n"/>
-      <c r="G193" s="100" t="n"/>
-      <c r="H193" s="100" t="n"/>
-    </row>
-    <row r="194" ht="15" customHeight="1" s="52">
-      <c r="A194" s="102" t="n"/>
-      <c r="B194" s="100" t="n"/>
-      <c r="C194" s="100" t="n"/>
-      <c r="D194" s="100" t="n"/>
-      <c r="E194" s="100" t="n"/>
-      <c r="F194" s="100" t="n"/>
-      <c r="G194" s="100" t="n"/>
-      <c r="H194" s="100" t="n"/>
-    </row>
-    <row r="195" ht="15" customHeight="1" s="52">
-      <c r="A195" s="102" t="n"/>
-      <c r="B195" s="100" t="n"/>
-      <c r="C195" s="100" t="n"/>
-      <c r="D195" s="100" t="n"/>
-      <c r="E195" s="100" t="n"/>
-      <c r="F195" s="100" t="n"/>
-      <c r="G195" s="100" t="n"/>
-      <c r="H195" s="100" t="n"/>
-    </row>
-    <row r="196" ht="15" customHeight="1" s="52">
-      <c r="A196" s="102" t="n"/>
-      <c r="B196" s="100" t="n"/>
-      <c r="C196" s="100" t="n"/>
-      <c r="D196" s="100" t="n"/>
-      <c r="E196" s="100" t="n"/>
-      <c r="F196" s="100" t="n"/>
-      <c r="G196" s="100" t="n"/>
-      <c r="H196" s="100" t="n"/>
-    </row>
-    <row r="197" ht="15" customHeight="1" s="52">
-      <c r="A197" s="102" t="n"/>
-      <c r="B197" s="100" t="n"/>
-      <c r="C197" s="100" t="n"/>
-      <c r="D197" s="100" t="n"/>
-      <c r="E197" s="100" t="n"/>
-      <c r="F197" s="100" t="n"/>
-      <c r="G197" s="100" t="n"/>
-      <c r="H197" s="100" t="n"/>
-    </row>
-    <row r="198" ht="15" customHeight="1" s="52">
-      <c r="A198" s="102" t="n"/>
-      <c r="B198" s="100" t="n"/>
-      <c r="C198" s="100" t="n"/>
-      <c r="D198" s="100" t="n"/>
-      <c r="E198" s="100" t="n"/>
-      <c r="F198" s="100" t="n"/>
-      <c r="G198" s="100" t="n"/>
-      <c r="H198" s="100" t="n"/>
-    </row>
-    <row r="199" ht="15" customHeight="1" s="52">
-      <c r="A199" s="102" t="n"/>
-      <c r="B199" s="100" t="n"/>
-      <c r="C199" s="100" t="n"/>
-      <c r="D199" s="100" t="n"/>
-      <c r="E199" s="100" t="n"/>
-      <c r="F199" s="100" t="n"/>
-      <c r="G199" s="100" t="n"/>
-      <c r="H199" s="100" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
 </file>
--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -23863,12 +23863,16 @@
       <c r="K5" s="115" t="n"/>
       <c r="L5" s="115" t="inlineStr">
         <is>
-          <t>WC + GL insurance ($2M/$2M) — secured; Cyber/Info Security insurance ($6M) — secured; eMACS awarded-vendor registration; SOC 2 Type 2 — decision open, gates Tier Two &gt; $100K</t>
+          <t>WC + GL insurance ($2M/$2M); Cyber/Info Security insurance ($6M); eMACS awarded-vendor registration; SOC 2 Type 2 (gates Tier Two &gt; $100K)</t>
         </is>
       </c>
       <c r="M5" s="115" t="n"/>
       <c r="N5" s="115" t="n"/>
-      <c r="O5" s="115" t="n"/>
+      <c r="O5" s="115" t="inlineStr">
+        <is>
+          <t>Insurance COIs secured; SOC 2 Type 2 path decision still open.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="115" t="inlineStr">
@@ -23905,7 +23909,7 @@
       <c r="H6" s="115" t="n"/>
       <c r="I6" s="115" t="inlineStr">
         <is>
-          <t>Broadband infrastructure buildout — outside the VBX healthcare IT lane.</t>
+          <t>Broadband infrastructure buildout for rural utilities.</t>
         </is>
       </c>
       <c r="J6" s="115" t="n"/>
@@ -23950,7 +23954,7 @@
       <c r="H7" s="115" t="n"/>
       <c r="I7" s="115" t="inlineStr">
         <is>
-          <t>Funds residency programs, not IT vendors — no delivery scope for VBX.</t>
+          <t>Grant program funding rural residency programs rather than IT vendors.</t>
         </is>
       </c>
       <c r="J7" s="115" t="n"/>
@@ -24103,7 +24107,7 @@
       </c>
       <c r="I10" s="115" t="inlineStr">
         <is>
-          <t>Custom RRM engine and historical reporting for the IHS Web-based Environmental Health Reporting System, with IHS Standard Code Book integration, FDA 2022 Food Code Annex 7 Form 3a e-inspection forms (web + offline), legacy migration and UAT, and help-desk/O&amp;M. Services-only — VBX is the integration teammate, not the platform vendor.</t>
+          <t>Custom RRM engine and historical reporting for the IHS Web-based Environmental Health Reporting System, with IHS Standard Code Book integration, FDA 2022 Food Code Annex 7 Form 3a e-inspection forms (web + offline), legacy migration and UAT, and help-desk/O&amp;M.</t>
         </is>
       </c>
       <c r="J10" s="115" t="inlineStr">
@@ -24166,7 +24170,7 @@
       </c>
       <c r="I11" s="115" t="inlineStr">
         <is>
-          <t>FHIR-native prior-authorization interoperability for Medicaid/CHIP fee-for-service under CMS-0057-F: CRD, a DTR approach, and PAS workflow, plus transformation of roughly 760 prior-authorization policies (largest guide 338pp / 153 PA policies) into executable rules. Vendor-hosted cloud-native; the incumbent integrator builds the FHIR adjudication endpoints at no cost. FHIR-native throughout — no X12 278.</t>
+          <t>FHIR-native prior-authorization interoperability for Medicaid/CHIP fee-for-service under CMS-0057-F: CRD, a DTR approach, and PAS workflow, plus transformation of roughly 760 prior-authorization policies (largest guide 338pp / 153 PA policies) into executable rules. Vendor-hosted cloud-native. FHIR-native throughout — no X12 278.</t>
         </is>
       </c>
       <c r="J11" s="115" t="inlineStr">
@@ -24174,14 +24178,10 @@
           <t>FHIR — Da Vinci CRD + PAS; DTR approach; Prior-authorization policy transformation; Cloud-native vendor-hosted delivery; Data engineering</t>
         </is>
       </c>
-      <c r="K11" s="115" t="inlineStr">
-        <is>
-          <t>Principal Architect; Sr. Solution Architect — policy transformation; Data Engineer; CISO</t>
-        </is>
-      </c>
+      <c r="K11" s="115" t="n"/>
       <c r="L11" s="115" t="inlineStr">
         <is>
-          <t>SOC 2 — not hard-mandated (Q&amp;A #42); Cyber liability — up to $10M may be required for high-risk data vs $6M held; Possible minimum-revenue rule (Q&amp;A #73) — unresolved</t>
+          <t>SOC 2 — not hard-mandated (Q&amp;A #42); Cyber liability — up to $10M may be required for high-risk data; Possible minimum-revenue rule (Q&amp;A #73)</t>
         </is>
       </c>
       <c r="M11" s="115" t="inlineStr">
@@ -24194,7 +24194,11 @@
           <t>Vendor onboard ~Q1 2027; full compliance 01/01/2028</t>
         </is>
       </c>
-      <c r="O11" s="115" t="n"/>
+      <c r="O11" s="115" t="inlineStr">
+        <is>
+          <t>Cyber liability held is $6M against a possible $10M requirement; minimum-revenue rule unresolved.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="115" t="inlineStr">
@@ -24460,7 +24464,7 @@
       <c r="K16" s="115" t="n"/>
       <c r="L16" s="115" t="inlineStr">
         <is>
-          <t>§3.5 OCI access — granted</t>
+          <t>§3.5 OCI access requirement</t>
         </is>
       </c>
       <c r="M16" s="115" t="n"/>
@@ -24567,7 +24571,7 @@
       </c>
       <c r="I18" s="115" t="inlineStr">
         <is>
-          <t>Intelligent coding assistance for HHS-RADV risk-adjustment data validation. VBX delivers as a subcontractor on a three-party team; per-question limit 3,000 characters.</t>
+          <t>Intelligent coding assistance for HHS-RADV risk-adjustment data validation. per-question limit 3,000 characters.</t>
         </is>
       </c>
       <c r="J18" s="115" t="inlineStr">
@@ -24578,7 +24582,7 @@
       <c r="K18" s="115" t="n"/>
       <c r="L18" s="115" t="inlineStr">
         <is>
-          <t>Team-wide COI attestations — all three executed; NDA — executed 8/16</t>
+          <t>Team-wide COI attestation; NDA</t>
         </is>
       </c>
       <c r="M18" s="115" t="n"/>
@@ -24624,11 +24628,7 @@
         </is>
       </c>
       <c r="J19" s="115" t="n"/>
-      <c r="K19" s="115" t="inlineStr">
-        <is>
-          <t>Quantum physicist (PhD) — key personnel</t>
-        </is>
-      </c>
+      <c r="K19" s="115" t="n"/>
       <c r="L19" s="115" t="n"/>
       <c r="M19" s="115" t="n"/>
       <c r="N19" s="115" t="n"/>
@@ -24676,12 +24676,16 @@
       <c r="K20" s="115" t="n"/>
       <c r="L20" s="115" t="inlineStr">
         <is>
-          <t>WA Small Business / VOSB reserved-lane status — not held</t>
+          <t>WA Small Business / VOSB reserved-lane status</t>
         </is>
       </c>
       <c r="M20" s="115" t="n"/>
       <c r="N20" s="115" t="n"/>
-      <c r="O20" s="115" t="n"/>
+      <c r="O20" s="115" t="inlineStr">
+        <is>
+          <t>WA Small Business / VOSB reserved-lane status not held.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="115" t="inlineStr">
@@ -24720,7 +24724,7 @@
       <c r="H21" s="115" t="n"/>
       <c r="I21" s="115" t="inlineStr">
         <is>
-          <t>VA benefits-system modernization at RFI stage. VBX sits in a subcontractor lane through a partner channel.</t>
+          <t>VA benefits-system modernization at RFI stage.</t>
         </is>
       </c>
       <c r="J21" s="115" t="n"/>
@@ -25023,7 +25027,7 @@
       <c r="K27" s="115" t="n"/>
       <c r="L27" s="115" t="inlineStr">
         <is>
-          <t>CMMC — DFARS 7021 Level 1 vs PWS 3.8 CUI Level 2 conflict UNRESOLVED; CUI//SP-SSEL handling</t>
+          <t>CMMC — DFARS 7021 Level 1 vs PWS 3.8 CUI Level 2 (conflicting in the solicitation); CUI//SP-SSEL handling</t>
         </is>
       </c>
       <c r="M27" s="115" t="n"/>
@@ -25075,7 +25079,7 @@
       <c r="H28" s="115" t="n"/>
       <c r="I28" s="115" t="inlineStr">
         <is>
-          <t>AI-powered pre-plan-check assistant for building-permit plan review — a vendor-hosted product buy with an embedded zero-cost incumbent.</t>
+          <t>AI-powered pre-plan-check assistant for building-permit plan review — a vendor-hosted product buy.</t>
         </is>
       </c>
       <c r="J28" s="115" t="n"/>
@@ -25126,14 +25130,14 @@
       <c r="H29" s="115" t="n"/>
       <c r="I29" s="115" t="inlineStr">
         <is>
-          <t>Cooperative catalog / price-list vehicle for AI and cloud solutions — a catalog buy requiring manufacturer LOAs and distribution margin. The EV-positive path is authorized-partner admission under an awardee, at zero B&amp;P and no admin-fee exposure.</t>
+          <t>Cooperative catalog / price-list vehicle for AI and cloud solutions — a catalog buy requiring manufacturer LOAs and distribution margin.</t>
         </is>
       </c>
       <c r="J29" s="115" t="n"/>
       <c r="K29" s="115" t="n"/>
       <c r="L29" s="115" t="inlineStr">
         <is>
-          <t>SOC 2 Type 2 — absent, not remediable by 9/8/26; FedRAMP / StateRAMP — not held; K-12 student privacy (NY Ed Law 2-d, CA SOPIPA) — posture unestablished</t>
+          <t>SOC 2 Type 2; FedRAMP / StateRAMP; K-12 student privacy (NY Ed Law 2-d, CA SOPIPA)</t>
         </is>
       </c>
       <c r="M29" s="115" t="n"/>
@@ -25144,7 +25148,7 @@
       </c>
       <c r="O29" s="115" t="inlineStr">
         <is>
-          <t>No catalog, manufacturer LOAs, distribution margin, or national sales force.</t>
+          <t>No catalog, manufacturer LOAs, distribution margin, or national sales force. SOC 2 Type 2 absent and not remediable by 9/8/26; FedRAMP/StateRAMP not held; K-12 student-privacy posture unestablished.</t>
         </is>
       </c>
     </row>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -23917,7 +23917,11 @@
       <c r="L6" s="115" t="n"/>
       <c r="M6" s="115" t="n"/>
       <c r="N6" s="115" t="n"/>
-      <c r="O6" s="115" t="n"/>
+      <c r="O6" s="115" t="inlineStr">
+        <is>
+          <t>No broadband infrastructure or outside-plant construction capability — the scope sits outside the healthcare IT lane.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="115" t="inlineStr">
@@ -24011,7 +24015,11 @@
       </c>
       <c r="M8" s="115" t="n"/>
       <c r="N8" s="115" t="n"/>
-      <c r="O8" s="115" t="n"/>
+      <c r="O8" s="115" t="inlineStr">
+        <is>
+          <t>The 150-FTE past-performance floor is far above current delivery capacity, and T4NG vehicle access is not held.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="115" t="inlineStr">
@@ -24066,7 +24074,11 @@
           <t>5-year BPA</t>
         </is>
       </c>
-      <c r="O9" s="115" t="n"/>
+      <c r="O9" s="115" t="inlineStr">
+        <is>
+          <t>The four scoring gaps are structural — past-performance citability, an enforced workshare floor, vehicle economics, and being named in the technical factor — and no teaming partner closes them.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="115" t="inlineStr">
@@ -24127,7 +24139,11 @@
           <t>2027–2032</t>
         </is>
       </c>
-      <c r="O10" s="115" t="n"/>
+      <c r="O10" s="115" t="inlineStr">
+        <is>
+          <t>No COTS environmental-health reporting platform on the bench. VBX contributes integration and custom build only, so the platform baseline has to come from the prime.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="115" t="inlineStr">
@@ -24247,7 +24263,11 @@
       </c>
       <c r="M12" s="115" t="n"/>
       <c r="N12" s="115" t="n"/>
-      <c r="O12" s="115" t="n"/>
+      <c r="O12" s="115" t="inlineStr">
+        <is>
+          <t>Not an IRS-authorized e-file transmission provider, and no five-year production track record. IRS Pub 1075 FTI regime, SOC 2 and WA Secretary of State registration are not held.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="115" t="inlineStr">
@@ -24300,7 +24320,11 @@
           <t>~5 years (~$9M est.)</t>
         </is>
       </c>
-      <c r="O13" s="115" t="n"/>
+      <c r="O13" s="115" t="inlineStr">
+        <is>
+          <t>No Secret facility clearance or cleared bench available at submission, and no CMMI-SVC Level 3 appraisal.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="115" t="inlineStr">
@@ -24469,7 +24493,11 @@
       </c>
       <c r="M16" s="115" t="n"/>
       <c r="N16" s="115" t="n"/>
-      <c r="O16" s="115" t="n"/>
+      <c r="O16" s="115" t="inlineStr">
+        <is>
+          <t>GSA MAS SIN 54151HEAL is not citable as currently held while it is under schedule-refresh remediation.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="115" t="inlineStr">
@@ -24587,7 +24615,11 @@
       </c>
       <c r="M18" s="115" t="n"/>
       <c r="N18" s="115" t="n"/>
-      <c r="O18" s="115" t="n"/>
+      <c r="O18" s="115" t="inlineStr">
+        <is>
+          <t>HITRUST assessor on staff but no HITRUST audit, and the GSA MAS SIN is not citable.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="115" t="inlineStr">
@@ -24621,7 +24653,11 @@
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="H19" s="115" t="n"/>
+      <c r="H19" s="115" t="inlineStr">
+        <is>
+          <t>Doctoral-level quantum physics key personnel contributed as technical depth on the prime's team.</t>
+        </is>
+      </c>
       <c r="I19" s="115" t="inlineStr">
         <is>
           <t>Quantum technical support delivered as workshare under a prime's pending award. Solicitation closed 7/1/26 — capture framing is moot; the live conversation is delivery workshare only.</t>
@@ -24930,7 +24966,11 @@
       </c>
       <c r="M25" s="115" t="n"/>
       <c r="N25" s="115" t="n"/>
-      <c r="O25" s="115" t="n"/>
+      <c r="O25" s="115" t="inlineStr">
+        <is>
+          <t>GSA MAS SIN 54151HEAL is suppressed pending schedule refresh, and is not the correct SIN for this scope.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="115" t="inlineStr">

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -21,6 +21,7 @@
     <sheet name="NDAs" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Agreements" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Actions" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Inbound_Leads" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="As_Of_Date" hidden="0" function="0" vbProcedure="0">Dashboard!$C$4</definedName>
@@ -38,7 +39,7 @@
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -193,6 +194,12 @@
       <color rgb="FF232D5A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFDC2626"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -299,7 +306,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -657,6 +664,24 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6722,7 +6747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="51" min="1" max="1"/>
@@ -6731,6 +6756,7 @@
     <col width="14" customWidth="1" style="51" min="4" max="4"/>
     <col width="50" customWidth="1" style="51" min="5" max="5"/>
     <col width="14" customWidth="1" style="51" min="6" max="7"/>
+    <col width="80" customWidth="1" style="52" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.75" customHeight="1" s="52">
@@ -6784,6 +6810,11 @@
           <t>Partner Classification</t>
         </is>
       </c>
+      <c r="H4" s="64" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="52">
       <c r="A5" s="106" t="n">
@@ -7573,6 +7604,38 @@
         </is>
       </c>
       <c r="G29" s="107" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="106" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="107" t="inlineStr">
+        <is>
+          <t>RavenOne Enterprises LLC</t>
+        </is>
+      </c>
+      <c r="C30" s="107" t="inlineStr">
+        <is>
+          <t>Charles M. Cedeño</t>
+        </is>
+      </c>
+      <c r="D30" s="107" t="n"/>
+      <c r="E30" s="107" t="inlineStr">
+        <is>
+          <t>ROS-NDA-001-VISIONBLOX v0.4</t>
+        </is>
+      </c>
+      <c r="F30" s="107" t="inlineStr">
+        <is>
+          <t>Signed by VBX — awaiting countersignature (not executed)</t>
+        </is>
+      </c>
+      <c r="G30" s="107" t="n"/>
+      <c r="H30" s="121" t="inlineStr">
+        <is>
+          <t>NOT a Wave 1-era inbound lead: RavenOne has been a teaming contact since August 2026 across five evaluated opportunities — VA Digital GI Bill RFI (pursue-conditional), VA PATS-R (watch), CDC KMTSS (no-bid), VA BioDose (Gate 1 kill), and Riverbay 4350 (no-bid). Puerto Rico LLC, not California — the IN-CA- prefix is retained only as a stable handle; this row belongs in the partner-ecosystem file, not Inbound. RIVERBAY 4350 CLOSED: no-bid issued 2026-09-23, record VBX_NoBid_Decision_Riverbay_4350_20260923.docx. Gate 1 failed on two independent triggers — vendor-type mismatch (managed service-desk operator buy) and past-performance floor (no corporate managed help-desk PP). Scoring not run per engine rule. Structural confirmation: approx $16.48 per live-coverage hour at full customer price, before RavenOne margin. Decline sent; transmitted no VBX information. NDA: ROS-NDA-001-VISIONBLOX v0.4, RavenOne counterproposal dated 2026-08-19 — VBX SIGNED, AWAITING RAVENONE COUNTERSIGNATURE. Not executed: no Effective Date until the last signature, so NDA-before-substance is NOT yet satisfied. Terms reviewed: no non-solicit, no non-compete; Section 2.2 SAM.gov carve-out and Section 8.4 freedom-of-action both favor VBX; 2-yr term / 2-yr survival; Section 8.5 bars name and logo use without written consent; Delaware governing law, venue at defendant's principal place of business. CLAIMED: HUBZone, SBA VetCert SDVOSB.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7753,7 +7816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="52" min="1" max="1"/>
@@ -7830,7 +7893,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="114" t="n">
+      <c r="A5" s="123" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="115" t="inlineStr">
@@ -7838,12 +7901,12 @@
           <t>Redirect LADBS B&amp;P to CMS ICAT (RFI 270196) + WA HCA FSIPAP Round 2 re-score</t>
         </is>
       </c>
-      <c r="C5" s="114" t="inlineStr">
+      <c r="C5" s="123" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D5" s="116" t="n">
+      <c r="D5" s="124" t="n">
         <v>46254</v>
       </c>
       <c r="E5" s="115" t="inlineStr">
@@ -7851,19 +7914,19 @@
           <t>ICAT package submitted on time</t>
         </is>
       </c>
-      <c r="F5" s="114" t="inlineStr">
+      <c r="F5" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G5" s="114" t="inlineStr">
+      <c r="G5" s="123" t="inlineStr">
         <is>
           <t>OPP-041 / LADBS AIP-PPC No-Bid 8/19/26</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="114" t="n">
+      <c r="A6" s="123" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="115" t="inlineStr">
@@ -7871,12 +7934,12 @@
           <t>Open SOC 2 Type 2 gap-assessment scoping with Tony Paul; cite as 3rd documented hosted-solution attestation blocker (after Montana Tier Two &gt;$100K, WA State)</t>
         </is>
       </c>
-      <c r="C6" s="114" t="inlineStr">
+      <c r="C6" s="123" t="inlineStr">
         <is>
           <t>Khaalis Wooden / Tony Paul</t>
         </is>
       </c>
-      <c r="D6" s="116" t="n">
+      <c r="D6" s="124" t="n">
         <v>46262</v>
       </c>
       <c r="E6" s="115" t="inlineStr">
@@ -7884,19 +7947,19 @@
           <t>Assessor shortlist returned</t>
         </is>
       </c>
-      <c r="F6" s="114" t="inlineStr">
+      <c r="F6" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G6" s="114" t="inlineStr">
+      <c r="G6" s="123" t="inlineStr">
         <is>
           <t>OPP-041 / LADBS AIP-PPC No-Bid 8/19/26</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="114" t="n">
+      <c r="A7" s="123" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="115" t="inlineStr">
@@ -7904,12 +7967,12 @@
           <t>Add intake screen: flag any scope containing "vendor-hosted", "SaaS", "subscription", or a Functional Requirements &amp; Use Case Matrix as vendor-type mismatch BEFORE scoring</t>
         </is>
       </c>
-      <c r="C7" s="114" t="inlineStr">
+      <c r="C7" s="123" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D7" s="116" t="n">
+      <c r="D7" s="124" t="n">
         <v>46265</v>
       </c>
       <c r="E7" s="115" t="inlineStr">
@@ -7917,19 +7980,19 @@
           <t>Screen in intake checklist</t>
         </is>
       </c>
-      <c r="F7" s="114" t="inlineStr">
+      <c r="F7" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G7" s="114" t="inlineStr">
+      <c r="G7" s="123" t="inlineStr">
         <is>
           <t>OPP-041 / LADBS AIP-PPC No-Bid 8/19/26</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="114" t="n">
+      <c r="A8" s="123" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="115" t="inlineStr">
@@ -7937,12 +8000,12 @@
           <t>Re-check RAMP for a follow-on ED19 services/integration requirement</t>
         </is>
       </c>
-      <c r="C8" s="114" t="inlineStr">
+      <c r="C8" s="123" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D8" s="116" t="n">
+      <c r="D8" s="124" t="n">
         <v>46310</v>
       </c>
       <c r="E8" s="115" t="inlineStr">
@@ -7950,19 +8013,19 @@
           <t>Search executed; recorded pursue / no-action</t>
         </is>
       </c>
-      <c r="F8" s="114" t="inlineStr">
+      <c r="F8" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G8" s="114" t="inlineStr">
+      <c r="G8" s="123" t="inlineStr">
         <is>
           <t>OPP-041 / LADBS AIP-PPC No-Bid 8/19/26</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="114" t="n">
+      <c r="A9" s="123" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="115" t="inlineStr">
@@ -7970,12 +8033,12 @@
           <t>Validate §5.7 ROM against VBX cost model</t>
         </is>
       </c>
-      <c r="C9" s="114" t="inlineStr">
+      <c r="C9" s="123" t="inlineStr">
         <is>
           <t>Akil Chellam / Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D9" s="116" t="n">
+      <c r="D9" s="124" t="n">
         <v>46258</v>
       </c>
       <c r="E9" s="115" t="inlineStr">
@@ -7983,19 +8046,19 @@
           <t>ROM confirmed or revised</t>
         </is>
       </c>
-      <c r="F9" s="114" t="inlineStr">
+      <c r="F9" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G9" s="114" t="inlineStr">
+      <c r="G9" s="123" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 14</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="114" t="n">
+      <c r="A10" s="123" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="115" t="inlineStr">
@@ -8003,12 +8066,12 @@
           <t>Confirm §5.4 SOC 2 / attestation language</t>
         </is>
       </c>
-      <c r="C10" s="114" t="inlineStr">
+      <c r="C10" s="123" t="inlineStr">
         <is>
           <t>Khaalis Wooden / Tony Paul</t>
         </is>
       </c>
-      <c r="D10" s="116" t="n">
+      <c r="D10" s="124" t="n">
         <v>46258</v>
       </c>
       <c r="E10" s="115" t="inlineStr">
@@ -8016,19 +8079,19 @@
           <t>Language approved</t>
         </is>
       </c>
-      <c r="F10" s="114" t="inlineStr">
+      <c r="F10" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G10" s="114" t="inlineStr">
+      <c r="G10" s="123" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 15</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="114" t="n">
+      <c r="A11" s="123" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="115" t="inlineStr">
@@ -8036,12 +8099,12 @@
           <t>Cyber-insurance tier check ($10M vs $6M held) with Grace Waring</t>
         </is>
       </c>
-      <c r="C11" s="114" t="inlineStr">
+      <c r="C11" s="123" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D11" s="116" t="n">
+      <c r="D11" s="124" t="n">
         <v>46258</v>
       </c>
       <c r="E11" s="115" t="inlineStr">
@@ -8049,19 +8112,19 @@
           <t>Tier confirmed</t>
         </is>
       </c>
-      <c r="F11" s="114" t="inlineStr">
+      <c r="F11" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G11" s="114" t="inlineStr">
+      <c r="G11" s="123" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 16</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="114" t="n">
+      <c r="A12" s="123" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="115" t="inlineStr">
@@ -8069,12 +8132,12 @@
           <t>Apply §4.7 per-page Confidential marks on §5.3 pages</t>
         </is>
       </c>
-      <c r="C12" s="114" t="inlineStr">
+      <c r="C12" s="123" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D12" s="116" t="n">
+      <c r="D12" s="124" t="n">
         <v>46259</v>
       </c>
       <c r="E12" s="115" t="inlineStr">
@@ -8082,19 +8145,19 @@
           <t>Marks applied</t>
         </is>
       </c>
-      <c r="F12" s="114" t="inlineStr">
+      <c r="F12" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G12" s="114" t="inlineStr">
+      <c r="G12" s="123" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 17</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="114" t="n">
+      <c r="A13" s="123" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="115" t="inlineStr">
@@ -8102,12 +8165,12 @@
           <t>Pink/red review + guardrail sweep</t>
         </is>
       </c>
-      <c r="C13" s="114" t="inlineStr">
+      <c r="C13" s="123" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D13" s="116" t="n">
+      <c r="D13" s="124" t="n">
         <v>46259</v>
       </c>
       <c r="E13" s="115" t="inlineStr">
@@ -8115,19 +8178,19 @@
           <t>Sweep complete</t>
         </is>
       </c>
-      <c r="F13" s="114" t="inlineStr">
+      <c r="F13" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G13" s="114" t="inlineStr">
+      <c r="G13" s="123" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 18</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="114" t="n">
+      <c r="A14" s="123" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="115" t="inlineStr">
@@ -8135,12 +8198,12 @@
           <t>Submit RFI response (email, ≤20pp, subject "RFI 2026HCA13_Visionblox LLC" + Attachment A, no zip)</t>
         </is>
       </c>
-      <c r="C14" s="114" t="inlineStr">
+      <c r="C14" s="123" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D14" s="116" t="n">
+      <c r="D14" s="124" t="n">
         <v>46260</v>
       </c>
       <c r="E14" s="115" t="inlineStr">
@@ -8148,16 +8211,3650 @@
           <t>Response submitted</t>
         </is>
       </c>
-      <c r="F14" s="114" t="inlineStr">
+      <c r="F14" s="123" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G14" s="114" t="inlineStr">
+      <c r="G14" s="123" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 19</t>
         </is>
       </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="123" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="115" t="inlineStr">
+        <is>
+          <t>Screen all 33 inbound-handoff firms (Stage 0–3) — 32 on Inbound_Leads + IN-CA-15</t>
+        </is>
+      </c>
+      <c r="C15" s="123" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D15" s="124" t="n"/>
+      <c r="E15" s="115" t="inlineStr">
+        <is>
+          <t>Stage 0–3 output logged for each firm before its call</t>
+        </is>
+      </c>
+      <c r="F15" s="123" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G15" s="123" t="inlineStr">
+        <is>
+          <t>Inbound handoff 2026-09-26 §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="123" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="115" t="inlineStr">
+        <is>
+          <t>Pull Wave 1 row WA-13 (already booked as IN-WA-02) from the 9/28 BCC</t>
+        </is>
+      </c>
+      <c r="C16" s="123" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D16" s="124" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E16" s="115" t="inlineStr">
+        <is>
+          <t>WA-13 address absent from the send list</t>
+        </is>
+      </c>
+      <c r="F16" s="123" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G16" s="123" t="inlineStr">
+        <is>
+          <t>Inbound handoff 2026-09-26 §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="123" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="115" t="inlineStr">
+        <is>
+          <t>Resolve Wave 1 MT-02 / MT-06 shared address: keep both rows as one contact, or drop one</t>
+        </is>
+      </c>
+      <c r="C17" s="123" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D17" s="124" t="n">
+        <v>46293</v>
+      </c>
+      <c r="E17" s="115" t="inlineStr">
+        <is>
+          <t>Decision recorded; BCC count final</t>
+        </is>
+      </c>
+      <c r="F17" s="123" t="inlineStr">
+        <is>
+          <t>Needs Khaalis decision</t>
+        </is>
+      </c>
+      <c r="G17" s="123" t="inlineStr">
+        <is>
+          <t>Inbound handoff 2026-09-26 §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="123" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="115" t="inlineStr">
+        <is>
+          <t>Chase countersignature on NDA #26 (IN-CA-15, NDAs sheet)</t>
+        </is>
+      </c>
+      <c r="C18" s="123" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D18" s="124" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E18" s="115" t="inlineStr">
+        <is>
+          <t>Countersigned copy received; Effective Date recorded</t>
+        </is>
+      </c>
+      <c r="F18" s="123" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G18" s="123" t="inlineStr">
+        <is>
+          <t>Inbound handoff 2026-09-26 §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="123" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="115" t="inlineStr">
+        <is>
+          <t>Resolve IN-CA-21 fee model in writing before its call</t>
+        </is>
+      </c>
+      <c r="C19" s="123" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D19" s="124" t="n">
+        <v>46301</v>
+      </c>
+      <c r="E19" s="115" t="inlineStr">
+        <is>
+          <t>Written fee position received before the call</t>
+        </is>
+      </c>
+      <c r="F19" s="123" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G19" s="123" t="inlineStr">
+        <is>
+          <t>Inbound handoff 2026-09-26 §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="123" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="115" t="inlineStr">
+        <is>
+          <t>Send bench replies — IN-CA-13, IN-CA-07</t>
+        </is>
+      </c>
+      <c r="C20" s="123" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D20" s="124" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E20" s="115" t="inlineStr">
+        <is>
+          <t>Both replies sent</t>
+        </is>
+      </c>
+      <c r="F20" s="122" t="inlineStr">
+        <is>
+          <t>OVERDUE</t>
+        </is>
+      </c>
+      <c r="G20" s="123" t="inlineStr">
+        <is>
+          <t>Inbound handoff 2026-09-26 §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="123" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="115" t="inlineStr">
+        <is>
+          <t>Retrieve reply text — IN-CA-16, IN-WA-03, IN-WA-04, IN-UNK-06</t>
+        </is>
+      </c>
+      <c r="C21" s="123" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D21" s="124" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E21" s="115" t="inlineStr">
+        <is>
+          <t>All four reply texts on file</t>
+        </is>
+      </c>
+      <c r="F21" s="122" t="inlineStr">
+        <is>
+          <t>OVERDUE</t>
+        </is>
+      </c>
+      <c r="G21" s="123" t="inlineStr">
+        <is>
+          <t>Inbound handoff 2026-09-26 §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="123" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="115" t="inlineStr">
+        <is>
+          <t>Decide whether to contact IN-WA-01 directly</t>
+        </is>
+      </c>
+      <c r="C22" s="123" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D22" s="124" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E22" s="115" t="inlineStr">
+        <is>
+          <t>Decision recorded</t>
+        </is>
+      </c>
+      <c r="F22" s="123" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G22" s="123" t="inlineStr">
+        <is>
+          <t>Inbound handoff 2026-09-26 §8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="123" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="115" t="inlineStr">
+        <is>
+          <t>Add intake filter: help-desk / NOC / managed end-user support = vendor-type mismatch at intake</t>
+        </is>
+      </c>
+      <c r="C23" s="123" t="inlineStr">
+        <is>
+          <t>Khaalis Wooden</t>
+        </is>
+      </c>
+      <c r="D23" s="124" t="n"/>
+      <c r="E23" s="115" t="inlineStr">
+        <is>
+          <t>Filter in intake checklist</t>
+        </is>
+      </c>
+      <c r="F23" s="123" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G23" s="123" t="inlineStr">
+        <is>
+          <t>Riverbay 4350 No-Bid 9/23/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="52" min="1" max="1"/>
+    <col width="34" customWidth="1" style="52" min="2" max="2"/>
+    <col width="26" customWidth="1" style="52" min="3" max="3"/>
+    <col width="34" customWidth="1" style="52" min="4" max="4"/>
+    <col width="18" customWidth="1" style="52" min="5" max="5"/>
+    <col width="28" customWidth="1" style="52" min="6" max="6"/>
+    <col width="32" customWidth="1" style="52" min="7" max="7"/>
+    <col width="16" customWidth="1" style="52" min="8" max="8"/>
+    <col width="26" customWidth="1" style="52" min="9" max="9"/>
+    <col width="16" customWidth="1" style="52" min="10" max="10"/>
+    <col width="9" customWidth="1" style="52" min="11" max="11"/>
+    <col width="22" customWidth="1" style="52" min="12" max="12"/>
+    <col width="44" customWidth="1" style="52" min="13" max="13"/>
+    <col width="15" customWidth="1" style="52" min="14" max="14"/>
+    <col width="12" customWidth="1" style="52" min="15" max="15"/>
+    <col width="13" customWidth="1" style="52" min="16" max="16"/>
+    <col width="80" customWidth="1" style="52" min="17" max="17"/>
+    <col width="11" customWidth="1" style="52" min="18" max="18"/>
+    <col width="60" customWidth="1" style="52" min="19" max="19"/>
+    <col width="10" customWidth="1" style="52" min="20" max="20"/>
+    <col width="16" customWidth="1" style="52" min="21" max="21"/>
+    <col width="44" customWidth="1" style="52" min="22" max="22"/>
+    <col width="15" customWidth="1" style="52" min="23" max="23"/>
+    <col width="8" customWidth="1" style="52" min="24" max="24"/>
+    <col width="16" customWidth="1" style="52" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.75" customHeight="1" s="52">
+      <c r="A1" s="109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INBOUND LEADS  —  pre-Wave 1 partner replies (UNSCREENED)</t>
+        </is>
+      </c>
+      <c r="B1" s="110" t="n"/>
+      <c r="C1" s="110" t="n"/>
+      <c r="D1" s="110" t="n"/>
+      <c r="E1" s="110" t="n"/>
+      <c r="F1" s="110" t="n"/>
+      <c r="G1" s="110" t="n"/>
+      <c r="H1" s="110" t="n"/>
+      <c r="I1" s="110" t="n"/>
+      <c r="J1" s="110" t="n"/>
+      <c r="K1" s="110" t="n"/>
+      <c r="L1" s="110" t="n"/>
+      <c r="M1" s="110" t="n"/>
+      <c r="N1" s="110" t="n"/>
+      <c r="O1" s="110" t="n"/>
+      <c r="P1" s="110" t="n"/>
+      <c r="Q1" s="110" t="n"/>
+      <c r="R1" s="110" t="n"/>
+      <c r="S1" s="110" t="n"/>
+      <c r="T1" s="110" t="n"/>
+      <c r="U1" s="110" t="n"/>
+      <c r="V1" s="110" t="n"/>
+      <c r="W1" s="110" t="n"/>
+      <c r="X1" s="110" t="n"/>
+      <c r="Y1" s="110" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INTERNAL ONLY — stripped from the published copy. CLAIMED = firm's own unverified assertion. Classification / Score / Verified stay EMPTY until screened. Log a call in Meetings only after it happens.</t>
+        </is>
+      </c>
+      <c r="B2" s="112" t="n"/>
+      <c r="C2" s="112" t="n"/>
+      <c r="D2" s="112" t="n"/>
+      <c r="E2" s="112" t="n"/>
+      <c r="F2" s="112" t="n"/>
+      <c r="G2" s="112" t="n"/>
+      <c r="H2" s="112" t="n"/>
+      <c r="I2" s="112" t="n"/>
+      <c r="J2" s="112" t="n"/>
+      <c r="K2" s="112" t="n"/>
+      <c r="L2" s="112" t="n"/>
+      <c r="M2" s="112" t="n"/>
+      <c r="N2" s="112" t="n"/>
+      <c r="O2" s="112" t="n"/>
+      <c r="P2" s="112" t="n"/>
+      <c r="Q2" s="112" t="n"/>
+      <c r="R2" s="112" t="n"/>
+      <c r="S2" s="112" t="n"/>
+      <c r="T2" s="112" t="n"/>
+      <c r="U2" s="112" t="n"/>
+      <c r="V2" s="112" t="n"/>
+      <c r="W2" s="112" t="n"/>
+      <c r="X2" s="112" t="n"/>
+      <c r="Y2" s="112" t="n"/>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="113" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="113" t="inlineStr">
+        <is>
+          <t>Firm (legal name)</t>
+        </is>
+      </c>
+      <c r="C4" s="113" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="D4" s="113" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="E4" s="113" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="F4" s="113" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="G4" s="113" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H4" s="113" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="I4" s="113" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="J4" s="113" t="inlineStr">
+        <is>
+          <t>UEI</t>
+        </is>
+      </c>
+      <c r="K4" s="113" t="inlineStr">
+        <is>
+          <t>CAGE</t>
+        </is>
+      </c>
+      <c r="L4" s="113" t="inlineStr">
+        <is>
+          <t>Primary NAICS</t>
+        </is>
+      </c>
+      <c r="M4" s="113" t="inlineStr">
+        <is>
+          <t>Why this firm</t>
+        </is>
+      </c>
+      <c r="N4" s="113" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O4" s="113" t="inlineStr">
+        <is>
+          <t>Call Date</t>
+        </is>
+      </c>
+      <c r="P4" s="113" t="inlineStr">
+        <is>
+          <t>Call Time (CT)</t>
+        </is>
+      </c>
+      <c r="Q4" s="113" t="inlineStr">
+        <is>
+          <t>Response notes</t>
+        </is>
+      </c>
+      <c r="R4" s="113" t="inlineStr">
+        <is>
+          <t>NDA status</t>
+        </is>
+      </c>
+      <c r="S4" s="113" t="inlineStr">
+        <is>
+          <t>Next step</t>
+        </is>
+      </c>
+      <c r="T4" s="113" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="U4" s="113" t="inlineStr">
+        <is>
+          <t>Source chat</t>
+        </is>
+      </c>
+      <c r="V4" s="113" t="inlineStr">
+        <is>
+          <t>Reserve Pool / Wave 1 match</t>
+        </is>
+      </c>
+      <c r="W4" s="113" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="X4" s="113" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Y4" s="113" t="inlineStr">
+        <is>
+          <t>SAM/SBA Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-01</t>
+        </is>
+      </c>
+      <c r="B5" s="125" t="inlineStr">
+        <is>
+          <t>Wilson Operations Group LLC</t>
+        </is>
+      </c>
+      <c r="C5" s="125" t="n"/>
+      <c r="D5" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training</t>
+        </is>
+      </c>
+      <c r="E5" s="125" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F5" s="125" t="inlineStr">
+        <is>
+          <t>Antonyo "Tony" Wilson</t>
+        </is>
+      </c>
+      <c r="G5" s="125" t="inlineStr">
+        <is>
+          <t>tony@wilsonopsgroup.com</t>
+        </is>
+      </c>
+      <c r="H5" s="125" t="inlineStr">
+        <is>
+          <t>6195006573</t>
+        </is>
+      </c>
+      <c r="I5" s="125" t="inlineStr">
+        <is>
+          <t>wilsonopsgroup.com</t>
+        </is>
+      </c>
+      <c r="J5" s="125" t="inlineStr">
+        <is>
+          <t>XL4RVNPNKR26</t>
+        </is>
+      </c>
+      <c r="K5" s="125" t="inlineStr">
+        <is>
+          <t>22MJ8</t>
+        </is>
+      </c>
+      <c r="L5" s="125" t="n"/>
+      <c r="M5" s="115" t="inlineStr">
+        <is>
+          <t>PM/operational readiness, change mgmt, training; CA contract participation</t>
+        </is>
+      </c>
+      <c r="N5" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O5" s="126" t="n">
+        <v>46293</v>
+      </c>
+      <c r="P5" s="125" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="Q5" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 8:29 AM. CLAIMED: CA DVBE, SB, SB-PW; SAM registered. DISCREPANCY: body lists CA certs only, signature block says service-disabled veteran-owned — no SBA SDVOSB claimed in text. Asked about pipeline, workshare and Montana-contract teaming — deferred to post-NDA. No cap statement yet.</t>
+        </is>
+      </c>
+      <c r="R5" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S5" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Mon 2026-09-28 1:00 PM CT</t>
+        </is>
+      </c>
+      <c r="T5" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U5" s="125" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="V5" s="115" t="inlineStr">
+        <is>
+          <t>Reserve Pool row 106 — UEI MATCH CONFIRMED (CA, Lane C, score 8.5, San Diego)</t>
+        </is>
+      </c>
+      <c r="W5" s="125" t="n"/>
+      <c r="X5" s="125" t="n"/>
+      <c r="Y5" s="125" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-02</t>
+        </is>
+      </c>
+      <c r="B6" s="125" t="inlineStr">
+        <is>
+          <t>VAERESOURCE LLC</t>
+        </is>
+      </c>
+      <c r="C6" s="125" t="n"/>
+      <c r="D6" s="115" t="inlineStr">
+        <is>
+          <t>A claimed — CORE OVERLAP FLAG</t>
+        </is>
+      </c>
+      <c r="E6" s="125" t="inlineStr">
+        <is>
+          <t>Los Angeles area</t>
+        </is>
+      </c>
+      <c r="F6" s="125" t="inlineStr">
+        <is>
+          <t>Aisha Umar</t>
+        </is>
+      </c>
+      <c r="G6" s="125" t="inlineStr">
+        <is>
+          <t>aumar@vaeresource.com</t>
+        </is>
+      </c>
+      <c r="H6" s="125" t="inlineStr">
+        <is>
+          <t>3238093621</t>
+        </is>
+      </c>
+      <c r="I6" s="125" t="n"/>
+      <c r="J6" s="125" t="inlineStr">
+        <is>
+          <t>J4VFG5KBJ6T9</t>
+        </is>
+      </c>
+      <c r="K6" s="125" t="inlineStr">
+        <is>
+          <t>8S7X6</t>
+        </is>
+      </c>
+      <c r="L6" s="125" t="inlineStr">
+        <is>
+          <t>541511</t>
+        </is>
+      </c>
+      <c r="M6" s="115" t="inlineStr">
+        <is>
+          <t>Cyber GRC / audit readiness (NIST AI RMF, 800-171, CMMC) — but self-stated primary NAICS is VBX core</t>
+        </is>
+      </c>
+      <c r="N6" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O6" s="126" t="n">
+        <v>46293</v>
+      </c>
+      <c r="P6" s="125" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="Q6" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 8:53 AM. CLAIMED: SBA SDVOSB/VOSB/WOSB (MySBA #101047), CA SB + DVBE. HARD-CHECK FLAG: states primary NAICS 541511 and leads with AI/ML, data engineering, cloud/app development = VBX core (Stage 2 overlap fail on her own words). Only non-competing scope is assessment/compliance. No cap statement yet.</t>
+        </is>
+      </c>
+      <c r="R6" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S6" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Mon 2026-09-28 1:30 PM CT — resolve overlap first</t>
+        </is>
+      </c>
+      <c r="T6" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U6" s="125" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="V6" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W6" s="125" t="n"/>
+      <c r="X6" s="125" t="n"/>
+      <c r="Y6" s="125" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-03</t>
+        </is>
+      </c>
+      <c r="B7" s="125" t="inlineStr">
+        <is>
+          <t>Apstelios</t>
+        </is>
+      </c>
+      <c r="C7" s="125" t="n"/>
+      <c r="D7" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training</t>
+        </is>
+      </c>
+      <c r="E7" s="125" t="n"/>
+      <c r="F7" s="125" t="inlineStr">
+        <is>
+          <t>James Thao</t>
+        </is>
+      </c>
+      <c r="G7" s="125" t="inlineStr">
+        <is>
+          <t>james@apstelios.com</t>
+        </is>
+      </c>
+      <c r="H7" s="125" t="n"/>
+      <c r="I7" s="125" t="n"/>
+      <c r="J7" s="125" t="n"/>
+      <c r="K7" s="125" t="n"/>
+      <c r="L7" s="125" t="n"/>
+      <c r="M7" s="115" t="inlineStr">
+        <is>
+          <t>Change mgmt, PMO, training delivery; CA-based</t>
+        </is>
+      </c>
+      <c r="N7" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O7" s="126" t="n">
+        <v>46294</v>
+      </c>
+      <c r="P7" s="125" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="Q7" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 9:07 AM. CLAIMED: SDVOSB; California based. THIN: no UEI, no CAGE, no capability statement, no legal-entity suffix. Identifiers requested.</t>
+        </is>
+      </c>
+      <c r="R7" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S7" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Tue 2026-09-29 1:00 PM CT</t>
+        </is>
+      </c>
+      <c r="T7" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U7" s="125" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="V7" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W7" s="125" t="n"/>
+      <c r="X7" s="125" t="n"/>
+      <c r="Y7" s="125" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-04</t>
+        </is>
+      </c>
+      <c r="B8" s="125" t="inlineStr">
+        <is>
+          <t>CD Veteran Services LLC</t>
+        </is>
+      </c>
+      <c r="C8" s="125" t="n"/>
+      <c r="D8" s="115" t="inlineStr">
+        <is>
+          <t>A · Assurance / Risk / Cyber GRC / C · Change Mgmt, PMO &amp; Training / E · Research, Evaluation &amp; GIS</t>
+        </is>
+      </c>
+      <c r="E8" s="125" t="n"/>
+      <c r="F8" s="125" t="inlineStr">
+        <is>
+          <t>Cromwell Dyette</t>
+        </is>
+      </c>
+      <c r="G8" s="125" t="inlineStr">
+        <is>
+          <t>cromwell.dyette@cdveteranservices.com</t>
+        </is>
+      </c>
+      <c r="H8" s="125" t="inlineStr">
+        <is>
+          <t>9782671597</t>
+        </is>
+      </c>
+      <c r="I8" s="125" t="inlineStr">
+        <is>
+          <t>cdveteranservices.com</t>
+        </is>
+      </c>
+      <c r="J8" s="125" t="n"/>
+      <c r="K8" s="125" t="n"/>
+      <c r="L8" s="125" t="n"/>
+      <c r="M8" s="115" t="inlineStr">
+        <is>
+          <t>Budget variance analysis, program financial health, cost tracking, desk procedures to public-sector audit standards</t>
+        </is>
+      </c>
+      <c r="N8" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O8" s="126" t="n">
+        <v>46293</v>
+      </c>
+      <c r="P8" s="125" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="Q8" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 9:18 AM. The CALIFORNIA/local lane of a two-entity pair; federal lane is [[Augustus Veteran Services]] (IN-UNK-01), same owner. CLAIMED: CA Small Business Micro + DVBE, Cert ID 2052444 thru 07/31/2028; LA County DVBE 101774, LSBE 101773. CAPACITY FLAG: "I am the owner and the person who performs the work." GEO FLAG: 978 area code (MA) against a stated CA lane.</t>
+        </is>
+      </c>
+      <c r="R8" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S8" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Mon 2026-09-28 2:00 PM CT (covers both entities)</t>
+        </is>
+      </c>
+      <c r="T8" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U8" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-22</t>
+        </is>
+      </c>
+      <c r="V8" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W8" s="125" t="n"/>
+      <c r="X8" s="125" t="n"/>
+      <c r="Y8" s="125" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-05</t>
+        </is>
+      </c>
+      <c r="B9" s="125" t="inlineStr">
+        <is>
+          <t>INK Ventures, LLC</t>
+        </is>
+      </c>
+      <c r="C9" s="125" t="n"/>
+      <c r="D9" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training</t>
+        </is>
+      </c>
+      <c r="E9" s="125" t="n"/>
+      <c r="F9" s="125" t="inlineStr">
+        <is>
+          <t>Rosalio Altamirano, DSW, PMP</t>
+        </is>
+      </c>
+      <c r="G9" s="125" t="inlineStr">
+        <is>
+          <t>rosalio@inkcontracting.com</t>
+        </is>
+      </c>
+      <c r="H9" s="125" t="inlineStr">
+        <is>
+          <t>5305742975</t>
+        </is>
+      </c>
+      <c r="I9" s="125" t="inlineStr">
+        <is>
+          <t>inkcontracting.com</t>
+        </is>
+      </c>
+      <c r="J9" s="125" t="n"/>
+      <c r="K9" s="125" t="n"/>
+      <c r="L9" s="125" t="n"/>
+      <c r="M9" s="115" t="inlineStr">
+        <is>
+          <t>Project mgmt, program mgmt, policy development, strategic planning</t>
+        </is>
+      </c>
+      <c r="N9" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O9" s="126" t="n">
+        <v>46294</v>
+      </c>
+      <c r="P9" s="125" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="Q9" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 9:55 AM with 4 attachments (cap statement + SB-DVBE cert + SEED + SBA SDVOSB). CLAIMED: SDVOSB, CA DVBE, Small Business, SMUD SEED Program. CORRECTION: an earlier chat log recorded a HUBZone claim — his actual reply does NOT claim HUBZone. Do not cite it.</t>
+        </is>
+      </c>
+      <c r="R9" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S9" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Tue 2026-09-29 1:30 PM CT</t>
+        </is>
+      </c>
+      <c r="T9" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U9" s="125" t="inlineStr">
+        <is>
+          <t>#1, #4 + email</t>
+        </is>
+      </c>
+      <c r="V9" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W9" s="125" t="n"/>
+      <c r="X9" s="125" t="n"/>
+      <c r="Y9" s="125" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-06</t>
+        </is>
+      </c>
+      <c r="B10" s="125" t="inlineStr">
+        <is>
+          <t>Orange Crew</t>
+        </is>
+      </c>
+      <c r="C10" s="125" t="inlineStr">
+        <is>
+          <t>Orange Crew / JTI Global Network</t>
+        </is>
+      </c>
+      <c r="D10" s="115" t="inlineStr">
+        <is>
+          <t>B · Network, Telecom &amp; Hardware — CORE OVERLAP FLAG</t>
+        </is>
+      </c>
+      <c r="E10" s="125" t="inlineStr">
+        <is>
+          <t>Santa Ana</t>
+        </is>
+      </c>
+      <c r="F10" s="125" t="inlineStr">
+        <is>
+          <t>Laith Pahlawan</t>
+        </is>
+      </c>
+      <c r="G10" s="125" t="inlineStr">
+        <is>
+          <t>laith.pahlawan@theorangecrew.com</t>
+        </is>
+      </c>
+      <c r="H10" s="125" t="inlineStr">
+        <is>
+          <t>7142028600</t>
+        </is>
+      </c>
+      <c r="I10" s="125" t="inlineStr">
+        <is>
+          <t>theorangecrew.net</t>
+        </is>
+      </c>
+      <c r="J10" s="125" t="inlineStr">
+        <is>
+          <t>U363NHKSARE9</t>
+        </is>
+      </c>
+      <c r="K10" s="125" t="inlineStr">
+        <is>
+          <t>84HE7</t>
+        </is>
+      </c>
+      <c r="L10" s="125" t="inlineStr">
+        <is>
+          <t>541512, 541513, 541519, 541618</t>
+        </is>
+      </c>
+      <c r="M10" s="115" t="inlineStr">
+        <is>
+          <t>Nationwide IT field services, cabling, Wi-Fi/VoIP, hardware install &amp; lifecycle — proposes VBX platform layer / OC field layer split</t>
+        </is>
+      </c>
+      <c r="N10" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O10" s="126" t="n">
+        <v>46293</v>
+      </c>
+      <c r="P10" s="125" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="Q10" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 9:56 AM. CLAIMED: CA Small Business, Cert ID 2022218. HARD-CHECK FLAG: self-describes as "an IT services and systems integration company"; primary NAICS include 541512 and 541519 = two VBX core codes; lists systems integration and cybersecurity as core. Proposed lane split is clean if real. UNEXPLAINED: second attachment titled "FA Capability statement.pptx" — may be a separate firm.</t>
+        </is>
+      </c>
+      <c r="R10" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S10" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Mon 2026-09-28 2:30 PM CT — resolve overlap first</t>
+        </is>
+      </c>
+      <c r="T10" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U10" s="125" t="inlineStr">
+        <is>
+          <t>#4 + email</t>
+        </is>
+      </c>
+      <c r="V10" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W10" s="125" t="n"/>
+      <c r="X10" s="125" t="n"/>
+      <c r="Y10" s="125" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-07</t>
+        </is>
+      </c>
+      <c r="B11" s="125" t="inlineStr">
+        <is>
+          <t>HumanEdge Gov Solutions</t>
+        </is>
+      </c>
+      <c r="C11" s="125" t="n"/>
+      <c r="D11" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training / A · Assurance / Risk / Cyber GRC</t>
+        </is>
+      </c>
+      <c r="E11" s="125" t="inlineStr">
+        <is>
+          <t>Los Angeles area</t>
+        </is>
+      </c>
+      <c r="F11" s="125" t="inlineStr">
+        <is>
+          <t>Sharee Legree</t>
+        </is>
+      </c>
+      <c r="G11" s="125" t="inlineStr">
+        <is>
+          <t>sharee@hegovsolutions.com</t>
+        </is>
+      </c>
+      <c r="H11" s="125" t="inlineStr">
+        <is>
+          <t>3238970706</t>
+        </is>
+      </c>
+      <c r="I11" s="125" t="inlineStr">
+        <is>
+          <t>hegovsolutions.com</t>
+        </is>
+      </c>
+      <c r="J11" s="125" t="n"/>
+      <c r="K11" s="125" t="n"/>
+      <c r="L11" s="125" t="n"/>
+      <c r="M11" s="115" t="inlineStr">
+        <is>
+          <t>PM/PMO, GRC and audit readiness, healthcare and government program support, staffing</t>
+        </is>
+      </c>
+      <c r="N11" s="125" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="O11" s="126" t="n"/>
+      <c r="P11" s="125" t="n"/>
+      <c r="Q11" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 10:27 AM. DECLINED the intro call: "no need for another general introduction call — reach out when you identify a specific contract." States she and Khaalis already connected earlier in 2026 (verify against records). CLAIMED: SDVOSB, WOSB, CA DVBE. No cap statement — being updated, promised. Partial overlap: lists IT and cybersecurity consulting.</t>
+        </is>
+      </c>
+      <c r="R11" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S11" s="115" t="inlineStr">
+        <is>
+          <t>Send bench reply; request updated cap statement when ready | Due 2026-09-25</t>
+        </is>
+      </c>
+      <c r="T11" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U11" s="125" t="inlineStr">
+        <is>
+          <t>#3 + email</t>
+        </is>
+      </c>
+      <c r="V11" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W11" s="125" t="n"/>
+      <c r="X11" s="125" t="n"/>
+      <c r="Y11" s="125" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-08</t>
+        </is>
+      </c>
+      <c r="B12" s="125" t="inlineStr">
+        <is>
+          <t>Testudo Logistics LLC</t>
+        </is>
+      </c>
+      <c r="C12" s="125" t="n"/>
+      <c r="D12" s="115" t="inlineStr">
+        <is>
+          <t>H · Staffing &amp; Workforce / D · Health Ops &amp; Revenue Cycle</t>
+        </is>
+      </c>
+      <c r="E12" s="125" t="inlineStr">
+        <is>
+          <t>Imperial Beach</t>
+        </is>
+      </c>
+      <c r="F12" s="125" t="inlineStr">
+        <is>
+          <t>Brian Connors</t>
+        </is>
+      </c>
+      <c r="G12" s="125" t="inlineStr">
+        <is>
+          <t>brian@testudologistics.com</t>
+        </is>
+      </c>
+      <c r="H12" s="125" t="n"/>
+      <c r="I12" s="125" t="n"/>
+      <c r="J12" s="125" t="n"/>
+      <c r="K12" s="125" t="n"/>
+      <c r="L12" s="125" t="n"/>
+      <c r="M12" s="115" t="inlineStr">
+        <is>
+          <t>Healthcare &amp; clinical staffing, contract staffing, healthcare ops support, workforce training; 45+ prime contracts since 2018</t>
+        </is>
+      </c>
+      <c r="N12" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O12" s="126" t="n">
+        <v>46294</v>
+      </c>
+      <c r="P12" s="125" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="Q12" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 10:46 AM with cap statement. CLAIMED: SBA SDVOSB; "California Disability Disability-Owned Business Enterprise" (CA DOBE — verify whether DOBE or DVBE, they are separate); pursuing SBA 8(a). Names VA, DoD, IHS and National Guard past performance — confirm which were prime vs sub. Strongest lane fit of the inbound set.</t>
+        </is>
+      </c>
+      <c r="R12" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S12" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Tue 2026-09-29 2:30 PM CT</t>
+        </is>
+      </c>
+      <c r="T12" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U12" s="125" t="inlineStr">
+        <is>
+          <t>#4 + email</t>
+        </is>
+      </c>
+      <c r="V12" s="115" t="inlineStr">
+        <is>
+          <t>Reserve Pool row 199 — name/contact match (CA, Lane H, score 8, Imperial Beach, UEI TVKUHNPQ4KJ3)</t>
+        </is>
+      </c>
+      <c r="W12" s="125" t="n"/>
+      <c r="X12" s="125" t="n"/>
+      <c r="Y12" s="125" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-09</t>
+        </is>
+      </c>
+      <c r="B13" s="125" t="inlineStr">
+        <is>
+          <t>Intuitive Agile Solution LLC</t>
+        </is>
+      </c>
+      <c r="C13" s="125" t="inlineStr">
+        <is>
+          <t>IAS</t>
+        </is>
+      </c>
+      <c r="D13" s="115" t="inlineStr">
+        <is>
+          <t>CORE OVERLAP FLAG</t>
+        </is>
+      </c>
+      <c r="E13" s="125" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F13" s="125" t="inlineStr">
+        <is>
+          <t>Luis E. Casillas</t>
+        </is>
+      </c>
+      <c r="G13" s="125" t="inlineStr">
+        <is>
+          <t>luis@intuitiveagilesolution.com</t>
+        </is>
+      </c>
+      <c r="H13" s="125" t="inlineStr">
+        <is>
+          <t>6197823747</t>
+        </is>
+      </c>
+      <c r="I13" s="125" t="inlineStr">
+        <is>
+          <t>intuitiveagilesolution.com</t>
+        </is>
+      </c>
+      <c r="J13" s="125" t="inlineStr">
+        <is>
+          <t>SMC7HCKPAK11</t>
+        </is>
+      </c>
+      <c r="K13" s="125" t="inlineStr">
+        <is>
+          <t>9YHR7</t>
+        </is>
+      </c>
+      <c r="L13" s="125" t="n"/>
+      <c r="M13" s="115" t="inlineStr">
+        <is>
+          <t>Non-competing slice would be requirements gathering, UAT, delivery coordination, security/privacy documentation</t>
+        </is>
+      </c>
+      <c r="N13" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O13" s="126" t="n">
+        <v>46295</v>
+      </c>
+      <c r="P13" s="125" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="Q13" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 11:37 AM with cap statement v3.0 + SBA approval letter. CLAIMED: SBA VetCert SDVOSB, CA DVBE (Cert 2053573), CA Bidder ID BID0132021. HARD-CHECK FLAG: core service areas are secure cloud and application modernization, software/platform modernization, AI-assisted knowledge tools, data and reporting systems = VBX core. POSTURE FLAG: states his primary goal is to understand VBX strategy, target markets and pipeline first.</t>
+        </is>
+      </c>
+      <c r="R13" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S13" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Wed 2026-09-30 2:00 PM CT — resolve overlap first</t>
+        </is>
+      </c>
+      <c r="T13" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U13" s="125" t="inlineStr">
+        <is>
+          <t>#4 + email</t>
+        </is>
+      </c>
+      <c r="V13" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W13" s="125" t="n"/>
+      <c r="X13" s="125" t="n"/>
+      <c r="Y13" s="125" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-10</t>
+        </is>
+      </c>
+      <c r="B14" s="125" t="inlineStr">
+        <is>
+          <t>EGA Group LLC</t>
+        </is>
+      </c>
+      <c r="C14" s="125" t="n"/>
+      <c r="D14" s="115" t="inlineStr">
+        <is>
+          <t>B · Network, Telecom &amp; Hardware / F · Contact Center &amp; Document Svcs</t>
+        </is>
+      </c>
+      <c r="E14" s="125" t="inlineStr">
+        <is>
+          <t>National City</t>
+        </is>
+      </c>
+      <c r="F14" s="125" t="inlineStr">
+        <is>
+          <t>Paul Rising</t>
+        </is>
+      </c>
+      <c r="G14" s="125" t="inlineStr">
+        <is>
+          <t>paul.rising@egagroupllc.com</t>
+        </is>
+      </c>
+      <c r="H14" s="125" t="inlineStr">
+        <is>
+          <t>6198974845</t>
+        </is>
+      </c>
+      <c r="I14" s="125" t="inlineStr">
+        <is>
+          <t>egagroupllc.com</t>
+        </is>
+      </c>
+      <c r="J14" s="125" t="n"/>
+      <c r="K14" s="125" t="n"/>
+      <c r="L14" s="125" t="n"/>
+      <c r="M14" s="115" t="inlineStr">
+        <is>
+          <t>Network cabling, telecom, IT hardware/product resale; contact center staffing and document scanning/digitization</t>
+        </is>
+      </c>
+      <c r="N14" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O14" s="126" t="n">
+        <v>46295</v>
+      </c>
+      <c r="P14" s="125" t="inlineStr">
+        <is>
+          <t>2:30 PM</t>
+        </is>
+      </c>
+      <c r="Q14" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 11:54 AM with cap statement; offered Calendly. CLAIMED: SDVOSB, CA DVBE, CA SB(Micro). CORRECTION: an earlier chat flagged EGA as network/cyber under 541512 overlapping VBX core — his actual reply states cabling/telecom/hardware resale plus contact center and scanning, i.e. Lanes B and F with NO overlap. Earlier flag was wrong; lane also differs from Reserve Pool (C).</t>
+        </is>
+      </c>
+      <c r="R14" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S14" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Wed 2026-09-30 2:30 PM CT</t>
+        </is>
+      </c>
+      <c r="T14" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U14" s="125" t="inlineStr">
+        <is>
+          <t>#1 + email</t>
+        </is>
+      </c>
+      <c r="V14" s="115" t="inlineStr">
+        <is>
+          <t>Reserve Pool row 61 — name/contact match (CA, Lane C, score 9, National City, UEI J8KRCRJ4NAY7)</t>
+        </is>
+      </c>
+      <c r="W14" s="125" t="n"/>
+      <c r="X14" s="125" t="n"/>
+      <c r="Y14" s="125" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-11</t>
+        </is>
+      </c>
+      <c r="B15" s="125" t="inlineStr">
+        <is>
+          <t>24HRC</t>
+        </is>
+      </c>
+      <c r="C15" s="125" t="n"/>
+      <c r="D15" s="115" t="inlineStr">
+        <is>
+          <t>None named</t>
+        </is>
+      </c>
+      <c r="E15" s="125" t="inlineStr">
+        <is>
+          <t>Orange County</t>
+        </is>
+      </c>
+      <c r="F15" s="125" t="inlineStr">
+        <is>
+          <t>Bobby Ameen</t>
+        </is>
+      </c>
+      <c r="G15" s="125" t="inlineStr">
+        <is>
+          <t>bobby@24hrc.com</t>
+        </is>
+      </c>
+      <c r="H15" s="125" t="inlineStr">
+        <is>
+          <t>9494076800</t>
+        </is>
+      </c>
+      <c r="I15" s="125" t="inlineStr">
+        <is>
+          <t>24hrc.com</t>
+        </is>
+      </c>
+      <c r="J15" s="125" t="n"/>
+      <c r="K15" s="125" t="n"/>
+      <c r="L15" s="125" t="n"/>
+      <c r="M15" s="115" t="inlineStr">
+        <is>
+          <t>No specific lane named — construction/restoration general contractor offering a four-firm team</t>
+        </is>
+      </c>
+      <c r="N15" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O15" s="126" t="n">
+        <v>46295</v>
+      </c>
+      <c r="P15" s="125" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="Q15" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 1:55 PM. STAGE 1 FAIL as written: names no specific alignment area ("this work identified in your gaps"), no certifications, no UEI/CAGE, no cap statement. Firm is a construction, restoration, renovation and emergency-response GC (CA LIC #895339, Certified Firm #118327) — not one of the eight lanes. Proposes a lean self-perform team of four 24HRC partner firms; broker-shaped. Clarifying questions sent.</t>
+        </is>
+      </c>
+      <c r="R15" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S15" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Wed 2026-09-30 1:00 PM CT — Stage 1 gate first</t>
+        </is>
+      </c>
+      <c r="T15" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U15" s="125" t="inlineStr">
+        <is>
+          <t>#2 + email</t>
+        </is>
+      </c>
+      <c r="V15" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W15" s="125" t="n"/>
+      <c r="X15" s="125" t="n"/>
+      <c r="Y15" s="125" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-12</t>
+        </is>
+      </c>
+      <c r="B16" s="125" t="inlineStr">
+        <is>
+          <t>Session Real Estate, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" s="125" t="inlineStr">
+        <is>
+          <t>Kenny Session Speaks</t>
+        </is>
+      </c>
+      <c r="D16" s="115" t="inlineStr">
+        <is>
+          <t>E · Research, Evaluation &amp; GIS / C · Change Mgmt, PMO &amp; Training</t>
+        </is>
+      </c>
+      <c r="E16" s="125" t="inlineStr">
+        <is>
+          <t>Oakland area</t>
+        </is>
+      </c>
+      <c r="F16" s="125" t="inlineStr">
+        <is>
+          <t>Kenneth "Kenny" Session</t>
+        </is>
+      </c>
+      <c r="G16" s="125" t="inlineStr">
+        <is>
+          <t>ksession@sessionrealestate.com</t>
+        </is>
+      </c>
+      <c r="H16" s="125" t="inlineStr">
+        <is>
+          <t>5102907990</t>
+        </is>
+      </c>
+      <c r="I16" s="125" t="n"/>
+      <c r="J16" s="125" t="n"/>
+      <c r="K16" s="125" t="n"/>
+      <c r="L16" s="125" t="n"/>
+      <c r="M16" s="115" t="inlineStr">
+        <is>
+          <t>Program evaluation, curriculum/training delivery, change mgmt — reentry and workforce programming for justice-involved populations</t>
+        </is>
+      </c>
+      <c r="N16" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O16" s="126" t="n">
+        <v>46293</v>
+      </c>
+      <c r="P16" s="125" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="Q16" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 2:37 PM; cap statement referenced as attached. CLAIMED: SDVOSB, CA DVBE. VERTICAL FLAG: corrections/probation/reentry does not clearly map to a VBX vertical (federal/SLED health IT, CAH/rural, Medicaid, public-sector AI adoption, state IT, tribal health) — resolve on call. Offered to send program examples and to execute an NDA.</t>
+        </is>
+      </c>
+      <c r="R16" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S16" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Mon 2026-09-28 10:00 AM CT</t>
+        </is>
+      </c>
+      <c r="T16" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U16" s="125" t="inlineStr">
+        <is>
+          <t>#2 + email</t>
+        </is>
+      </c>
+      <c r="V16" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W16" s="125" t="n"/>
+      <c r="X16" s="125" t="n"/>
+      <c r="Y16" s="125" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-13</t>
+        </is>
+      </c>
+      <c r="B17" s="125" t="inlineStr">
+        <is>
+          <t>PURECJ HOLDING LLC</t>
+        </is>
+      </c>
+      <c r="C17" s="125" t="inlineStr">
+        <is>
+          <t>Bastion Supply &amp; Logistics</t>
+        </is>
+      </c>
+      <c r="D17" s="115" t="inlineStr">
+        <is>
+          <t>Self-declared NO FIT (adjacency: B · Network, Telecom &amp; Hardware)</t>
+        </is>
+      </c>
+      <c r="E17" s="125" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="F17" s="125" t="inlineStr">
+        <is>
+          <t>Charles Liu, MBA</t>
+        </is>
+      </c>
+      <c r="G17" s="125" t="inlineStr">
+        <is>
+          <t>charles@bastionserve.com</t>
+        </is>
+      </c>
+      <c r="H17" s="125" t="inlineStr">
+        <is>
+          <t>2137889999</t>
+        </is>
+      </c>
+      <c r="I17" s="125" t="inlineStr">
+        <is>
+          <t>bastionserve.com</t>
+        </is>
+      </c>
+      <c r="J17" s="125" t="inlineStr">
+        <is>
+          <t>YG65G9MUT8S4</t>
+        </is>
+      </c>
+      <c r="K17" s="125" t="inlineStr">
+        <is>
+          <t>9ZKD4</t>
+        </is>
+      </c>
+      <c r="L17" s="125" t="inlineStr">
+        <is>
+          <t>488510, 541611, 541614, 541618, 561210</t>
+        </is>
+      </c>
+      <c r="M17" s="115" t="inlineStr">
+        <is>
+          <t>Adjacency only: hardware staging/delivery, equipment moves, site-to-site transport on deployments</t>
+        </is>
+      </c>
+      <c r="N17" s="125" t="inlineStr">
+        <is>
+          <t>Parked</t>
+        </is>
+      </c>
+      <c r="O17" s="126" t="n"/>
+      <c r="P17" s="125" t="n"/>
+      <c r="Q17" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 4:03 PM with cap statement. SELF-DISQUALIFIED, in writing: "our lane is not on your list." Freight and material movement; NAICS 488510 primary. CLAIMED: SBA VetCert #98307 SDVOSB/VOSB, CA Cert #2052517 DVBE/SB-Micro, FMCSA Broker of Property (USDOT #5796599, MC 64902043), DIR PWCR 2000032002 thru 2027-06-30. Candid and well-documented — keep on file for CA deployment logistics.</t>
+        </is>
+      </c>
+      <c r="R17" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S17" s="115" t="inlineStr">
+        <is>
+          <t>Send bench reply; hold for CA task orders carrying hardware logistics | Due 2026-09-25</t>
+        </is>
+      </c>
+      <c r="T17" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U17" s="125" t="inlineStr">
+        <is>
+          <t>#1 + email</t>
+        </is>
+      </c>
+      <c r="V17" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W17" s="125" t="n"/>
+      <c r="X17" s="125" t="n"/>
+      <c r="Y17" s="125" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-14</t>
+        </is>
+      </c>
+      <c r="B18" s="125" t="inlineStr">
+        <is>
+          <t>Hutchings Ventures, LLC</t>
+        </is>
+      </c>
+      <c r="C18" s="125" t="n"/>
+      <c r="D18" s="115" t="inlineStr">
+        <is>
+          <t>D · Health Ops &amp; Revenue Cycle</t>
+        </is>
+      </c>
+      <c r="E18" s="125" t="inlineStr">
+        <is>
+          <t>Torrance</t>
+        </is>
+      </c>
+      <c r="F18" s="125" t="inlineStr">
+        <is>
+          <t>Jean A. Hutchings</t>
+        </is>
+      </c>
+      <c r="G18" s="125" t="inlineStr">
+        <is>
+          <t>info@hutchingsventures.com</t>
+        </is>
+      </c>
+      <c r="H18" s="125" t="inlineStr">
+        <is>
+          <t>3109742363</t>
+        </is>
+      </c>
+      <c r="I18" s="125" t="inlineStr">
+        <is>
+          <t>hutchingsventures.com/government-solutions</t>
+        </is>
+      </c>
+      <c r="J18" s="125" t="inlineStr">
+        <is>
+          <t>LM7DA7CZ4M46</t>
+        </is>
+      </c>
+      <c r="K18" s="125" t="n"/>
+      <c r="L18" s="125" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="M18" s="115" t="inlineStr">
+        <is>
+          <t>Healthcare operations, revenue cycle, change mgmt, project support, end-user training</t>
+        </is>
+      </c>
+      <c r="N18" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O18" s="126" t="n">
+        <v>46294</v>
+      </c>
+      <c r="P18" s="125" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="Q18" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 8:14 PM with cap statement. No certifications claimed in the reply. CAPACITY / ATTRIBUTION FLAG: describes 30+ years of the founder's own operational leadership and her EMR/EMA implementation experience — confirm what Hutchings Ventures has delivered as a FIRM versus the founder's prior-employer work.</t>
+        </is>
+      </c>
+      <c r="R18" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S18" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Tue 2026-09-29 10:00 AM CT</t>
+        </is>
+      </c>
+      <c r="T18" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U18" s="125" t="inlineStr">
+        <is>
+          <t>#1 + email</t>
+        </is>
+      </c>
+      <c r="V18" s="115" t="inlineStr">
+        <is>
+          <t>Reserve Pool row 7 — UEI/name match (CA, Lane C, score 10, Torrance)</t>
+        </is>
+      </c>
+      <c r="W18" s="125" t="n"/>
+      <c r="X18" s="125" t="n"/>
+      <c r="Y18" s="125" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-16</t>
+        </is>
+      </c>
+      <c r="B19" s="125" t="inlineStr">
+        <is>
+          <t>DVBE Connect, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" s="125" t="n"/>
+      <c r="D19" s="115" t="inlineStr">
+        <is>
+          <t>H · Staffing &amp; Workforce</t>
+        </is>
+      </c>
+      <c r="E19" s="125" t="inlineStr">
+        <is>
+          <t>Folsom</t>
+        </is>
+      </c>
+      <c r="F19" s="125" t="inlineStr">
+        <is>
+          <t>Jack Batchelor (fwd by Christopher Haney)</t>
+        </is>
+      </c>
+      <c r="G19" s="125" t="inlineStr">
+        <is>
+          <t>@dvbeconnect.com</t>
+        </is>
+      </c>
+      <c r="H19" s="125" t="n"/>
+      <c r="I19" s="125" t="n"/>
+      <c r="J19" s="125" t="inlineStr">
+        <is>
+          <t>ET7UYCCVTCQ3</t>
+        </is>
+      </c>
+      <c r="K19" s="125" t="n"/>
+      <c r="L19" s="125" t="inlineStr">
+        <is>
+          <t>561311</t>
+        </is>
+      </c>
+      <c r="M19" s="115" t="inlineStr">
+        <is>
+          <t>Per Reserve Pool: Lane H staffing/workforce</t>
+        </is>
+      </c>
+      <c r="N19" s="125" t="inlineStr">
+        <is>
+          <t>Replied</t>
+        </is>
+      </c>
+      <c r="O19" s="126" t="n"/>
+      <c r="P19" s="125" t="n"/>
+      <c r="Q19" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 (chat #3). Listed contact Chris Haney forwarded internally to Jack Batchelor. Threads to the 2026-09-21 6:00 AM send. Reply text not yet uploaded — content unknown beyond the fact of a reply.</t>
+        </is>
+      </c>
+      <c r="R19" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S19" s="115" t="inlineStr">
+        <is>
+          <t>Retrieve reply text, screen (Stage 0–3), then schedule | Due 2026-09-25</t>
+        </is>
+      </c>
+      <c r="T19" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U19" s="125" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="V19" s="115" t="inlineStr">
+        <is>
+          <t>Reserve Pool row 379 — CA, Lane H, score 7, Folsom</t>
+        </is>
+      </c>
+      <c r="W19" s="125" t="n"/>
+      <c r="X19" s="125" t="n"/>
+      <c r="Y19" s="125" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-17</t>
+        </is>
+      </c>
+      <c r="B20" s="125" t="inlineStr">
+        <is>
+          <t>Client Cloudcare</t>
+        </is>
+      </c>
+      <c r="C20" s="125" t="n"/>
+      <c r="D20" s="115" t="inlineStr">
+        <is>
+          <t>A · Assurance / Risk / Cyber GRC / C · Change Mgmt, PMO &amp; Training / E · Research, Evaluation &amp; GIS</t>
+        </is>
+      </c>
+      <c r="E20" s="125" t="inlineStr">
+        <is>
+          <t>San Diego area</t>
+        </is>
+      </c>
+      <c r="F20" s="125" t="inlineStr">
+        <is>
+          <t>Mary Crozier, CEO + Founder</t>
+        </is>
+      </c>
+      <c r="G20" s="125" t="inlineStr">
+        <is>
+          <t>mary@clientcloudcare.com</t>
+        </is>
+      </c>
+      <c r="H20" s="125" t="inlineStr">
+        <is>
+          <t>6194325488</t>
+        </is>
+      </c>
+      <c r="I20" s="125" t="inlineStr">
+        <is>
+          <t>clientcloudcare.com</t>
+        </is>
+      </c>
+      <c r="J20" s="125" t="inlineStr">
+        <is>
+          <t>NJBEZFGMDAW9</t>
+        </is>
+      </c>
+      <c r="K20" s="125" t="inlineStr">
+        <is>
+          <t>9TYN2</t>
+        </is>
+      </c>
+      <c r="L20" s="125" t="n"/>
+      <c r="M20" s="115" t="inlineStr">
+        <is>
+          <t>Salesforce managed services + QA/beta testing, independent risk assessment, audit readiness, change mgmt, PMO, training, program evaluation</t>
+        </is>
+      </c>
+      <c r="N20" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O20" s="126" t="n">
+        <v>46295</v>
+      </c>
+      <c r="P20" s="125" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="Q20" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-22 12:16 PM. Explicitly states it does not compete as a technology builder with VBX. CLAIMED: WOSB/EDWOSB; registered in WA, MT and CA; authorized fulfillment partner on Carahsoft NASPO ValuePoint #LS4983. Mission focus on veteran and military-spouse employment. Offered a booking link; VBX proposed a time instead. No cap statement yet.</t>
+        </is>
+      </c>
+      <c r="R20" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S20" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Wed 2026-09-30 10:30 AM CT</t>
+        </is>
+      </c>
+      <c r="T20" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U20" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-22</t>
+        </is>
+      </c>
+      <c r="V20" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W20" s="125" t="n"/>
+      <c r="X20" s="125" t="n"/>
+      <c r="Y20" s="125" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="125" t="inlineStr">
+        <is>
+          <t>IN-WA-01</t>
+        </is>
+      </c>
+      <c r="B21" s="125" t="inlineStr">
+        <is>
+          <t>Hughes Group LLC</t>
+        </is>
+      </c>
+      <c r="C21" s="125" t="n"/>
+      <c r="D21" s="115" t="inlineStr">
+        <is>
+          <t>Unstated — self-described "tag along sub"</t>
+        </is>
+      </c>
+      <c r="E21" s="125" t="n"/>
+      <c r="F21" s="125" t="inlineStr">
+        <is>
+          <t>Aubrey R. Robertson, Dir. of Government Services</t>
+        </is>
+      </c>
+      <c r="G21" s="125" t="inlineStr">
+        <is>
+          <t>BusDev@hughesgroup.biz</t>
+        </is>
+      </c>
+      <c r="H21" s="125" t="inlineStr">
+        <is>
+          <t>2533565027</t>
+        </is>
+      </c>
+      <c r="I21" s="125" t="inlineStr">
+        <is>
+          <t>hughesgroupllc.com</t>
+        </is>
+      </c>
+      <c r="J21" s="125" t="inlineStr">
+        <is>
+          <t>GFK7ANN57833</t>
+        </is>
+      </c>
+      <c r="K21" s="125" t="n"/>
+      <c r="L21" s="125" t="n"/>
+      <c r="M21" s="115" t="inlineStr">
+        <is>
+          <t>Unknown — raised hand via referral; WA-area area code</t>
+        </is>
+      </c>
+      <c r="N21" s="125" t="inlineStr">
+        <is>
+          <t>Replied</t>
+        </is>
+      </c>
+      <c r="O21" s="126" t="n"/>
+      <c r="P21" s="125" t="n"/>
+      <c r="Q21" s="115" t="inlineStr">
+        <is>
+          <t>Surfaced 2026-09-21 6:26 PM by forwarding the VBX outreach to [[The Green Technology Group]] (IN-UNK-05) and writing "we'd like to do this type of work, we're better suited a tag along sub." Never contacted VBX directly. 253 area code = Washington. No certifications, lane or cap statement offered. Uses "Entity ID" rather than UEI — verify the identifier format.</t>
+        </is>
+      </c>
+      <c r="R21" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S21" s="115" t="inlineStr">
+        <is>
+          <t>Decide whether to contact directly; if yes, send Wave 1 note | Due 2026-09-30</t>
+        </is>
+      </c>
+      <c r="T21" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U21" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-22</t>
+        </is>
+      </c>
+      <c r="V21" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W21" s="125" t="n"/>
+      <c r="X21" s="125" t="n"/>
+      <c r="Y21" s="125" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="125" t="inlineStr">
+        <is>
+          <t>IN-WA-02</t>
+        </is>
+      </c>
+      <c r="B22" s="125" t="inlineStr">
+        <is>
+          <t>Lucid Consulting Group LLC</t>
+        </is>
+      </c>
+      <c r="C22" s="125" t="n"/>
+      <c r="D22" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training</t>
+        </is>
+      </c>
+      <c r="E22" s="125" t="inlineStr">
+        <is>
+          <t>Bellevue</t>
+        </is>
+      </c>
+      <c r="F22" s="125" t="inlineStr">
+        <is>
+          <t>Mahta Redda</t>
+        </is>
+      </c>
+      <c r="G22" s="125" t="inlineStr">
+        <is>
+          <t>mredda@lucid-company.com</t>
+        </is>
+      </c>
+      <c r="H22" s="125" t="inlineStr">
+        <is>
+          <t>4255187783</t>
+        </is>
+      </c>
+      <c r="I22" s="125" t="inlineStr">
+        <is>
+          <t>lucidconsulting.co</t>
+        </is>
+      </c>
+      <c r="J22" s="125" t="inlineStr">
+        <is>
+          <t>LM97RMCF2415</t>
+        </is>
+      </c>
+      <c r="K22" s="125" t="n"/>
+      <c r="L22" s="125" t="n"/>
+      <c r="M22" s="115" t="inlineStr">
+        <is>
+          <t>Change mgmt, PMO, program evaluation, healthcare/regulated program support, professional staffing</t>
+        </is>
+      </c>
+      <c r="N22" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O22" s="126" t="n">
+        <v>46295</v>
+      </c>
+      <c r="P22" s="125" t="inlineStr">
+        <is>
+          <t>10:00 AM</t>
+        </is>
+      </c>
+      <c r="Q22" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-22 10:27 AM with Lucid Gov Capability Statement. CLAIMED: SBA WOSB, WBENC WBE, NWMSDC MBE, OMWBE DBE, SBA Small Business, SAM registered; 15+ yrs, ~10 yrs as Tier 1 Preferred Supplier to Microsoft. Comfortable with a mutual NDA pre-discussion. ON THE WAVE 1 LIST — EXCLUDE WA-13 FROM THE 9/28 SEND.</t>
+        </is>
+      </c>
+      <c r="R22" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S22" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Wed 2026-09-30 10:00 AM CT</t>
+        </is>
+      </c>
+      <c r="T22" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U22" s="125" t="inlineStr">
+        <is>
+          <t>#2 + email</t>
+        </is>
+      </c>
+      <c r="V22" s="115" t="inlineStr">
+        <is>
+          <t>WAVE 1: WA-13 (Lane C, Bellevue) — Wave 1 Status left Not Contacted per instruction</t>
+        </is>
+      </c>
+      <c r="W22" s="125" t="n"/>
+      <c r="X22" s="125" t="n"/>
+      <c r="Y22" s="125" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="125" t="inlineStr">
+        <is>
+          <t>IN-WA-03</t>
+        </is>
+      </c>
+      <c r="B23" s="125" t="inlineStr">
+        <is>
+          <t>Kaizen Construction &amp; Development</t>
+        </is>
+      </c>
+      <c r="C23" s="125" t="n"/>
+      <c r="D23" s="115" t="inlineStr">
+        <is>
+          <t>None named</t>
+        </is>
+      </c>
+      <c r="E23" s="125" t="n"/>
+      <c r="F23" s="125" t="n"/>
+      <c r="G23" s="125" t="n"/>
+      <c r="H23" s="125" t="n"/>
+      <c r="I23" s="125" t="n"/>
+      <c r="J23" s="125" t="n"/>
+      <c r="K23" s="125" t="n"/>
+      <c r="L23" s="125" t="n"/>
+      <c r="M23" s="115" t="inlineStr">
+        <is>
+          <t>Cap statement only; NAICS 236220 construction — no lane match evident</t>
+        </is>
+      </c>
+      <c r="N23" s="125" t="inlineStr">
+        <is>
+          <t>Replied</t>
+        </is>
+      </c>
+      <c r="O23" s="126" t="n"/>
+      <c r="P23" s="125" t="n"/>
+      <c r="Q23" s="115" t="inlineStr">
+        <is>
+          <t>Capability statement PDF surfaced in chat #2; no matching reply email located. CLAIMED: SDVOSB. NAICS 236220 per statement. NOT the same firm as Reserve Pool "Modern Kaizen LLC" (CA, different UEI).</t>
+        </is>
+      </c>
+      <c r="R23" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S23" s="115" t="inlineStr">
+        <is>
+          <t>Locate reply email, then screen (Stage 0–3) | Due 2026-09-25</t>
+        </is>
+      </c>
+      <c r="T23" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U23" s="125" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="V23" s="115" t="inlineStr">
+        <is>
+          <t>None found (Modern Kaizen LLC is a different firm)</t>
+        </is>
+      </c>
+      <c r="W23" s="125" t="n"/>
+      <c r="X23" s="125" t="n"/>
+      <c r="Y23" s="125" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="125" t="inlineStr">
+        <is>
+          <t>IN-WA-04</t>
+        </is>
+      </c>
+      <c r="B24" s="125" t="inlineStr">
+        <is>
+          <t>KR Project Works, LLC</t>
+        </is>
+      </c>
+      <c r="C24" s="125" t="n"/>
+      <c r="D24" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training</t>
+        </is>
+      </c>
+      <c r="E24" s="125" t="inlineStr">
+        <is>
+          <t>Kirkland</t>
+        </is>
+      </c>
+      <c r="F24" s="125" t="inlineStr">
+        <is>
+          <t>Kelly Rush</t>
+        </is>
+      </c>
+      <c r="G24" s="125" t="n"/>
+      <c r="H24" s="125" t="n"/>
+      <c r="I24" s="125" t="n"/>
+      <c r="J24" s="125" t="inlineStr">
+        <is>
+          <t>NDTWPTFMTRM8</t>
+        </is>
+      </c>
+      <c r="K24" s="125" t="n"/>
+      <c r="L24" s="125" t="inlineStr">
+        <is>
+          <t>541611</t>
+        </is>
+      </c>
+      <c r="M24" s="115" t="inlineStr">
+        <is>
+          <t>Per Reserve Pool and cap statement: PM/consulting</t>
+        </is>
+      </c>
+      <c r="N24" s="125" t="inlineStr">
+        <is>
+          <t>Replied</t>
+        </is>
+      </c>
+      <c r="O24" s="126" t="n"/>
+      <c r="P24" s="125" t="n"/>
+      <c r="Q24" s="115" t="inlineStr">
+        <is>
+          <t>Capability statement PDF surfaced in chat #2; no matching reply email located. CLAIMED: WOSB. NAICS 541611 per statement.</t>
+        </is>
+      </c>
+      <c r="R24" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S24" s="115" t="inlineStr">
+        <is>
+          <t>Locate reply email, then screen (Stage 0–3) | Due 2026-09-25</t>
+        </is>
+      </c>
+      <c r="T24" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U24" s="125" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="V24" s="115" t="inlineStr">
+        <is>
+          <t>Reserve Pool row 402 — WA, Lane C, score 8.5, Kirkland</t>
+        </is>
+      </c>
+      <c r="W24" s="125" t="n"/>
+      <c r="X24" s="125" t="n"/>
+      <c r="Y24" s="125" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="125" t="inlineStr">
+        <is>
+          <t>IN-UNK-01</t>
+        </is>
+      </c>
+      <c r="B25" s="125" t="inlineStr">
+        <is>
+          <t>Augustus Veteran Services LLC</t>
+        </is>
+      </c>
+      <c r="C25" s="125" t="n"/>
+      <c r="D25" s="115" t="inlineStr">
+        <is>
+          <t>A · Assurance / Risk / Cyber GRC / C · Change Mgmt, PMO &amp; Training / E · Research, Evaluation &amp; GIS</t>
+        </is>
+      </c>
+      <c r="E25" s="125" t="n"/>
+      <c r="F25" s="125" t="inlineStr">
+        <is>
+          <t>Cromwell Dyette</t>
+        </is>
+      </c>
+      <c r="G25" s="125" t="inlineStr">
+        <is>
+          <t>cromwell.dyette@cdveteranservices.com</t>
+        </is>
+      </c>
+      <c r="H25" s="125" t="inlineStr">
+        <is>
+          <t>9782671597</t>
+        </is>
+      </c>
+      <c r="I25" s="125" t="n"/>
+      <c r="J25" s="125" t="inlineStr">
+        <is>
+          <t>HRJ4LLW2MCN8</t>
+        </is>
+      </c>
+      <c r="K25" s="125" t="inlineStr">
+        <is>
+          <t>20E24</t>
+        </is>
+      </c>
+      <c r="L25" s="125" t="n"/>
+      <c r="M25" s="115" t="inlineStr">
+        <is>
+          <t>Federal lane of the CD Veteran Services pair — independent assessment, PMO support, program evaluation</t>
+        </is>
+      </c>
+      <c r="N25" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O25" s="126" t="n">
+        <v>46293</v>
+      </c>
+      <c r="P25" s="125" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="Q25" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 9:18 AM as the FEDERAL lane of a two-entity pair with [[CD Veteran Services LLC]] (IN-CA-04), same owner, one call covers both. CLAIMED: SBA certified SDVOSB and VOSB, SAM registration active; raised SDVOSB sole-source eligibility up to $5M under 15 USC 657f in the context of a future federal JV. CAPACITY FLAG: owner performs the work. State of operation not stated.</t>
+        </is>
+      </c>
+      <c r="R25" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S25" s="115" t="inlineStr">
+        <is>
+          <t>Covered by the CD Veteran Services call, Mon 2026-09-28 2:00 PM CT</t>
+        </is>
+      </c>
+      <c r="T25" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U25" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-22</t>
+        </is>
+      </c>
+      <c r="V25" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W25" s="125" t="n"/>
+      <c r="X25" s="125" t="n"/>
+      <c r="Y25" s="125" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="125" t="inlineStr">
+        <is>
+          <t>IN-UNK-02</t>
+        </is>
+      </c>
+      <c r="B26" s="125" t="inlineStr">
+        <is>
+          <t>Waypoint 33 LLC</t>
+        </is>
+      </c>
+      <c r="C26" s="125" t="inlineStr">
+        <is>
+          <t>WP33</t>
+        </is>
+      </c>
+      <c r="D26" s="115" t="inlineStr">
+        <is>
+          <t>E · Research, Evaluation &amp; GIS / B · Network, Telecom &amp; Hardware</t>
+        </is>
+      </c>
+      <c r="E26" s="125" t="n"/>
+      <c r="F26" s="125" t="inlineStr">
+        <is>
+          <t>Randall René, Principal Advisor &amp; Founder</t>
+        </is>
+      </c>
+      <c r="G26" s="125" t="inlineStr">
+        <is>
+          <t>randall@waypoint33.com</t>
+        </is>
+      </c>
+      <c r="H26" s="125" t="n"/>
+      <c r="I26" s="125" t="inlineStr">
+        <is>
+          <t>waypoint33.com / waypoint33gov.com</t>
+        </is>
+      </c>
+      <c r="J26" s="125" t="inlineStr">
+        <is>
+          <t>VHR1VQ9NRQT3</t>
+        </is>
+      </c>
+      <c r="K26" s="125" t="inlineStr">
+        <is>
+          <t>15PU3</t>
+        </is>
+      </c>
+      <c r="L26" s="125" t="n"/>
+      <c r="M26" s="115" t="inlineStr">
+        <is>
+          <t>GIS and telecom strategy advisory; ArcGIS-native RF planning, network/telecom infrastructure planning, digital twin</t>
+        </is>
+      </c>
+      <c r="N26" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O26" s="126" t="n">
+        <v>46294</v>
+      </c>
+      <c r="P26" s="125" t="inlineStr">
+        <is>
+          <t>2:00 PM</t>
+        </is>
+      </c>
+      <c r="Q26" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 10:36 AM. CLAIMED: SDVOSB, SAM registered; CA DVBE AWAITING, not held — do not cite as current. Exclusive U.S. distributor for Cellular Expert (ArcGIS-native RF planning platform) — clarify whether advisory services are delivered independently of the platform. No cap statement; referred to website. Also references unnamed partner firms. State of operation not stated.</t>
+        </is>
+      </c>
+      <c r="R26" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S26" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Tue 2026-09-29 2:00 PM CT</t>
+        </is>
+      </c>
+      <c r="T26" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U26" s="125" t="inlineStr">
+        <is>
+          <t>#3 + email</t>
+        </is>
+      </c>
+      <c r="V26" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W26" s="125" t="n"/>
+      <c r="X26" s="125" t="n"/>
+      <c r="Y26" s="125" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="125" t="inlineStr">
+        <is>
+          <t>IN-UNK-03</t>
+        </is>
+      </c>
+      <c r="B27" s="125" t="inlineStr">
+        <is>
+          <t>Prestige Development Group</t>
+        </is>
+      </c>
+      <c r="C27" s="125" t="inlineStr">
+        <is>
+          <t>PDG</t>
+        </is>
+      </c>
+      <c r="D27" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training / E · Research, Evaluation &amp; GIS / H · Staffing &amp; Workforce — CORE OVERLAP FLAG</t>
+        </is>
+      </c>
+      <c r="E27" s="125" t="n"/>
+      <c r="F27" s="125" t="inlineStr">
+        <is>
+          <t>Tiffany Jorge</t>
+        </is>
+      </c>
+      <c r="G27" s="125" t="inlineStr">
+        <is>
+          <t>tiffanyj@prestigedevelopment.tech</t>
+        </is>
+      </c>
+      <c r="H27" s="125" t="n"/>
+      <c r="I27" s="125" t="n"/>
+      <c r="J27" s="125" t="n"/>
+      <c r="K27" s="125" t="n"/>
+      <c r="L27" s="125" t="n"/>
+      <c r="M27" s="115" t="inlineStr">
+        <is>
+          <t>PMO support, change mgmt, GIS/geospatial, technical and contract staffing, workforce solutions</t>
+        </is>
+      </c>
+      <c r="N27" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O27" s="126" t="n">
+        <v>46293</v>
+      </c>
+      <c r="P27" s="125" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="Q27" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 5:00 PM with Capability Statement 2026. CLAIMED: SBA HUBZone, EDWOSB, recently awarded GSA MAS. HARD-CHECK FLAG: own reply lists technical capabilities across cloud modernization, AI, data, GIS and IT services = VBX core. SIGNATURE MISMATCH: sender is "Tiffany Jorge", email signed "Tiffany Sequeira" — resolve identity. Raised reciprocal teaming and a possible future JV. State of operation not stated.</t>
+        </is>
+      </c>
+      <c r="R27" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S27" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Mon 2026-09-28 10:30 AM CT — resolve overlap and identity first</t>
+        </is>
+      </c>
+      <c r="T27" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U27" s="125" t="inlineStr">
+        <is>
+          <t>#1 + email</t>
+        </is>
+      </c>
+      <c r="V27" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W27" s="125" t="n"/>
+      <c r="X27" s="125" t="n"/>
+      <c r="Y27" s="125" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="125" t="inlineStr">
+        <is>
+          <t>IN-UNK-04</t>
+        </is>
+      </c>
+      <c r="B28" s="125" t="inlineStr">
+        <is>
+          <t>Binnacle Services, LLC</t>
+        </is>
+      </c>
+      <c r="C28" s="125" t="n"/>
+      <c r="D28" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training / D · Health Ops &amp; Revenue Cycle</t>
+        </is>
+      </c>
+      <c r="E28" s="125" t="n"/>
+      <c r="F28" s="125" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="G28" s="125" t="inlineStr">
+        <is>
+          <t>brian@binnacleservices.com</t>
+        </is>
+      </c>
+      <c r="H28" s="125" t="n"/>
+      <c r="I28" s="125" t="n"/>
+      <c r="J28" s="125" t="n"/>
+      <c r="K28" s="125" t="n"/>
+      <c r="L28" s="125" t="n"/>
+      <c r="M28" s="115" t="inlineStr">
+        <is>
+          <t>Healthcare IT implementation, PM, organizational change mgmt, end-user training and adoption, healthcare operations</t>
+        </is>
+      </c>
+      <c r="N28" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O28" s="126" t="n">
+        <v>46294</v>
+      </c>
+      <c r="P28" s="125" t="inlineStr">
+        <is>
+          <t>10:30 AM</t>
+        </is>
+      </c>
+      <c r="Q28" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 11:03 PM with cap statement. CLAIMED: VetCert-verified SDVOSB. Cites large-scale federal healthcare EHR modernization and deployment. Offered to execute a mutual NDA before specifics. PARTIAL OVERLAP: "healthcare IT implementation" and support for federal IT acquisition / product-reseller opportunities — clarify the boundary. State of operation not stated.</t>
+        </is>
+      </c>
+      <c r="R28" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S28" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Tue 2026-09-29 10:30 AM CT</t>
+        </is>
+      </c>
+      <c r="T28" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U28" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-22</t>
+        </is>
+      </c>
+      <c r="V28" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W28" s="125" t="n"/>
+      <c r="X28" s="125" t="n"/>
+      <c r="Y28" s="125" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="125" t="inlineStr">
+        <is>
+          <t>IN-UNK-05</t>
+        </is>
+      </c>
+      <c r="B29" s="125" t="inlineStr">
+        <is>
+          <t>The Green Technology Group, LLC</t>
+        </is>
+      </c>
+      <c r="C29" s="125" t="inlineStr">
+        <is>
+          <t>TGTG</t>
+        </is>
+      </c>
+      <c r="D29" s="115" t="inlineStr">
+        <is>
+          <t>B · Network, Telecom &amp; Hardware claimed — CORE OVERLAP + TARGET-STATE FLAG</t>
+        </is>
+      </c>
+      <c r="E29" s="125" t="n"/>
+      <c r="F29" s="125" t="inlineStr">
+        <is>
+          <t>Emmitt Davis, Capture Manager</t>
+        </is>
+      </c>
+      <c r="G29" s="125" t="inlineStr">
+        <is>
+          <t>edavis@tgtgllc.com</t>
+        </is>
+      </c>
+      <c r="H29" s="125" t="inlineStr">
+        <is>
+          <t>2566821927</t>
+        </is>
+      </c>
+      <c r="I29" s="125" t="inlineStr">
+        <is>
+          <t>tgtgllc.com</t>
+        </is>
+      </c>
+      <c r="J29" s="125" t="n"/>
+      <c r="K29" s="125" t="n"/>
+      <c r="L29" s="125" t="n"/>
+      <c r="M29" s="115" t="inlineStr">
+        <is>
+          <t>Network services and field infrastructure would be the only non-competing slice</t>
+        </is>
+      </c>
+      <c r="N29" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O29" s="126" t="n">
+        <v>46295</v>
+      </c>
+      <c r="P29" s="125" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="Q29" s="115" t="inlineStr">
+        <is>
+          <t>Received 2026-09-22 8:32 AM as a FORWARD from Aubrey Robertson at [[Hughes Group LLC]] (IN-WA-01) — not from the VBX send list. TWO HARD-CHECK FLAGS: (1) overlap — self-describes as specializing in Managed Services, Systems/Software Development, Infrastructure IT, plus application development and cybersecurity = VBX core; (2) target state — 256 area code is Huntsville AL, no MT/WA/CA presence named. POSTURE FLAG: read the outreach as a solicitation ("the below opportunity fits well with TGTG core capability") and offered to sub on work that does not exist. CLAIMED: Top-Secret certified SDVOSB, prime on T4NG (Dexteritech), NASA SEWP VI, GSA IT 70, SEAPORT; in business since 2008.</t>
+        </is>
+      </c>
+      <c r="R29" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S29" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-09-25 | Done when: output block logged | Call Wed 2026-09-30 1:30 PM CT — resolve overlap and state first</t>
+        </is>
+      </c>
+      <c r="T29" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U29" s="125" t="inlineStr">
+        <is>
+          <t>#4 + email</t>
+        </is>
+      </c>
+      <c r="V29" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W29" s="125" t="n"/>
+      <c r="X29" s="125" t="n"/>
+      <c r="Y29" s="125" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="125" t="inlineStr">
+        <is>
+          <t>IN-UNK-06</t>
+        </is>
+      </c>
+      <c r="B30" s="125" t="inlineStr">
+        <is>
+          <t>meetasi.com (legal name unconfirmed)</t>
+        </is>
+      </c>
+      <c r="C30" s="125" t="n"/>
+      <c r="D30" s="115" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E30" s="125" t="n"/>
+      <c r="F30" s="125" t="inlineStr">
+        <is>
+          <t>Shawn Sharma</t>
+        </is>
+      </c>
+      <c r="G30" s="125" t="inlineStr">
+        <is>
+          <t>@meetasi.com (domain)</t>
+        </is>
+      </c>
+      <c r="H30" s="125" t="n"/>
+      <c r="I30" s="125" t="n"/>
+      <c r="J30" s="125" t="n"/>
+      <c r="K30" s="125" t="n"/>
+      <c r="L30" s="125" t="n"/>
+      <c r="M30" s="115" t="inlineStr">
+        <is>
+          <t>Unknown — reply text not yet retrieved</t>
+        </is>
+      </c>
+      <c r="N30" s="125" t="inlineStr">
+        <is>
+          <t>Replied</t>
+        </is>
+      </c>
+      <c r="O30" s="126" t="n"/>
+      <c r="P30" s="125" t="n"/>
+      <c r="Q30" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-21 (chat #2). Firm legal name, state, certifications and lane all unidentified. Reply text not uploaded.</t>
+        </is>
+      </c>
+      <c r="R30" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S30" s="115" t="inlineStr">
+        <is>
+          <t>Retrieve reply text, then screen (Stage 0–3) | Due 2026-09-25</t>
+        </is>
+      </c>
+      <c r="T30" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U30" s="125" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="V30" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W30" s="125" t="n"/>
+      <c r="X30" s="125" t="n"/>
+      <c r="Y30" s="125" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-18</t>
+        </is>
+      </c>
+      <c r="B31" s="125" t="inlineStr">
+        <is>
+          <t>TheOpsArchitect.io LLC</t>
+        </is>
+      </c>
+      <c r="C31" s="125" t="n"/>
+      <c r="D31" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training — CORE OVERLAP FLAG</t>
+        </is>
+      </c>
+      <c r="E31" s="125" t="inlineStr">
+        <is>
+          <t>Berkeley</t>
+        </is>
+      </c>
+      <c r="F31" s="125" t="inlineStr">
+        <is>
+          <t>Alina Schenk, CEO/Founder</t>
+        </is>
+      </c>
+      <c r="G31" s="125" t="inlineStr">
+        <is>
+          <t>alina@theopsarchitect.io</t>
+        </is>
+      </c>
+      <c r="H31" s="125" t="inlineStr">
+        <is>
+          <t>5023159574</t>
+        </is>
+      </c>
+      <c r="I31" s="125" t="inlineStr">
+        <is>
+          <t>theopsarchitect.io</t>
+        </is>
+      </c>
+      <c r="J31" s="125" t="inlineStr">
+        <is>
+          <t>NGXDQLBVXGK5</t>
+        </is>
+      </c>
+      <c r="K31" s="125" t="inlineStr">
+        <is>
+          <t>22H15</t>
+        </is>
+      </c>
+      <c r="L31" s="125" t="inlineStr">
+        <is>
+          <t>541512 (primary), 541611, 541618, 611420</t>
+        </is>
+      </c>
+      <c r="M31" s="115" t="inlineStr">
+        <is>
+          <t>Change mgmt, end-user training and adoption is the non-competing slice; CRM/system-of-record builds and data migration are not</t>
+        </is>
+      </c>
+      <c r="N31" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O31" s="126" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P31" s="125" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="Q31" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-22 12:57 PM; followed up 2026-09-25 12:09 PM with a cap statement reorganized around change mgmt, training and adoption. CLAIMED: SBA WOSB certified 2026-08-18, SAM active. TWO FLAGS: (1) overlap — primary NAICS 541512 and the delivered work is system-of-record builds, data migration and process automation = VBX core; (2) capacity — statement says "one practitioner, end to end. No handoffs, no subcontracting." NO GOVERNMENT PAST PERFORMANCE: engagements listed are an industrial equipment distributor and a Berkeley nonprofit. Also a Zoho Business Advisor and HighLevel affiliate partner (reseller posture). Email carries an unsubscribe link — VBX is on a marketing sequence.</t>
+        </is>
+      </c>
+      <c r="R31" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S31" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-10-02 | Done when: output block logged | Call Mon 2026-10-05 1:00 PM CT — resolve overlap and capacity first</t>
+        </is>
+      </c>
+      <c r="T31" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U31" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-26</t>
+        </is>
+      </c>
+      <c r="V31" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W31" s="125" t="n"/>
+      <c r="X31" s="125" t="n"/>
+      <c r="Y31" s="125" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-19</t>
+        </is>
+      </c>
+      <c r="B32" s="125" t="inlineStr">
+        <is>
+          <t>Ewald &amp; Wasserman Research Consultants, LLC</t>
+        </is>
+      </c>
+      <c r="C32" s="125" t="n"/>
+      <c r="D32" s="115" t="inlineStr">
+        <is>
+          <t>E · Research, Evaluation &amp; GIS</t>
+        </is>
+      </c>
+      <c r="E32" s="125" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="F32" s="125" t="inlineStr">
+        <is>
+          <t>Katrin Ewald, Ph.D.</t>
+        </is>
+      </c>
+      <c r="G32" s="125" t="inlineStr">
+        <is>
+          <t>katrin.ewald@eandwresearch.com</t>
+        </is>
+      </c>
+      <c r="H32" s="125" t="inlineStr">
+        <is>
+          <t>4152307750</t>
+        </is>
+      </c>
+      <c r="I32" s="125" t="inlineStr">
+        <is>
+          <t>eandwresearch.com</t>
+        </is>
+      </c>
+      <c r="J32" s="125" t="n"/>
+      <c r="K32" s="125" t="n"/>
+      <c r="L32" s="125" t="n"/>
+      <c r="M32" s="115" t="inlineStr">
+        <is>
+          <t>Social science survey research, multi-mode data collection, program evaluation and needs assessment; health services and public health expertise</t>
+        </is>
+      </c>
+      <c r="N32" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O32" s="126" t="n">
+        <v>46300</v>
+      </c>
+      <c r="P32" s="125" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="Q32" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-23 3:39 PM. ASKED A CLARIFYING QUESTION rather than assuming — whether her survey research is what VBX meant by "program evaluation and user research." Answered in the reply: yes. Holds real research infrastructure — telephone lab, web survey systems, and field teams for in-person survey and field observation in CA and nationally. Domains: traffic safety, energy, health services, public health. GAPS: listed NO certifications (did not answer item 2), no UEI/CAGE, no capability statement — all requested. Strongest Lane E fit received to date.</t>
+        </is>
+      </c>
+      <c r="R32" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S32" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-10-02 | Done when: output block logged | Call Mon 2026-10-05 1:30 PM CT</t>
+        </is>
+      </c>
+      <c r="T32" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U32" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-26</t>
+        </is>
+      </c>
+      <c r="V32" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W32" s="125" t="n"/>
+      <c r="X32" s="125" t="n"/>
+      <c r="Y32" s="125" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-20</t>
+        </is>
+      </c>
+      <c r="B33" s="125" t="inlineStr">
+        <is>
+          <t>OJMMH Enterprise, LLC</t>
+        </is>
+      </c>
+      <c r="C33" s="125" t="n"/>
+      <c r="D33" s="115" t="inlineStr">
+        <is>
+          <t>A · Assurance / Risk / Cyber GRC</t>
+        </is>
+      </c>
+      <c r="E33" s="125" t="inlineStr">
+        <is>
+          <t>Long Beach area</t>
+        </is>
+      </c>
+      <c r="F33" s="125" t="inlineStr">
+        <is>
+          <t>Oumoeurt M. Mousa, Founder &amp; Member</t>
+        </is>
+      </c>
+      <c r="G33" s="125" t="inlineStr">
+        <is>
+          <t>oumoeurt@ojmmhenterprise.com</t>
+        </is>
+      </c>
+      <c r="H33" s="125" t="inlineStr">
+        <is>
+          <t>5622040090</t>
+        </is>
+      </c>
+      <c r="I33" s="125" t="inlineStr">
+        <is>
+          <t>ojmmhenterprise.com</t>
+        </is>
+      </c>
+      <c r="J33" s="125" t="inlineStr">
+        <is>
+          <t>VYHHHJWN9RJ9</t>
+        </is>
+      </c>
+      <c r="K33" s="125" t="inlineStr">
+        <is>
+          <t>22BD1</t>
+        </is>
+      </c>
+      <c r="L33" s="125" t="n"/>
+      <c r="M33" s="115" t="inlineStr">
+        <is>
+          <t>Cloud governance, risk assessment, audit readiness; control mapping against NIST SP 800-53, NIST AI RMF, ISO/IEC 42001, FedRAMP; Cloud FinOps and AI cost analysis</t>
+        </is>
+      </c>
+      <c r="N33" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O33" s="126" t="n">
+        <v>46301</v>
+      </c>
+      <c r="P33" s="125" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="Q33" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-23 11:59 PM with cap statement; answered all three questions cleanly. CLAIMED: SBA-certified SDVOSB and VOSB. CLEANEST LANE A FIT RECEIVED TO DATE — independent assessment and audit readiness, not build work, so no overlap. Requested the VBX mutual NDA for review ahead of the call. UNVERIFIED: which agencies/programs the assessments were delivered for, and whether as prime or through a prime.</t>
+        </is>
+      </c>
+      <c r="R33" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S33" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-10-02 | Done when: output block logged | Call Tue 2026-10-06 1:00 PM CT</t>
+        </is>
+      </c>
+      <c r="T33" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U33" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-26</t>
+        </is>
+      </c>
+      <c r="V33" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W33" s="125" t="n"/>
+      <c r="X33" s="125" t="n"/>
+      <c r="Y33" s="125" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-21</t>
+        </is>
+      </c>
+      <c r="B34" s="125" t="inlineStr">
+        <is>
+          <t>Veteran Property Managers LLC</t>
+        </is>
+      </c>
+      <c r="C34" s="125" t="inlineStr">
+        <is>
+          <t>VPM</t>
+        </is>
+      </c>
+      <c r="D34" s="115" t="inlineStr">
+        <is>
+          <t>C claimed — FEE-MODEL + NAME/CAPABILITY FLAGS</t>
+        </is>
+      </c>
+      <c r="E34" s="125" t="inlineStr">
+        <is>
+          <t>CA (stated)</t>
+        </is>
+      </c>
+      <c r="F34" s="125" t="inlineStr">
+        <is>
+          <t>Sandy Blair, CEO</t>
+        </is>
+      </c>
+      <c r="G34" s="125" t="inlineStr">
+        <is>
+          <t>info@vpmcontracts.com</t>
+        </is>
+      </c>
+      <c r="H34" s="125" t="inlineStr">
+        <is>
+          <t>8056199193 / 6786772190</t>
+        </is>
+      </c>
+      <c r="I34" s="125" t="inlineStr">
+        <is>
+          <t>vpmcontracts.com</t>
+        </is>
+      </c>
+      <c r="J34" s="125" t="n"/>
+      <c r="K34" s="125" t="inlineStr">
+        <is>
+          <t>9JNX8</t>
+        </is>
+      </c>
+      <c r="L34" s="125" t="n"/>
+      <c r="M34" s="115" t="inlineStr">
+        <is>
+          <t>Claims CA capture, proposal support, compliance documentation, standup, training and reporting</t>
+        </is>
+      </c>
+      <c r="N34" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O34" s="126" t="n">
+        <v>46301</v>
+      </c>
+      <c r="P34" s="125" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="Q34" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-24 9:32 AM with cap statement + watermarked sample work product. FOUR FLAGS: (1) FEE MODEL — proposes pricing at market rate against a written work order "with an engagement deposit before we open the files," i.e. VBX pays THEM up front; that is a vendor, not a teaming partner, and VBX does not pay deposits or retainers to partners. Resolve before the call. (2) NAME/CAPABILITY MISMATCH — legal name is Veteran Property Managers LLC; property management has no evident link to capture and compliance documentation. (3) FUNCTION OVERLAP — "California capture, proposal support" is VBX's own internal capture function. (4) PRE-NDA PROBING — asked four opportunity-specific questions (urgency, launch date, whether an SDVOSB line in the SOW, which state first) and referenced MAPS scope by name. CLAIMED: SDVOSB, WOSB, SBA VetCert. NO UEI PROVIDED — requested.</t>
+        </is>
+      </c>
+      <c r="R34" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S34" s="115" t="inlineStr">
+        <is>
+          <t>Resolve fee model in writing FIRST; screen (Stage 0–3) | Due 2026-10-02 | Call Tue 2026-10-06 1:30 PM CT only if the fee answer clears</t>
+        </is>
+      </c>
+      <c r="T34" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U34" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-26</t>
+        </is>
+      </c>
+      <c r="V34" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W34" s="125" t="n"/>
+      <c r="X34" s="125" t="n"/>
+      <c r="Y34" s="125" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-22</t>
+        </is>
+      </c>
+      <c r="B35" s="125" t="inlineStr">
+        <is>
+          <t>Horizon Line Group LLC</t>
+        </is>
+      </c>
+      <c r="C35" s="125" t="n"/>
+      <c r="D35" s="115" t="inlineStr">
+        <is>
+          <t>B · Network, Telecom &amp; Hardware / D · Health Ops &amp; Revenue Cycle</t>
+        </is>
+      </c>
+      <c r="E35" s="125" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F35" s="125" t="inlineStr">
+        <is>
+          <t>Elen Woldemichael, Managing Member</t>
+        </is>
+      </c>
+      <c r="G35" s="125" t="inlineStr">
+        <is>
+          <t>info@horizonlinegrp.com</t>
+        </is>
+      </c>
+      <c r="H35" s="125" t="inlineStr">
+        <is>
+          <t>6192439885</t>
+        </is>
+      </c>
+      <c r="I35" s="125" t="inlineStr">
+        <is>
+          <t>horizonlinegrp.com</t>
+        </is>
+      </c>
+      <c r="J35" s="125" t="inlineStr">
+        <is>
+          <t>PGJWMG7AW7Q7</t>
+        </is>
+      </c>
+      <c r="K35" s="125" t="inlineStr">
+        <is>
+          <t>17MT4</t>
+        </is>
+      </c>
+      <c r="L35" s="125" t="inlineStr">
+        <is>
+          <t>423450, 423990, 424120, 541611, 541614</t>
+        </is>
+      </c>
+      <c r="M35" s="115" t="inlineStr">
+        <is>
+          <t>Procurement, sourcing and vendor coordination across medical, lab, dental, office, industrial and facility supply; clinical research operations support</t>
+        </is>
+      </c>
+      <c r="N35" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O35" s="126" t="n">
+        <v>46302</v>
+      </c>
+      <c r="P35" s="125" t="inlineStr">
+        <is>
+          <t>1:00 PM</t>
+        </is>
+      </c>
+      <c r="Q35" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-25 1:34 PM with cap statement. CLAIMED: SBA WOSB, SBA EDWOSB, HUBZone, CA Small Business (SB/Micro), active SAM — an unusually strong set-aside stack if all verify. MATURITY FLAG: incorporated 2025 in California; the capability statement contains NO past-performance section, only "Leadership Experience" describing the owner's prior clinical research work, plus supplier relationships. Confirm what the FIRM has delivered and for whom.</t>
+        </is>
+      </c>
+      <c r="R35" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S35" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-10-02 | Done when: output block logged | Call Wed 2026-10-07 1:00 PM CT</t>
+        </is>
+      </c>
+      <c r="T35" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U35" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-26</t>
+        </is>
+      </c>
+      <c r="V35" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W35" s="125" t="n"/>
+      <c r="X35" s="125" t="n"/>
+      <c r="Y35" s="125" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="125" t="inlineStr">
+        <is>
+          <t>IN-CA-23</t>
+        </is>
+      </c>
+      <c r="B36" s="125" t="inlineStr">
+        <is>
+          <t>Pacific Bioethics LLC</t>
+        </is>
+      </c>
+      <c r="C36" s="125" t="n"/>
+      <c r="D36" s="115" t="inlineStr">
+        <is>
+          <t>C · Change Mgmt, PMO &amp; Training</t>
+        </is>
+      </c>
+      <c r="E36" s="125" t="inlineStr">
+        <is>
+          <t>Los Angeles County</t>
+        </is>
+      </c>
+      <c r="F36" s="125" t="inlineStr">
+        <is>
+          <t>Latelle J. Barton II, MD, HEC-C</t>
+        </is>
+      </c>
+      <c r="G36" s="125" t="inlineStr">
+        <is>
+          <t>lb@pacificbioethics.com</t>
+        </is>
+      </c>
+      <c r="H36" s="125" t="n"/>
+      <c r="I36" s="125" t="inlineStr">
+        <is>
+          <t>pacificbioethics.com</t>
+        </is>
+      </c>
+      <c r="J36" s="125" t="inlineStr">
+        <is>
+          <t>KTK7WVZM4BN7</t>
+        </is>
+      </c>
+      <c r="K36" s="125" t="inlineStr">
+        <is>
+          <t>145G2</t>
+        </is>
+      </c>
+      <c r="L36" s="125" t="inlineStr">
+        <is>
+          <t>611430, 541690, 541611, 624190</t>
+        </is>
+      </c>
+      <c r="M36" s="115" t="inlineStr">
+        <is>
+          <t>Applied healthcare ethics — clinical and organizational ethics consultation, healthcare workforce education, ethics-informed policy support, case-based training</t>
+        </is>
+      </c>
+      <c r="N36" s="125" t="inlineStr">
+        <is>
+          <t>Call Scheduled</t>
+        </is>
+      </c>
+      <c r="O36" s="126" t="n">
+        <v>46302</v>
+      </c>
+      <c r="P36" s="125" t="inlineStr">
+        <is>
+          <t>1:30 PM</t>
+        </is>
+      </c>
+      <c r="Q36" s="115" t="inlineStr">
+        <is>
+          <t>Replied 2026-09-25 2:56 PM with federal capability statement. CLAIMED: SBA-certified VOSB, California Small Business/Microbusiness, LA County LSBE. HEC-C certified clinical ethicist; federal hospital experience (military/VAMC); focus on behavioral health, correctional healthcare, VHA and veteran populations. Raised the ethical and workforce implications of AI in healthcare — touches VBX AI and CAH work. TWO FLAGS: (1) capacity — practice appears to run through one physician; (2) past performance section describes education, interdisciplinary team support and US Navy medical service rather than delivered contracts. Confirm how engagements have been contracted.</t>
+        </is>
+      </c>
+      <c r="R36" s="125" t="inlineStr">
+        <is>
+          <t>Not sent</t>
+        </is>
+      </c>
+      <c r="S36" s="115" t="inlineStr">
+        <is>
+          <t>Screen (Stage 0–3) before call | Due 2026-10-02 | Done when: output block logged | Call Wed 2026-10-07 1:30 PM CT</t>
+        </is>
+      </c>
+      <c r="T36" s="125" t="inlineStr">
+        <is>
+          <t>Khaalis</t>
+        </is>
+      </c>
+      <c r="U36" s="125" t="inlineStr">
+        <is>
+          <t>email 2026-09-26</t>
+        </is>
+      </c>
+      <c r="V36" s="115" t="inlineStr">
+        <is>
+          <t>None found</t>
+        </is>
+      </c>
+      <c r="W36" s="125" t="n"/>
+      <c r="X36" s="125" t="n"/>
+      <c r="Y36" s="125" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D72" s="107" t="inlineStr">
         <is>
-          <t>HUBZone / SDVOSB (self-reported VetCert; UEI W5D6US648735; CAGE 0QPK0; PR)</t>
+          <t>HUBZone / SDVOSB (self-reported VetCert; PR)</t>
         </is>
       </c>
       <c r="E72" s="108" t="n">
@@ -7633,7 +7633,7 @@
       <c r="G30" s="107" t="n"/>
       <c r="H30" s="121" t="inlineStr">
         <is>
-          <t>NOT a Wave 1-era inbound lead: RavenOne has been a teaming contact since August 2026 across five evaluated opportunities — VA Digital GI Bill RFI (pursue-conditional), VA PATS-R (watch), CDC KMTSS (no-bid), VA BioDose (Gate 1 kill), and Riverbay 4350 (no-bid). Puerto Rico LLC, not California — the IN-CA- prefix is retained only as a stable handle; this row belongs in the partner-ecosystem file, not Inbound. RIVERBAY 4350 CLOSED: no-bid issued 2026-09-23, record VBX_NoBid_Decision_Riverbay_4350_20260923.docx. Gate 1 failed on two independent triggers — vendor-type mismatch (managed service-desk operator buy) and past-performance floor (no corporate managed help-desk PP). Scoring not run per engine rule. Structural confirmation: approx $16.48 per live-coverage hour at full customer price, before RavenOne margin. Decline sent; transmitted no VBX information. NDA: ROS-NDA-001-VISIONBLOX v0.4, RavenOne counterproposal dated 2026-08-19 — VBX SIGNED, AWAITING RAVENONE COUNTERSIGNATURE. Not executed: no Effective Date until the last signature, so NDA-before-substance is NOT yet satisfied. Terms reviewed: no non-solicit, no non-compete; Section 2.2 SAM.gov carve-out and Section 8.4 freedom-of-action both favor VBX; 2-yr term / 2-yr survival; Section 8.5 bars name and logo use without written consent; Delaware governing law, venue at defendant's principal place of business. CLAIMED: HUBZone, SBA VetCert SDVOSB.</t>
+          <t>NOT a Wave 1-era inbound lead: RavenOne has been a teaming contact since August 2026 across five evaluated opportunities — VA Digital GI Bill RFI (pursue-conditional), VA PATS-R (watch), CDC KMTSS (no-bid), VA BioDose (Gate 1 kill), and Riverbay 4350 (no-bid). Puerto Rico LLC, not California — the IN-CA- prefix is retained only as a stable handle; this row belongs in the partner-ecosystem file, not Inbound. RIVERBAY 4350 CLOSED: no-bid issued 2026-09-23, record VBX_NoBid_Decision_Riverbay_4350_20260923.docx. Gate 1 failed on two independent triggers — vendor-type mismatch (managed service-desk operator buy) and past-performance floor (no corporate managed help-desk PP). Scoring not run per engine rule. Structural confirmation: approx $16.48 per live-coverage hour at full customer price, before RavenOne margin. Decline sent; transmitted no VBX information. NDA: ROS-NDA-001-VISIONBLOX v0.4, RavenOne counterproposal dated 2026-08-19 — VBX SIGNED, AWAITING RAVENONE COUNTERSIGNATURE. Not executed: no Effective Date until the last signature, so NDA-before-substance is NOT yet satisfied. Terms reviewed: no non-solicit, no non-compete; Section 2.2 SAM.gov carve-out and Section 8.4 freedom-of-action both favor VBX; 2-yr term / 2-yr survival; Section 8.5 bars name and logo use without written consent; Delaware governing law, venue at defendant's principal place of business. CLAIMED: HUBZone, SBA VetCert SDVOSB. | Identifiers (moved from Screenings!D72, 2026-09-26; published column): UEI W5D6US648735; CAGE 0QPK0.</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="123" t="n">
+      <c r="A5" s="125" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="115" t="inlineStr">
@@ -7901,12 +7901,12 @@
           <t>Redirect LADBS B&amp;P to CMS ICAT (RFI 270196) + WA HCA FSIPAP Round 2 re-score</t>
         </is>
       </c>
-      <c r="C5" s="123" t="inlineStr">
+      <c r="C5" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D5" s="124" t="n">
+      <c r="D5" s="126" t="n">
         <v>46254</v>
       </c>
       <c r="E5" s="115" t="inlineStr">
@@ -7914,19 +7914,19 @@
           <t>ICAT package submitted on time</t>
         </is>
       </c>
-      <c r="F5" s="123" t="inlineStr">
+      <c r="F5" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G5" s="123" t="inlineStr">
+      <c r="G5" s="125" t="inlineStr">
         <is>
           <t>OPP-041 / LADBS AIP-PPC No-Bid 8/19/26</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="123" t="n">
+      <c r="A6" s="125" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="115" t="inlineStr">
@@ -7934,12 +7934,12 @@
           <t>Open SOC 2 Type 2 gap-assessment scoping with Tony Paul; cite as 3rd documented hosted-solution attestation blocker (after Montana Tier Two &gt;$100K, WA State)</t>
         </is>
       </c>
-      <c r="C6" s="123" t="inlineStr">
+      <c r="C6" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden / Tony Paul</t>
         </is>
       </c>
-      <c r="D6" s="124" t="n">
+      <c r="D6" s="126" t="n">
         <v>46262</v>
       </c>
       <c r="E6" s="115" t="inlineStr">
@@ -7947,19 +7947,19 @@
           <t>Assessor shortlist returned</t>
         </is>
       </c>
-      <c r="F6" s="123" t="inlineStr">
+      <c r="F6" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G6" s="123" t="inlineStr">
+      <c r="G6" s="125" t="inlineStr">
         <is>
           <t>OPP-041 / LADBS AIP-PPC No-Bid 8/19/26</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="123" t="n">
+      <c r="A7" s="125" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="115" t="inlineStr">
@@ -7967,12 +7967,12 @@
           <t>Add intake screen: flag any scope containing "vendor-hosted", "SaaS", "subscription", or a Functional Requirements &amp; Use Case Matrix as vendor-type mismatch BEFORE scoring</t>
         </is>
       </c>
-      <c r="C7" s="123" t="inlineStr">
+      <c r="C7" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D7" s="124" t="n">
+      <c r="D7" s="126" t="n">
         <v>46265</v>
       </c>
       <c r="E7" s="115" t="inlineStr">
@@ -7980,19 +7980,19 @@
           <t>Screen in intake checklist</t>
         </is>
       </c>
-      <c r="F7" s="123" t="inlineStr">
+      <c r="F7" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G7" s="123" t="inlineStr">
+      <c r="G7" s="125" t="inlineStr">
         <is>
           <t>OPP-041 / LADBS AIP-PPC No-Bid 8/19/26</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="123" t="n">
+      <c r="A8" s="125" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="115" t="inlineStr">
@@ -8000,12 +8000,12 @@
           <t>Re-check RAMP for a follow-on ED19 services/integration requirement</t>
         </is>
       </c>
-      <c r="C8" s="123" t="inlineStr">
+      <c r="C8" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D8" s="124" t="n">
+      <c r="D8" s="126" t="n">
         <v>46310</v>
       </c>
       <c r="E8" s="115" t="inlineStr">
@@ -8013,19 +8013,19 @@
           <t>Search executed; recorded pursue / no-action</t>
         </is>
       </c>
-      <c r="F8" s="123" t="inlineStr">
+      <c r="F8" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G8" s="123" t="inlineStr">
+      <c r="G8" s="125" t="inlineStr">
         <is>
           <t>OPP-041 / LADBS AIP-PPC No-Bid 8/19/26</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="123" t="n">
+      <c r="A9" s="125" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="115" t="inlineStr">
@@ -8033,12 +8033,12 @@
           <t>Validate §5.7 ROM against VBX cost model</t>
         </is>
       </c>
-      <c r="C9" s="123" t="inlineStr">
+      <c r="C9" s="125" t="inlineStr">
         <is>
           <t>Akil Chellam / Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D9" s="124" t="n">
+      <c r="D9" s="126" t="n">
         <v>46258</v>
       </c>
       <c r="E9" s="115" t="inlineStr">
@@ -8046,19 +8046,19 @@
           <t>ROM confirmed or revised</t>
         </is>
       </c>
-      <c r="F9" s="123" t="inlineStr">
+      <c r="F9" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G9" s="123" t="inlineStr">
+      <c r="G9" s="125" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 14</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="123" t="n">
+      <c r="A10" s="125" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="115" t="inlineStr">
@@ -8066,12 +8066,12 @@
           <t>Confirm §5.4 SOC 2 / attestation language</t>
         </is>
       </c>
-      <c r="C10" s="123" t="inlineStr">
+      <c r="C10" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden / Tony Paul</t>
         </is>
       </c>
-      <c r="D10" s="124" t="n">
+      <c r="D10" s="126" t="n">
         <v>46258</v>
       </c>
       <c r="E10" s="115" t="inlineStr">
@@ -8079,19 +8079,19 @@
           <t>Language approved</t>
         </is>
       </c>
-      <c r="F10" s="123" t="inlineStr">
+      <c r="F10" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G10" s="123" t="inlineStr">
+      <c r="G10" s="125" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 15</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="123" t="n">
+      <c r="A11" s="125" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="115" t="inlineStr">
@@ -8099,12 +8099,12 @@
           <t>Cyber-insurance tier check ($10M vs $6M held) with Grace Waring</t>
         </is>
       </c>
-      <c r="C11" s="123" t="inlineStr">
+      <c r="C11" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D11" s="124" t="n">
+      <c r="D11" s="126" t="n">
         <v>46258</v>
       </c>
       <c r="E11" s="115" t="inlineStr">
@@ -8112,19 +8112,19 @@
           <t>Tier confirmed</t>
         </is>
       </c>
-      <c r="F11" s="123" t="inlineStr">
+      <c r="F11" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G11" s="123" t="inlineStr">
+      <c r="G11" s="125" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 16</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="123" t="n">
+      <c r="A12" s="125" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="115" t="inlineStr">
@@ -8132,12 +8132,12 @@
           <t>Apply §4.7 per-page Confidential marks on §5.3 pages</t>
         </is>
       </c>
-      <c r="C12" s="123" t="inlineStr">
+      <c r="C12" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D12" s="124" t="n">
+      <c r="D12" s="126" t="n">
         <v>46259</v>
       </c>
       <c r="E12" s="115" t="inlineStr">
@@ -8145,19 +8145,19 @@
           <t>Marks applied</t>
         </is>
       </c>
-      <c r="F12" s="123" t="inlineStr">
+      <c r="F12" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G12" s="123" t="inlineStr">
+      <c r="G12" s="125" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 17</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="123" t="n">
+      <c r="A13" s="125" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="115" t="inlineStr">
@@ -8165,12 +8165,12 @@
           <t>Pink/red review + guardrail sweep</t>
         </is>
       </c>
-      <c r="C13" s="123" t="inlineStr">
+      <c r="C13" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D13" s="124" t="n">
+      <c r="D13" s="126" t="n">
         <v>46259</v>
       </c>
       <c r="E13" s="115" t="inlineStr">
@@ -8178,19 +8178,19 @@
           <t>Sweep complete</t>
         </is>
       </c>
-      <c r="F13" s="123" t="inlineStr">
+      <c r="F13" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G13" s="123" t="inlineStr">
+      <c r="G13" s="125" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 18</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="123" t="n">
+      <c r="A14" s="125" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="115" t="inlineStr">
@@ -8198,12 +8198,12 @@
           <t>Submit RFI response (email, ≤20pp, subject "RFI 2026HCA13_Visionblox LLC" + Attachment A, no zip)</t>
         </is>
       </c>
-      <c r="C14" s="123" t="inlineStr">
+      <c r="C14" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D14" s="124" t="n">
+      <c r="D14" s="126" t="n">
         <v>46260</v>
       </c>
       <c r="E14" s="115" t="inlineStr">
@@ -8211,19 +8211,19 @@
           <t>Response submitted</t>
         </is>
       </c>
-      <c r="F14" s="123" t="inlineStr">
+      <c r="F14" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G14" s="123" t="inlineStr">
+      <c r="G14" s="125" t="inlineStr">
         <is>
           <t>OPP-024 / WA HCA FSIPAP RFI 2026HCA13 (Rev.6 8/19/26) · step 19</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="123" t="n">
+      <c r="A15" s="125" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="115" t="inlineStr">
@@ -8231,30 +8231,30 @@
           <t>Screen all 33 inbound-handoff firms (Stage 0–3) — 32 on Inbound_Leads + IN-CA-15</t>
         </is>
       </c>
-      <c r="C15" s="123" t="inlineStr">
+      <c r="C15" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D15" s="124" t="n"/>
+      <c r="D15" s="126" t="n"/>
       <c r="E15" s="115" t="inlineStr">
         <is>
           <t>Stage 0–3 output logged for each firm before its call</t>
         </is>
       </c>
-      <c r="F15" s="123" t="inlineStr">
+      <c r="F15" s="125" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="G15" s="123" t="inlineStr">
+      <c r="G15" s="125" t="inlineStr">
         <is>
           <t>Inbound handoff 2026-09-26 §8</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="123" t="n">
+      <c r="A16" s="125" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="115" t="inlineStr">
@@ -8262,12 +8262,12 @@
           <t>Pull Wave 1 row WA-13 (already booked as IN-WA-02) from the 9/28 BCC</t>
         </is>
       </c>
-      <c r="C16" s="123" t="inlineStr">
+      <c r="C16" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D16" s="124" t="n">
+      <c r="D16" s="126" t="n">
         <v>46293</v>
       </c>
       <c r="E16" s="115" t="inlineStr">
@@ -8275,19 +8275,19 @@
           <t>WA-13 address absent from the send list</t>
         </is>
       </c>
-      <c r="F16" s="123" t="inlineStr">
+      <c r="F16" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G16" s="123" t="inlineStr">
+      <c r="G16" s="125" t="inlineStr">
         <is>
           <t>Inbound handoff 2026-09-26 §8</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="123" t="n">
+      <c r="A17" s="125" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="115" t="inlineStr">
@@ -8295,12 +8295,12 @@
           <t>Resolve Wave 1 MT-02 / MT-06 shared address: keep both rows as one contact, or drop one</t>
         </is>
       </c>
-      <c r="C17" s="123" t="inlineStr">
+      <c r="C17" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D17" s="124" t="n">
+      <c r="D17" s="126" t="n">
         <v>46293</v>
       </c>
       <c r="E17" s="115" t="inlineStr">
@@ -8308,19 +8308,19 @@
           <t>Decision recorded; BCC count final</t>
         </is>
       </c>
-      <c r="F17" s="123" t="inlineStr">
+      <c r="F17" s="125" t="inlineStr">
         <is>
           <t>Needs Khaalis decision</t>
         </is>
       </c>
-      <c r="G17" s="123" t="inlineStr">
+      <c r="G17" s="125" t="inlineStr">
         <is>
           <t>Inbound handoff 2026-09-26 §8</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="123" t="n">
+      <c r="A18" s="125" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="115" t="inlineStr">
@@ -8328,12 +8328,12 @@
           <t>Chase countersignature on NDA #26 (IN-CA-15, NDAs sheet)</t>
         </is>
       </c>
-      <c r="C18" s="123" t="inlineStr">
+      <c r="C18" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D18" s="124" t="n">
+      <c r="D18" s="126" t="n">
         <v>46295</v>
       </c>
       <c r="E18" s="115" t="inlineStr">
@@ -8341,19 +8341,19 @@
           <t>Countersigned copy received; Effective Date recorded</t>
         </is>
       </c>
-      <c r="F18" s="123" t="inlineStr">
+      <c r="F18" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G18" s="123" t="inlineStr">
+      <c r="G18" s="125" t="inlineStr">
         <is>
           <t>Inbound handoff 2026-09-26 §8</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="123" t="n">
+      <c r="A19" s="125" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="115" t="inlineStr">
@@ -8361,12 +8361,12 @@
           <t>Resolve IN-CA-21 fee model in writing before its call</t>
         </is>
       </c>
-      <c r="C19" s="123" t="inlineStr">
+      <c r="C19" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D19" s="124" t="n">
+      <c r="D19" s="126" t="n">
         <v>46301</v>
       </c>
       <c r="E19" s="115" t="inlineStr">
@@ -8374,19 +8374,19 @@
           <t>Written fee position received before the call</t>
         </is>
       </c>
-      <c r="F19" s="123" t="inlineStr">
+      <c r="F19" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G19" s="123" t="inlineStr">
+      <c r="G19" s="125" t="inlineStr">
         <is>
           <t>Inbound handoff 2026-09-26 §8</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="123" t="n">
+      <c r="A20" s="125" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="115" t="inlineStr">
@@ -8394,12 +8394,12 @@
           <t>Send bench replies — IN-CA-13, IN-CA-07</t>
         </is>
       </c>
-      <c r="C20" s="123" t="inlineStr">
+      <c r="C20" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D20" s="124" t="n">
+      <c r="D20" s="126" t="n">
         <v>46290</v>
       </c>
       <c r="E20" s="115" t="inlineStr">
@@ -8412,14 +8412,14 @@
           <t>OVERDUE</t>
         </is>
       </c>
-      <c r="G20" s="123" t="inlineStr">
+      <c r="G20" s="125" t="inlineStr">
         <is>
           <t>Inbound handoff 2026-09-26 §8</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="123" t="n">
+      <c r="A21" s="125" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="115" t="inlineStr">
@@ -8427,12 +8427,12 @@
           <t>Retrieve reply text — IN-CA-16, IN-WA-03, IN-WA-04, IN-UNK-06</t>
         </is>
       </c>
-      <c r="C21" s="123" t="inlineStr">
+      <c r="C21" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D21" s="124" t="n">
+      <c r="D21" s="126" t="n">
         <v>46290</v>
       </c>
       <c r="E21" s="115" t="inlineStr">
@@ -8445,14 +8445,14 @@
           <t>OVERDUE</t>
         </is>
       </c>
-      <c r="G21" s="123" t="inlineStr">
+      <c r="G21" s="125" t="inlineStr">
         <is>
           <t>Inbound handoff 2026-09-26 §8</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="123" t="n">
+      <c r="A22" s="125" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="115" t="inlineStr">
@@ -8460,12 +8460,12 @@
           <t>Decide whether to contact IN-WA-01 directly</t>
         </is>
       </c>
-      <c r="C22" s="123" t="inlineStr">
+      <c r="C22" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D22" s="124" t="n">
+      <c r="D22" s="126" t="n">
         <v>46295</v>
       </c>
       <c r="E22" s="115" t="inlineStr">
@@ -8473,19 +8473,19 @@
           <t>Decision recorded</t>
         </is>
       </c>
-      <c r="F22" s="123" t="inlineStr">
+      <c r="F22" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G22" s="123" t="inlineStr">
+      <c r="G22" s="125" t="inlineStr">
         <is>
           <t>Inbound handoff 2026-09-26 §8</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="123" t="n">
+      <c r="A23" s="125" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="115" t="inlineStr">
@@ -8493,23 +8493,23 @@
           <t>Add intake filter: help-desk / NOC / managed end-user support = vendor-type mismatch at intake</t>
         </is>
       </c>
-      <c r="C23" s="123" t="inlineStr">
+      <c r="C23" s="125" t="inlineStr">
         <is>
           <t>Khaalis Wooden</t>
         </is>
       </c>
-      <c r="D23" s="124" t="n"/>
+      <c r="D23" s="126" t="n"/>
       <c r="E23" s="115" t="inlineStr">
         <is>
           <t>Filter in intake checklist</t>
         </is>
       </c>
-      <c r="F23" s="123" t="inlineStr">
+      <c r="F23" s="125" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G23" s="123" t="inlineStr">
+      <c r="G23" s="125" t="inlineStr">
         <is>
           <t>Riverbay 4350 No-Bid 9/23/26</t>
         </is>

--- a/VBX_Command_Center_v1.1.xlsx
+++ b/VBX_Command_Center_v1.1.xlsx
@@ -1691,11 +1691,11 @@
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C37:E37"/>
     <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C15:E15"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C15:E15"/>
     <mergeCell ref="C12:E12"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="C38:E38"/>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C4" s="56" t="n">
-        <v>46247</v>
+        <v>46294</v>
       </c>
       <c r="D4" s="57" t="inlineStr">
         <is>
